--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -517,7 +517,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>{'name': 'Thái Nguyễn', 'link': 'https://www.google.com/maps/contrib/105517365260915933657?hl=vi', 'contributor_id': '105517365260915933657', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXLOkY3FUSH3Mz-aapJXPQUgoCFlQP20PICWZGzVI3cPkRkBIt_ew=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 65, 'photos': 172}</t>
+          <t>{'name': 'Thái Nguyễn', 'link': 'https://www.google.com/maps/contrib/105517365260915933657?hl=vi', 'contributor_id': '105517365260915933657', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXLOkY3FUSH3Mz-aapJXPQUgoCFlQP20PICWZGzVI3cPkRkBIt_ew=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 65, 'photos': 175}</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -623,7 +623,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 365, 'photos': 2590}</t>
+          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 365, 'photos': 2592}</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -688,7 +688,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 300, 'photos': 3584}</t>
+          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 299, 'photos': 3584}</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -728,7 +728,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 24}</t>
+          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 11, 'photos': 24}</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1015,7 +1015,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 10, 'photos': 19}</t>
+          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 10, 'photos': 41}</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1035,7 +1035,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 140, 'photos': 571}</t>
+          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 141, 'photos': 571}</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1204,7 +1204,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 534, 'photos': 4107}</t>
+          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 533, 'photos': 4107}</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10 tháng trước</t>
+          <t>11 tháng trước</t>
         </is>
       </c>
     </row>

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -623,7 +623,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 365, 'photos': 2592}</t>
+          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 366, 'photos': 2592}</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -668,7 +668,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>{'name': 'THANH NGUYEN', 'link': 'https://www.google.com/maps/contrib/110418688752170937071?hl=vi', 'contributor_id': '110418688752170937071', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIBtT-SxDlGGJM5jA47OmxpGvFdaG6EOeSswcBwx4VuXgnOdQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 69, 'photos': 199}</t>
+          <t>{'name': 'THANH NGUYEN', 'link': 'https://www.google.com/maps/contrib/110418688752170937071?hl=vi', 'contributor_id': '110418688752170937071', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIBtT-SxDlGGJM5jA47OmxpGvFdaG6EOeSswcBwx4VuXgnOdQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 69, 'photos': 207}</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -995,7 +995,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 250, 'photos': 4788}</t>
+          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 251, 'photos': 4847}</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1015,7 +1015,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 10, 'photos': 41}</t>
+          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
         </is>
       </c>
       <c r="B26" t="n">

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -668,7 +668,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>{'name': 'THANH NGUYEN', 'link': 'https://www.google.com/maps/contrib/110418688752170937071?hl=vi', 'contributor_id': '110418688752170937071', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIBtT-SxDlGGJM5jA47OmxpGvFdaG6EOeSswcBwx4VuXgnOdQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 69, 'photos': 207}</t>
+          <t>{'name': 'THANH NGUYEN', 'link': 'https://www.google.com/maps/contrib/110418688752170937071?hl=vi', 'contributor_id': '110418688752170937071', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIBtT-SxDlGGJM5jA47OmxpGvFdaG6EOeSswcBwx4VuXgnOdQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 70, 'photos': 207}</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -688,7 +688,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 299, 'photos': 3584}</t>
+          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 299, 'photos': 3604}</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -995,7 +995,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 251, 'photos': 4847}</t>
+          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 250, 'photos': 4847}</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>9 tháng trước</t>
         </is>
       </c>
     </row>

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -623,7 +623,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 366, 'photos': 2592}</t>
+          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 299, 'photos': 3604}</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -631,44 +631,39 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nơi rất đáng để tham quan, trãi nghiệm chút it về cầu kính và kết hợp đi ngắm thác nước.
-Có nhiều nơi lên hình đẹp, cảnh đẹp. Có bán đặc sản Mộc Châu rất đa dạng.
-😍😍👍</t>
+          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Thời gian chỉnh sửa: 5 tháng trước</t>
+          <t>4 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>{'name': 'Vĩ Lê Bá', 'link': 'https://www.google.com/maps/contrib/115860838984920745696?hl=vi', 'contributor_id': '115860838984920745696', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7wdRrYJWeEmKs7YInZz_FDg-T90l2ImigSwJKL2hWmQu75bzm=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 59, 'photos': 93}</t>
+          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 325}</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Đẹp thì đẹp sơ sơ nhưng không gian vẫn khá là thoải mái
-Đi bộ oklea nhưng mà vẫn còn quá nhỏ, đi cỡ 30 phút là xong mất tiêu r
-Tuỳ ngà lượng khách sẽ khác nhau và ảnh hưởng lớn tớ trải nghiệm
-Nói chung là vẫn okela</t>
+          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5 tháng trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>{'name': 'THANH NGUYEN', 'link': 'https://www.google.com/maps/contrib/110418688752170937071?hl=vi', 'contributor_id': '110418688752170937071', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIBtT-SxDlGGJM5jA47OmxpGvFdaG6EOeSswcBwx4VuXgnOdQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 70, 'photos': 207}</t>
+          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 11, 'photos': 24}</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -676,147 +671,87 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>thác đẹp nhưng nên đi vào mùa nước sẽ thấy sự khác biệt hơn nhiều</t>
+          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>5 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 299, 'photos': 3604}</t>
+          <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'reviews': 16, 'photos': 114}</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>5</v>
       </c>
       <c r="C10" t="inlineStr">
-        <is>
-          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>4 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 325}</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>6 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 11, 'photos': 24}</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>5 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'reviews': 16, 'photos': 114}</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" t="inlineStr">
         <is>
           <t>Đi tầm trưa nắng đẹp
 Thác nhỏ, đi cũng không mất quá nhiều thời gian
 Có cầu kính</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>6 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>{'name': 'Nghĩa Nguyễn Trung', 'link': 'https://www.google.com/maps/contrib/107253778101970197900?hl=vi', 'contributor_id': '107253778101970197900', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUNLHg5XlpgtWVVTp_oJKOYAejqmQORtgQ_Oe2vusE5W_sQoZc5=s120-c-rp-mo-ba12-br100', 'reviews': 275, 'photos': 1279}</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>Khu vực thác nước đẹp, nhiều cảnh quan, nhiều góc chụp đẹp.</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>2 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>{'name': 'Frugal Flow', 'link': 'https://www.google.com/maps/contrib/107453311426556875441?hl=vi', 'contributor_id': '107453311426556875441', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUspWRVGEEQ_LyS16qRB57xWZ-kgNRIjgdLPY8T7HzvNMFlILCV=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 85}</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>5</v>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Đi vào một ngày nắng. Nắng hắt lên mặt nước long lanh nên xinh xắn hẳn:&gt; Chỉ là thác nay có vẻ hơi ít nc nên không như mình tưởng tượng.</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>6 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'reviews': 219, 'photos': 308}</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B13" t="n">
         <v>3</v>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Trải nghiệm vừa phải
 Giá vé theo trải nghiệm đi nhiều thác khác nhau của mình thì là khá cao so với các nơi khác, mình đi vào dịp tết nên thác ít nước.
@@ -824,38 +759,98 @@
 Cá nhân nếu quay lại Mộc Châu sẽ không đến thác này lần nào nữa</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>6 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>{'name': 'La Meu', 'link': 'https://www.google.com/maps/contrib/108858956358165703026?hl=vi', 'contributor_id': '108858956358165703026', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVKW-aZD0iBs1KBFQlmzfMiMTfjpd4PfUn4GO-K2tEt1PLpZ3YY=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 117}</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>5</v>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Thác Dải Yếm là điểm du lịch rất đáng đi. Đường đi dễ, xe máy hay ô tô đều thuận tiện. Không gian mát mẻ, thiên nhiên đẹp và trong lành.
 Nước thác xanh biếc, chảy mạnh nhưng nhìn rất êm và thơ mộng, chụp hình lên đẹp lắm. Khu vực được làm lối đi khá an toàn, dễ tham quan.
 Nhân viên ở đây dễ thương, nhiệt tình, hướng dẫn khách rất chu đáo và thân thiện. Phù hợp đi chơi cùng gia đình hoặc bạn bè để thư giãn, nghỉ ngơi.</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'reviews': 24, 'photos': 255}</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>6 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 1090}</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>11 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'reviews': 24, 'photos': 255}</t>
+          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -863,39 +858,39 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
+          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
+          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
+          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7 tháng trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 1090}</t>
+          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 115, 'photos': 84}</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -903,59 +898,59 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
+          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>11 tháng trước</t>
+          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
+          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 3220}</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
+          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2 tháng trước</t>
+          <t>9 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
+          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 250, 'photos': 4847}</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
+          <t>Cảnh quan đẹp, ng dân thân thiện</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2 tháng trước</t>
+          <t>5 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 115, 'photos': 84}</t>
+          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -963,19 +958,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
+          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>7 tháng trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 3220}</t>
+          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 141, 'photos': 571}</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -983,85 +978,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
+          <t>View đẹp, chỉ tiếc là ghé hồi tháng 5 lúc đang mùa mưa, nên không được đi trải nghiệm nhiều.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>10 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 250, 'photos': 4847}</t>
+          <t>{'name': 'Linh Nguyễn', 'link': 'https://www.google.com/maps/contrib/109820275513447282944?hl=vi', 'contributor_id': '109820275513447282944', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVpZ-SNyOn6byhXW5cnkMUzIYl8pLeo3scME3-VG4n2ps2S2tYx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 992}</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>5</v>
       </c>
       <c r="C25" t="inlineStr">
-        <is>
-          <t>Cảnh quan đẹp, ng dân thân thiện</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>5 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>5</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>8 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 141, 'photos': 571}</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>4</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>View đẹp, chỉ tiếc là ghé hồi tháng 5 lúc đang mùa mưa, nên không được đi trải nghiệm nhiều.</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>10 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>{'name': 'Linh Nguyễn', 'link': 'https://www.google.com/maps/contrib/109820275513447282944?hl=vi', 'contributor_id': '109820275513447282944', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVpZ-SNyOn6byhXW5cnkMUzIYl8pLeo3scME3-VG4n2ps2S2tYx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 992}</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>5</v>
-      </c>
-      <c r="C28" t="inlineStr">
         <is>
           <t>Thác đẹp, suối nước tự nhiên, đường đi dọc suối sạch sẽ
 Một số địa điểm du lịch ở Mộc Châu mọi người có thể tham khảo
@@ -1074,56 +1009,117 @@
 2. Cá Hồi Thanh Bảy</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 80, 'photos': 185}</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>6 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>{'name': 'Anh Tuấn Trần', 'link': 'https://www.google.com/maps/contrib/106361750645670984745?hl=vi', 'contributor_id': '106361750645670984745', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXiNjEqD4gV0wYaTlBDaztRxN3Bz6wZiiUqJ5pnHqrMT1HyLF_rBg=s120-c-rp-mo-ba12-br100', 'reviews': 956, 'photos': 4071}</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Chẳng hiểu Mộc Châu làm du lịch kiểu gì mà chỗ nào cũng bắt mua vé và giá vé quá cao. Cứ một điểm tham quan là 100k/người mà chẳng có gì đặc sắc cả. Thác dải yếm có quá nhiều công trình nhân tạo. Kể cả 100k/người cho cả Thác Dải Yếm + Cầu Kính thì mình vẫn thấy đắt - không tương xứng. Đây còn vé riêng cho thác và riêng cho cầu kính mặc dù cả 2 này là cùng một điêm. Không muốn quay lại bao giờ nữa.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2 năm trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 80, 'photos': 185}</t>
+          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 71, 'photos': 496}</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
+          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>3 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>{'name': 'Anh Tuấn Trần', 'link': 'https://www.google.com/maps/contrib/106361750645670984745?hl=vi', 'contributor_id': '106361750645670984745', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXiNjEqD4gV0wYaTlBDaztRxN3Bz6wZiiUqJ5pnHqrMT1HyLF_rBg=s120-c-rp-mo-ba12-br100', 'reviews': 956, 'photos': 4071}</t>
+          <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'reviews': 78, 'photos': 260}</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chẳng hiểu Mộc Châu làm du lịch kiểu gì mà chỗ nào cũng bắt mua vé và giá vé quá cao. Cứ một điểm tham quan là 100k/người mà chẳng có gì đặc sắc cả. Thác dải yếm có quá nhiều công trình nhân tạo. Kể cả 100k/người cho cả Thác Dải Yếm + Cầu Kính thì mình vẫn thấy đắt - không tương xứng. Đây còn vé riêng cho thác và riêng cho cầu kính mặc dù cả 2 này là cùng một điêm. Không muốn quay lại bao giờ nữa.</t>
+          <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
+Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2 năm trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
+          <t>{'name': 'Mai Nguyễn', 'link': 'https://www.google.com/maps/contrib/101330344304584692421?hl=vi', 'contributor_id': '101330344304584692421', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocLN09xUhcK1CuSvLI4U-MC1m1LployphMNgUrT9xqkPlzqHlA=s120-c-rp-mo-br100', 'reviews': 5, 'photos': 7}</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1131,106 +1127,45 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
+          <t>Cảnh đẹp, có cả trải nghiệm cầu kính và zipline mà giá phải chăng hơn bên khu cầu kính bạch long</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 71, 'photos': 496}</t>
+          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 533, 'photos': 4107}</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
+          <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'reviews': 78, 'photos': 260}</t>
+          <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 574}</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C33" t="inlineStr">
-        <is>
-          <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
-Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>{'name': 'Mai Nguyễn', 'link': 'https://www.google.com/maps/contrib/101330344304584692421?hl=vi', 'contributor_id': '101330344304584692421', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocLN09xUhcK1CuSvLI4U-MC1m1LployphMNgUrT9xqkPlzqHlA=s120-c-rp-mo-br100', 'reviews': 5, 'photos': 7}</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>5</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Cảnh đẹp, có cả trải nghiệm cầu kính và zipline mà giá phải chăng hơn bên khu cầu kính bạch long</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>6 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 533, 'photos': 4107}</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>4</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 574}</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>5</v>
-      </c>
-      <c r="C36" t="inlineStr">
         <is>
           <t>Đúng tên gọi của nó. Thác cũng rất đẹp. Nếu vào mùa nước chắc còn đẹp hơn.
 Cảnh quan cũng rất sạch đẹp.
@@ -1239,6 +1174,66 @@
 - vé vào cổng giá phù hợp</t>
         </is>
       </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4192}</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Thời gian chỉnh sửa: 2 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 518}</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>5</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
           <t>một năm trước</t>
@@ -1248,7 +1243,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4192}</t>
+          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1256,19 +1251,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
+          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Thời gian chỉnh sửa: 2 năm trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 518}</t>
+          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 1623}</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1276,19 +1271,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
+          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>9 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
+          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 50, 'photos': 144}</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1296,7 +1291,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
+          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1308,7 +1303,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
+          <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWyzcZkQykW_QPymZ2fTMwerDVUm-XhQ6WZ0NqbjNzbEznIxcF7AQ=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 3857}</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1316,39 +1311,40 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
+          <t>Thác Dải Yếm, còn được gọi là thác Nàng, thác Bản Vặt, là một thác nước hùng vĩ nằm ở xã Mường Sang, huyện Mộc Châu, tỉnh Sơn La. Thác có chiều cao khoảng 100m, chia thành hai dòng thác chính, trông giống như một dải yếm đào mềm mại uốn lượn quanh vách núi.
+Thác Dải Yếm là một địa điểm du lịch hấp dẫn, thu hút khách du lịch trong và ngoài nước. Đây là nơi du khách có thể chiêm ngưỡng vẻ đẹp hùng vĩ của thác nước và tìm hiểu về truyền thuyết về thác.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>2 năm trước</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 1623}</t>
+          <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'reviews': 97, 'photos': 178}</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+          <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 50, 'photos': 144}</t>
+          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'reviews': 27, 'photos': 260}</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1356,7 +1352,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
+          <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1368,28 +1364,28 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWyzcZkQykW_QPymZ2fTMwerDVUm-XhQ6WZ0NqbjNzbEznIxcF7AQ=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 3857}</t>
+          <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'reviews': 75, 'photos': 503}</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm, còn được gọi là thác Nàng, thác Bản Vặt, là một thác nước hùng vĩ nằm ở xã Mường Sang, huyện Mộc Châu, tỉnh Sơn La. Thác có chiều cao khoảng 100m, chia thành hai dòng thác chính, trông giống như một dải yếm đào mềm mại uốn lượn quanh vách núi.
-Thác Dải Yếm là một địa điểm du lịch hấp dẫn, thu hút khách du lịch trong và ngoài nước. Đây là nơi du khách có thể chiêm ngưỡng vẻ đẹp hùng vĩ của thác nước và tìm hiểu về truyền thuyết về thác.</t>
+          <t>Thác Dải Yếm nằm trên dòng suối Vặt khởi nguồn từ hai khe nước Bó Co Lắm và Bo Tá Cháu ở đầu bản Vặt, một bản của người Thái có lịch sử lâu đời. Suối Vặt chảy được 5 km đổ vào suối Bó Sập, một dòng suối lớn bắt nguồn từ bản Bó Sập giáp biên giới Việt Lào rồi chảy về đất Yên Châu. Tại nơi hợp lưu của hai suối, dòng nước gặp một vùng đá vôi và đổ xuống phía dưới tạo thành thác Dải Yếm.[5]
+Thác Dải Yếm bao gồm hai phần, thác nước phía trên rộng 70 mét, thác nước phía dưới nằm cách đó 150-200 mét. Vào mùa khô, thác phía dưới chỉ có một dòng chảy từ độ cao 50 m xuống triền đá ở dưới. hai thác đổ xuống với tổng chiều cao 100m, một bên được chia làm 9 tầng, bên còn lại 5 tầng. Cách giữa hai phần thác là một bãi đất phẳng thuận tiện cho việc tham quan của du khách. Thảm thực vật trên đỉnh thác cũng khá phong phú.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2 năm trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'reviews': 97, 'photos': 178}</t>
+          <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'reviews': 8, 'photos': 90}</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1397,86 +1393,25 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
+          <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>11 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'reviews': 27, 'photos': 260}</t>
+          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 152, 'photos': 1287}</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>4</v>
       </c>
       <c r="C45" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'reviews': 75, 'photos': 503}</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>4</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm nằm trên dòng suối Vặt khởi nguồn từ hai khe nước Bó Co Lắm và Bo Tá Cháu ở đầu bản Vặt, một bản của người Thái có lịch sử lâu đời. Suối Vặt chảy được 5 km đổ vào suối Bó Sập, một dòng suối lớn bắt nguồn từ bản Bó Sập giáp biên giới Việt Lào rồi chảy về đất Yên Châu. Tại nơi hợp lưu của hai suối, dòng nước gặp một vùng đá vôi và đổ xuống phía dưới tạo thành thác Dải Yếm.[5]
-Thác Dải Yếm bao gồm hai phần, thác nước phía trên rộng 70 mét, thác nước phía dưới nằm cách đó 150-200 mét. Vào mùa khô, thác phía dưới chỉ có một dòng chảy từ độ cao 50 m xuống triền đá ở dưới. hai thác đổ xuống với tổng chiều cao 100m, một bên được chia làm 9 tầng, bên còn lại 5 tầng. Cách giữa hai phần thác là một bãi đất phẳng thuận tiện cho việc tham quan của du khách. Thảm thực vật trên đỉnh thác cũng khá phong phú.</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'reviews': 8, 'photos': 90}</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>4</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>11 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 152, 'photos': 1287}</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>4</v>
-      </c>
-      <c r="C48" t="inlineStr">
         <is>
           <t>Thác nhỏ cũng đẹp nhưng được trang trí dành cho du lịch rồi về độ rộng nhiều tầng và thiên nhiên thì không bằng thác Nàng Tiên hoặc thác Chiềng Khoa.
 Thác Dải Yếm được đầu tư khang trang nhưng đi bộ từ bãi gửi xe vào thác hơi bị xa (vé gửi xe 30k), đường đi vào và khu thác bên trong nhiều khu chụp ảnh checkin được trang trí chụp ảnh đẹp mắt. Giá vé tháng 1/2024 là 80k/ người vào cổng nhưng đến 30/4/2024 tăng lên 100k/ng giá vé hơi cao với việc vào ngắm thác.
@@ -1484,27 +1419,27 @@
 - Bản thân mình cảm nhận thì cũng bình thường thác không cao không rộng dài đẹp nhiều tầng bằng thác Nàng Tiên hoặc Chiềng Khoa. Nói chung đi du lịch Mộc Châu ghé qua cho biết thôi. Chứ để quay lại thì ít khả năng.</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>2 năm trước</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>{'name': 'Hung Tran', 'link': 'https://www.google.com/maps/contrib/111025160790635631721?hl=vi', 'contributor_id': '111025160790635631721', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXJvHNQsMohKHo9fo2c_guCokbfqlcHTDulcTBswdAfP6GIiZRa=s120-c-rp-mo-ba12-br100', 'reviews': 120, 'photos': 1783}</t>
         </is>
       </c>
-      <c r="B49" t="n">
-        <v>5</v>
-      </c>
-      <c r="C49" t="inlineStr">
+      <c r="B46" t="n">
+        <v>5</v>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>Mới đi Thác Dải Yếm mà thấy cảnh ở đây quá ấn tượng. Nước từ thác chảy xuống nhìn thôi đã mát cả mắt, mát hơn một phần do cái thời tiết mát mẻ nơi miền núi này. Đường đến thác hơi gồ ghề tí nên đi lại cẩn thận xíu nhưng được cái khung cảnh thiên nhiên trời ban, thấy cũng quá ổn. Có mấy gian hàng bán đặc sản địa phương, cứ thấy ghé thử, giá nơi này cũng dễ chịu. Mọi thứ rất thư thái, không đông đúc, thích hợp để đi vào ngày nghỉ. Thêm vài chỗ ngồi nghỉ ngơi thì tuyệt!</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>8 tháng trước</t>
         </is>

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>{'name': 'ZjmLee YTBer', 'link': 'https://www.google.com/maps/contrib/100979561872983589256?hl=vi', 'contributor_id': '100979561872983589256', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU6i9poRXPBKYv-WgZHmB9chW6jRPCOh3klZ1Z7Yv_DOaukn4g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 80, 'photos': 1252}</t>
+          <t>{'name': 'ZjmLee YTBer', 'link': 'https://www.google.com/maps/contrib/100979561872983589256?hl=vi', 'contributor_id': '100979561872983589256', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU6i9poRXPBKYv-WgZHmB9chW6jRPCOh3klZ1Z7Yv_DOaukn4g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 80, 'photos': 1243}</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -623,7 +623,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 299, 'photos': 3604}</t>
+          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 366, 'photos': 2592}</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -631,39 +631,44 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
+          <t>Nơi rất đáng để tham quan, trãi nghiệm chút it về cầu kính và kết hợp đi ngắm thác nước.
+Có nhiều nơi lên hình đẹp, cảnh đẹp. Có bán đặc sản Mộc Châu rất đa dạng.
+😍😍👍</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4 tháng trước</t>
+          <t>Thời gian chỉnh sửa: 5 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 325}</t>
+          <t>{'name': 'Vĩ Lê Bá', 'link': 'https://www.google.com/maps/contrib/115860838984920745696?hl=vi', 'contributor_id': '115860838984920745696', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7wdRrYJWeEmKs7YInZz_FDg-T90l2ImigSwJKL2hWmQu75bzm=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 59, 'photos': 93}</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
+          <t>Đẹp thì đẹp sơ sơ nhưng không gian vẫn khá là thoải mái
+Đi bộ oklea nhưng mà vẫn còn quá nhỏ, đi cỡ 30 phút là xong mất tiêu r
+Tuỳ ngà lượng khách sẽ khác nhau và ảnh hưởng lớn tớ trải nghiệm
+Nói chung là vẫn okela</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>5 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 11, 'photos': 24}</t>
+          <t>{'name': 'THANH NGUYEN', 'link': 'https://www.google.com/maps/contrib/110418688752170937071?hl=vi', 'contributor_id': '110418688752170937071', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIBtT-SxDlGGJM5jA47OmxpGvFdaG6EOeSswcBwx4VuXgnOdQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 70, 'photos': 207}</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -671,87 +676,147 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
+          <t>thác đẹp nhưng nên đi vào mùa nước sẽ thấy sự khác biệt hơn nhiều</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5 tháng trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 299, 'photos': 3600}</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>4 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 325}</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>6 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 11, 'photos': 24}</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>5 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'reviews': 16, 'photos': 114}</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Đi tầm trưa nắng đẹp
 Thác nhỏ, đi cũng không mất quá nhiều thời gian
 Có cầu kính</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>6 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>{'name': 'Nghĩa Nguyễn Trung', 'link': 'https://www.google.com/maps/contrib/107253778101970197900?hl=vi', 'contributor_id': '107253778101970197900', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUNLHg5XlpgtWVVTp_oJKOYAejqmQORtgQ_Oe2vusE5W_sQoZc5=s120-c-rp-mo-ba12-br100', 'reviews': 275, 'photos': 1279}</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Khu vực thác nước đẹp, nhiều cảnh quan, nhiều góc chụp đẹp.</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>2 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>{'name': 'Frugal Flow', 'link': 'https://www.google.com/maps/contrib/107453311426556875441?hl=vi', 'contributor_id': '107453311426556875441', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUspWRVGEEQ_LyS16qRB57xWZ-kgNRIjgdLPY8T7HzvNMFlILCV=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 85}</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Đi vào một ngày nắng. Nắng hắt lên mặt nước long lanh nên xinh xắn hẳn:&gt; Chỉ là thác nay có vẻ hơi ít nc nên không như mình tưởng tượng.</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>6 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'reviews': 219, 'photos': 308}</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B16" t="n">
         <v>3</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Trải nghiệm vừa phải
 Giá vé theo trải nghiệm đi nhiều thác khác nhau của mình thì là khá cao so với các nơi khác, mình đi vào dịp tết nên thác ít nước.
@@ -759,98 +824,38 @@
 Cá nhân nếu quay lại Mộc Châu sẽ không đến thác này lần nào nữa</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>6 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>{'name': 'La Meu', 'link': 'https://www.google.com/maps/contrib/108858956358165703026?hl=vi', 'contributor_id': '108858956358165703026', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVKW-aZD0iBs1KBFQlmzfMiMTfjpd4PfUn4GO-K2tEt1PLpZ3YY=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 117}</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Thác Dải Yếm là điểm du lịch rất đáng đi. Đường đi dễ, xe máy hay ô tô đều thuận tiện. Không gian mát mẻ, thiên nhiên đẹp và trong lành.
 Nước thác xanh biếc, chảy mạnh nhưng nhìn rất êm và thơ mộng, chụp hình lên đẹp lắm. Khu vực được làm lối đi khá an toàn, dễ tham quan.
 Nhân viên ở đây dễ thương, nhiệt tình, hướng dẫn khách rất chu đáo và thân thiện. Phù hợp đi chơi cùng gia đình hoặc bạn bè để thư giãn, nghỉ ngơi.</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>8 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'reviews': 24, 'photos': 255}</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>5</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>6 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>8 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 1090}</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>5</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>11 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
+          <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'reviews': 24, 'photos': 255}</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -858,39 +863,39 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
+          <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2 tháng trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
+          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
+          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2 tháng trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 115, 'photos': 84}</t>
+          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 1090}</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -898,59 +903,59 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
+          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7 tháng trước</t>
+          <t>11 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 3220}</t>
+          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
+          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 250, 'photos': 4847}</t>
+          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cảnh quan đẹp, ng dân thân thiện</t>
+          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5 tháng trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
+          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 115, 'photos': 84}</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -958,19 +963,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
+          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 141, 'photos': 571}</t>
+          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 3220}</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -978,25 +983,85 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>View đẹp, chỉ tiếc là ghé hồi tháng 5 lúc đang mùa mưa, nên không được đi trải nghiệm nhiều.</t>
+          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10 tháng trước</t>
+          <t>9 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 250, 'photos': 4811}</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Cảnh quan đẹp, ng dân thân thiện</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>5 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>8 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 141, 'photos': 571}</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>View đẹp, chỉ tiếc là ghé hồi tháng 5 lúc đang mùa mưa, nên không được đi trải nghiệm nhiều.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>10 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>{'name': 'Linh Nguyễn', 'link': 'https://www.google.com/maps/contrib/109820275513447282944?hl=vi', 'contributor_id': '109820275513447282944', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVpZ-SNyOn6byhXW5cnkMUzIYl8pLeo3scME3-VG4n2ps2S2tYx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 992}</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>5</v>
-      </c>
-      <c r="C25" t="inlineStr">
+      <c r="B28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>Thác đẹp, suối nước tự nhiên, đường đi dọc suối sạch sẽ
 Một số địa điểm du lịch ở Mộc Châu mọi người có thể tham khảo
@@ -1009,163 +1074,163 @@
 2. Cá Hồi Thanh Bảy</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>2 năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 80, 'photos': 185}</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>4</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>6 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>{'name': 'Anh Tuấn Trần', 'link': 'https://www.google.com/maps/contrib/106361750645670984745?hl=vi', 'contributor_id': '106361750645670984745', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXiNjEqD4gV0wYaTlBDaztRxN3Bz6wZiiUqJ5pnHqrMT1HyLF_rBg=s120-c-rp-mo-ba12-br100', 'reviews': 956, 'photos': 4071}</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Chẳng hiểu Mộc Châu làm du lịch kiểu gì mà chỗ nào cũng bắt mua vé và giá vé quá cao. Cứ một điểm tham quan là 100k/người mà chẳng có gì đặc sắc cả. Thác dải yếm có quá nhiều công trình nhân tạo. Kể cả 100k/người cho cả Thác Dải Yếm + Cầu Kính thì mình vẫn thấy đắt - không tương xứng. Đây còn vé riêng cho thác và riêng cho cầu kính mặc dù cả 2 này là cùng một điêm. Không muốn quay lại bao giờ nữa.</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2 năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>5</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 71, 'photos': 496}</t>
+          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 80, 'photos': 185}</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
+          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3 tháng trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>{'name': 'Anh Tuấn Trần', 'link': 'https://www.google.com/maps/contrib/106361750645670984745?hl=vi', 'contributor_id': '106361750645670984745', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXiNjEqD4gV0wYaTlBDaztRxN3Bz6wZiiUqJ5pnHqrMT1HyLF_rBg=s120-c-rp-mo-ba12-br100', 'reviews': 956, 'photos': 4071}</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Chẳng hiểu Mộc Châu làm du lịch kiểu gì mà chỗ nào cũng bắt mua vé và giá vé quá cao. Cứ một điểm tham quan là 100k/người mà chẳng có gì đặc sắc cả. Thác dải yếm có quá nhiều công trình nhân tạo. Kể cả 100k/người cho cả Thác Dải Yếm + Cầu Kính thì mình vẫn thấy đắt - không tương xứng. Đây còn vé riêng cho thác và riêng cho cầu kính mặc dù cả 2 này là cùng một điêm. Không muốn quay lại bao giờ nữa.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 71, 'photos': 496}</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>3 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'reviews': 78, 'photos': 260}</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B33" t="n">
         <v>4</v>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
 Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>{'name': 'Mai Nguyễn', 'link': 'https://www.google.com/maps/contrib/101330344304584692421?hl=vi', 'contributor_id': '101330344304584692421', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocLN09xUhcK1CuSvLI4U-MC1m1LployphMNgUrT9xqkPlzqHlA=s120-c-rp-mo-br100', 'reviews': 5, 'photos': 7}</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>5</v>
-      </c>
-      <c r="C31" t="inlineStr">
+      <c r="B34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>Cảnh đẹp, có cả trải nghiệm cầu kính và zipline mà giá phải chăng hơn bên khu cầu kính bạch long</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>6 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 533, 'photos': 4107}</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="B35" t="n">
         <v>4</v>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 574}</t>
         </is>
       </c>
-      <c r="B33" t="n">
-        <v>5</v>
-      </c>
-      <c r="C33" t="inlineStr">
+      <c r="B36" t="n">
+        <v>5</v>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>Đúng tên gọi của nó. Thác cũng rất đẹp. Nếu vào mùa nước chắc còn đẹp hơn.
 Cảnh quan cũng rất sạch đẹp.
@@ -1174,66 +1239,6 @@
 - vé vào cổng giá phù hợp</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4192}</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>5</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Thời gian chỉnh sửa: 2 năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 518}</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>5</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>4</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
-        </is>
-      </c>
       <c r="D36" t="inlineStr">
         <is>
           <t>một năm trước</t>
@@ -1243,7 +1248,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
+          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4192}</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1251,19 +1256,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
+          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>Thời gian chỉnh sửa: 2 năm trước</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 1623}</t>
+          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 518}</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1271,19 +1276,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 50, 'photos': 144}</t>
+          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1291,7 +1296,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
+          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1303,115 +1308,175 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWyzcZkQykW_QPymZ2fTMwerDVUm-XhQ6WZ0NqbjNzbEznIxcF7AQ=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 3857}</t>
+          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>5</v>
       </c>
       <c r="C40" t="inlineStr">
+        <is>
+          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 1623}</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>5</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>9 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 50, 'photos': 144}</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>4</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWyzcZkQykW_QPymZ2fTMwerDVUm-XhQ6WZ0NqbjNzbEznIxcF7AQ=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 3872}</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>5</v>
+      </c>
+      <c r="C43" t="inlineStr">
         <is>
           <t>Thác Dải Yếm, còn được gọi là thác Nàng, thác Bản Vặt, là một thác nước hùng vĩ nằm ở xã Mường Sang, huyện Mộc Châu, tỉnh Sơn La. Thác có chiều cao khoảng 100m, chia thành hai dòng thác chính, trông giống như một dải yếm đào mềm mại uốn lượn quanh vách núi.
 Thác Dải Yếm là một địa điểm du lịch hấp dẫn, thu hút khách du lịch trong và ngoài nước. Đây là nơi du khách có thể chiêm ngưỡng vẻ đẹp hùng vĩ của thác nước và tìm hiểu về truyền thuyết về thác.</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>2 năm trước</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'reviews': 97, 'photos': 178}</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="B44" t="n">
         <v>4</v>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'reviews': 27, 'photos': 260}</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B45" t="n">
         <v>4</v>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'reviews': 75, 'photos': 503}</t>
         </is>
       </c>
-      <c r="B43" t="n">
+      <c r="B46" t="n">
         <v>4</v>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Thác Dải Yếm nằm trên dòng suối Vặt khởi nguồn từ hai khe nước Bó Co Lắm và Bo Tá Cháu ở đầu bản Vặt, một bản của người Thái có lịch sử lâu đời. Suối Vặt chảy được 5 km đổ vào suối Bó Sập, một dòng suối lớn bắt nguồn từ bản Bó Sập giáp biên giới Việt Lào rồi chảy về đất Yên Châu. Tại nơi hợp lưu của hai suối, dòng nước gặp một vùng đá vôi và đổ xuống phía dưới tạo thành thác Dải Yếm.[5]
 Thác Dải Yếm bao gồm hai phần, thác nước phía trên rộng 70 mét, thác nước phía dưới nằm cách đó 150-200 mét. Vào mùa khô, thác phía dưới chỉ có một dòng chảy từ độ cao 50 m xuống triền đá ở dưới. hai thác đổ xuống với tổng chiều cao 100m, một bên được chia làm 9 tầng, bên còn lại 5 tầng. Cách giữa hai phần thác là một bãi đất phẳng thuận tiện cho việc tham quan của du khách. Thảm thực vật trên đỉnh thác cũng khá phong phú.</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'reviews': 8, 'photos': 90}</t>
         </is>
       </c>
-      <c r="B44" t="n">
+      <c r="B47" t="n">
         <v>4</v>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>11 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 152, 'photos': 1287}</t>
         </is>
       </c>
-      <c r="B45" t="n">
+      <c r="B48" t="n">
         <v>4</v>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Thác nhỏ cũng đẹp nhưng được trang trí dành cho du lịch rồi về độ rộng nhiều tầng và thiên nhiên thì không bằng thác Nàng Tiên hoặc thác Chiềng Khoa.
 Thác Dải Yếm được đầu tư khang trang nhưng đi bộ từ bãi gửi xe vào thác hơi bị xa (vé gửi xe 30k), đường đi vào và khu thác bên trong nhiều khu chụp ảnh checkin được trang trí chụp ảnh đẹp mắt. Giá vé tháng 1/2024 là 80k/ người vào cổng nhưng đến 30/4/2024 tăng lên 100k/ng giá vé hơi cao với việc vào ngắm thác.
@@ -1419,27 +1484,27 @@
 - Bản thân mình cảm nhận thì cũng bình thường thác không cao không rộng dài đẹp nhiều tầng bằng thác Nàng Tiên hoặc Chiềng Khoa. Nói chung đi du lịch Mộc Châu ghé qua cho biết thôi. Chứ để quay lại thì ít khả năng.</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>2 năm trước</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>{'name': 'Hung Tran', 'link': 'https://www.google.com/maps/contrib/111025160790635631721?hl=vi', 'contributor_id': '111025160790635631721', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXJvHNQsMohKHo9fo2c_guCokbfqlcHTDulcTBswdAfP6GIiZRa=s120-c-rp-mo-ba12-br100', 'reviews': 120, 'photos': 1783}</t>
         </is>
       </c>
-      <c r="B46" t="n">
-        <v>5</v>
-      </c>
-      <c r="C46" t="inlineStr">
+      <c r="B49" t="n">
+        <v>5</v>
+      </c>
+      <c r="C49" t="inlineStr">
         <is>
           <t>Mới đi Thác Dải Yếm mà thấy cảnh ở đây quá ấn tượng. Nước từ thác chảy xuống nhìn thôi đã mát cả mắt, mát hơn một phần do cái thời tiết mát mẻ nơi miền núi này. Đường đến thác hơi gồ ghề tí nên đi lại cẩn thận xíu nhưng được cái khung cảnh thiên nhiên trời ban, thấy cũng quá ổn. Có mấy gian hàng bán đặc sản địa phương, cứ thấy ghé thử, giá nơi này cũng dễ chịu. Mọi thứ rất thư thái, không đông đúc, thích hợp để đi vào ngày nghỉ. Thêm vài chỗ ngồi nghỉ ngơi thì tuyệt!</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>8 tháng trước</t>
         </is>

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -688,7 +688,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 299, 'photos': 3600}</t>
+          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 301, 'photos': 3600}</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -728,7 +728,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 11, 'photos': 24}</t>
+          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 24}</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3 tháng trước</t>
+          <t>4 tháng trước</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 50, 'photos': 144}</t>
+          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 49, 'photos': 144}</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1368,7 +1368,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWyzcZkQykW_QPymZ2fTMwerDVUm-XhQ6WZ0NqbjNzbEznIxcF7AQ=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 3872}</t>
+          <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWyzcZkQykW_QPymZ2fTMwerDVUm-XhQ6WZ0NqbjNzbEznIxcF7AQ=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 3873}</t>
         </is>
       </c>
       <c r="B43" t="n">

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -453,13 +453,33 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>{'name': 'Hanh Vu', 'link': 'https://www.google.com/maps/contrib/101916078015092582424?hl=vi', 'contributor_id': '101916078015092582424', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWKKa85i2VN2RSjhkp53oKKDcXbjK49YmqN3D2BpL8QOof8ZRlo=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 28, 'photos': 33}</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Thác Dải Yếm nằm trong khu du lịch sinh thái Thác Dải Yếm, vé vào 150k/người. Bên trong có thác nước nhưng nước khá đục nên không tắm được, có thêm cầu kính tình yêu để chụp ảnh. Mình thấy khu này không có quá nhiều điểm để tham quan, chủ yếu vào ngắm thác và chụp ảnh, nên nếu kỳ vọng có nhiều hoạt động thì sẽ hơi ít.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>một tuần trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>{'name': 'Hưng Nguyễn Duy (Hưng Photo)', 'link': 'https://www.google.com/maps/contrib/110173941936897044295?hl=vi', 'contributor_id': '110173941936897044295', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXshx7xq3ntsswbv03kbw9Z9KIntVjsKdM747CeNwqebP-xH_RO=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 192, 'photos': 2146}</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>Địa điểm du lịch nổi tiếng nên khám phá khi tới Mộc Châu.
 Chỗ để xe rộng rãi (Phí gửi xe là 30N)
@@ -468,26 +488,6 @@
 Có bán nhiều đồ lưu niệm và đặc sản núi rừng Tây Bắc.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>4 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>{'name': 'Cửu Quang Nguyễn', 'link': 'https://www.google.com/maps/contrib/107704339232071144994?hl=vi', 'contributor_id': '107704339232071144994', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV2_oJLqzlVCtXNV77ConxSPDhhMhFP-czjeCf6uCm7cabO88k=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 78, 'photos': 356}</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm nằm trong khu du lịch sinh thái thác Dải Yếm, đường đi khá tiện lợi để ghé vào, tuy nhiên cần chú ý lối vào có khúc cua dốc khá ngoặt. Vé vào là 150k/người, bên trong có khá nhiều vị trí để du ngoạn và ngắm cảnh, đặc biệt là khu vực thác nước rất hùng vĩ và mát mẻ, có cầu dẫn vào nhìn rất thơ mộng và tuyệt vời. Nếu có dịp ghé lên Mộc Châu thì nên ghé vào đây chơi 1 lần để du ngoạn thắng cảnh thiên nhiên tại nơi đây.</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>4 tháng trước</t>
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Anh Quân', 'link': 'https://www.google.com/maps/contrib/111631093743063403454?hl=vi', 'contributor_id': '111631093743063403454', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIy-NjGEZ7ggp1yhLvVSe2iSDFAUAF4AILlK1IHBmSbkPzlKg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 9, 'photos': 24}</t>
+          <t>{'name': 'Cửu Quang Nguyễn', 'link': 'https://www.google.com/maps/contrib/107704339232071144994?hl=vi', 'contributor_id': '107704339232071144994', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV2_oJLqzlVCtXNV77ConxSPDhhMhFP-czjeCf6uCm7cabO88k=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 78, 'photos': 356}</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -505,25 +505,45 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cảnh đẹp, nhưng xu là đi ngay lúc mưa nên thác có nước như cf</t>
+          <t>Thác Dải Yếm nằm trong khu du lịch sinh thái thác Dải Yếm, đường đi khá tiện lợi để ghé vào, tuy nhiên cần chú ý lối vào có khúc cua dốc khá ngoặt. Vé vào là 150k/người, bên trong có khá nhiều vị trí để du ngoạn và ngắm cảnh, đặc biệt là khu vực thác nước rất hùng vĩ và mát mẻ, có cầu dẫn vào nhìn rất thơ mộng và tuyệt vời. Nếu có dịp ghé lên Mộc Châu thì nên ghé vào đây chơi 1 lần để du ngoạn thắng cảnh thiên nhiên tại nơi đây.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>một tháng trước</t>
+          <t>5 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>{'name': 'Nguyễn Anh Quân', 'link': 'https://www.google.com/maps/contrib/111631093743063403454?hl=vi', 'contributor_id': '111631093743063403454', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIy-NjGEZ7ggp1yhLvVSe2iSDFAUAF4AILlK1IHBmSbkPzlKg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 9, 'photos': 24}</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Cảnh đẹp, nhưng xu là đi ngay lúc mưa nên thác có nước như cf</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>một tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>{'name': 'Thái Nguyễn', 'link': 'https://www.google.com/maps/contrib/105517365260915933657?hl=vi', 'contributor_id': '105517365260915933657', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXLOkY3FUSH3Mz-aapJXPQUgoCFlQP20PICWZGzVI3cPkRkBIt_ew=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 65, 'photos': 175}</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>Nếu đi cùng Lover sẽ đẹp hơn.
 Nếu tự nhìn lại
@@ -591,22 +611,22 @@
 Hơn cả tới thiên đường</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>{'name': 'ZjmLee YTBer', 'link': 'https://www.google.com/maps/contrib/100979561872983589256?hl=vi', 'contributor_id': '100979561872983589256', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU6i9poRXPBKYv-WgZHmB9chW6jRPCOh3klZ1Z7Yv_DOaukn4g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 80, 'photos': 1243}</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>{'name': 'ZjmLee YTBer', 'link': 'https://www.google.com/maps/contrib/100979561872983589256?hl=vi', 'contributor_id': '100979561872983589256', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU6i9poRXPBKYv-WgZHmB9chW6jRPCOh3klZ1Z7Yv_DOaukn4g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 79, 'photos': 1243}</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>Nghe người địa phương kể lại thì cái tên “Dải Yếm” xuất phát từ truyền thuyết của người Thái. Họ nói rằng dòng thác trắng xóa từ trên cao đổ xuống giống như dải yếm của người con gái, nên từ đó cái tên này được gọi luôn cho tới bây giờ. Nghe vậy nên đứng nhìn dòng thác cũng thấy có chút gì đó rất nên thơ.
 Đi bộ quanh khu thác khá dễ, có lối đi và bậc đá để xuống gần chân thác. Nếu đi vào mùa nước nhiều thì thác nhìn đẹp hơn, nước trắng xóa và tiếng thác nghe rất đã tai. Còn những ngày nắng nhẹ thì không khí ở đây khá chill, kiểu ngồi nghỉ một chút, nghe tiếng nước và nhìn rừng cây xung quanh cũng thấy thư giãn.
@@ -614,44 +634,44 @@
 Nếu đang đi du lịch tự túc ở Mộc Châu, thì Thác Dải Yếm là một nơi khá đáng ghé qua. Không cần quá nhiều thời gian, chỉ cần dành khoảng một tiếng dạo quanh thôi cũng đủ để cảm nhận được một góc thiên nhiên rất đặc trưng của vùng núi này.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>6 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 366, 'photos': 2592}</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>Nơi rất đáng để tham quan, trãi nghiệm chút it về cầu kính và kết hợp đi ngắm thác nước.
 Có nhiều nơi lên hình đẹp, cảnh đẹp. Có bán đặc sản Mộc Châu rất đa dạng.
 😍😍👍</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Thời gian chỉnh sửa: 5 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>{'name': 'Vĩ Lê Bá', 'link': 'https://www.google.com/maps/contrib/115860838984920745696?hl=vi', 'contributor_id': '115860838984920745696', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7wdRrYJWeEmKs7YInZz_FDg-T90l2ImigSwJKL2hWmQu75bzm=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 59, 'photos': 93}</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B9" t="n">
         <v>4</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Đẹp thì đẹp sơ sơ nhưng không gian vẫn khá là thoải mái
 Đi bộ oklea nhưng mà vẫn còn quá nhỏ, đi cỡ 30 phút là xong mất tiêu r
@@ -659,36 +679,16 @@
 Nói chung là vẫn okela</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>5 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>{'name': 'THANH NGUYEN', 'link': 'https://www.google.com/maps/contrib/110418688752170937071?hl=vi', 'contributor_id': '110418688752170937071', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIBtT-SxDlGGJM5jA47OmxpGvFdaG6EOeSswcBwx4VuXgnOdQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 70, 'photos': 207}</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>thác đẹp nhưng nên đi vào mùa nước sẽ thấy sự khác biệt hơn nhiều</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 301, 'photos': 3600}</t>
+          <t>{'name': 'THANH NGUYEN', 'link': 'https://www.google.com/maps/contrib/110418688752170937071?hl=vi', 'contributor_id': '110418688752170937071', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIBtT-SxDlGGJM5jA47OmxpGvFdaG6EOeSswcBwx4VuXgnOdQ=s120-c-rp-mo-ba12-br100', 'reviews': 70, 'photos': 207}</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -696,19 +696,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
+          <t>thác đẹp nhưng nên đi vào mùa nước sẽ thấy sự khác biệt hơn nhiều</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4 tháng trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 325}</t>
+          <t>{'name': 'Nguyễn Anh Quân', 'link': 'https://www.google.com/maps/contrib/111631093743063403454?hl=vi', 'contributor_id': '111631093743063403454', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIy-NjGEZ7ggp1yhLvVSe2iSDFAUAF4AILlK1IHBmSbkPzlKg=s120-c-rp-mo-ba12-br100', 'reviews': 9, 'photos': 24}</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -716,19 +716,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
+          <t>Cảnh đẹp, nhưng xu là đi ngay lúc mưa nên thác có nước như cf</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>một tháng trước</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 24}</t>
+          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 300, 'photos': 3600}</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -736,71 +736,71 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
+          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5 tháng trước</t>
+          <t>4 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 143, 'photos': 325}</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>6 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 24}</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>5 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'reviews': 16, 'photos': 114}</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Đi tầm trưa nắng đẹp
 Thác nhỏ, đi cũng không mất quá nhiều thời gian
 Có cầu kính</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>6 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>{'name': 'Nghĩa Nguyễn Trung', 'link': 'https://www.google.com/maps/contrib/107253778101970197900?hl=vi', 'contributor_id': '107253778101970197900', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUNLHg5XlpgtWVVTp_oJKOYAejqmQORtgQ_Oe2vusE5W_sQoZc5=s120-c-rp-mo-ba12-br100', 'reviews': 275, 'photos': 1279}</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Khu vực thác nước đẹp, nhiều cảnh quan, nhiều góc chụp đẹp.</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>{'name': 'Frugal Flow', 'link': 'https://www.google.com/maps/contrib/107453311426556875441?hl=vi', 'contributor_id': '107453311426556875441', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUspWRVGEEQ_LyS16qRB57xWZ-kgNRIjgdLPY8T7HzvNMFlILCV=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 85}</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>5</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Đi vào một ngày nắng. Nắng hắt lên mặt nước long lanh nên xinh xắn hẳn:&gt; Chỉ là thác nay có vẻ hơi ít nc nên không như mình tưởng tượng.</t>
-        </is>
-      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>6 tháng trước</t>
@@ -810,13 +810,53 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>{'name': 'Nghĩa Nguyễn Trung', 'link': 'https://www.google.com/maps/contrib/107253778101970197900?hl=vi', 'contributor_id': '107253778101970197900', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUNLHg5XlpgtWVVTp_oJKOYAejqmQORtgQ_Oe2vusE5W_sQoZc5=s120-c-rp-mo-ba12-br100', 'reviews': 275, 'photos': 1279}</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Khu vực thác nước đẹp, nhiều cảnh quan, nhiều góc chụp đẹp.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>{'name': 'Frugal Flow', 'link': 'https://www.google.com/maps/contrib/107453311426556875441?hl=vi', 'contributor_id': '107453311426556875441', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUspWRVGEEQ_LyS16qRB57xWZ-kgNRIjgdLPY8T7HzvNMFlILCV=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 85}</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Đi vào một ngày nắng. Nắng hắt lên mặt nước long lanh nên xinh xắn hẳn:&gt; Chỉ là thác nay có vẻ hơi ít nc nên không như mình tưởng tượng.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>6 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'reviews': 219, 'photos': 308}</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B18" t="n">
         <v>3</v>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Trải nghiệm vừa phải
 Giá vé theo trải nghiệm đi nhiều thác khác nhau của mình thì là khá cao so với các nơi khác, mình đi vào dịp tết nên thác ít nước.
@@ -824,68 +864,28 @@
 Cá nhân nếu quay lại Mộc Châu sẽ không đến thác này lần nào nữa</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>6 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>{'name': 'La Meu', 'link': 'https://www.google.com/maps/contrib/108858956358165703026?hl=vi', 'contributor_id': '108858956358165703026', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVKW-aZD0iBs1KBFQlmzfMiMTfjpd4PfUn4GO-K2tEt1PLpZ3YY=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 117}</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>5</v>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Thác Dải Yếm là điểm du lịch rất đáng đi. Đường đi dễ, xe máy hay ô tô đều thuận tiện. Không gian mát mẻ, thiên nhiên đẹp và trong lành.
 Nước thác xanh biếc, chảy mạnh nhưng nhìn rất êm và thơ mộng, chụp hình lên đẹp lắm. Khu vực được làm lối đi khá an toàn, dễ tham quan.
 Nhân viên ở đây dễ thương, nhiệt tình, hướng dẫn khách rất chu đáo và thân thiện. Phù hợp đi chơi cùng gia đình hoặc bạn bè để thư giãn, nghỉ ngơi.</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>8 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'reviews': 24, 'photos': 255}</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>5</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>6 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>3</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
-        </is>
-      </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>8 tháng trước</t>
@@ -895,7 +895,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 1090}</t>
+          <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'reviews': 24, 'photos': 255}</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -903,59 +903,59 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
+          <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>11 tháng trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
+          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
+          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2 tháng trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
+          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 1090}</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
+          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2 tháng trước</t>
+          <t>11 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 115, 'photos': 84}</t>
+          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -963,19 +963,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
+          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>7 tháng trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 3220}</t>
+          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -983,19 +983,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
+          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 250, 'photos': 4811}</t>
+          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 115, 'photos': 84}</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1003,65 +1003,105 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cảnh quan đẹp, ng dân thân thiện</t>
+          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>5 tháng trước</t>
+          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
+          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 3220}</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
+          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>9 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 141, 'photos': 571}</t>
+          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 250, 'photos': 4775}</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>View đẹp, chỉ tiếc là ghé hồi tháng 5 lúc đang mùa mưa, nên không được đi trải nghiệm nhiều.</t>
+          <t>Cảnh quan đẹp, ng dân thân thiện</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10 tháng trước</t>
+          <t>5 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>8 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 141, 'photos': 571}</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>View đẹp, chỉ tiếc là ghé hồi tháng 5 lúc đang mùa mưa, nên không được đi trải nghiệm nhiều.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>10 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>{'name': 'Linh Nguyễn', 'link': 'https://www.google.com/maps/contrib/109820275513447282944?hl=vi', 'contributor_id': '109820275513447282944', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVpZ-SNyOn6byhXW5cnkMUzIYl8pLeo3scME3-VG4n2ps2S2tYx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 992}</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>5</v>
-      </c>
-      <c r="C28" t="inlineStr">
+      <c r="B30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>Thác đẹp, suối nước tự nhiên, đường đi dọc suối sạch sẽ
 Một số địa điểm du lịch ở Mộc Châu mọi người có thể tham khảo
@@ -1074,46 +1114,6 @@
 2. Cá Hồi Thanh Bảy</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2 năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 80, 'photos': 185}</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>4</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>6 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>{'name': 'Anh Tuấn Trần', 'link': 'https://www.google.com/maps/contrib/106361750645670984745?hl=vi', 'contributor_id': '106361750645670984745', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXiNjEqD4gV0wYaTlBDaztRxN3Bz6wZiiUqJ5pnHqrMT1HyLF_rBg=s120-c-rp-mo-ba12-br100', 'reviews': 956, 'photos': 4071}</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Chẳng hiểu Mộc Châu làm du lịch kiểu gì mà chỗ nào cũng bắt mua vé và giá vé quá cao. Cứ một điểm tham quan là 100k/người mà chẳng có gì đặc sắc cả. Thác dải yếm có quá nhiều công trình nhân tạo. Kể cả 100k/người cho cả Thác Dải Yếm + Cầu Kính thì mình vẫn thấy đắt - không tương xứng. Đây còn vé riêng cho thác và riêng cho cầu kính mặc dù cả 2 này là cùng một điêm. Không muốn quay lại bao giờ nữa.</t>
-        </is>
-      </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>2 năm trước</t>
@@ -1123,98 +1123,98 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
+          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 80, 'photos': 185}</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
+          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 71, 'photos': 496}</t>
+          <t>{'name': 'Anh Tuấn Trần', 'link': 'https://www.google.com/maps/contrib/106361750645670984745?hl=vi', 'contributor_id': '106361750645670984745', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXiNjEqD4gV0wYaTlBDaztRxN3Bz6wZiiUqJ5pnHqrMT1HyLF_rBg=s120-c-rp-mo-ba12-br100', 'reviews': 956, 'photos': 4071}</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
+          <t>Chẳng hiểu Mộc Châu làm du lịch kiểu gì mà chỗ nào cũng bắt mua vé và giá vé quá cao. Cứ một điểm tham quan là 100k/người mà chẳng có gì đặc sắc cả. Thác dải yếm có quá nhiều công trình nhân tạo. Kể cả 100k/người cho cả Thác Dải Yếm + Cầu Kính thì mình vẫn thấy đắt - không tương xứng. Đây còn vé riêng cho thác và riêng cho cầu kính mặc dù cả 2 này là cùng một điêm. Không muốn quay lại bao giờ nữa.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4 tháng trước</t>
+          <t>2 năm trước</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 71, 'photos': 496}</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>4 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'reviews': 78, 'photos': 260}</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="B35" t="n">
         <v>4</v>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
 Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>{'name': 'Mai Nguyễn', 'link': 'https://www.google.com/maps/contrib/101330344304584692421?hl=vi', 'contributor_id': '101330344304584692421', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocLN09xUhcK1CuSvLI4U-MC1m1LployphMNgUrT9xqkPlzqHlA=s120-c-rp-mo-br100', 'reviews': 5, 'photos': 7}</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>5</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Cảnh đẹp, có cả trải nghiệm cầu kính và zipline mà giá phải chăng hơn bên khu cầu kính bạch long</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>6 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 533, 'photos': 4107}</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>4</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
-        </is>
-      </c>
       <c r="D35" t="inlineStr">
         <is>
           <t>một năm trước</t>
@@ -1224,13 +1224,53 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>{'name': 'Mai Nguyễn', 'link': 'https://www.google.com/maps/contrib/101330344304584692421?hl=vi', 'contributor_id': '101330344304584692421', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocLN09xUhcK1CuSvLI4U-MC1m1LployphMNgUrT9xqkPlzqHlA=s120-c-rp-mo-br100', 'reviews': 5, 'photos': 7}</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>5</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Cảnh đẹp, có cả trải nghiệm cầu kính và zipline mà giá phải chăng hơn bên khu cầu kính bạch long</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>6 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 533, 'photos': 4107}</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>4</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 574}</t>
         </is>
       </c>
-      <c r="B36" t="n">
-        <v>5</v>
-      </c>
-      <c r="C36" t="inlineStr">
+      <c r="B38" t="n">
+        <v>5</v>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>Đúng tên gọi của nó. Thác cũng rất đẹp. Nếu vào mùa nước chắc còn đẹp hơn.
 Cảnh quan cũng rất sạch đẹp.
@@ -1239,46 +1279,6 @@
 - vé vào cổng giá phù hợp</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4192}</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>5</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Thời gian chỉnh sửa: 2 năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 518}</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>5</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
-        </is>
-      </c>
       <c r="D38" t="inlineStr">
         <is>
           <t>một năm trước</t>
@@ -1288,27 +1288,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
+          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4192}</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
+          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>Thời gian chỉnh sửa: 2 năm trước</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
+          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 518}</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
+          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1328,35 +1328,35 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 1623}</t>
+          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 49, 'photos': 144}</t>
+          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
+          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1368,68 +1368,68 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWyzcZkQykW_QPymZ2fTMwerDVUm-XhQ6WZ0NqbjNzbEznIxcF7AQ=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 3873}</t>
+          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 1623}</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>5</v>
       </c>
       <c r="C43" t="inlineStr">
+        <is>
+          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>9 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 49, 'photos': 144}</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>4</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWyzcZkQykW_QPymZ2fTMwerDVUm-XhQ6WZ0NqbjNzbEznIxcF7AQ=s120-c-rp-mo-ba12-br100', 'reviews': 149, 'photos': 3873}</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>5</v>
+      </c>
+      <c r="C45" t="inlineStr">
         <is>
           <t>Thác Dải Yếm, còn được gọi là thác Nàng, thác Bản Vặt, là một thác nước hùng vĩ nằm ở xã Mường Sang, huyện Mộc Châu, tỉnh Sơn La. Thác có chiều cao khoảng 100m, chia thành hai dòng thác chính, trông giống như một dải yếm đào mềm mại uốn lượn quanh vách núi.
 Thác Dải Yếm là một địa điểm du lịch hấp dẫn, thu hút khách du lịch trong và ngoài nước. Đây là nơi du khách có thể chiêm ngưỡng vẻ đẹp hùng vĩ của thác nước và tìm hiểu về truyền thuyết về thác.</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>2 năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'reviews': 97, 'photos': 178}</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>4</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'reviews': 27, 'photos': 260}</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>4</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'reviews': 75, 'photos': 503}</t>
+          <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'reviews': 97, 'photos': 178}</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1437,76 +1437,73 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'reviews': 27, 'photos': 260}</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>4</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'reviews': 75, 'photos': 503}</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>4</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
           <t>Thác Dải Yếm nằm trên dòng suối Vặt khởi nguồn từ hai khe nước Bó Co Lắm và Bo Tá Cháu ở đầu bản Vặt, một bản của người Thái có lịch sử lâu đời. Suối Vặt chảy được 5 km đổ vào suối Bó Sập, một dòng suối lớn bắt nguồn từ bản Bó Sập giáp biên giới Việt Lào rồi chảy về đất Yên Châu. Tại nơi hợp lưu của hai suối, dòng nước gặp một vùng đá vôi và đổ xuống phía dưới tạo thành thác Dải Yếm.[5]
 Thác Dải Yếm bao gồm hai phần, thác nước phía trên rộng 70 mét, thác nước phía dưới nằm cách đó 150-200 mét. Vào mùa khô, thác phía dưới chỉ có một dòng chảy từ độ cao 50 m xuống triền đá ở dưới. hai thác đổ xuống với tổng chiều cao 100m, một bên được chia làm 9 tầng, bên còn lại 5 tầng. Cách giữa hai phần thác là một bãi đất phẳng thuận tiện cho việc tham quan của du khách. Thảm thực vật trên đỉnh thác cũng khá phong phú.</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'reviews': 8, 'photos': 90}</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>4</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>11 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 152, 'photos': 1287}</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>4</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Thác nhỏ cũng đẹp nhưng được trang trí dành cho du lịch rồi về độ rộng nhiều tầng và thiên nhiên thì không bằng thác Nàng Tiên hoặc thác Chiềng Khoa.
-Thác Dải Yếm được đầu tư khang trang nhưng đi bộ từ bãi gửi xe vào thác hơi bị xa (vé gửi xe 30k), đường đi vào và khu thác bên trong nhiều khu chụp ảnh checkin được trang trí chụp ảnh đẹp mắt. Giá vé tháng 1/2024 là 80k/ người vào cổng nhưng đến 30/4/2024 tăng lên 100k/ng giá vé hơi cao với việc vào ngắm thác.
-Muốn lên cầu kính giá vé riêng 100k/người. Lên cầu kính chơi ngắm cảnh cũng ok. Từ cầu kính nhìn đi mấy quả đồi phía dưới bị đào bới làm đường nhìn không được thiên nhiên cho lắm.
-- Bản thân mình cảm nhận thì cũng bình thường thác không cao không rộng dài đẹp nhiều tầng bằng thác Nàng Tiên hoặc Chiềng Khoa. Nói chung đi du lịch Mộc Châu ghé qua cho biết thôi. Chứ để quay lại thì ít khả năng.</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2 năm trước</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>{'name': 'Hung Tran', 'link': 'https://www.google.com/maps/contrib/111025160790635631721?hl=vi', 'contributor_id': '111025160790635631721', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXJvHNQsMohKHo9fo2c_guCokbfqlcHTDulcTBswdAfP6GIiZRa=s120-c-rp-mo-ba12-br100', 'reviews': 120, 'photos': 1783}</t>
+          <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'reviews': 8, 'photos': 90}</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Mới đi Thác Dải Yếm mà thấy cảnh ở đây quá ấn tượng. Nước từ thác chảy xuống nhìn thôi đã mát cả mắt, mát hơn một phần do cái thời tiết mát mẻ nơi miền núi này. Đường đến thác hơi gồ ghề tí nên đi lại cẩn thận xíu nhưng được cái khung cảnh thiên nhiên trời ban, thấy cũng quá ổn. Có mấy gian hàng bán đặc sản địa phương, cứ thấy ghé thử, giá nơi này cũng dễ chịu. Mọi thứ rất thư thái, không đông đúc, thích hợp để đi vào ngày nghỉ. Thêm vài chỗ ngồi nghỉ ngơi thì tuyệt!</t>
+          <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>11 tháng trước</t>
         </is>
       </c>
     </row>

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -517,33 +517,13 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Anh Quân', 'link': 'https://www.google.com/maps/contrib/111631093743063403454?hl=vi', 'contributor_id': '111631093743063403454', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIy-NjGEZ7ggp1yhLvVSe2iSDFAUAF4AILlK1IHBmSbkPzlKg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 9, 'photos': 24}</t>
+          <t>{'name': 'Thái Nguyễn', 'link': 'https://www.google.com/maps/contrib/105517365260915933657?hl=vi', 'contributor_id': '105517365260915933657', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXLOkY3FUSH3Mz-aapJXPQUgoCFlQP20PICWZGzVI3cPkRkBIt_ew=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 65, 'photos': 175}</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>5</v>
       </c>
       <c r="C5" t="inlineStr">
-        <is>
-          <t>Cảnh đẹp, nhưng xu là đi ngay lúc mưa nên thác có nước như cf</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>một tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>{'name': 'Thái Nguyễn', 'link': 'https://www.google.com/maps/contrib/105517365260915933657?hl=vi', 'contributor_id': '105517365260915933657', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXLOkY3FUSH3Mz-aapJXPQUgoCFlQP20PICWZGzVI3cPkRkBIt_ew=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 65, 'photos': 175}</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" t="inlineStr">
         <is>
           <t>Nếu đi cùng Lover sẽ đẹp hơn.
 Nếu tự nhìn lại
@@ -611,22 +591,22 @@
 Hơn cả tới thiên đường</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>{'name': 'ZjmLee YTBer', 'link': 'https://www.google.com/maps/contrib/100979561872983589256?hl=vi', 'contributor_id': '100979561872983589256', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU6i9poRXPBKYv-WgZHmB9chW6jRPCOh3klZ1Z7Yv_DOaukn4g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 79, 'photos': 1243}</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>Nghe người địa phương kể lại thì cái tên “Dải Yếm” xuất phát từ truyền thuyết của người Thái. Họ nói rằng dòng thác trắng xóa từ trên cao đổ xuống giống như dải yếm của người con gái, nên từ đó cái tên này được gọi luôn cho tới bây giờ. Nghe vậy nên đứng nhìn dòng thác cũng thấy có chút gì đó rất nên thơ.
 Đi bộ quanh khu thác khá dễ, có lối đi và bậc đá để xuống gần chân thác. Nếu đi vào mùa nước nhiều thì thác nhìn đẹp hơn, nước trắng xóa và tiếng thác nghe rất đã tai. Còn những ngày nắng nhẹ thì không khí ở đây khá chill, kiểu ngồi nghỉ một chút, nghe tiếng nước và nhìn rừng cây xung quanh cũng thấy thư giãn.
@@ -634,44 +614,44 @@
 Nếu đang đi du lịch tự túc ở Mộc Châu, thì Thác Dải Yếm là một nơi khá đáng ghé qua. Không cần quá nhiều thời gian, chỉ cần dành khoảng một tiếng dạo quanh thôi cũng đủ để cảm nhận được một góc thiên nhiên rất đặc trưng của vùng núi này.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>6 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 366, 'photos': 2592}</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>Nơi rất đáng để tham quan, trãi nghiệm chút it về cầu kính và kết hợp đi ngắm thác nước.
 Có nhiều nơi lên hình đẹp, cảnh đẹp. Có bán đặc sản Mộc Châu rất đa dạng.
 😍😍👍</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Thời gian chỉnh sửa: 5 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>{'name': 'Vĩ Lê Bá', 'link': 'https://www.google.com/maps/contrib/115860838984920745696?hl=vi', 'contributor_id': '115860838984920745696', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7wdRrYJWeEmKs7YInZz_FDg-T90l2ImigSwJKL2hWmQu75bzm=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 59, 'photos': 93}</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>{'name': 'Vĩ Lê Bá', 'link': 'https://www.google.com/maps/contrib/115860838984920745696?hl=vi', 'contributor_id': '115860838984920745696', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7wdRrYJWeEmKs7YInZz_FDg-T90l2ImigSwJKL2hWmQu75bzm=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 59, 'photos': 94}</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>4</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Đẹp thì đẹp sơ sơ nhưng không gian vẫn khá là thoải mái
 Đi bộ oklea nhưng mà vẫn còn quá nhỏ, đi cỡ 30 phút là xong mất tiêu r
@@ -679,16 +659,36 @@
 Nói chung là vẫn okela</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>5 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>{'name': 'THANH NGUYEN', 'link': 'https://www.google.com/maps/contrib/110418688752170937071?hl=vi', 'contributor_id': '110418688752170937071', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIBtT-SxDlGGJM5jA47OmxpGvFdaG6EOeSswcBwx4VuXgnOdQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 70, 'photos': 207}</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>thác đẹp nhưng nên đi vào mùa nước sẽ thấy sự khác biệt hơn nhiều</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5 tháng trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>{'name': 'THANH NGUYEN', 'link': 'https://www.google.com/maps/contrib/110418688752170937071?hl=vi', 'contributor_id': '110418688752170937071', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIBtT-SxDlGGJM5jA47OmxpGvFdaG6EOeSswcBwx4VuXgnOdQ=s120-c-rp-mo-ba12-br100', 'reviews': 70, 'photos': 207}</t>
+          <t>{'name': 'Nguyễn Anh Quân', 'link': 'https://www.google.com/maps/contrib/111631093743063403454?hl=vi', 'contributor_id': '111631093743063403454', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIy-NjGEZ7ggp1yhLvVSe2iSDFAUAF4AILlK1IHBmSbkPzlKg=s120-c-rp-mo-ba12-br100', 'reviews': 9, 'photos': 24}</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -696,19 +696,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>thác đẹp nhưng nên đi vào mùa nước sẽ thấy sự khác biệt hơn nhiều</t>
+          <t>Cảnh đẹp, nhưng xu là đi ngay lúc mưa nên thác có nước như cf</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>một tháng trước</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Anh Quân', 'link': 'https://www.google.com/maps/contrib/111631093743063403454?hl=vi', 'contributor_id': '111631093743063403454', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIy-NjGEZ7ggp1yhLvVSe2iSDFAUAF4AILlK1IHBmSbkPzlKg=s120-c-rp-mo-ba12-br100', 'reviews': 9, 'photos': 24}</t>
+          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 300, 'photos': 3600}</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -716,19 +716,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cảnh đẹp, nhưng xu là đi ngay lúc mưa nên thác có nước như cf</t>
+          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>một tháng trước</t>
+          <t>4 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 300, 'photos': 3600}</t>
+          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 143, 'photos': 325}</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -736,19 +736,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
+          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4 tháng trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 143, 'photos': 325}</t>
+          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 24}</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -756,61 +756,61 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
+          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>5 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 24}</t>
+          <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'reviews': 16, 'photos': 114}</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>5</v>
       </c>
       <c r="C14" t="inlineStr">
-        <is>
-          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>5 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'reviews': 16, 'photos': 114}</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>5</v>
-      </c>
-      <c r="C15" t="inlineStr">
         <is>
           <t>Đi tầm trưa nắng đẹp
 Thác nhỏ, đi cũng không mất quá nhiều thời gian
 Có cầu kính</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>6 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>{'name': 'Nghĩa Nguyễn Trung', 'link': 'https://www.google.com/maps/contrib/107253778101970197900?hl=vi', 'contributor_id': '107253778101970197900', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUNLHg5XlpgtWVVTp_oJKOYAejqmQORtgQ_Oe2vusE5W_sQoZc5=s120-c-rp-mo-ba12-br100', 'reviews': 275, 'photos': 1279}</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Khu vực thác nước đẹp, nhiều cảnh quan, nhiều góc chụp đẹp.</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>{'name': 'Nghĩa Nguyễn Trung', 'link': 'https://www.google.com/maps/contrib/107253778101970197900?hl=vi', 'contributor_id': '107253778101970197900', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUNLHg5XlpgtWVVTp_oJKOYAejqmQORtgQ_Oe2vusE5W_sQoZc5=s120-c-rp-mo-ba12-br100', 'reviews': 275, 'photos': 1279}</t>
+          <t>{'name': 'Frugal Flow', 'link': 'https://www.google.com/maps/contrib/107453311426556875441?hl=vi', 'contributor_id': '107453311426556875441', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUspWRVGEEQ_LyS16qRB57xWZ-kgNRIjgdLPY8T7HzvNMFlILCV=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 85}</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -818,45 +818,25 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Khu vực thác nước đẹp, nhiều cảnh quan, nhiều góc chụp đẹp.</t>
+          <t>Đi vào một ngày nắng. Nắng hắt lên mặt nước long lanh nên xinh xắn hẳn:&gt; Chỉ là thác nay có vẻ hơi ít nc nên không như mình tưởng tượng.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2 tháng trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>{'name': 'Frugal Flow', 'link': 'https://www.google.com/maps/contrib/107453311426556875441?hl=vi', 'contributor_id': '107453311426556875441', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUspWRVGEEQ_LyS16qRB57xWZ-kgNRIjgdLPY8T7HzvNMFlILCV=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 85}</t>
+          <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'reviews': 219, 'photos': 308}</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C17" t="inlineStr">
-        <is>
-          <t>Đi vào một ngày nắng. Nắng hắt lên mặt nước long lanh nên xinh xắn hẳn:&gt; Chỉ là thác nay có vẻ hơi ít nc nên không như mình tưởng tượng.</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>6 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'reviews': 219, 'photos': 308}</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>3</v>
-      </c>
-      <c r="C18" t="inlineStr">
         <is>
           <t>Trải nghiệm vừa phải
 Giá vé theo trải nghiệm đi nhiều thác khác nhau của mình thì là khá cao so với các nơi khác, mình đi vào dịp tết nên thác ít nước.
@@ -864,78 +844,98 @@
 Cá nhân nếu quay lại Mộc Châu sẽ không đến thác này lần nào nữa</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>6 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>{'name': 'La Meu', 'link': 'https://www.google.com/maps/contrib/108858956358165703026?hl=vi', 'contributor_id': '108858956358165703026', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVKW-aZD0iBs1KBFQlmzfMiMTfjpd4PfUn4GO-K2tEt1PLpZ3YY=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 117}</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>5</v>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>Thác Dải Yếm là điểm du lịch rất đáng đi. Đường đi dễ, xe máy hay ô tô đều thuận tiện. Không gian mát mẻ, thiên nhiên đẹp và trong lành.
 Nước thác xanh biếc, chảy mạnh nhưng nhìn rất êm và thơ mộng, chụp hình lên đẹp lắm. Khu vực được làm lối đi khá an toàn, dễ tham quan.
 Nhân viên ở đây dễ thương, nhiệt tình, hướng dẫn khách rất chu đáo và thân thiện. Phù hợp đi chơi cùng gia đình hoặc bạn bè để thư giãn, nghỉ ngơi.</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>8 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'reviews': 24, 'photos': 255}</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'reviews': 24, 'photos': 255}</t>
+          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
+          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
+          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 1090}</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
+          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 1090}</t>
+          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -943,27 +943,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
+          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>11 tháng trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
+          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
+          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -975,67 +975,67 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
+          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 115, 'photos': 84}</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
+          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2 tháng trước</t>
+          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 115, 'photos': 84}</t>
+          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 3220}</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
+          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>7 tháng trước</t>
+          <t>9 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 3220}</t>
+          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 250, 'photos': 4822}</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
+          <t>Cảnh quan đẹp, ng dân thân thiện</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>5 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 250, 'photos': 4775}</t>
+          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1043,65 +1043,45 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cảnh quan đẹp, ng dân thân thiện</t>
+          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5 tháng trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
+          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 141, 'photos': 570}</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
+          <t>View đẹp, chỉ tiếc là ghé hồi tháng 5 lúc đang mùa mưa, nên không được đi trải nghiệm nhiều.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>10 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 141, 'photos': 571}</t>
+          <t>{'name': 'Linh Nguyễn', 'link': 'https://www.google.com/maps/contrib/109820275513447282944?hl=vi', 'contributor_id': '109820275513447282944', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVpZ-SNyOn6byhXW5cnkMUzIYl8pLeo3scME3-VG4n2ps2S2tYx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 992}</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C29" t="inlineStr">
-        <is>
-          <t>View đẹp, chỉ tiếc là ghé hồi tháng 5 lúc đang mùa mưa, nên không được đi trải nghiệm nhiều.</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>10 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>{'name': 'Linh Nguyễn', 'link': 'https://www.google.com/maps/contrib/109820275513447282944?hl=vi', 'contributor_id': '109820275513447282944', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVpZ-SNyOn6byhXW5cnkMUzIYl8pLeo3scME3-VG4n2ps2S2tYx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 992}</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>5</v>
-      </c>
-      <c r="C30" t="inlineStr">
         <is>
           <t>Thác đẹp, suối nước tự nhiên, đường đi dọc suối sạch sẽ
 Một số địa điểm du lịch ở Mộc Châu mọi người có thể tham khảo
@@ -1114,56 +1094,76 @@
 2. Cá Hồi Thanh Bảy</t>
         </is>
       </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 80, 'photos': 188}</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2 năm trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 80, 'photos': 185}</t>
+          <t>{'name': 'Anh Tuấn Trần', 'link': 'https://www.google.com/maps/contrib/106361750645670984745?hl=vi', 'contributor_id': '106361750645670984745', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXiNjEqD4gV0wYaTlBDaztRxN3Bz6wZiiUqJ5pnHqrMT1HyLF_rBg=s120-c-rp-mo-ba12-br100', 'reviews': 956, 'photos': 4080}</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
+          <t>Chẳng hiểu Mộc Châu làm du lịch kiểu gì mà chỗ nào cũng bắt mua vé và giá vé quá cao. Cứ một điểm tham quan là 100k/người mà chẳng có gì đặc sắc cả. Thác dải yếm có quá nhiều công trình nhân tạo. Kể cả 100k/người cho cả Thác Dải Yếm + Cầu Kính thì mình vẫn thấy đắt - không tương xứng. Đây còn vé riêng cho thác và riêng cho cầu kính mặc dù cả 2 này là cùng một điêm. Không muốn quay lại bao giờ nữa.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>2 năm trước</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>{'name': 'Anh Tuấn Trần', 'link': 'https://www.google.com/maps/contrib/106361750645670984745?hl=vi', 'contributor_id': '106361750645670984745', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXiNjEqD4gV0wYaTlBDaztRxN3Bz6wZiiUqJ5pnHqrMT1HyLF_rBg=s120-c-rp-mo-ba12-br100', 'reviews': 956, 'photos': 4071}</t>
+          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chẳng hiểu Mộc Châu làm du lịch kiểu gì mà chỗ nào cũng bắt mua vé và giá vé quá cao. Cứ một điểm tham quan là 100k/người mà chẳng có gì đặc sắc cả. Thác dải yếm có quá nhiều công trình nhân tạo. Kể cả 100k/người cho cả Thác Dải Yếm + Cầu Kính thì mình vẫn thấy đắt - không tương xứng. Đây còn vé riêng cho thác và riêng cho cầu kính mặc dù cả 2 này là cùng một điêm. Không muốn quay lại bao giờ nữa.</t>
+          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2 năm trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
+          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 71, 'photos': 496}</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1171,106 +1171,86 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
+          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>4 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 71, 'photos': 496}</t>
+          <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'reviews': 78, 'photos': 260}</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
+          <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
+Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>4 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'reviews': 78, 'photos': 260}</t>
+          <t>{'name': 'Mai Nguyễn', 'link': 'https://www.google.com/maps/contrib/101330344304584692421?hl=vi', 'contributor_id': '101330344304584692421', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocLN09xUhcK1CuSvLI4U-MC1m1LployphMNgUrT9xqkPlzqHlA=s120-c-rp-mo-br100', 'reviews': 5, 'photos': 7}</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
-Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
+          <t>Cảnh đẹp, có cả trải nghiệm cầu kính và zipline mà giá phải chăng hơn bên khu cầu kính bạch long</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>{'name': 'Mai Nguyễn', 'link': 'https://www.google.com/maps/contrib/101330344304584692421?hl=vi', 'contributor_id': '101330344304584692421', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocLN09xUhcK1CuSvLI4U-MC1m1LployphMNgUrT9xqkPlzqHlA=s120-c-rp-mo-br100', 'reviews': 5, 'photos': 7}</t>
+          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 533, 'photos': 4107}</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cảnh đẹp, có cả trải nghiệm cầu kính và zipline mà giá phải chăng hơn bên khu cầu kính bạch long</t>
+          <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 533, 'photos': 4107}</t>
+          <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 574}</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C37" t="inlineStr">
-        <is>
-          <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 574}</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>5</v>
-      </c>
-      <c r="C38" t="inlineStr">
         <is>
           <t>Đúng tên gọi của nó. Thác cũng rất đẹp. Nếu vào mùa nước chắc còn đẹp hơn.
 Cảnh quan cũng rất sạch đẹp.
@@ -1279,16 +1259,36 @@
 - vé vào cổng giá phù hợp</t>
         </is>
       </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4192}</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>5</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>Thời gian chỉnh sửa: 2 năm trước</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4192}</t>
+          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 518}</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1296,27 +1296,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
+          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Thời gian chỉnh sửa: 2 năm trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 518}</t>
+          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
+          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1328,15 +1328,15 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
+          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
+          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1348,7 +1348,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
+          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 1623}</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1356,80 +1356,80 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
+          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>9 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 1623}</t>
+          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 49, 'photos': 144}</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 49, 'photos': 144}</t>
+          <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWyzcZkQykW_QPymZ2fTMwerDVUm-XhQ6WZ0NqbjNzbEznIxcF7AQ=s120-c-rp-mo-ba12-br100', 'reviews': 149, 'photos': 3873}</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
+          <t>Thác Dải Yếm, còn được gọi là thác Nàng, thác Bản Vặt, là một thác nước hùng vĩ nằm ở xã Mường Sang, huyện Mộc Châu, tỉnh Sơn La. Thác có chiều cao khoảng 100m, chia thành hai dòng thác chính, trông giống như một dải yếm đào mềm mại uốn lượn quanh vách núi.
+Thác Dải Yếm là một địa điểm du lịch hấp dẫn, thu hút khách du lịch trong và ngoài nước. Đây là nơi du khách có thể chiêm ngưỡng vẻ đẹp hùng vĩ của thác nước và tìm hiểu về truyền thuyết về thác.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>2 năm trước</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWyzcZkQykW_QPymZ2fTMwerDVUm-XhQ6WZ0NqbjNzbEznIxcF7AQ=s120-c-rp-mo-ba12-br100', 'reviews': 149, 'photos': 3873}</t>
+          <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'reviews': 97, 'photos': 178}</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm, còn được gọi là thác Nàng, thác Bản Vặt, là một thác nước hùng vĩ nằm ở xã Mường Sang, huyện Mộc Châu, tỉnh Sơn La. Thác có chiều cao khoảng 100m, chia thành hai dòng thác chính, trông giống như một dải yếm đào mềm mại uốn lượn quanh vách núi.
-Thác Dải Yếm là một địa điểm du lịch hấp dẫn, thu hút khách du lịch trong và ngoài nước. Đây là nơi du khách có thể chiêm ngưỡng vẻ đẹp hùng vĩ của thác nước và tìm hiểu về truyền thuyết về thác.</t>
+          <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2 năm trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'reviews': 97, 'photos': 178}</t>
+          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'reviews': 27, 'photos': 260}</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
+          <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1449,7 +1449,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'reviews': 27, 'photos': 260}</t>
+          <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'reviews': 75, 'photos': 503}</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1457,7 +1457,8 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
+          <t>Thác Dải Yếm nằm trên dòng suối Vặt khởi nguồn từ hai khe nước Bó Co Lắm và Bo Tá Cháu ở đầu bản Vặt, một bản của người Thái có lịch sử lâu đời. Suối Vặt chảy được 5 km đổ vào suối Bó Sập, một dòng suối lớn bắt nguồn từ bản Bó Sập giáp biên giới Việt Lào rồi chảy về đất Yên Châu. Tại nơi hợp lưu của hai suối, dòng nước gặp một vùng đá vôi và đổ xuống phía dưới tạo thành thác Dải Yếm.[5]
+Thác Dải Yếm bao gồm hai phần, thác nước phía trên rộng 70 mét, thác nước phía dưới nằm cách đó 150-200 mét. Vào mùa khô, thác phía dưới chỉ có một dòng chảy từ độ cao 50 m xuống triền đá ở dưới. hai thác đổ xuống với tổng chiều cao 100m, một bên được chia làm 9 tầng, bên còn lại 5 tầng. Cách giữa hai phần thác là một bãi đất phẳng thuận tiện cho việc tham quan của du khách. Thảm thực vật trên đỉnh thác cũng khá phong phú.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1469,7 +1470,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'reviews': 75, 'photos': 503}</t>
+          <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'reviews': 8, 'photos': 90}</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1477,20 +1478,19 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm nằm trên dòng suối Vặt khởi nguồn từ hai khe nước Bó Co Lắm và Bo Tá Cháu ở đầu bản Vặt, một bản của người Thái có lịch sử lâu đời. Suối Vặt chảy được 5 km đổ vào suối Bó Sập, một dòng suối lớn bắt nguồn từ bản Bó Sập giáp biên giới Việt Lào rồi chảy về đất Yên Châu. Tại nơi hợp lưu của hai suối, dòng nước gặp một vùng đá vôi và đổ xuống phía dưới tạo thành thác Dải Yếm.[5]
-Thác Dải Yếm bao gồm hai phần, thác nước phía trên rộng 70 mét, thác nước phía dưới nằm cách đó 150-200 mét. Vào mùa khô, thác phía dưới chỉ có một dòng chảy từ độ cao 50 m xuống triền đá ở dưới. hai thác đổ xuống với tổng chiều cao 100m, một bên được chia làm 9 tầng, bên còn lại 5 tầng. Cách giữa hai phần thác là một bãi đất phẳng thuận tiện cho việc tham quan của du khách. Thảm thực vật trên đỉnh thác cũng khá phong phú.</t>
+          <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>11 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'reviews': 8, 'photos': 90}</t>
+          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 152, 'photos': 1287}</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1498,12 +1498,15 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
+          <t>Thác nhỏ cũng đẹp nhưng được trang trí dành cho du lịch rồi về độ rộng nhiều tầng và thiên nhiên thì không bằng thác Nàng Tiên hoặc thác Chiềng Khoa.
+Thác Dải Yếm được đầu tư khang trang nhưng đi bộ từ bãi gửi xe vào thác hơi bị xa (vé gửi xe 30k), đường đi vào và khu thác bên trong nhiều khu chụp ảnh checkin được trang trí chụp ảnh đẹp mắt. Giá vé tháng 1/2024 là 80k/ người vào cổng nhưng đến 30/4/2024 tăng lên 100k/ng giá vé hơi cao với việc vào ngắm thác.
+Muốn lên cầu kính giá vé riêng 100k/người. Lên cầu kính chơi ngắm cảnh cũng ok. Từ cầu kính nhìn đi mấy quả đồi phía dưới bị đào bới làm đường nhìn không được thiên nhiên cho lắm.
+- Bản thân mình cảm nhận thì cũng bình thường thác không cao không rộng dài đẹp nhiều tầng bằng thác Nàng Tiên hoặc Chiềng Khoa. Nói chung đi du lịch Mộc Châu ghé qua cho biết thôi. Chứ để quay lại thì ít khả năng.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>11 tháng trước</t>
+          <t>2 năm trước</t>
         </is>
       </c>
     </row>

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>một tuần trước</t>
+          <t>2 tuần trước</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>{'name': 'Vĩ Lê Bá', 'link': 'https://www.google.com/maps/contrib/115860838984920745696?hl=vi', 'contributor_id': '115860838984920745696', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7wdRrYJWeEmKs7YInZz_FDg-T90l2ImigSwJKL2hWmQu75bzm=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 59, 'photos': 94}</t>
+          <t>{'name': 'Vĩ Lê Bá', 'link': 'https://www.google.com/maps/contrib/115860838984920745696?hl=vi', 'contributor_id': '115860838984920745696', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7wdRrYJWeEmKs7YInZz_FDg-T90l2ImigSwJKL2hWmQu75bzm=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 60, 'photos': 94}</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -708,7 +708,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 300, 'photos': 3600}</t>
+          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 301, 'photos': 3605}</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1015,7 +1015,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 250, 'photos': 4822}</t>
+          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 251, 'photos': 4822}</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1103,7 +1103,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 80, 'photos': 188}</t>
+          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 81, 'photos': 188}</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1123,27 +1123,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>{'name': 'Anh Tuấn Trần', 'link': 'https://www.google.com/maps/contrib/106361750645670984745?hl=vi', 'contributor_id': '106361750645670984745', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXiNjEqD4gV0wYaTlBDaztRxN3Bz6wZiiUqJ5pnHqrMT1HyLF_rBg=s120-c-rp-mo-ba12-br100', 'reviews': 956, 'photos': 4080}</t>
+          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chẳng hiểu Mộc Châu làm du lịch kiểu gì mà chỗ nào cũng bắt mua vé và giá vé quá cao. Cứ một điểm tham quan là 100k/người mà chẳng có gì đặc sắc cả. Thác dải yếm có quá nhiều công trình nhân tạo. Kể cả 100k/người cho cả Thác Dải Yếm + Cầu Kính thì mình vẫn thấy đắt - không tương xứng. Đây còn vé riêng cho thác và riêng cho cầu kính mặc dù cả 2 này là cùng một điêm. Không muốn quay lại bao giờ nữa.</t>
+          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2 năm trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
+          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 71, 'photos': 496}</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1151,106 +1151,86 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
+          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>4 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 71, 'photos': 496}</t>
+          <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'reviews': 78, 'photos': 260}</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
+          <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
+Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'reviews': 78, 'photos': 260}</t>
+          <t>{'name': 'Mai Nguyễn', 'link': 'https://www.google.com/maps/contrib/101330344304584692421?hl=vi', 'contributor_id': '101330344304584692421', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocLN09xUhcK1CuSvLI4U-MC1m1LployphMNgUrT9xqkPlzqHlA=s120-c-rp-mo-br100', 'reviews': 5, 'photos': 7}</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
-Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
+          <t>Cảnh đẹp, có cả trải nghiệm cầu kính và zipline mà giá phải chăng hơn bên khu cầu kính bạch long</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>{'name': 'Mai Nguyễn', 'link': 'https://www.google.com/maps/contrib/101330344304584692421?hl=vi', 'contributor_id': '101330344304584692421', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocLN09xUhcK1CuSvLI4U-MC1m1LployphMNgUrT9xqkPlzqHlA=s120-c-rp-mo-br100', 'reviews': 5, 'photos': 7}</t>
+          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 533, 'photos': 4107}</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cảnh đẹp, có cả trải nghiệm cầu kính và zipline mà giá phải chăng hơn bên khu cầu kính bạch long</t>
+          <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 533, 'photos': 4107}</t>
+          <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 574}</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C36" t="inlineStr">
-        <is>
-          <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 574}</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>5</v>
-      </c>
-      <c r="C37" t="inlineStr">
         <is>
           <t>Đúng tên gọi của nó. Thác cũng rất đẹp. Nếu vào mùa nước chắc còn đẹp hơn.
 Cảnh quan cũng rất sạch đẹp.
@@ -1259,16 +1239,36 @@
 - vé vào cổng giá phù hợp</t>
         </is>
       </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4192}</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>5</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>Thời gian chỉnh sửa: 2 năm trước</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4192}</t>
+          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 518}</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1276,27 +1276,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
+          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Thời gian chỉnh sửa: 2 năm trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 518}</t>
+          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
+          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1308,15 +1308,15 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
+          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
+          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1328,7 +1328,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
+          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 1623}</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1336,32 +1336,33 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
+          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>9 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 1623}</t>
+          <t>{'name': 'ninh Men', 'link': 'https://www.google.com/maps/contrib/103025469094717120638?hl=vi', 'contributor_id': '103025469094717120638', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJr8a3WVJHmayMF2FvRRdJjmyVlo0gmvjXedEtF6z5_xuOtxg=s120-c-rp-mo-ba12-br100', 'reviews': 22, 'photos': 139}</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+          <t>Đi Thác Dải Yếm đúng hôm… uống trà sữa trân châu. 😭
+Vé 150k/người nhưng cá nhân mình thấy hơi hụt hẫng. Thác không quá đặc biệt, đi một vòng là hết, chủ yếu là chụp ảnh. Nếu không thích check-in thì chắc sẽ thấy hơi “không có gì” so với giá vé.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>một tháng trước</t>
         </is>
       </c>
     </row>
@@ -1470,27 +1471,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'reviews': 8, 'photos': 90}</t>
+          <t>{'name': 'Chi Ho', 'link': 'https://www.google.com/maps/contrib/102731288821463748765?hl=vi', 'contributor_id': '102731288821463748765', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWV3y9KiqGo7jILq-ZzBkSw28LDZHnwKXBhstpTEeRvr9jffKE=s120-c-rp-mo-ba12-br100', 'reviews': 85, 'photos': 1528}</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
+          <t>Thác Dải Yếm đẹp và hùng vĩ, xứng đáng cho chuyến picnic cuối tuần. Đường đi hơi gập ghềnh nhưng đến nơi thì quên hết mệt mỏi. Nước mát rượi, âm thanh róc rách rất thư giãn. Tiếc là hơi đông vào cuối tuần, nhưng cảnh đẹp bù đắp tất cả! Nên đi vào ngày thường nếu muốn yên tĩnh hơn.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>11 tháng trước</t>
+          <t>một tháng trước</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 152, 'photos': 1287}</t>
+          <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'reviews': 8, 'photos': 90}</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1498,15 +1499,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Thác nhỏ cũng đẹp nhưng được trang trí dành cho du lịch rồi về độ rộng nhiều tầng và thiên nhiên thì không bằng thác Nàng Tiên hoặc thác Chiềng Khoa.
-Thác Dải Yếm được đầu tư khang trang nhưng đi bộ từ bãi gửi xe vào thác hơi bị xa (vé gửi xe 30k), đường đi vào và khu thác bên trong nhiều khu chụp ảnh checkin được trang trí chụp ảnh đẹp mắt. Giá vé tháng 1/2024 là 80k/ người vào cổng nhưng đến 30/4/2024 tăng lên 100k/ng giá vé hơi cao với việc vào ngắm thác.
-Muốn lên cầu kính giá vé riêng 100k/người. Lên cầu kính chơi ngắm cảnh cũng ok. Từ cầu kính nhìn đi mấy quả đồi phía dưới bị đào bới làm đường nhìn không được thiên nhiên cho lắm.
-- Bản thân mình cảm nhận thì cũng bình thường thác không cao không rộng dài đẹp nhiều tầng bằng thác Nàng Tiên hoặc Chiềng Khoa. Nói chung đi du lịch Mộc Châu ghé qua cho biết thôi. Chứ để quay lại thì ít khả năng.</t>
+          <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2 năm trước</t>
+          <t>11 tháng trước</t>
         </is>
       </c>
     </row>

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -623,7 +623,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 366, 'photos': 2592}</t>
+          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 366, 'photos': 2604}</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1015,7 +1015,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 251, 'photos': 4822}</t>
+          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 251, 'photos': 4810}</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1055,7 +1055,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 141, 'photos': 570}</t>
+          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 140, 'photos': 570}</t>
         </is>
       </c>
       <c r="B28" t="n">

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,33 +497,13 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>{'name': 'Cửu Quang Nguyễn', 'link': 'https://www.google.com/maps/contrib/107704339232071144994?hl=vi', 'contributor_id': '107704339232071144994', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV2_oJLqzlVCtXNV77ConxSPDhhMhFP-czjeCf6uCm7cabO88k=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 78, 'photos': 356}</t>
+          <t>{'name': 'Thái Nguyễn', 'link': 'https://www.google.com/maps/contrib/105517365260915933657?hl=vi', 'contributor_id': '105517365260915933657', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXLOkY3FUSH3Mz-aapJXPQUgoCFlQP20PICWZGzVI3cPkRkBIt_ew=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 65, 'photos': 175}</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>5</v>
       </c>
       <c r="C4" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm nằm trong khu du lịch sinh thái thác Dải Yếm, đường đi khá tiện lợi để ghé vào, tuy nhiên cần chú ý lối vào có khúc cua dốc khá ngoặt. Vé vào là 150k/người, bên trong có khá nhiều vị trí để du ngoạn và ngắm cảnh, đặc biệt là khu vực thác nước rất hùng vĩ và mát mẻ, có cầu dẫn vào nhìn rất thơ mộng và tuyệt vời. Nếu có dịp ghé lên Mộc Châu thì nên ghé vào đây chơi 1 lần để du ngoạn thắng cảnh thiên nhiên tại nơi đây.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>5 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>{'name': 'Thái Nguyễn', 'link': 'https://www.google.com/maps/contrib/105517365260915933657?hl=vi', 'contributor_id': '105517365260915933657', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXLOkY3FUSH3Mz-aapJXPQUgoCFlQP20PICWZGzVI3cPkRkBIt_ew=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 65, 'photos': 175}</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C5" t="inlineStr">
         <is>
           <t>Nếu đi cùng Lover sẽ đẹp hơn.
 Nếu tự nhìn lại
@@ -591,22 +571,22 @@
 Hơn cả tới thiên đường</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>{'name': 'ZjmLee YTBer', 'link': 'https://www.google.com/maps/contrib/100979561872983589256?hl=vi', 'contributor_id': '100979561872983589256', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU6i9poRXPBKYv-WgZHmB9chW6jRPCOh3klZ1Z7Yv_DOaukn4g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 79, 'photos': 1243}</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="B5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>Nghe người địa phương kể lại thì cái tên “Dải Yếm” xuất phát từ truyền thuyết của người Thái. Họ nói rằng dòng thác trắng xóa từ trên cao đổ xuống giống như dải yếm của người con gái, nên từ đó cái tên này được gọi luôn cho tới bây giờ. Nghe vậy nên đứng nhìn dòng thác cũng thấy có chút gì đó rất nên thơ.
 Đi bộ quanh khu thác khá dễ, có lối đi và bậc đá để xuống gần chân thác. Nếu đi vào mùa nước nhiều thì thác nhìn đẹp hơn, nước trắng xóa và tiếng thác nghe rất đã tai. Còn những ngày nắng nhẹ thì không khí ở đây khá chill, kiểu ngồi nghỉ một chút, nghe tiếng nước và nhìn rừng cây xung quanh cũng thấy thư giãn.
@@ -614,61 +594,78 @@
 Nếu đang đi du lịch tự túc ở Mộc Châu, thì Thác Dải Yếm là một nơi khá đáng ghé qua. Không cần quá nhiều thời gian, chỉ cần dành khoảng một tiếng dạo quanh thôi cũng đủ để cảm nhận được một góc thiên nhiên rất đặc trưng của vùng núi này.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>6 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 366, 'photos': 2604}</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 367, 'photos': 2607}</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>Nơi rất đáng để tham quan, trãi nghiệm chút it về cầu kính và kết hợp đi ngắm thác nước.
 Có nhiều nơi lên hình đẹp, cảnh đẹp. Có bán đặc sản Mộc Châu rất đa dạng.
 😍😍👍</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Thời gian chỉnh sửa: 5 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>{'name': 'Nguyễn Anh Quân', 'link': 'https://www.google.com/maps/contrib/111631093743063403454?hl=vi', 'contributor_id': '111631093743063403454', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIy-NjGEZ7ggp1yhLvVSe2iSDFAUAF4AILlK1IHBmSbkPzlKg=s120-c-rp-mo-ba12-br100', 'reviews': 9, 'photos': 24}</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Cảnh đẹp, nhưng xu là đi ngay lúc mưa nên thác có nước như cf</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Thời gian chỉnh sửa: 5 tháng trước</t>
+          <t>một tháng trước</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>{'name': 'Vĩ Lê Bá', 'link': 'https://www.google.com/maps/contrib/115860838984920745696?hl=vi', 'contributor_id': '115860838984920745696', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7wdRrYJWeEmKs7YInZz_FDg-T90l2ImigSwJKL2hWmQu75bzm=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 60, 'photos': 94}</t>
+          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 301, 'photos': 3605}</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Đẹp thì đẹp sơ sơ nhưng không gian vẫn khá là thoải mái
-Đi bộ oklea nhưng mà vẫn còn quá nhỏ, đi cỡ 30 phút là xong mất tiêu r
-Tuỳ ngà lượng khách sẽ khác nhau và ảnh hưởng lớn tớ trải nghiệm
-Nói chung là vẫn okela</t>
+          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5 tháng trước</t>
+          <t>4 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>{'name': 'THANH NGUYEN', 'link': 'https://www.google.com/maps/contrib/110418688752170937071?hl=vi', 'contributor_id': '110418688752170937071', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIBtT-SxDlGGJM5jA47OmxpGvFdaG6EOeSswcBwx4VuXgnOdQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 70, 'photos': 207}</t>
+          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 24}</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -676,167 +673,87 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>thác đẹp nhưng nên đi vào mùa nước sẽ thấy sự khác biệt hơn nhiều</t>
+          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>5 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Anh Quân', 'link': 'https://www.google.com/maps/contrib/111631093743063403454?hl=vi', 'contributor_id': '111631093743063403454', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIy-NjGEZ7ggp1yhLvVSe2iSDFAUAF4AILlK1IHBmSbkPzlKg=s120-c-rp-mo-ba12-br100', 'reviews': 9, 'photos': 24}</t>
+          <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'reviews': 16, 'photos': 114}</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>5</v>
       </c>
       <c r="C10" t="inlineStr">
-        <is>
-          <t>Cảnh đẹp, nhưng xu là đi ngay lúc mưa nên thác có nước như cf</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>một tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 301, 'photos': 3605}</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>4 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 143, 'photos': 325}</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>6 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 24}</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>5 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'reviews': 16, 'photos': 114}</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" t="inlineStr">
         <is>
           <t>Đi tầm trưa nắng đẹp
 Thác nhỏ, đi cũng không mất quá nhiều thời gian
 Có cầu kính</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>6 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>{'name': 'Nghĩa Nguyễn Trung', 'link': 'https://www.google.com/maps/contrib/107253778101970197900?hl=vi', 'contributor_id': '107253778101970197900', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUNLHg5XlpgtWVVTp_oJKOYAejqmQORtgQ_Oe2vusE5W_sQoZc5=s120-c-rp-mo-ba12-br100', 'reviews': 275, 'photos': 1279}</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>5</v>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>Khu vực thác nước đẹp, nhiều cảnh quan, nhiều góc chụp đẹp.</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>2 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>{'name': 'Frugal Flow', 'link': 'https://www.google.com/maps/contrib/107453311426556875441?hl=vi', 'contributor_id': '107453311426556875441', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUspWRVGEEQ_LyS16qRB57xWZ-kgNRIjgdLPY8T7HzvNMFlILCV=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 85}</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>5</v>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Đi vào một ngày nắng. Nắng hắt lên mặt nước long lanh nên xinh xắn hẳn:&gt; Chỉ là thác nay có vẻ hơi ít nc nên không như mình tưởng tượng.</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>6 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'reviews': 219, 'photos': 308}</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B13" t="n">
         <v>3</v>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Trải nghiệm vừa phải
 Giá vé theo trải nghiệm đi nhiều thác khác nhau của mình thì là khá cao so với các nơi khác, mình đi vào dịp tết nên thác ít nước.
@@ -844,98 +761,178 @@
 Cá nhân nếu quay lại Mộc Châu sẽ không đến thác này lần nào nữa</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>6 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>{'name': 'La Meu', 'link': 'https://www.google.com/maps/contrib/108858956358165703026?hl=vi', 'contributor_id': '108858956358165703026', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVKW-aZD0iBs1KBFQlmzfMiMTfjpd4PfUn4GO-K2tEt1PLpZ3YY=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 117}</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>5</v>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Thác Dải Yếm là điểm du lịch rất đáng đi. Đường đi dễ, xe máy hay ô tô đều thuận tiện. Không gian mát mẻ, thiên nhiên đẹp và trong lành.
 Nước thác xanh biếc, chảy mạnh nhưng nhìn rất êm và thơ mộng, chụp hình lên đẹp lắm. Khu vực được làm lối đi khá an toàn, dễ tham quan.
 Nhân viên ở đây dễ thương, nhiệt tình, hướng dẫn khách rất chu đáo và thân thiện. Phù hợp đi chơi cùng gia đình hoặc bạn bè để thư giãn, nghỉ ngơi.</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'reviews': 24, 'photos': 255}</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>6 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 1090}</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'reviews': 24, 'photos': 255}</t>
+          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
+          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
+          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 115, 'photos': 84}</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
+          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 1090}</t>
+          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 3220}</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
+          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>9 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
+          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 251, 'photos': 4810}</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -943,145 +940,45 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
+          <t>Cảnh quan đẹp, ng dân thân thiện</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2 tháng trước</t>
+          <t>5 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
+          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
+          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2 tháng trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 115, 'photos': 84}</t>
+          <t>{'name': 'Linh Nguyễn', 'link': 'https://www.google.com/maps/contrib/109820275513447282944?hl=vi', 'contributor_id': '109820275513447282944', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVpZ-SNyOn6byhXW5cnkMUzIYl8pLeo3scME3-VG4n2ps2S2tYx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 992}</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>5</v>
       </c>
       <c r="C24" t="inlineStr">
-        <is>
-          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>7 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 3220}</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>4</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>9 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 251, 'photos': 4810}</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>5</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Cảnh quan đẹp, ng dân thân thiện</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>5 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>5</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>8 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 140, 'photos': 570}</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>4</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>View đẹp, chỉ tiếc là ghé hồi tháng 5 lúc đang mùa mưa, nên không được đi trải nghiệm nhiều.</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>10 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>{'name': 'Linh Nguyễn', 'link': 'https://www.google.com/maps/contrib/109820275513447282944?hl=vi', 'contributor_id': '109820275513447282944', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVpZ-SNyOn6byhXW5cnkMUzIYl8pLeo3scME3-VG4n2ps2S2tYx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 992}</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>5</v>
-      </c>
-      <c r="C29" t="inlineStr">
         <is>
           <t>Thác đẹp, suối nước tự nhiên, đường đi dọc suối sạch sẽ
 Một số địa điểm du lịch ở Mộc Châu mọi người có thể tham khảo
@@ -1094,16 +991,117 @@
 2. Cá Hồi Thanh Bảy</t>
         </is>
       </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 81, 'photos': 188}</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>6 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 71, 'photos': 496}</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>4 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'reviews': 78, 'photos': 260}</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
+Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>{'name': 'Mai Nguyễn', 'link': 'https://www.google.com/maps/contrib/101330344304584692421?hl=vi', 'contributor_id': '101330344304584692421', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocLN09xUhcK1CuSvLI4U-MC1m1LployphMNgUrT9xqkPlzqHlA=s120-c-rp-mo-br100', 'reviews': 5, 'photos': 7}</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>5</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Cảnh đẹp, có cả trải nghiệm cầu kính và zipline mà giá phải chăng hơn bên khu cầu kính bạch long</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2 năm trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 81, 'photos': 188}</t>
+          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 533, 'photos': 4107}</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1111,126 +1109,25 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
+          <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
+          <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 574}</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>5</v>
       </c>
       <c r="C31" t="inlineStr">
-        <is>
-          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 71, 'photos': 496}</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>5</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>4 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'reviews': 78, 'photos': 260}</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>4</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
-Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>{'name': 'Mai Nguyễn', 'link': 'https://www.google.com/maps/contrib/101330344304584692421?hl=vi', 'contributor_id': '101330344304584692421', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocLN09xUhcK1CuSvLI4U-MC1m1LployphMNgUrT9xqkPlzqHlA=s120-c-rp-mo-br100', 'reviews': 5, 'photos': 7}</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>5</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Cảnh đẹp, có cả trải nghiệm cầu kính và zipline mà giá phải chăng hơn bên khu cầu kính bạch long</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>6 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 533, 'photos': 4107}</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>4</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 574}</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>5</v>
-      </c>
-      <c r="C36" t="inlineStr">
         <is>
           <t>Đúng tên gọi của nó. Thác cũng rất đẹp. Nếu vào mùa nước chắc còn đẹp hơn.
 Cảnh quan cũng rất sạch đẹp.
@@ -1239,36 +1136,136 @@
 - vé vào cổng giá phù hợp</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4192}</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Thời gian chỉnh sửa: 2 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 518}</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>5</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 1623}</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>5</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>9 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4192}</t>
+          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 49, 'photos': 144}</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
+          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Thời gian chỉnh sửa: 2 năm trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 518}</t>
+          <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWyzcZkQykW_QPymZ2fTMwerDVUm-XhQ6WZ0NqbjNzbEznIxcF7AQ=s120-c-rp-mo-ba12-br100', 'reviews': 149, 'photos': 3873}</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1276,19 +1273,20 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
+          <t>Thác Dải Yếm, còn được gọi là thác Nàng, thác Bản Vặt, là một thác nước hùng vĩ nằm ở xã Mường Sang, huyện Mộc Châu, tỉnh Sơn La. Thác có chiều cao khoảng 100m, chia thành hai dòng thác chính, trông giống như một dải yếm đào mềm mại uốn lượn quanh vách núi.
+Thác Dải Yếm là một địa điểm du lịch hấp dẫn, thu hút khách du lịch trong và ngoài nước. Đây là nơi du khách có thể chiêm ngưỡng vẻ đẹp hùng vĩ của thác nước và tìm hiểu về truyền thuyết về thác.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>2 năm trước</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
+          <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'reviews': 97, 'photos': 178}</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1296,7 +1294,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
+          <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1308,15 +1306,15 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
+          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'reviews': 27, 'photos': 260}</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
+          <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1328,27 +1326,28 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 1623}</t>
+          <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'reviews': 75, 'photos': 503}</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+          <t>Thác Dải Yếm nằm trên dòng suối Vặt khởi nguồn từ hai khe nước Bó Co Lắm và Bo Tá Cháu ở đầu bản Vặt, một bản của người Thái có lịch sử lâu đời. Suối Vặt chảy được 5 km đổ vào suối Bó Sập, một dòng suối lớn bắt nguồn từ bản Bó Sập giáp biên giới Việt Lào rồi chảy về đất Yên Châu. Tại nơi hợp lưu của hai suối, dòng nước gặp một vùng đá vôi và đổ xuống phía dưới tạo thành thác Dải Yếm.[5]
+Thác Dải Yếm bao gồm hai phần, thác nước phía trên rộng 70 mét, thác nước phía dưới nằm cách đó 150-200 mét. Vào mùa khô, thác phía dưới chỉ có một dòng chảy từ độ cao 50 m xuống triền đá ở dưới. hai thác đổ xuống với tổng chiều cao 100m, một bên được chia làm 9 tầng, bên còn lại 5 tầng. Cách giữa hai phần thác là một bãi đất phẳng thuận tiện cho việc tham quan của du khách. Thảm thực vật trên đỉnh thác cũng khá phong phú.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>{'name': 'ninh Men', 'link': 'https://www.google.com/maps/contrib/103025469094717120638?hl=vi', 'contributor_id': '103025469094717120638', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJr8a3WVJHmayMF2FvRRdJjmyVlo0gmvjXedEtF6z5_xuOtxg=s120-c-rp-mo-ba12-br100', 'reviews': 22, 'photos': 139}</t>
+          <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'reviews': 8, 'photos': 90}</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1356,20 +1355,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Đi Thác Dải Yếm đúng hôm… uống trà sữa trân châu. 😭
-Vé 150k/người nhưng cá nhân mình thấy hơi hụt hẫng. Thác không quá đặc biệt, đi một vòng là hết, chủ yếu là chụp ảnh. Nếu không thích check-in thì chắc sẽ thấy hơi “không có gì” so với giá vé.</t>
+          <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>một tháng trước</t>
+          <t>11 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 49, 'photos': 144}</t>
+          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 152, 'photos': 1281}</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1377,60 +1375,62 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
+          <t>Thác nhỏ cũng đẹp nhưng được trang trí dành cho du lịch rồi về độ rộng nhiều tầng và thiên nhiên thì không bằng thác Nàng Tiên hoặc thác Chiềng Khoa.
+Thác Dải Yếm được đầu tư khang trang nhưng đi bộ từ bãi gửi xe vào thác hơi bị xa (vé gửi xe 30k), đường đi vào và khu thác bên trong nhiều khu chụp ảnh checkin được trang trí chụp ảnh đẹp mắt. Giá vé tháng 1/2024 là 80k/ người vào cổng nhưng đến 30/4/2024 tăng lên 100k/ng giá vé hơi cao với việc vào ngắm thác.
+Muốn lên cầu kính giá vé riêng 100k/người. Lên cầu kính chơi ngắm cảnh cũng ok. Từ cầu kính nhìn đi mấy quả đồi phía dưới bị đào bới làm đường nhìn không được thiên nhiên cho lắm.
+- Bản thân mình cảm nhận thì cũng bình thường thác không cao không rộng dài đẹp nhiều tầng bằng thác Nàng Tiên hoặc Chiềng Khoa. Nói chung đi du lịch Mộc Châu ghé qua cho biết thôi. Chứ để quay lại thì ít khả năng.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>2 năm trước</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWyzcZkQykW_QPymZ2fTMwerDVUm-XhQ6WZ0NqbjNzbEznIxcF7AQ=s120-c-rp-mo-ba12-br100', 'reviews': 149, 'photos': 3873}</t>
+          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 140, 'photos': 570}</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm, còn được gọi là thác Nàng, thác Bản Vặt, là một thác nước hùng vĩ nằm ở xã Mường Sang, huyện Mộc Châu, tỉnh Sơn La. Thác có chiều cao khoảng 100m, chia thành hai dòng thác chính, trông giống như một dải yếm đào mềm mại uốn lượn quanh vách núi.
-Thác Dải Yếm là một địa điểm du lịch hấp dẫn, thu hút khách du lịch trong và ngoài nước. Đây là nơi du khách có thể chiêm ngưỡng vẻ đẹp hùng vĩ của thác nước và tìm hiểu về truyền thuyết về thác.</t>
+          <t>View đẹp, chỉ tiếc là ghé hồi tháng 5 lúc đang mùa mưa, nên không được đi trải nghiệm nhiều.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2 năm trước</t>
+          <t>10 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'reviews': 97, 'photos': 178}</t>
+          <t>{'name': 'Hung Tran', 'link': 'https://www.google.com/maps/contrib/111025160790635631721?hl=vi', 'contributor_id': '111025160790635631721', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXJvHNQsMohKHo9fo2c_guCokbfqlcHTDulcTBswdAfP6GIiZRa=s120-c-rp-mo-ba12-br100', 'reviews': 120, 'photos': 1783}</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
+          <t>Mới đi Thác Dải Yếm mà thấy cảnh ở đây quá ấn tượng. Nước từ thác chảy xuống nhìn thôi đã mát cả mắt, mát hơn một phần do cái thời tiết mát mẻ nơi miền núi này. Đường đến thác hơi gồ ghề tí nên đi lại cẩn thận xíu nhưng được cái khung cảnh thiên nhiên trời ban, thấy cũng quá ổn. Có mấy gian hàng bán đặc sản địa phương, cứ thấy ghé thử, giá nơi này cũng dễ chịu. Mọi thứ rất thư thái, không đông đúc, thích hợp để đi vào ngày nghỉ. Thêm vài chỗ ngồi nghỉ ngơi thì tuyệt!</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'reviews': 27, 'photos': 260}</t>
+          <t>{'name': 'Nguyen Hung Son', 'link': 'https://www.google.com/maps/contrib/103602300698496865451?hl=vi', 'contributor_id': '103602300698496865451', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUZaCtGsEksmQHBlNq8Xrol7h098HYLQGNUZgSqhr55eCVudl46og=s120-c-rp-mo-ba12-br100', 'reviews': 74, 'photos': 2146}</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1438,73 +1438,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
+          <t>Thác Dải Yếm dường như trở thành một công viên. Lối vào thác khi đi qua cổng và đến Suối Hẹn Hò, khách thăm quan có thể đi theo đường bê tông hoặc đi xuống suối hẹn hò men theo đường lát đá ven suối và núi. Đa phần cá cảnh quan ở đây đã được cải tạo. Các trò chơi như Cầu Kính, Zipline và có lẽ đặc biệt nhất vẫn là check-in tại Thác Dải Yếm khi đầy nước. Vé vào cửa 100k/người lớn, trẻ em 50k (&lt;1,2m). Vé cầu kính 100k, Zipline 50k.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'reviews': 75, 'photos': 503}</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>4</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm nằm trên dòng suối Vặt khởi nguồn từ hai khe nước Bó Co Lắm và Bo Tá Cháu ở đầu bản Vặt, một bản của người Thái có lịch sử lâu đời. Suối Vặt chảy được 5 km đổ vào suối Bó Sập, một dòng suối lớn bắt nguồn từ bản Bó Sập giáp biên giới Việt Lào rồi chảy về đất Yên Châu. Tại nơi hợp lưu của hai suối, dòng nước gặp một vùng đá vôi và đổ xuống phía dưới tạo thành thác Dải Yếm.[5]
-Thác Dải Yếm bao gồm hai phần, thác nước phía trên rộng 70 mét, thác nước phía dưới nằm cách đó 150-200 mét. Vào mùa khô, thác phía dưới chỉ có một dòng chảy từ độ cao 50 m xuống triền đá ở dưới. hai thác đổ xuống với tổng chiều cao 100m, một bên được chia làm 9 tầng, bên còn lại 5 tầng. Cách giữa hai phần thác là một bãi đất phẳng thuận tiện cho việc tham quan của du khách. Thảm thực vật trên đỉnh thác cũng khá phong phú.</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>{'name': 'Chi Ho', 'link': 'https://www.google.com/maps/contrib/102731288821463748765?hl=vi', 'contributor_id': '102731288821463748765', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWV3y9KiqGo7jILq-ZzBkSw28LDZHnwKXBhstpTEeRvr9jffKE=s120-c-rp-mo-ba12-br100', 'reviews': 85, 'photos': 1528}</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>5</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm đẹp và hùng vĩ, xứng đáng cho chuyến picnic cuối tuần. Đường đi hơi gập ghềnh nhưng đến nơi thì quên hết mệt mỏi. Nước mát rượi, âm thanh róc rách rất thư giãn. Tiếc là hơi đông vào cuối tuần, nhưng cảnh đẹp bù đắp tất cả! Nên đi vào ngày thường nếu muốn yên tĩnh hơn.</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>một tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'reviews': 8, 'photos': 90}</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>4</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>11 tháng trước</t>
+          <t>2 năm trước</t>
         </is>
       </c>
     </row>

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7 tháng trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 367, 'photos': 2607}</t>
+          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 369, 'photos': 2607}</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -665,7 +665,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 24}</t>
+          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 143, 'photos': 325}</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -673,61 +673,61 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
+          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5 tháng trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 24}</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>5 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'reviews': 16, 'photos': 114}</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>Đi tầm trưa nắng đẹp
 Thác nhỏ, đi cũng không mất quá nhiều thời gian
 Có cầu kính</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>6 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>{'name': 'Nghĩa Nguyễn Trung', 'link': 'https://www.google.com/maps/contrib/107253778101970197900?hl=vi', 'contributor_id': '107253778101970197900', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUNLHg5XlpgtWVVTp_oJKOYAejqmQORtgQ_Oe2vusE5W_sQoZc5=s120-c-rp-mo-ba12-br100', 'reviews': 275, 'photos': 1279}</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Khu vực thác nước đẹp, nhiều cảnh quan, nhiều góc chụp đẹp.</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>{'name': 'Frugal Flow', 'link': 'https://www.google.com/maps/contrib/107453311426556875441?hl=vi', 'contributor_id': '107453311426556875441', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUspWRVGEEQ_LyS16qRB57xWZ-kgNRIjgdLPY8T7HzvNMFlILCV=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 85}</t>
+          <t>{'name': 'Nghĩa Nguyễn Trung', 'link': 'https://www.google.com/maps/contrib/107253778101970197900?hl=vi', 'contributor_id': '107253778101970197900', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUNLHg5XlpgtWVVTp_oJKOYAejqmQORtgQ_Oe2vusE5W_sQoZc5=s120-c-rp-mo-ba12-br100', 'reviews': 275, 'photos': 1279}</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -735,25 +735,45 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Đi vào một ngày nắng. Nắng hắt lên mặt nước long lanh nên xinh xắn hẳn:&gt; Chỉ là thác nay có vẻ hơi ít nc nên không như mình tưởng tượng.</t>
+          <t>Khu vực thác nước đẹp, nhiều cảnh quan, nhiều góc chụp đẹp.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>{'name': 'Frugal Flow', 'link': 'https://www.google.com/maps/contrib/107453311426556875441?hl=vi', 'contributor_id': '107453311426556875441', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUspWRVGEEQ_LyS16qRB57xWZ-kgNRIjgdLPY8T7HzvNMFlILCV=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 85}</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Đi vào một ngày nắng. Nắng hắt lên mặt nước long lanh nên xinh xắn hẳn:&gt; Chỉ là thác nay có vẻ hơi ít nc nên không như mình tưởng tượng.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>6 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'reviews': 219, 'photos': 308}</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B14" t="n">
         <v>3</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Trải nghiệm vừa phải
 Giá vé theo trải nghiệm đi nhiều thác khác nhau của mình thì là khá cao so với các nơi khác, mình đi vào dịp tết nên thác ít nước.
@@ -761,98 +781,78 @@
 Cá nhân nếu quay lại Mộc Châu sẽ không đến thác này lần nào nữa</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>6 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>{'name': 'La Meu', 'link': 'https://www.google.com/maps/contrib/108858956358165703026?hl=vi', 'contributor_id': '108858956358165703026', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVKW-aZD0iBs1KBFQlmzfMiMTfjpd4PfUn4GO-K2tEt1PLpZ3YY=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 117}</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Thác Dải Yếm là điểm du lịch rất đáng đi. Đường đi dễ, xe máy hay ô tô đều thuận tiện. Không gian mát mẻ, thiên nhiên đẹp và trong lành.
 Nước thác xanh biếc, chảy mạnh nhưng nhìn rất êm và thơ mộng, chụp hình lên đẹp lắm. Khu vực được làm lối đi khá an toàn, dễ tham quan.
 Nhân viên ở đây dễ thương, nhiệt tình, hướng dẫn khách rất chu đáo và thân thiện. Phù hợp đi chơi cùng gia đình hoặc bạn bè để thư giãn, nghỉ ngơi.</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>8 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'reviews': 24, 'photos': 255}</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>5</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
-        </is>
-      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>9 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
+          <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'reviews': 24, 'photos': 255}</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
+          <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 1090}</t>
+          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
+          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
+          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 1090}</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -860,39 +860,39 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
+          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
+          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 143, 'photos': 325}</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
+          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2 tháng trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 115, 'photos': 84}</t>
+          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -900,19 +900,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
+          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7 tháng trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 3220}</t>
+          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -920,19 +920,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
+          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 251, 'photos': 4810}</t>
+          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 115, 'photos': 84}</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -940,45 +940,85 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cảnh quan đẹp, ng dân thân thiện</t>
+          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5 tháng trước</t>
+          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
+          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 3220}</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
+          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>9 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 250, 'photos': 4810}</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Cảnh quan đẹp, ng dân thân thiện</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>5 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>8 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>{'name': 'Linh Nguyễn', 'link': 'https://www.google.com/maps/contrib/109820275513447282944?hl=vi', 'contributor_id': '109820275513447282944', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVpZ-SNyOn6byhXW5cnkMUzIYl8pLeo3scME3-VG4n2ps2S2tYx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 992}</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>5</v>
-      </c>
-      <c r="C24" t="inlineStr">
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>Thác đẹp, suối nước tự nhiên, đường đi dọc suối sạch sẽ
 Một số địa điểm du lịch ở Mộc Châu mọi người có thể tham khảo
@@ -991,143 +1031,143 @@
 2. Cá Hồi Thanh Bảy</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>2 năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 81, 'photos': 188}</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>4</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>6 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>5</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 71, 'photos': 496}</t>
+          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 81, 'photos': 188}</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
+          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4 tháng trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>{'name': 'Anh Tuấn Trần', 'link': 'https://www.google.com/maps/contrib/106361750645670984745?hl=vi', 'contributor_id': '106361750645670984745', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXiNjEqD4gV0wYaTlBDaztRxN3Bz6wZiiUqJ5pnHqrMT1HyLF_rBg=s120-c-rp-mo-ba12-br100', 'reviews': 958, 'photos': 4098}</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Chẳng hiểu Mộc Châu làm du lịch kiểu gì mà chỗ nào cũng bắt mua vé và giá vé quá cao. Cứ một điểm tham quan là 100k/người mà chẳng có gì đặc sắc cả. Thác dải yếm có quá nhiều công trình nhân tạo. Kể cả 100k/người cho cả Thác Dải Yếm + Cầu Kính thì mình vẫn thấy đắt - không tương xứng. Đây còn vé riêng cho thác và riêng cho cầu kính mặc dù cả 2 này là cùng một điêm. Không muốn quay lại bao giờ nữa.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>5</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 71, 'photos': 496}</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>4 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'reviews': 78, 'photos': 260}</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="B31" t="n">
         <v>4</v>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
 Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>{'name': 'Mai Nguyễn', 'link': 'https://www.google.com/maps/contrib/101330344304584692421?hl=vi', 'contributor_id': '101330344304584692421', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocLN09xUhcK1CuSvLI4U-MC1m1LployphMNgUrT9xqkPlzqHlA=s120-c-rp-mo-br100', 'reviews': 5, 'photos': 7}</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>5</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Cảnh đẹp, có cả trải nghiệm cầu kính và zipline mà giá phải chăng hơn bên khu cầu kính bạch long</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>6 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 533, 'photos': 4107}</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B32" t="n">
         <v>4</v>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 574}</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>5</v>
-      </c>
-      <c r="C31" t="inlineStr">
+      <c r="B33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>Đúng tên gọi của nó. Thác cũng rất đẹp. Nếu vào mùa nước chắc còn đẹp hơn.
 Cảnh quan cũng rất sạch đẹp.
@@ -1136,46 +1176,6 @@
 - vé vào cổng giá phù hợp</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4192}</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>5</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Thời gian chỉnh sửa: 2 năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 518}</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>5</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
-        </is>
-      </c>
       <c r="D33" t="inlineStr">
         <is>
           <t>một năm trước</t>
@@ -1185,27 +1185,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
+          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4192}</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
+          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>Thời gian chỉnh sửa: 2 năm trước</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
+          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 518}</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
+          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1225,35 +1225,35 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 1623}</t>
+          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 49, 'photos': 144}</t>
+          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
+          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1265,68 +1265,68 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 1623}</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>5</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>9 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 49, 'photos': 144}</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>4</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWyzcZkQykW_QPymZ2fTMwerDVUm-XhQ6WZ0NqbjNzbEznIxcF7AQ=s120-c-rp-mo-ba12-br100', 'reviews': 149, 'photos': 3873}</t>
         </is>
       </c>
-      <c r="B38" t="n">
-        <v>5</v>
-      </c>
-      <c r="C38" t="inlineStr">
+      <c r="B40" t="n">
+        <v>5</v>
+      </c>
+      <c r="C40" t="inlineStr">
         <is>
           <t>Thác Dải Yếm, còn được gọi là thác Nàng, thác Bản Vặt, là một thác nước hùng vĩ nằm ở xã Mường Sang, huyện Mộc Châu, tỉnh Sơn La. Thác có chiều cao khoảng 100m, chia thành hai dòng thác chính, trông giống như một dải yếm đào mềm mại uốn lượn quanh vách núi.
 Thác Dải Yếm là một địa điểm du lịch hấp dẫn, thu hút khách du lịch trong và ngoài nước. Đây là nơi du khách có thể chiêm ngưỡng vẻ đẹp hùng vĩ của thác nước và tìm hiểu về truyền thuyết về thác.</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>2 năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'reviews': 97, 'photos': 178}</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>4</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'reviews': 27, 'photos': 260}</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>4</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'reviews': 75, 'photos': 503}</t>
+          <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'reviews': 97, 'photos': 178}</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1334,46 +1334,86 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'reviews': 27, 'photos': 260}</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>4</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'reviews': 75, 'photos': 503}</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>4</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>Thác Dải Yếm nằm trên dòng suối Vặt khởi nguồn từ hai khe nước Bó Co Lắm và Bo Tá Cháu ở đầu bản Vặt, một bản của người Thái có lịch sử lâu đời. Suối Vặt chảy được 5 km đổ vào suối Bó Sập, một dòng suối lớn bắt nguồn từ bản Bó Sập giáp biên giới Việt Lào rồi chảy về đất Yên Châu. Tại nơi hợp lưu của hai suối, dòng nước gặp một vùng đá vôi và đổ xuống phía dưới tạo thành thác Dải Yếm.[5]
 Thác Dải Yếm bao gồm hai phần, thác nước phía trên rộng 70 mét, thác nước phía dưới nằm cách đó 150-200 mét. Vào mùa khô, thác phía dưới chỉ có một dòng chảy từ độ cao 50 m xuống triền đá ở dưới. hai thác đổ xuống với tổng chiều cao 100m, một bên được chia làm 9 tầng, bên còn lại 5 tầng. Cách giữa hai phần thác là một bãi đất phẳng thuận tiện cho việc tham quan của du khách. Thảm thực vật trên đỉnh thác cũng khá phong phú.</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'reviews': 8, 'photos': 90}</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B44" t="n">
         <v>4</v>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>11 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 152, 'photos': 1281}</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 151, 'photos': 1281}</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
         <v>4</v>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Thác nhỏ cũng đẹp nhưng được trang trí dành cho du lịch rồi về độ rộng nhiều tầng và thiên nhiên thì không bằng thác Nàng Tiên hoặc thác Chiềng Khoa.
 Thác Dải Yếm được đầu tư khang trang nhưng đi bộ từ bãi gửi xe vào thác hơi bị xa (vé gửi xe 30k), đường đi vào và khu thác bên trong nhiều khu chụp ảnh checkin được trang trí chụp ảnh đẹp mắt. Giá vé tháng 1/2024 là 80k/ người vào cổng nhưng đến 30/4/2024 tăng lên 100k/ng giá vé hơi cao với việc vào ngắm thác.
@@ -1381,56 +1421,16 @@
 - Bản thân mình cảm nhận thì cũng bình thường thác không cao không rộng dài đẹp nhiều tầng bằng thác Nàng Tiên hoặc Chiềng Khoa. Nói chung đi du lịch Mộc Châu ghé qua cho biết thôi. Chứ để quay lại thì ít khả năng.</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>2 năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 140, 'photos': 570}</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>4</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>View đẹp, chỉ tiếc là ghé hồi tháng 5 lúc đang mùa mưa, nên không được đi trải nghiệm nhiều.</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>10 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>{'name': 'Hung Tran', 'link': 'https://www.google.com/maps/contrib/111025160790635631721?hl=vi', 'contributor_id': '111025160790635631721', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXJvHNQsMohKHo9fo2c_guCokbfqlcHTDulcTBswdAfP6GIiZRa=s120-c-rp-mo-ba12-br100', 'reviews': 120, 'photos': 1783}</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>5</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Mới đi Thác Dải Yếm mà thấy cảnh ở đây quá ấn tượng. Nước từ thác chảy xuống nhìn thôi đã mát cả mắt, mát hơn một phần do cái thời tiết mát mẻ nơi miền núi này. Đường đến thác hơi gồ ghề tí nên đi lại cẩn thận xíu nhưng được cái khung cảnh thiên nhiên trời ban, thấy cũng quá ổn. Có mấy gian hàng bán đặc sản địa phương, cứ thấy ghé thử, giá nơi này cũng dễ chịu. Mọi thứ rất thư thái, không đông đúc, thích hợp để đi vào ngày nghỉ. Thêm vài chỗ ngồi nghỉ ngơi thì tuyệt!</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyen Hung Son', 'link': 'https://www.google.com/maps/contrib/103602300698496865451?hl=vi', 'contributor_id': '103602300698496865451', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUZaCtGsEksmQHBlNq8Xrol7h098HYLQGNUZgSqhr55eCVudl46og=s120-c-rp-mo-ba12-br100', 'reviews': 74, 'photos': 2146}</t>
+          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 140, 'photos': 570}</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1438,12 +1438,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm dường như trở thành một công viên. Lối vào thác khi đi qua cổng và đến Suối Hẹn Hò, khách thăm quan có thể đi theo đường bê tông hoặc đi xuống suối hẹn hò men theo đường lát đá ven suối và núi. Đa phần cá cảnh quan ở đây đã được cải tạo. Các trò chơi như Cầu Kính, Zipline và có lẽ đặc biệt nhất vẫn là check-in tại Thác Dải Yếm khi đầy nước. Vé vào cửa 100k/người lớn, trẻ em 50k (&lt;1,2m). Vé cầu kính 100k, Zipline 50k.</t>
+          <t>View đẹp, chỉ tiếc là ghé hồi tháng 5 lúc đang mùa mưa, nên không được đi trải nghiệm nhiều.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2 năm trước</t>
+          <t>10 tháng trước</t>
         </is>
       </c>
     </row>

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -645,7 +645,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 301, 'photos': 3605}</t>
+          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 301, 'photos': 3603}</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -665,7 +665,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 143, 'photos': 325}</t>
+          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 24}</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -673,61 +673,61 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
+          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>5 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 24}</t>
+          <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'reviews': 16, 'photos': 114}</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>5</v>
       </c>
       <c r="C10" t="inlineStr">
-        <is>
-          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>5 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'reviews': 16, 'photos': 114}</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" t="inlineStr">
         <is>
           <t>Đi tầm trưa nắng đẹp
 Thác nhỏ, đi cũng không mất quá nhiều thời gian
 Có cầu kính</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>6 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>{'name': 'Nghĩa Nguyễn Trung', 'link': 'https://www.google.com/maps/contrib/107253778101970197900?hl=vi', 'contributor_id': '107253778101970197900', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUNLHg5XlpgtWVVTp_oJKOYAejqmQORtgQ_Oe2vusE5W_sQoZc5=s120-c-rp-mo-ba12-br100', 'reviews': 275, 'photos': 1279}</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Khu vực thác nước đẹp, nhiều cảnh quan, nhiều góc chụp đẹp.</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>{'name': 'Nghĩa Nguyễn Trung', 'link': 'https://www.google.com/maps/contrib/107253778101970197900?hl=vi', 'contributor_id': '107253778101970197900', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUNLHg5XlpgtWVVTp_oJKOYAejqmQORtgQ_Oe2vusE5W_sQoZc5=s120-c-rp-mo-ba12-br100', 'reviews': 275, 'photos': 1279}</t>
+          <t>{'name': 'Frugal Flow', 'link': 'https://www.google.com/maps/contrib/107453311426556875441?hl=vi', 'contributor_id': '107453311426556875441', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUspWRVGEEQ_LyS16qRB57xWZ-kgNRIjgdLPY8T7HzvNMFlILCV=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 85}</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -735,45 +735,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Khu vực thác nước đẹp, nhiều cảnh quan, nhiều góc chụp đẹp.</t>
+          <t>Đi vào một ngày nắng. Nắng hắt lên mặt nước long lanh nên xinh xắn hẳn:&gt; Chỉ là thác nay có vẻ hơi ít nc nên không như mình tưởng tượng.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2 tháng trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>{'name': 'Frugal Flow', 'link': 'https://www.google.com/maps/contrib/107453311426556875441?hl=vi', 'contributor_id': '107453311426556875441', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUspWRVGEEQ_LyS16qRB57xWZ-kgNRIjgdLPY8T7HzvNMFlILCV=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 85}</t>
+          <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'reviews': 219, 'photos': 308}</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="inlineStr">
-        <is>
-          <t>Đi vào một ngày nắng. Nắng hắt lên mặt nước long lanh nên xinh xắn hẳn:&gt; Chỉ là thác nay có vẻ hơi ít nc nên không như mình tưởng tượng.</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>6 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'reviews': 219, 'photos': 308}</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>3</v>
-      </c>
-      <c r="C14" t="inlineStr">
         <is>
           <t>Trải nghiệm vừa phải
 Giá vé theo trải nghiệm đi nhiều thác khác nhau của mình thì là khá cao so với các nơi khác, mình đi vào dịp tết nên thác ít nước.
@@ -781,78 +761,98 @@
 Cá nhân nếu quay lại Mộc Châu sẽ không đến thác này lần nào nữa</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>6 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>{'name': 'La Meu', 'link': 'https://www.google.com/maps/contrib/108858956358165703026?hl=vi', 'contributor_id': '108858956358165703026', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVKW-aZD0iBs1KBFQlmzfMiMTfjpd4PfUn4GO-K2tEt1PLpZ3YY=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 117}</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>5</v>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Thác Dải Yếm là điểm du lịch rất đáng đi. Đường đi dễ, xe máy hay ô tô đều thuận tiện. Không gian mát mẻ, thiên nhiên đẹp và trong lành.
 Nước thác xanh biếc, chảy mạnh nhưng nhìn rất êm và thơ mộng, chụp hình lên đẹp lắm. Khu vực được làm lối đi khá an toàn, dễ tham quan.
 Nhân viên ở đây dễ thương, nhiệt tình, hướng dẫn khách rất chu đáo và thân thiện. Phù hợp đi chơi cùng gia đình hoặc bạn bè để thư giãn, nghỉ ngơi.</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>9 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'reviews': 24, 'photos': 255}</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'reviews': 24, 'photos': 255}</t>
+          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
+          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
+          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 1090}</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
+          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 1090}</t>
+          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 143, 'photos': 325}</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -860,19 +860,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
+          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 143, 'photos': 325}</t>
+          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -880,27 +880,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
+          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
+          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
+          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -912,67 +912,67 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
+          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 115, 'photos': 84}</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
+          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2 tháng trước</t>
+          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 115, 'photos': 84}</t>
+          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 3220}</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
+          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>7 tháng trước</t>
+          <t>9 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 3220}</t>
+          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 250, 'photos': 4810}</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
+          <t>Cảnh quan đẹp, ng dân thân thiện</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>5 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 250, 'photos': 4810}</t>
+          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -980,45 +980,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cảnh quan đẹp, ng dân thân thiện</t>
+          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>5 tháng trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
+          <t>{'name': 'Linh Nguyễn', 'link': 'https://www.google.com/maps/contrib/109820275513447282944?hl=vi', 'contributor_id': '109820275513447282944', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVpZ-SNyOn6byhXW5cnkMUzIYl8pLeo3scME3-VG4n2ps2S2tYx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 992}</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>5</v>
       </c>
       <c r="C25" t="inlineStr">
-        <is>
-          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>8 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>{'name': 'Linh Nguyễn', 'link': 'https://www.google.com/maps/contrib/109820275513447282944?hl=vi', 'contributor_id': '109820275513447282944', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVpZ-SNyOn6byhXW5cnkMUzIYl8pLeo3scME3-VG4n2ps2S2tYx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 992}</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>5</v>
-      </c>
-      <c r="C26" t="inlineStr">
         <is>
           <t>Thác đẹp, suối nước tự nhiên, đường đi dọc suối sạch sẽ
 Một số địa điểm du lịch ở Mộc Châu mọi người có thể tham khảo
@@ -1031,56 +1011,76 @@
 2. Cá Hồi Thanh Bảy</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 81, 'photos': 188}</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2 năm trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 81, 'photos': 188}</t>
+          <t>{'name': 'Anh Tuấn Trần', 'link': 'https://www.google.com/maps/contrib/106361750645670984745?hl=vi', 'contributor_id': '106361750645670984745', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXiNjEqD4gV0wYaTlBDaztRxN3Bz6wZiiUqJ5pnHqrMT1HyLF_rBg=s120-c-rp-mo-ba12-br100', 'reviews': 958, 'photos': 4098}</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
+          <t>Chẳng hiểu Mộc Châu làm du lịch kiểu gì mà chỗ nào cũng bắt mua vé và giá vé quá cao. Cứ một điểm tham quan là 100k/người mà chẳng có gì đặc sắc cả. Thác dải yếm có quá nhiều công trình nhân tạo. Kể cả 100k/người cho cả Thác Dải Yếm + Cầu Kính thì mình vẫn thấy đắt - không tương xứng. Đây còn vé riêng cho thác và riêng cho cầu kính mặc dù cả 2 này là cùng một điêm. Không muốn quay lại bao giờ nữa.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>2 năm trước</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>{'name': 'Anh Tuấn Trần', 'link': 'https://www.google.com/maps/contrib/106361750645670984745?hl=vi', 'contributor_id': '106361750645670984745', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXiNjEqD4gV0wYaTlBDaztRxN3Bz6wZiiUqJ5pnHqrMT1HyLF_rBg=s120-c-rp-mo-ba12-br100', 'reviews': 958, 'photos': 4098}</t>
+          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chẳng hiểu Mộc Châu làm du lịch kiểu gì mà chỗ nào cũng bắt mua vé và giá vé quá cao. Cứ một điểm tham quan là 100k/người mà chẳng có gì đặc sắc cả. Thác dải yếm có quá nhiều công trình nhân tạo. Kể cả 100k/người cho cả Thác Dải Yếm + Cầu Kính thì mình vẫn thấy đắt - không tương xứng. Đây còn vé riêng cho thác và riêng cho cầu kính mặc dù cả 2 này là cùng một điêm. Không muốn quay lại bao giờ nữa.</t>
+          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2 năm trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
+          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 71, 'photos': 496}</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1088,39 +1088,40 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
+          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>4 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 71, 'photos': 496}</t>
+          <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'reviews': 78, 'photos': 260}</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
+          <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
+Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'reviews': 78, 'photos': 260}</t>
+          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 533, 'photos': 4107}</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1128,8 +1129,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
-Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
+          <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1141,33 +1141,13 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 533, 'photos': 4107}</t>
+          <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 574}</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C32" t="inlineStr">
-        <is>
-          <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 574}</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>5</v>
-      </c>
-      <c r="C33" t="inlineStr">
         <is>
           <t>Đúng tên gọi của nó. Thác cũng rất đẹp. Nếu vào mùa nước chắc còn đẹp hơn.
 Cảnh quan cũng rất sạch đẹp.
@@ -1176,16 +1156,36 @@
 - vé vào cổng giá phù hợp</t>
         </is>
       </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4192}</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>Thời gian chỉnh sửa: 2 năm trước</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4192}</t>
+          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 518}</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1193,27 +1193,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
+          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Thời gian chỉnh sửa: 2 năm trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 518}</t>
+          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
+          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1225,15 +1225,15 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
+          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
+          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1245,7 +1245,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
+          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 1623}</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1253,80 +1253,80 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
+          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>9 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 1623}</t>
+          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 49, 'photos': 144}</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 49, 'photos': 144}</t>
+          <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWyzcZkQykW_QPymZ2fTMwerDVUm-XhQ6WZ0NqbjNzbEznIxcF7AQ=s120-c-rp-mo-ba12-br100', 'reviews': 149, 'photos': 3873}</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
+          <t>Thác Dải Yếm, còn được gọi là thác Nàng, thác Bản Vặt, là một thác nước hùng vĩ nằm ở xã Mường Sang, huyện Mộc Châu, tỉnh Sơn La. Thác có chiều cao khoảng 100m, chia thành hai dòng thác chính, trông giống như một dải yếm đào mềm mại uốn lượn quanh vách núi.
+Thác Dải Yếm là một địa điểm du lịch hấp dẫn, thu hút khách du lịch trong và ngoài nước. Đây là nơi du khách có thể chiêm ngưỡng vẻ đẹp hùng vĩ của thác nước và tìm hiểu về truyền thuyết về thác.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>2 năm trước</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWyzcZkQykW_QPymZ2fTMwerDVUm-XhQ6WZ0NqbjNzbEznIxcF7AQ=s120-c-rp-mo-ba12-br100', 'reviews': 149, 'photos': 3873}</t>
+          <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'reviews': 97, 'photos': 178}</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm, còn được gọi là thác Nàng, thác Bản Vặt, là một thác nước hùng vĩ nằm ở xã Mường Sang, huyện Mộc Châu, tỉnh Sơn La. Thác có chiều cao khoảng 100m, chia thành hai dòng thác chính, trông giống như một dải yếm đào mềm mại uốn lượn quanh vách núi.
-Thác Dải Yếm là một địa điểm du lịch hấp dẫn, thu hút khách du lịch trong và ngoài nước. Đây là nơi du khách có thể chiêm ngưỡng vẻ đẹp hùng vĩ của thác nước và tìm hiểu về truyền thuyết về thác.</t>
+          <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2 năm trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'reviews': 97, 'photos': 178}</t>
+          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'reviews': 27, 'photos': 260}</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
+          <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1346,7 +1346,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'reviews': 27, 'photos': 260}</t>
+          <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'reviews': 75, 'photos': 503}</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1354,7 +1354,8 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
+          <t>Thác Dải Yếm nằm trên dòng suối Vặt khởi nguồn từ hai khe nước Bó Co Lắm và Bo Tá Cháu ở đầu bản Vặt, một bản của người Thái có lịch sử lâu đời. Suối Vặt chảy được 5 km đổ vào suối Bó Sập, một dòng suối lớn bắt nguồn từ bản Bó Sập giáp biên giới Việt Lào rồi chảy về đất Yên Châu. Tại nơi hợp lưu của hai suối, dòng nước gặp một vùng đá vôi và đổ xuống phía dưới tạo thành thác Dải Yếm.[5]
+Thác Dải Yếm bao gồm hai phần, thác nước phía trên rộng 70 mét, thác nước phía dưới nằm cách đó 150-200 mét. Vào mùa khô, thác phía dưới chỉ có một dòng chảy từ độ cao 50 m xuống triền đá ở dưới. hai thác đổ xuống với tổng chiều cao 100m, một bên được chia làm 9 tầng, bên còn lại 5 tầng. Cách giữa hai phần thác là một bãi đất phẳng thuận tiện cho việc tham quan của du khách. Thảm thực vật trên đỉnh thác cũng khá phong phú.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1366,7 +1367,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'reviews': 75, 'photos': 503}</t>
+          <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'reviews': 8, 'photos': 90}</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1374,46 +1375,25 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm nằm trên dòng suối Vặt khởi nguồn từ hai khe nước Bó Co Lắm và Bo Tá Cháu ở đầu bản Vặt, một bản của người Thái có lịch sử lâu đời. Suối Vặt chảy được 5 km đổ vào suối Bó Sập, một dòng suối lớn bắt nguồn từ bản Bó Sập giáp biên giới Việt Lào rồi chảy về đất Yên Châu. Tại nơi hợp lưu của hai suối, dòng nước gặp một vùng đá vôi và đổ xuống phía dưới tạo thành thác Dải Yếm.[5]
-Thác Dải Yếm bao gồm hai phần, thác nước phía trên rộng 70 mét, thác nước phía dưới nằm cách đó 150-200 mét. Vào mùa khô, thác phía dưới chỉ có một dòng chảy từ độ cao 50 m xuống triền đá ở dưới. hai thác đổ xuống với tổng chiều cao 100m, một bên được chia làm 9 tầng, bên còn lại 5 tầng. Cách giữa hai phần thác là một bãi đất phẳng thuận tiện cho việc tham quan của du khách. Thảm thực vật trên đỉnh thác cũng khá phong phú.</t>
+          <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>11 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'reviews': 8, 'photos': 90}</t>
+          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 151, 'photos': 1281}</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>4</v>
       </c>
       <c r="C44" t="inlineStr">
-        <is>
-          <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>11 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 151, 'photos': 1281}</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>4</v>
-      </c>
-      <c r="C45" t="inlineStr">
         <is>
           <t>Thác nhỏ cũng đẹp nhưng được trang trí dành cho du lịch rồi về độ rộng nhiều tầng và thiên nhiên thì không bằng thác Nàng Tiên hoặc thác Chiềng Khoa.
 Thác Dải Yếm được đầu tư khang trang nhưng đi bộ từ bãi gửi xe vào thác hơi bị xa (vé gửi xe 30k), đường đi vào và khu thác bên trong nhiều khu chụp ảnh checkin được trang trí chụp ảnh đẹp mắt. Giá vé tháng 1/2024 là 80k/ người vào cổng nhưng đến 30/4/2024 tăng lên 100k/ng giá vé hơi cao với việc vào ngắm thác.
@@ -1421,29 +1401,49 @@
 - Bản thân mình cảm nhận thì cũng bình thường thác không cao không rộng dài đẹp nhiều tầng bằng thác Nàng Tiên hoặc Chiềng Khoa. Nói chung đi du lịch Mộc Châu ghé qua cho biết thôi. Chứ để quay lại thì ít khả năng.</t>
         </is>
       </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 140, 'photos': 570}</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>4</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>View đẹp, chỉ tiếc là ghé hồi tháng 5 lúc đang mùa mưa, nên không được đi trải nghiệm nhiều.</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2 năm trước</t>
+          <t>10 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 140, 'photos': 570}</t>
+          <t>{'name': 'Hung Tran', 'link': 'https://www.google.com/maps/contrib/111025160790635631721?hl=vi', 'contributor_id': '111025160790635631721', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXJvHNQsMohKHo9fo2c_guCokbfqlcHTDulcTBswdAfP6GIiZRa=s120-c-rp-mo-ba12-br100', 'reviews': 120, 'photos': 1783}</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>View đẹp, chỉ tiếc là ghé hồi tháng 5 lúc đang mùa mưa, nên không được đi trải nghiệm nhiều.</t>
+          <t>Mới đi Thác Dải Yếm mà thấy cảnh ở đây quá ấn tượng. Nước từ thác chảy xuống nhìn thôi đã mát cả mắt, mát hơn một phần do cái thời tiết mát mẻ nơi miền núi này. Đường đến thác hơi gồ ghề tí nên đi lại cẩn thận xíu nhưng được cái khung cảnh thiên nhiên trời ban, thấy cũng quá ổn. Có mấy gian hàng bán đặc sản địa phương, cứ thấy ghé thử, giá nơi này cũng dễ chịu. Mọi thứ rất thư thái, không đông đúc, thích hợp để đi vào ngày nghỉ. Thêm vài chỗ ngồi nghỉ ngơi thì tuyệt!</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>10 tháng trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>{'name': 'Hưng Nguyễn Duy (Hưng Photo)', 'link': 'https://www.google.com/maps/contrib/110173941936897044295?hl=vi', 'contributor_id': '110173941936897044295', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXshx7xq3ntsswbv03kbw9Z9KIntVjsKdM747CeNwqebP-xH_RO=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 192, 'photos': 2146}</t>
+          <t>{'name': 'Hưng Nguyễn Duy (Hưng Photo)', 'link': 'https://www.google.com/maps/contrib/110173941936897044295?hl=vi', 'contributor_id': '110173941936897044295', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXshx7xq3ntsswbv03kbw9Z9KIntVjsKdM747CeNwqebP-xH_RO=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 192, 'photos': 2169}</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -497,13 +497,308 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>{'name': 'Thái Nguyễn', 'link': 'https://www.google.com/maps/contrib/105517365260915933657?hl=vi', 'contributor_id': '105517365260915933657', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXLOkY3FUSH3Mz-aapJXPQUgoCFlQP20PICWZGzVI3cPkRkBIt_ew=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 65, 'photos': 175}</t>
+          <t>{'name': 'ZjmLee YTBer', 'link': 'https://www.google.com/maps/contrib/100979561872983589256?hl=vi', 'contributor_id': '100979561872983589256', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU6i9poRXPBKYv-WgZHmB9chW6jRPCOh3klZ1Z7Yv_DOaukn4g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 79, 'photos': 1243}</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>5</v>
       </c>
       <c r="C4" t="inlineStr">
+        <is>
+          <t>Nghe người địa phương kể lại thì cái tên “Dải Yếm” xuất phát từ truyền thuyết của người Thái. Họ nói rằng dòng thác trắng xóa từ trên cao đổ xuống giống như dải yếm của người con gái, nên từ đó cái tên này được gọi luôn cho tới bây giờ. Nghe vậy nên đứng nhìn dòng thác cũng thấy có chút gì đó rất nên thơ.
+Đi bộ quanh khu thác khá dễ, có lối đi và bậc đá để xuống gần chân thác. Nếu đi vào mùa nước nhiều thì thác nhìn đẹp hơn, nước trắng xóa và tiếng thác nghe rất đã tai. Còn những ngày nắng nhẹ thì không khí ở đây khá chill, kiểu ngồi nghỉ một chút, nghe tiếng nước và nhìn rừng cây xung quanh cũng thấy thư giãn.
+Mình thấy Thác Dải Yếm hợp với kiểu du lịch nhẹ nhàng: dừng chân, đi bộ một vòng, chụp vài bức ảnh rồi tiếp tục hành trình khám phá Mộc Châu. Nó không phải kiểu điểm du lịch quá hoành tráng, nhưng lại có cái nét mộc mạc và dễ chịu đúng chất cao nguyên.
+Nếu đang đi du lịch tự túc ở Mộc Châu, thì Thác Dải Yếm là một nơi khá đáng ghé qua. Không cần quá nhiều thời gian, chỉ cần dành khoảng một tiếng dạo quanh thôi cũng đủ để cảm nhận được một góc thiên nhiên rất đặc trưng của vùng núi này.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 368, 'photos': 2592}</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Nơi rất đáng để tham quan, trãi nghiệm chút it về cầu kính và kết hợp đi ngắm thác nước.
+Có nhiều nơi lên hình đẹp, cảnh đẹp. Có bán đặc sản Mộc Châu rất đa dạng.
+😍😍👍</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Thời gian chỉnh sửa: 5 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>{'name': 'Vĩ Lê Bá', 'link': 'https://www.google.com/maps/contrib/115860838984920745696?hl=vi', 'contributor_id': '115860838984920745696', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7wdRrYJWeEmKs7YInZz_FDg-T90l2ImigSwJKL2hWmQu75bzm=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 60, 'photos': 94}</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Đẹp thì đẹp sơ sơ nhưng không gian vẫn khá là thoải mái
+Đi bộ oklea nhưng mà vẫn còn quá nhỏ, đi cỡ 30 phút là xong mất tiêu r
+Tuỳ ngà lượng khách sẽ khác nhau và ảnh hưởng lớn tớ trải nghiệm
+Nói chung là vẫn okela</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>{'name': 'THANH NGUYEN', 'link': 'https://www.google.com/maps/contrib/110418688752170937071?hl=vi', 'contributor_id': '110418688752170937071', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIBtT-SxDlGGJM5jA47OmxpGvFdaG6EOeSswcBwx4VuXgnOdQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 70, 'photos': 207}</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>thác đẹp nhưng nên đi vào mùa nước sẽ thấy sự khác biệt hơn nhiều</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>{'name': 'Cửu Quang Nguyễn', 'link': 'https://www.google.com/maps/contrib/107704339232071144994?hl=vi', 'contributor_id': '107704339232071144994', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV2_oJLqzlVCtXNV77ConxSPDhhMhFP-czjeCf6uCm7cabO88k=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 77, 'photos': 346}</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Thác Dải Yếm nằm trong khu du lịch sinh thái thác Dải Yếm, đường đi khá tiện lợi để ghé vào, tuy nhiên cần chú ý lối vào có khúc cua dốc khá ngoặt. Vé vào là 150k/người, bên trong có khá nhiều vị trí để du ngoạn và ngắm cảnh, đặc biệt là khu vực thác nước rất hùng vĩ và mát mẻ, có cầu dẫn vào nhìn rất thơ mộng và tuyệt vời. Nếu có dịp ghé lên Mộc Châu thì nên ghé vào đây chơi 1 lần để du ngoạn thắng cảnh thiên nhiên tại nơi đây.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>5 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>{'name': 'Nguyễn Anh Quân', 'link': 'https://www.google.com/maps/contrib/111631093743063403454?hl=vi', 'contributor_id': '111631093743063403454', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIy-NjGEZ7ggp1yhLvVSe2iSDFAUAF4AILlK1IHBmSbkPzlKg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 9, 'photos': 24}</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Cảnh đẹp, nhưng xu là đi ngay lúc mưa nên thác có nước như cf</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>một tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 301, 'photos': 3603}</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>4 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 24}</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>5 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'reviews': 16, 'photos': 114}</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Đi tầm trưa nắng đẹp
+Thác nhỏ, đi cũng không mất quá nhiều thời gian
+Có cầu kính</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>6 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>{'name': 'Nghĩa Nguyễn Trung', 'link': 'https://www.google.com/maps/contrib/107253778101970197900?hl=vi', 'contributor_id': '107253778101970197900', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUNLHg5XlpgtWVVTp_oJKOYAejqmQORtgQ_Oe2vusE5W_sQoZc5=s120-c-rp-mo-ba12-br100', 'reviews': 275, 'photos': 1279}</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Khu vực thác nước đẹp, nhiều cảnh quan, nhiều góc chụp đẹp.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>{'name': 'Frugal Flow', 'link': 'https://www.google.com/maps/contrib/107453311426556875441?hl=vi', 'contributor_id': '107453311426556875441', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUspWRVGEEQ_LyS16qRB57xWZ-kgNRIjgdLPY8T7HzvNMFlILCV=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 85}</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Đi vào một ngày nắng. Nắng hắt lên mặt nước long lanh nên xinh xắn hẳn:&gt; Chỉ là thác nay có vẻ hơi ít nc nên không như mình tưởng tượng.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>6 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'reviews': 219, 'photos': 308}</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Trải nghiệm vừa phải
+Giá vé theo trải nghiệm đi nhiều thác khác nhau của mình thì là khá cao so với các nơi khác, mình đi vào dịp tết nên thác ít nước.
+Cảnh quan xung quanh thác ở mức bình thường.
+Cá nhân nếu quay lại Mộc Châu sẽ không đến thác này lần nào nữa</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>6 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>{'name': 'La Meu', 'link': 'https://www.google.com/maps/contrib/108858956358165703026?hl=vi', 'contributor_id': '108858956358165703026', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVKW-aZD0iBs1KBFQlmzfMiMTfjpd4PfUn4GO-K2tEt1PLpZ3YY=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 117}</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Thác Dải Yếm là điểm du lịch rất đáng đi. Đường đi dễ, xe máy hay ô tô đều thuận tiện. Không gian mát mẻ, thiên nhiên đẹp và trong lành.
+Nước thác xanh biếc, chảy mạnh nhưng nhìn rất êm và thơ mộng, chụp hình lên đẹp lắm. Khu vực được làm lối đi khá an toàn, dễ tham quan.
+Nhân viên ở đây dễ thương, nhiệt tình, hướng dẫn khách rất chu đáo và thân thiện. Phù hợp đi chơi cùng gia đình hoặc bạn bè để thư giãn, nghỉ ngơi.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>9 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'reviews': 24, 'photos': 255}</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>6 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>{'name': 'Thái Nguyễn', 'link': 'https://www.google.com/maps/contrib/105517365260915933657?hl=vi', 'contributor_id': '105517365260915933657', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXLOkY3FUSH3Mz-aapJXPQUgoCFlQP20PICWZGzVI3cPkRkBIt_ew=s120-c-rp-mo-ba12-br100', 'reviews': 65, 'photos': 175}</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>Nếu đi cùng Lover sẽ đẹp hơn.
 Nếu tự nhìn lại
@@ -571,348 +866,56 @@
 Hơn cả tới thiên đường</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>8 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>{'name': 'ZjmLee YTBer', 'link': 'https://www.google.com/maps/contrib/100979561872983589256?hl=vi', 'contributor_id': '100979561872983589256', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU6i9poRXPBKYv-WgZHmB9chW6jRPCOh3klZ1Z7Yv_DOaukn4g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 79, 'photos': 1243}</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Nghe người địa phương kể lại thì cái tên “Dải Yếm” xuất phát từ truyền thuyết của người Thái. Họ nói rằng dòng thác trắng xóa từ trên cao đổ xuống giống như dải yếm của người con gái, nên từ đó cái tên này được gọi luôn cho tới bây giờ. Nghe vậy nên đứng nhìn dòng thác cũng thấy có chút gì đó rất nên thơ.
-Đi bộ quanh khu thác khá dễ, có lối đi và bậc đá để xuống gần chân thác. Nếu đi vào mùa nước nhiều thì thác nhìn đẹp hơn, nước trắng xóa và tiếng thác nghe rất đã tai. Còn những ngày nắng nhẹ thì không khí ở đây khá chill, kiểu ngồi nghỉ một chút, nghe tiếng nước và nhìn rừng cây xung quanh cũng thấy thư giãn.
-Mình thấy Thác Dải Yếm hợp với kiểu du lịch nhẹ nhàng: dừng chân, đi bộ một vòng, chụp vài bức ảnh rồi tiếp tục hành trình khám phá Mộc Châu. Nó không phải kiểu điểm du lịch quá hoành tráng, nhưng lại có cái nét mộc mạc và dễ chịu đúng chất cao nguyên.
-Nếu đang đi du lịch tự túc ở Mộc Châu, thì Thác Dải Yếm là một nơi khá đáng ghé qua. Không cần quá nhiều thời gian, chỉ cần dành khoảng một tiếng dạo quanh thôi cũng đủ để cảm nhận được một góc thiên nhiên rất đặc trưng của vùng núi này.</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>6 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 369, 'photos': 2607}</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Nơi rất đáng để tham quan, trãi nghiệm chút it về cầu kính và kết hợp đi ngắm thác nước.
-Có nhiều nơi lên hình đẹp, cảnh đẹp. Có bán đặc sản Mộc Châu rất đa dạng.
-😍😍👍</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Thời gian chỉnh sửa: 5 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>{'name': 'Nguyễn Anh Quân', 'link': 'https://www.google.com/maps/contrib/111631093743063403454?hl=vi', 'contributor_id': '111631093743063403454', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIy-NjGEZ7ggp1yhLvVSe2iSDFAUAF4AILlK1IHBmSbkPzlKg=s120-c-rp-mo-ba12-br100', 'reviews': 9, 'photos': 24}</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Cảnh đẹp, nhưng xu là đi ngay lúc mưa nên thác có nước như cf</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>một tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 301, 'photos': 3603}</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>4 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 24}</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>5 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'reviews': 16, 'photos': 114}</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Đi tầm trưa nắng đẹp
-Thác nhỏ, đi cũng không mất quá nhiều thời gian
-Có cầu kính</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>6 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>{'name': 'Nghĩa Nguyễn Trung', 'link': 'https://www.google.com/maps/contrib/107253778101970197900?hl=vi', 'contributor_id': '107253778101970197900', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUNLHg5XlpgtWVVTp_oJKOYAejqmQORtgQ_Oe2vusE5W_sQoZc5=s120-c-rp-mo-ba12-br100', 'reviews': 275, 'photos': 1279}</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Khu vực thác nước đẹp, nhiều cảnh quan, nhiều góc chụp đẹp.</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>{'name': 'Frugal Flow', 'link': 'https://www.google.com/maps/contrib/107453311426556875441?hl=vi', 'contributor_id': '107453311426556875441', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUspWRVGEEQ_LyS16qRB57xWZ-kgNRIjgdLPY8T7HzvNMFlILCV=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 85}</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Đi vào một ngày nắng. Nắng hắt lên mặt nước long lanh nên xinh xắn hẳn:&gt; Chỉ là thác nay có vẻ hơi ít nc nên không như mình tưởng tượng.</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>6 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'reviews': 219, 'photos': 308}</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>3</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Trải nghiệm vừa phải
-Giá vé theo trải nghiệm đi nhiều thác khác nhau của mình thì là khá cao so với các nơi khác, mình đi vào dịp tết nên thác ít nước.
-Cảnh quan xung quanh thác ở mức bình thường.
-Cá nhân nếu quay lại Mộc Châu sẽ không đến thác này lần nào nữa</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>6 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>{'name': 'La Meu', 'link': 'https://www.google.com/maps/contrib/108858956358165703026?hl=vi', 'contributor_id': '108858956358165703026', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVKW-aZD0iBs1KBFQlmzfMiMTfjpd4PfUn4GO-K2tEt1PLpZ3YY=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 117}</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm là điểm du lịch rất đáng đi. Đường đi dễ, xe máy hay ô tô đều thuận tiện. Không gian mát mẻ, thiên nhiên đẹp và trong lành.
-Nước thác xanh biếc, chảy mạnh nhưng nhìn rất êm và thơ mộng, chụp hình lên đẹp lắm. Khu vực được làm lối đi khá an toàn, dễ tham quan.
-Nhân viên ở đây dễ thương, nhiệt tình, hướng dẫn khách rất chu đáo và thân thiện. Phù hợp đi chơi cùng gia đình hoặc bạn bè để thư giãn, nghỉ ngơi.</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>9 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'reviews': 24, 'photos': 255}</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>5</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>6 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>8 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 1090}</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>5</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 143, 'photos': 325}</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>5</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
+          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
+          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2 tháng trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
+          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 1090}</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
+          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 115, 'photos': 84}</t>
+          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 143, 'photos': 325}</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -920,59 +923,59 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
+          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7 tháng trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 3220}</t>
+          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
+          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 250, 'photos': 4810}</t>
+          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cảnh quan đẹp, ng dân thân thiện</t>
+          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5 tháng trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
+          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 115, 'photos': 84}</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -980,25 +983,85 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
+          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 3220}</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>9 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 250, 'photos': 4825}</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Cảnh quan đẹp, ng dân thân thiện</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>5 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>8 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>{'name': 'Linh Nguyễn', 'link': 'https://www.google.com/maps/contrib/109820275513447282944?hl=vi', 'contributor_id': '109820275513447282944', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVpZ-SNyOn6byhXW5cnkMUzIYl8pLeo3scME3-VG4n2ps2S2tYx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 992}</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>5</v>
-      </c>
-      <c r="C25" t="inlineStr">
+      <c r="B28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>Thác đẹp, suối nước tự nhiên, đường đi dọc suối sạch sẽ
 Một số địa điểm du lịch ở Mộc Châu mọi người có thể tham khảo
@@ -1011,143 +1074,123 @@
 2. Cá Hồi Thanh Bảy</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>2 năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 81, 'photos': 188}</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>4</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>6 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>{'name': 'Anh Tuấn Trần', 'link': 'https://www.google.com/maps/contrib/106361750645670984745?hl=vi', 'contributor_id': '106361750645670984745', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXiNjEqD4gV0wYaTlBDaztRxN3Bz6wZiiUqJ5pnHqrMT1HyLF_rBg=s120-c-rp-mo-ba12-br100', 'reviews': 958, 'photos': 4098}</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Chẳng hiểu Mộc Châu làm du lịch kiểu gì mà chỗ nào cũng bắt mua vé và giá vé quá cao. Cứ một điểm tham quan là 100k/người mà chẳng có gì đặc sắc cả. Thác dải yếm có quá nhiều công trình nhân tạo. Kể cả 100k/người cho cả Thác Dải Yếm + Cầu Kính thì mình vẫn thấy đắt - không tương xứng. Đây còn vé riêng cho thác và riêng cho cầu kính mặc dù cả 2 này là cùng một điêm. Không muốn quay lại bao giờ nữa.</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2 năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>5</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 71, 'photos': 496}</t>
+          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 81, 'photos': 188}</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
+          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4 tháng trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 71, 'photos': 496}</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>4 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'reviews': 78, 'photos': 260}</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B32" t="n">
         <v>4</v>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
 Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 533, 'photos': 4107}</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 532, 'photos': 4107}</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
         <v>4</v>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 574}</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>5</v>
-      </c>
-      <c r="C32" t="inlineStr">
+      <c r="B34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>Đúng tên gọi của nó. Thác cũng rất đẹp. Nếu vào mùa nước chắc còn đẹp hơn.
 Cảnh quan cũng rất sạch đẹp.
@@ -1156,46 +1199,6 @@
 - vé vào cổng giá phù hợp</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4192}</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>5</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Thời gian chỉnh sửa: 2 năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 518}</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>5</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
-        </is>
-      </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>một năm trước</t>
@@ -1205,27 +1208,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
+          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4192}</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
+          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>Thời gian chỉnh sửa: 2 năm trước</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
+          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 518}</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1233,7 +1236,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
+          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1245,35 +1248,35 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 1623}</t>
+          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 49, 'photos': 144}</t>
+          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
+          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1285,115 +1288,196 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 1623}</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>5</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>9 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>{'name': 'ninh Men', 'link': 'https://www.google.com/maps/contrib/103025469094717120638?hl=vi', 'contributor_id': '103025469094717120638', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJr8a3WVJHmayMF2FvRRdJjmyVlo0gmvjXedEtF6z5_xuOtxg=s120-c-rp-mo-ba12-br100', 'reviews': 28, 'photos': 163}</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>4</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Đi Thác Dải Yếm đúng hôm… uống trà sữa trân châu. 😭
+Vé 150k/người nhưng cá nhân mình thấy hơi hụt hẫng. Thác không quá đặc biệt, đi một vòng là hết, chủ yếu là chụp ảnh. Nếu không thích check-in thì chắc sẽ thấy hơi “không có gì” so với giá vé.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>một tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 49, 'photos': 144}</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWyzcZkQykW_QPymZ2fTMwerDVUm-XhQ6WZ0NqbjNzbEznIxcF7AQ=s120-c-rp-mo-ba12-br100', 'reviews': 149, 'photos': 3873}</t>
         </is>
       </c>
-      <c r="B39" t="n">
-        <v>5</v>
-      </c>
-      <c r="C39" t="inlineStr">
+      <c r="B42" t="n">
+        <v>5</v>
+      </c>
+      <c r="C42" t="inlineStr">
         <is>
           <t>Thác Dải Yếm, còn được gọi là thác Nàng, thác Bản Vặt, là một thác nước hùng vĩ nằm ở xã Mường Sang, huyện Mộc Châu, tỉnh Sơn La. Thác có chiều cao khoảng 100m, chia thành hai dòng thác chính, trông giống như một dải yếm đào mềm mại uốn lượn quanh vách núi.
 Thác Dải Yếm là một địa điểm du lịch hấp dẫn, thu hút khách du lịch trong và ngoài nước. Đây là nơi du khách có thể chiêm ngưỡng vẻ đẹp hùng vĩ của thác nước và tìm hiểu về truyền thuyết về thác.</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>2 năm trước</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'reviews': 97, 'photos': 178}</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="B43" t="n">
         <v>4</v>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'reviews': 27, 'photos': 260}</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="B44" t="n">
         <v>4</v>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'reviews': 75, 'photos': 503}</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B45" t="n">
         <v>4</v>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Thác Dải Yếm nằm trên dòng suối Vặt khởi nguồn từ hai khe nước Bó Co Lắm và Bo Tá Cháu ở đầu bản Vặt, một bản của người Thái có lịch sử lâu đời. Suối Vặt chảy được 5 km đổ vào suối Bó Sập, một dòng suối lớn bắt nguồn từ bản Bó Sập giáp biên giới Việt Lào rồi chảy về đất Yên Châu. Tại nơi hợp lưu của hai suối, dòng nước gặp một vùng đá vôi và đổ xuống phía dưới tạo thành thác Dải Yếm.[5]
 Thác Dải Yếm bao gồm hai phần, thác nước phía trên rộng 70 mét, thác nước phía dưới nằm cách đó 150-200 mét. Vào mùa khô, thác phía dưới chỉ có một dòng chảy từ độ cao 50 m xuống triền đá ở dưới. hai thác đổ xuống với tổng chiều cao 100m, một bên được chia làm 9 tầng, bên còn lại 5 tầng. Cách giữa hai phần thác là một bãi đất phẳng thuận tiện cho việc tham quan của du khách. Thảm thực vật trên đỉnh thác cũng khá phong phú.</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>{'name': 'Chi Ho', 'link': 'https://www.google.com/maps/contrib/102731288821463748765?hl=vi', 'contributor_id': '102731288821463748765', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWV3y9KiqGo7jILq-ZzBkSw28LDZHnwKXBhstpTEeRvr9jffKE=s120-c-rp-mo-ba12-br100', 'reviews': 85, 'photos': 1528}</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>5</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Thác Dải Yếm đẹp và hùng vĩ, xứng đáng cho chuyến picnic cuối tuần. Đường đi hơi gập ghềnh nhưng đến nơi thì quên hết mệt mỏi. Nước mát rượi, âm thanh róc rách rất thư giãn. Tiếc là hơi đông vào cuối tuần, nhưng cảnh đẹp bù đắp tất cả! Nên đi vào ngày thường nếu muốn yên tĩnh hơn.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>một tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'reviews': 8, 'photos': 90}</t>
         </is>
       </c>
-      <c r="B43" t="n">
+      <c r="B47" t="n">
         <v>4</v>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>11 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 151, 'photos': 1281}</t>
         </is>
       </c>
-      <c r="B44" t="n">
+      <c r="B48" t="n">
         <v>4</v>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Thác nhỏ cũng đẹp nhưng được trang trí dành cho du lịch rồi về độ rộng nhiều tầng và thiên nhiên thì không bằng thác Nàng Tiên hoặc thác Chiềng Khoa.
 Thác Dải Yếm được đầu tư khang trang nhưng đi bộ từ bãi gửi xe vào thác hơi bị xa (vé gửi xe 30k), đường đi vào và khu thác bên trong nhiều khu chụp ảnh checkin được trang trí chụp ảnh đẹp mắt. Giá vé tháng 1/2024 là 80k/ người vào cổng nhưng đến 30/4/2024 tăng lên 100k/ng giá vé hơi cao với việc vào ngắm thác.
@@ -1401,49 +1485,29 @@
 - Bản thân mình cảm nhận thì cũng bình thường thác không cao không rộng dài đẹp nhiều tầng bằng thác Nàng Tiên hoặc Chiềng Khoa. Nói chung đi du lịch Mộc Châu ghé qua cho biết thôi. Chứ để quay lại thì ít khả năng.</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>2 năm trước</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 140, 'photos': 570}</t>
         </is>
       </c>
-      <c r="B45" t="n">
+      <c r="B49" t="n">
         <v>4</v>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>View đẹp, chỉ tiếc là ghé hồi tháng 5 lúc đang mùa mưa, nên không được đi trải nghiệm nhiều.</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>10 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>{'name': 'Hung Tran', 'link': 'https://www.google.com/maps/contrib/111025160790635631721?hl=vi', 'contributor_id': '111025160790635631721', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXJvHNQsMohKHo9fo2c_guCokbfqlcHTDulcTBswdAfP6GIiZRa=s120-c-rp-mo-ba12-br100', 'reviews': 120, 'photos': 1783}</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>5</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Mới đi Thác Dải Yếm mà thấy cảnh ở đây quá ấn tượng. Nước từ thác chảy xuống nhìn thôi đã mát cả mắt, mát hơn một phần do cái thời tiết mát mẻ nơi miền núi này. Đường đến thác hơi gồ ghề tí nên đi lại cẩn thận xíu nhưng được cái khung cảnh thiên nhiên trời ban, thấy cũng quá ổn. Có mấy gian hàng bán đặc sản địa phương, cứ thấy ghé thử, giá nơi này cũng dễ chịu. Mọi thứ rất thư thái, không đông đúc, thích hợp để đi vào ngày nghỉ. Thêm vài chỗ ngồi nghỉ ngơi thì tuyệt!</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>8 tháng trước</t>
         </is>
       </c>
     </row>

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -473,7 +473,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>{'name': 'Hưng Nguyễn Duy (Hưng Photo)', 'link': 'https://www.google.com/maps/contrib/110173941936897044295?hl=vi', 'contributor_id': '110173941936897044295', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXshx7xq3ntsswbv03kbw9Z9KIntVjsKdM747CeNwqebP-xH_RO=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 192, 'photos': 2169}</t>
+          <t>{'name': 'Hưng Nguyễn Duy (Hưng Photo)', 'link': 'https://www.google.com/maps/contrib/110173941936897044295?hl=vi', 'contributor_id': '110173941936897044295', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXshx7xq3ntsswbv03kbw9Z9KIntVjsKdM747CeNwqebP-xH_RO=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 191, 'photos': 2169}</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -625,7 +625,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 301, 'photos': 3603}</t>
+          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 300, 'photos': 3603}</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -785,7 +785,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7 tháng trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 250, 'photos': 4825}</t>
+          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 251, 'photos': 4970}</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>7 tháng trước</t>
         </is>
       </c>
     </row>

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2 tuần trước</t>
+          <t>3 tuần trước</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 251, 'photos': 4970}</t>
+          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 252, 'photos': 4970}</t>
         </is>
       </c>
       <c r="B26" t="n">

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,7 +520,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 368, 'photos': 2592}</t>
+          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 368, 'photos': 2605}</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -565,7 +565,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>{'name': 'THANH NGUYEN', 'link': 'https://www.google.com/maps/contrib/110418688752170937071?hl=vi', 'contributor_id': '110418688752170937071', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIBtT-SxDlGGJM5jA47OmxpGvFdaG6EOeSswcBwx4VuXgnOdQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 70, 'photos': 207}</t>
+          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 299, 'photos': 3602}</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -573,19 +573,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>thác đẹp nhưng nên đi vào mùa nước sẽ thấy sự khác biệt hơn nhiều</t>
+          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7 tháng trước</t>
+          <t>4 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>{'name': 'Cửu Quang Nguyễn', 'link': 'https://www.google.com/maps/contrib/107704339232071144994?hl=vi', 'contributor_id': '107704339232071144994', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV2_oJLqzlVCtXNV77ConxSPDhhMhFP-czjeCf6uCm7cabO88k=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 77, 'photos': 346}</t>
+          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 24}</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -593,7 +593,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm nằm trong khu du lịch sinh thái thác Dải Yếm, đường đi khá tiện lợi để ghé vào, tuy nhiên cần chú ý lối vào có khúc cua dốc khá ngoặt. Vé vào là 150k/người, bên trong có khá nhiều vị trí để du ngoạn và ngắm cảnh, đặc biệt là khu vực thác nước rất hùng vĩ và mát mẻ, có cầu dẫn vào nhìn rất thơ mộng và tuyệt vời. Nếu có dịp ghé lên Mộc Châu thì nên ghé vào đây chơi 1 lần để du ngoạn thắng cảnh thiên nhiên tại nơi đây.</t>
+          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -605,135 +605,75 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Anh Quân', 'link': 'https://www.google.com/maps/contrib/111631093743063403454?hl=vi', 'contributor_id': '111631093743063403454', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIy-NjGEZ7ggp1yhLvVSe2iSDFAUAF4AILlK1IHBmSbkPzlKg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 9, 'photos': 24}</t>
+          <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'reviews': 16, 'photos': 114}</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>5</v>
       </c>
       <c r="C9" t="inlineStr">
-        <is>
-          <t>Cảnh đẹp, nhưng xu là đi ngay lúc mưa nên thác có nước như cf</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>một tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 300, 'photos': 3603}</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>4 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 24}</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>5 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'reviews': 16, 'photos': 114}</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" t="inlineStr">
         <is>
           <t>Đi tầm trưa nắng đẹp
 Thác nhỏ, đi cũng không mất quá nhiều thời gian
 Có cầu kính</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>6 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>{'name': 'Nghĩa Nguyễn Trung', 'link': 'https://www.google.com/maps/contrib/107253778101970197900?hl=vi', 'contributor_id': '107253778101970197900', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUNLHg5XlpgtWVVTp_oJKOYAejqmQORtgQ_Oe2vusE5W_sQoZc5=s120-c-rp-mo-ba12-br100', 'reviews': 275, 'photos': 1279}</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>Khu vực thác nước đẹp, nhiều cảnh quan, nhiều góc chụp đẹp.</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>2 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>{'name': 'Frugal Flow', 'link': 'https://www.google.com/maps/contrib/107453311426556875441?hl=vi', 'contributor_id': '107453311426556875441', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUspWRVGEEQ_LyS16qRB57xWZ-kgNRIjgdLPY8T7HzvNMFlILCV=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 85}</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>Đi vào một ngày nắng. Nắng hắt lên mặt nước long lanh nên xinh xắn hẳn:&gt; Chỉ là thác nay có vẻ hơi ít nc nên không như mình tưởng tượng.</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>6 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'reviews': 219, 'photos': 308}</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B12" t="n">
         <v>3</v>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Trải nghiệm vừa phải
 Giá vé theo trải nghiệm đi nhiều thác khác nhau của mình thì là khá cao so với các nơi khác, mình đi vào dịp tết nên thác ít nước.
@@ -741,64 +681,64 @@
 Cá nhân nếu quay lại Mộc Châu sẽ không đến thác này lần nào nữa</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>{'name': 'La Meu', 'link': 'https://www.google.com/maps/contrib/108858956358165703026?hl=vi', 'contributor_id': '108858956358165703026', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVKW-aZD0iBs1KBFQlmzfMiMTfjpd4PfUn4GO-K2tEt1PLpZ3YY=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 117}</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>5</v>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Thác Dải Yếm là điểm du lịch rất đáng đi. Đường đi dễ, xe máy hay ô tô đều thuận tiện. Không gian mát mẻ, thiên nhiên đẹp và trong lành.
 Nước thác xanh biếc, chảy mạnh nhưng nhìn rất êm và thơ mộng, chụp hình lên đẹp lắm. Khu vực được làm lối đi khá an toàn, dễ tham quan.
 Nhân viên ở đây dễ thương, nhiệt tình, hướng dẫn khách rất chu đáo và thân thiện. Phù hợp đi chơi cùng gia đình hoặc bạn bè để thư giãn, nghỉ ngơi.</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>9 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'reviews': 24, 'photos': 255}</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>5</v>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>{'name': 'Thái Nguyễn', 'link': 'https://www.google.com/maps/contrib/105517365260915933657?hl=vi', 'contributor_id': '105517365260915933657', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXLOkY3FUSH3Mz-aapJXPQUgoCFlQP20PICWZGzVI3cPkRkBIt_ew=s120-c-rp-mo-ba12-br100', 'reviews': 65, 'photos': 175}</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>5</v>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Nếu đi cùng Lover sẽ đẹp hơn.
 Nếu tự nhìn lại
@@ -866,56 +806,116 @@
 Hơn cả tới thiên đường</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 1090}</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 143, 'photos': 325}</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
+          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
+          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 1090}</t>
+          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
+          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 143, 'photos': 325}</t>
+          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 115, 'photos': 84}</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -923,59 +923,59 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
+          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
+          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 3220}</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
+          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2 tháng trước</t>
+          <t>10 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
+          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 252, 'photos': 5011}</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
+          <t>Cảnh quan đẹp, ng dân thân thiện</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2 tháng trước</t>
+          <t>5 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 115, 'photos': 84}</t>
+          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -983,7 +983,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
+          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -995,73 +995,13 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 3220}</t>
+          <t>{'name': 'Linh Nguyễn', 'link': 'https://www.google.com/maps/contrib/109820275513447282944?hl=vi', 'contributor_id': '109820275513447282944', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVpZ-SNyOn6byhXW5cnkMUzIYl8pLeo3scME3-VG4n2ps2S2tYx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 992}</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" t="inlineStr">
-        <is>
-          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>9 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 252, 'photos': 4970}</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>5</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Cảnh quan đẹp, ng dân thân thiện</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>5 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>5</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>8 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>{'name': 'Linh Nguyễn', 'link': 'https://www.google.com/maps/contrib/109820275513447282944?hl=vi', 'contributor_id': '109820275513447282944', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVpZ-SNyOn6byhXW5cnkMUzIYl8pLeo3scME3-VG4n2ps2S2tYx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 992}</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>5</v>
-      </c>
-      <c r="C28" t="inlineStr">
         <is>
           <t>Thác đẹp, suối nước tự nhiên, đường đi dọc suối sạch sẽ
 Một số địa điểm du lịch ở Mộc Châu mọi người có thể tham khảo
@@ -1074,16 +1014,76 @@
 2. Cá Hồi Thanh Bảy</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 81, 'photos': 188}</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>7 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 71, 'photos': 496}</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2 năm trước</t>
+          <t>4 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 81, 'photos': 188}</t>
+          <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'reviews': 78, 'photos': 260}</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1091,27 +1091,28 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
+          <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
+Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
+          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 532, 'photos': 4109}</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
+          <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1123,74 +1124,13 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 71, 'photos': 496}</t>
+          <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 574}</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>5</v>
       </c>
       <c r="C31" t="inlineStr">
-        <is>
-          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>4 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'reviews': 78, 'photos': 260}</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>4</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
-Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 532, 'photos': 4107}</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>4</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 574}</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>5</v>
-      </c>
-      <c r="C34" t="inlineStr">
         <is>
           <t>Đúng tên gọi của nó. Thác cũng rất đẹp. Nếu vào mùa nước chắc còn đẹp hơn.
 Cảnh quan cũng rất sạch đẹp.
@@ -1199,6 +1139,66 @@
 - vé vào cổng giá phù hợp</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4192}</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Thời gian chỉnh sửa: 2 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 518}</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>một năm trước</t>
@@ -1208,7 +1208,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4192}</t>
+          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1216,19 +1216,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
+          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Thời gian chỉnh sửa: 2 năm trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 518}</t>
+          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 1623}</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1236,19 +1236,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
+          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>9 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
+          <t>{'name': 'ninh Men', 'link': 'https://www.google.com/maps/contrib/103025469094717120638?hl=vi', 'contributor_id': '103025469094717120638', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJr8a3WVJHmayMF2FvRRdJjmyVlo0gmvjXedEtF6z5_xuOtxg=s120-c-rp-mo-ba12-br100', 'reviews': 28, 'photos': 163}</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1256,27 +1256,28 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
+          <t>Đi Thác Dải Yếm đúng hôm… uống trà sữa trân châu. 😭
+Vé 150k/người nhưng cá nhân mình thấy hơi hụt hẫng. Thác không quá đặc biệt, đi một vòng là hết, chủ yếu là chụp ảnh. Nếu không thích check-in thì chắc sẽ thấy hơi “không có gì” so với giá vé.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>một tháng trước</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
+          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 49, 'photos': 144}</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
+          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1288,7 +1289,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 1623}</t>
+          <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWyzcZkQykW_QPymZ2fTMwerDVUm-XhQ6WZ0NqbjNzbEznIxcF7AQ=s120-c-rp-mo-ba12-br100', 'reviews': 149, 'photos': 3873}</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1296,19 +1297,20 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+          <t>Thác Dải Yếm, còn được gọi là thác Nàng, thác Bản Vặt, là một thác nước hùng vĩ nằm ở xã Mường Sang, huyện Mộc Châu, tỉnh Sơn La. Thác có chiều cao khoảng 100m, chia thành hai dòng thác chính, trông giống như một dải yếm đào mềm mại uốn lượn quanh vách núi.
+Thác Dải Yếm là một địa điểm du lịch hấp dẫn, thu hút khách du lịch trong và ngoài nước. Đây là nơi du khách có thể chiêm ngưỡng vẻ đẹp hùng vĩ của thác nước và tìm hiểu về truyền thuyết về thác.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>2 năm trước</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>{'name': 'ninh Men', 'link': 'https://www.google.com/maps/contrib/103025469094717120638?hl=vi', 'contributor_id': '103025469094717120638', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJr8a3WVJHmayMF2FvRRdJjmyVlo0gmvjXedEtF6z5_xuOtxg=s120-c-rp-mo-ba12-br100', 'reviews': 28, 'photos': 163}</t>
+          <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'reviews': 97, 'photos': 178}</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1316,20 +1318,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Đi Thác Dải Yếm đúng hôm… uống trà sữa trân châu. 😭
-Vé 150k/người nhưng cá nhân mình thấy hơi hụt hẫng. Thác không quá đặc biệt, đi một vòng là hết, chủ yếu là chụp ảnh. Nếu không thích check-in thì chắc sẽ thấy hơi “không có gì” so với giá vé.</t>
+          <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>một tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 49, 'photos': 144}</t>
+          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'reviews': 27, 'photos': 260}</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1337,7 +1338,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
+          <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1349,48 +1350,48 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWyzcZkQykW_QPymZ2fTMwerDVUm-XhQ6WZ0NqbjNzbEznIxcF7AQ=s120-c-rp-mo-ba12-br100', 'reviews': 149, 'photos': 3873}</t>
+          <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'reviews': 75, 'photos': 503}</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm, còn được gọi là thác Nàng, thác Bản Vặt, là một thác nước hùng vĩ nằm ở xã Mường Sang, huyện Mộc Châu, tỉnh Sơn La. Thác có chiều cao khoảng 100m, chia thành hai dòng thác chính, trông giống như một dải yếm đào mềm mại uốn lượn quanh vách núi.
-Thác Dải Yếm là một địa điểm du lịch hấp dẫn, thu hút khách du lịch trong và ngoài nước. Đây là nơi du khách có thể chiêm ngưỡng vẻ đẹp hùng vĩ của thác nước và tìm hiểu về truyền thuyết về thác.</t>
+          <t>Thác Dải Yếm nằm trên dòng suối Vặt khởi nguồn từ hai khe nước Bó Co Lắm và Bo Tá Cháu ở đầu bản Vặt, một bản của người Thái có lịch sử lâu đời. Suối Vặt chảy được 5 km đổ vào suối Bó Sập, một dòng suối lớn bắt nguồn từ bản Bó Sập giáp biên giới Việt Lào rồi chảy về đất Yên Châu. Tại nơi hợp lưu của hai suối, dòng nước gặp một vùng đá vôi và đổ xuống phía dưới tạo thành thác Dải Yếm.[5]
+Thác Dải Yếm bao gồm hai phần, thác nước phía trên rộng 70 mét, thác nước phía dưới nằm cách đó 150-200 mét. Vào mùa khô, thác phía dưới chỉ có một dòng chảy từ độ cao 50 m xuống triền đá ở dưới. hai thác đổ xuống với tổng chiều cao 100m, một bên được chia làm 9 tầng, bên còn lại 5 tầng. Cách giữa hai phần thác là một bãi đất phẳng thuận tiện cho việc tham quan của du khách. Thảm thực vật trên đỉnh thác cũng khá phong phú.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2 năm trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'reviews': 97, 'photos': 178}</t>
+          <t>{'name': 'Chi Ho', 'link': 'https://www.google.com/maps/contrib/102731288821463748765?hl=vi', 'contributor_id': '102731288821463748765', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWV3y9KiqGo7jILq-ZzBkSw28LDZHnwKXBhstpTEeRvr9jffKE=s120-c-rp-mo-ba12-br100', 'reviews': 85, 'photos': 1528}</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
+          <t>Thác Dải Yếm đẹp và hùng vĩ, xứng đáng cho chuyến picnic cuối tuần. Đường đi hơi gập ghềnh nhưng đến nơi thì quên hết mệt mỏi. Nước mát rượi, âm thanh róc rách rất thư giãn. Tiếc là hơi đông vào cuối tuần, nhưng cảnh đẹp bù đắp tất cả! Nên đi vào ngày thường nếu muốn yên tĩnh hơn.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>một tháng trước</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'reviews': 27, 'photos': 260}</t>
+          <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'reviews': 8, 'photos': 90}</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1398,86 +1399,25 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
+          <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>11 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'reviews': 75, 'photos': 503}</t>
+          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 151, 'photos': 1281}</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>4</v>
       </c>
       <c r="C45" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm nằm trên dòng suối Vặt khởi nguồn từ hai khe nước Bó Co Lắm và Bo Tá Cháu ở đầu bản Vặt, một bản của người Thái có lịch sử lâu đời. Suối Vặt chảy được 5 km đổ vào suối Bó Sập, một dòng suối lớn bắt nguồn từ bản Bó Sập giáp biên giới Việt Lào rồi chảy về đất Yên Châu. Tại nơi hợp lưu của hai suối, dòng nước gặp một vùng đá vôi và đổ xuống phía dưới tạo thành thác Dải Yếm.[5]
-Thác Dải Yếm bao gồm hai phần, thác nước phía trên rộng 70 mét, thác nước phía dưới nằm cách đó 150-200 mét. Vào mùa khô, thác phía dưới chỉ có một dòng chảy từ độ cao 50 m xuống triền đá ở dưới. hai thác đổ xuống với tổng chiều cao 100m, một bên được chia làm 9 tầng, bên còn lại 5 tầng. Cách giữa hai phần thác là một bãi đất phẳng thuận tiện cho việc tham quan của du khách. Thảm thực vật trên đỉnh thác cũng khá phong phú.</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>{'name': 'Chi Ho', 'link': 'https://www.google.com/maps/contrib/102731288821463748765?hl=vi', 'contributor_id': '102731288821463748765', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWV3y9KiqGo7jILq-ZzBkSw28LDZHnwKXBhstpTEeRvr9jffKE=s120-c-rp-mo-ba12-br100', 'reviews': 85, 'photos': 1528}</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>5</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm đẹp và hùng vĩ, xứng đáng cho chuyến picnic cuối tuần. Đường đi hơi gập ghềnh nhưng đến nơi thì quên hết mệt mỏi. Nước mát rượi, âm thanh róc rách rất thư giãn. Tiếc là hơi đông vào cuối tuần, nhưng cảnh đẹp bù đắp tất cả! Nên đi vào ngày thường nếu muốn yên tĩnh hơn.</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>một tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'reviews': 8, 'photos': 90}</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>4</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>11 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 151, 'photos': 1281}</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>4</v>
-      </c>
-      <c r="C48" t="inlineStr">
         <is>
           <t>Thác nhỏ cũng đẹp nhưng được trang trí dành cho du lịch rồi về độ rộng nhiều tầng và thiên nhiên thì không bằng thác Nàng Tiên hoặc thác Chiềng Khoa.
 Thác Dải Yếm được đầu tư khang trang nhưng đi bộ từ bãi gửi xe vào thác hơi bị xa (vé gửi xe 30k), đường đi vào và khu thác bên trong nhiều khu chụp ảnh checkin được trang trí chụp ảnh đẹp mắt. Giá vé tháng 1/2024 là 80k/ người vào cổng nhưng đến 30/4/2024 tăng lên 100k/ng giá vé hơi cao với việc vào ngắm thác.
@@ -1485,27 +1425,27 @@
 - Bản thân mình cảm nhận thì cũng bình thường thác không cao không rộng dài đẹp nhiều tầng bằng thác Nàng Tiên hoặc Chiềng Khoa. Nói chung đi du lịch Mộc Châu ghé qua cho biết thôi. Chứ để quay lại thì ít khả năng.</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>2 năm trước</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 140, 'photos': 570}</t>
         </is>
       </c>
-      <c r="B49" t="n">
+      <c r="B46" t="n">
         <v>4</v>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>View đẹp, chỉ tiếc là ghé hồi tháng 5 lúc đang mùa mưa, nên không được đi trải nghiệm nhiều.</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>10 tháng trước</t>
         </is>

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -565,7 +565,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 299, 'photos': 3602}</t>
+          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 300, 'photos': 3602}</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -835,7 +835,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 1090}</t>
+          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 1080}</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -908,7 +908,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2 tháng trước</t>
+          <t>3 tháng trước</t>
         </is>
       </c>
     </row>
@@ -955,7 +955,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 252, 'photos': 5011}</t>
+          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 252, 'photos': 5006}</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -988,7 +988,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>9 tháng trước</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 532, 'photos': 4109}</t>
+          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 533, 'photos': 4109}</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1434,7 +1434,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 140, 'photos': 570}</t>
+          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 140, 'photos': 563}</t>
         </is>
       </c>
       <c r="B46" t="n">

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -520,7 +520,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 368, 'photos': 2605}</t>
+          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 368, 'photos': 2608}</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -565,7 +565,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 300, 'photos': 3602}</t>
+          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 299, 'photos': 3602}</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -620,7 +620,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'reviews': 219, 'photos': 308}</t>
+          <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'reviews': 219, 'photos': 307}</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -835,7 +835,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 1080}</t>
+          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 90, 'photos': 1080}</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -935,7 +935,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 3220}</t>
+          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 3220}</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1063,7 +1063,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 71, 'photos': 496}</t>
+          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 72, 'photos': 496}</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1104,7 +1104,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 533, 'photos': 4109}</t>
+          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 532, 'photos': 4109}</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1248,7 +1248,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>{'name': 'ninh Men', 'link': 'https://www.google.com/maps/contrib/103025469094717120638?hl=vi', 'contributor_id': '103025469094717120638', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJr8a3WVJHmayMF2FvRRdJjmyVlo0gmvjXedEtF6z5_xuOtxg=s120-c-rp-mo-ba12-br100', 'reviews': 28, 'photos': 163}</t>
+          <t>{'name': 'ninh Men', 'link': 'https://www.google.com/maps/contrib/103025469094717120638?hl=vi', 'contributor_id': '103025469094717120638', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJr8a3WVJHmayMF2FvRRdJjmyVlo0gmvjXedEtF6z5_xuOtxg=s120-c-rp-mo-ba12-br100', 'reviews': 29, 'photos': 163}</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1434,7 +1434,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 140, 'photos': 563}</t>
+          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 138, 'photos': 564}</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>10 tháng trước</t>
+          <t>11 tháng trước</t>
         </is>
       </c>
     </row>

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,7 +520,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 368, 'photos': 2608}</t>
+          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 369, 'photos': 2614}</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -565,7 +565,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 299, 'photos': 3602}</t>
+          <t>{'name': 'THANH NGUYEN', 'link': 'https://www.google.com/maps/contrib/110418688752170937071?hl=vi', 'contributor_id': '110418688752170937071', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIBtT-SxDlGGJM5jA47OmxpGvFdaG6EOeSswcBwx4VuXgnOdQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 70, 'photos': 207}</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -573,19 +573,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
+          <t>thác đẹp nhưng nên đi vào mùa nước sẽ thấy sự khác biệt hơn nhiều</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4 tháng trước</t>
+          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 24}</t>
+          <t>{'name': 'Cửu Quang Nguyễn', 'link': 'https://www.google.com/maps/contrib/107704339232071144994?hl=vi', 'contributor_id': '107704339232071144994', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV2_oJLqzlVCtXNV77ConxSPDhhMhFP-czjeCf6uCm7cabO88k=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 77, 'photos': 349}</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -593,7 +593,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
+          <t>Thác Dải Yếm nằm trong khu du lịch sinh thái thác Dải Yếm, đường đi khá tiện lợi để ghé vào, tuy nhiên cần chú ý lối vào có khúc cua dốc khá ngoặt. Vé vào là 150k/người, bên trong có khá nhiều vị trí để du ngoạn và ngắm cảnh, đặc biệt là khu vực thác nước rất hùng vĩ và mát mẻ, có cầu dẫn vào nhìn rất thơ mộng và tuyệt vời. Nếu có dịp ghé lên Mộc Châu thì nên ghé vào đây chơi 1 lần để du ngoạn thắng cảnh thiên nhiên tại nơi đây.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -605,75 +605,135 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>{'name': 'Nguyễn Anh Quân', 'link': 'https://www.google.com/maps/contrib/111631093743063403454?hl=vi', 'contributor_id': '111631093743063403454', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIy-NjGEZ7ggp1yhLvVSe2iSDFAUAF4AILlK1IHBmSbkPzlKg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 9, 'photos': 24}</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Cảnh đẹp, nhưng xu là đi ngay lúc mưa nên thác có nước như cf</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>một tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 299, 'photos': 3602}</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>4 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 25}</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>5 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'reviews': 16, 'photos': 114}</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Đi tầm trưa nắng đẹp
 Thác nhỏ, đi cũng không mất quá nhiều thời gian
 Có cầu kính</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>{'name': 'Nghĩa Nguyễn Trung', 'link': 'https://www.google.com/maps/contrib/107253778101970197900?hl=vi', 'contributor_id': '107253778101970197900', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUNLHg5XlpgtWVVTp_oJKOYAejqmQORtgQ_Oe2vusE5W_sQoZc5=s120-c-rp-mo-ba12-br100', 'reviews': 275, 'photos': 1279}</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Khu vực thác nước đẹp, nhiều cảnh quan, nhiều góc chụp đẹp.</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>2 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>{'name': 'Frugal Flow', 'link': 'https://www.google.com/maps/contrib/107453311426556875441?hl=vi', 'contributor_id': '107453311426556875441', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUspWRVGEEQ_LyS16qRB57xWZ-kgNRIjgdLPY8T7HzvNMFlILCV=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 85}</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Đi vào một ngày nắng. Nắng hắt lên mặt nước long lanh nên xinh xắn hẳn:&gt; Chỉ là thác nay có vẻ hơi ít nc nên không như mình tưởng tượng.</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>6 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'reviews': 219, 'photos': 307}</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B15" t="n">
         <v>3</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Trải nghiệm vừa phải
 Giá vé theo trải nghiệm đi nhiều thác khác nhau của mình thì là khá cao so với các nơi khác, mình đi vào dịp tết nên thác ít nước.
@@ -681,64 +741,64 @@
 Cá nhân nếu quay lại Mộc Châu sẽ không đến thác này lần nào nữa</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>{'name': 'La Meu', 'link': 'https://www.google.com/maps/contrib/108858956358165703026?hl=vi', 'contributor_id': '108858956358165703026', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVKW-aZD0iBs1KBFQlmzfMiMTfjpd4PfUn4GO-K2tEt1PLpZ3YY=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 117}</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>Thác Dải Yếm là điểm du lịch rất đáng đi. Đường đi dễ, xe máy hay ô tô đều thuận tiện. Không gian mát mẻ, thiên nhiên đẹp và trong lành.
 Nước thác xanh biếc, chảy mạnh nhưng nhìn rất êm và thơ mộng, chụp hình lên đẹp lắm. Khu vực được làm lối đi khá an toàn, dễ tham quan.
 Nhân viên ở đây dễ thương, nhiệt tình, hướng dẫn khách rất chu đáo và thân thiện. Phù hợp đi chơi cùng gia đình hoặc bạn bè để thư giãn, nghỉ ngơi.</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>9 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'reviews': 24, 'photos': 255}</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>{'name': 'Thái Nguyễn', 'link': 'https://www.google.com/maps/contrib/105517365260915933657?hl=vi', 'contributor_id': '105517365260915933657', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXLOkY3FUSH3Mz-aapJXPQUgoCFlQP20PICWZGzVI3cPkRkBIt_ew=s120-c-rp-mo-ba12-br100', 'reviews': 65, 'photos': 175}</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>5</v>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>Nếu đi cùng Lover sẽ đẹp hơn.
 Nếu tự nhìn lại
@@ -806,116 +866,56 @@
 Hơn cả tới thiên đường</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>8 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>8 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 90, 'photos': 1080}</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>5</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 143, 'photos': 325}</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>5</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
+          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
+          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2 tháng trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
+          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 90, 'photos': 1080}</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
+          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 115, 'photos': 84}</t>
+          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 143, 'photos': 325}</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -923,59 +923,59 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
+          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 3220}</t>
+          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
+          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10 tháng trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 252, 'photos': 5006}</t>
+          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cảnh quan đẹp, ng dân thân thiện</t>
+          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5 tháng trước</t>
+          <t>3 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
+          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 115, 'photos': 84}</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -983,25 +983,85 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
+          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 3220}</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>10 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 251, 'photos': 5006}</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Cảnh quan đẹp, ng dân thân thiện</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>5 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>9 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>{'name': 'Linh Nguyễn', 'link': 'https://www.google.com/maps/contrib/109820275513447282944?hl=vi', 'contributor_id': '109820275513447282944', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVpZ-SNyOn6byhXW5cnkMUzIYl8pLeo3scME3-VG4n2ps2S2tYx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 992}</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>5</v>
-      </c>
-      <c r="C25" t="inlineStr">
+      <c r="B28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>Thác đẹp, suối nước tự nhiên, đường đi dọc suối sạch sẽ
 Một số địa điểm du lịch ở Mộc Châu mọi người có thể tham khảo
@@ -1014,76 +1074,16 @@
 2. Cá Hồi Thanh Bảy</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>2 năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 81, 'photos': 188}</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>4</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>7 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>5</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 72, 'photos': 496}</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>5</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>4 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'reviews': 78, 'photos': 260}</t>
+          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 81, 'photos': 188}</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1091,46 +1091,106 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>7 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 72, 'photos': 501}</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>4 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'reviews': 78, 'photos': 260}</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
 Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 532, 'photos': 4109}</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B33" t="n">
         <v>4</v>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 574}</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>5</v>
-      </c>
-      <c r="C31" t="inlineStr">
+      <c r="B34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>Đúng tên gọi của nó. Thác cũng rất đẹp. Nếu vào mùa nước chắc còn đẹp hơn.
 Cảnh quan cũng rất sạch đẹp.
@@ -1139,66 +1199,6 @@
 - vé vào cổng giá phù hợp</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4192}</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>5</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Thời gian chỉnh sửa: 2 năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 518}</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>5</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>4</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
-        </is>
-      </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>một năm trước</t>
@@ -1208,7 +1208,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
+          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4192}</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1216,19 +1216,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
+          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>Thời gian chỉnh sửa: 2 năm trước</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 1623}</t>
+          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 518}</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1236,19 +1236,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>{'name': 'ninh Men', 'link': 'https://www.google.com/maps/contrib/103025469094717120638?hl=vi', 'contributor_id': '103025469094717120638', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJr8a3WVJHmayMF2FvRRdJjmyVlo0gmvjXedEtF6z5_xuOtxg=s120-c-rp-mo-ba12-br100', 'reviews': 29, 'photos': 163}</t>
+          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1256,168 +1256,228 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>5</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 1623}</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>5</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>9 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>{'name': 'ninh Men', 'link': 'https://www.google.com/maps/contrib/103025469094717120638?hl=vi', 'contributor_id': '103025469094717120638', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJr8a3WVJHmayMF2FvRRdJjmyVlo0gmvjXedEtF6z5_xuOtxg=s120-c-rp-mo-ba12-br100', 'reviews': 29, 'photos': 168}</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>4</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
           <t>Đi Thác Dải Yếm đúng hôm… uống trà sữa trân châu. 😭
 Vé 150k/người nhưng cá nhân mình thấy hơi hụt hẫng. Thác không quá đặc biệt, đi một vòng là hết, chủ yếu là chụp ảnh. Nếu không thích check-in thì chắc sẽ thấy hơi “không có gì” so với giá vé.</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>một tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 49, 'photos': 144}</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B41" t="n">
         <v>4</v>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWyzcZkQykW_QPymZ2fTMwerDVUm-XhQ6WZ0NqbjNzbEznIxcF7AQ=s120-c-rp-mo-ba12-br100', 'reviews': 149, 'photos': 3873}</t>
         </is>
       </c>
-      <c r="B39" t="n">
-        <v>5</v>
-      </c>
-      <c r="C39" t="inlineStr">
+      <c r="B42" t="n">
+        <v>5</v>
+      </c>
+      <c r="C42" t="inlineStr">
         <is>
           <t>Thác Dải Yếm, còn được gọi là thác Nàng, thác Bản Vặt, là một thác nước hùng vĩ nằm ở xã Mường Sang, huyện Mộc Châu, tỉnh Sơn La. Thác có chiều cao khoảng 100m, chia thành hai dòng thác chính, trông giống như một dải yếm đào mềm mại uốn lượn quanh vách núi.
 Thác Dải Yếm là một địa điểm du lịch hấp dẫn, thu hút khách du lịch trong và ngoài nước. Đây là nơi du khách có thể chiêm ngưỡng vẻ đẹp hùng vĩ của thác nước và tìm hiểu về truyền thuyết về thác.</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>2 năm trước</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'reviews': 97, 'photos': 178}</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="B43" t="n">
         <v>4</v>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'reviews': 27, 'photos': 260}</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="B44" t="n">
         <v>4</v>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'reviews': 75, 'photos': 503}</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B45" t="n">
         <v>4</v>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Thác Dải Yếm nằm trên dòng suối Vặt khởi nguồn từ hai khe nước Bó Co Lắm và Bo Tá Cháu ở đầu bản Vặt, một bản của người Thái có lịch sử lâu đời. Suối Vặt chảy được 5 km đổ vào suối Bó Sập, một dòng suối lớn bắt nguồn từ bản Bó Sập giáp biên giới Việt Lào rồi chảy về đất Yên Châu. Tại nơi hợp lưu của hai suối, dòng nước gặp một vùng đá vôi và đổ xuống phía dưới tạo thành thác Dải Yếm.[5]
 Thác Dải Yếm bao gồm hai phần, thác nước phía trên rộng 70 mét, thác nước phía dưới nằm cách đó 150-200 mét. Vào mùa khô, thác phía dưới chỉ có một dòng chảy từ độ cao 50 m xuống triền đá ở dưới. hai thác đổ xuống với tổng chiều cao 100m, một bên được chia làm 9 tầng, bên còn lại 5 tầng. Cách giữa hai phần thác là một bãi đất phẳng thuận tiện cho việc tham quan của du khách. Thảm thực vật trên đỉnh thác cũng khá phong phú.</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>{'name': 'Chi Ho', 'link': 'https://www.google.com/maps/contrib/102731288821463748765?hl=vi', 'contributor_id': '102731288821463748765', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWV3y9KiqGo7jILq-ZzBkSw28LDZHnwKXBhstpTEeRvr9jffKE=s120-c-rp-mo-ba12-br100', 'reviews': 85, 'photos': 1528}</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>5</v>
-      </c>
-      <c r="C43" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>{'name': 'Chi Ho', 'link': 'https://www.google.com/maps/contrib/102731288821463748765?hl=vi', 'contributor_id': '102731288821463748765', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWV3y9KiqGo7jILq-ZzBkSw28LDZHnwKXBhstpTEeRvr9jffKE=s120-c-rp-mo-ba12-br100', 'reviews': 85, 'photos': 1540}</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>5</v>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>Thác Dải Yếm đẹp và hùng vĩ, xứng đáng cho chuyến picnic cuối tuần. Đường đi hơi gập ghềnh nhưng đến nơi thì quên hết mệt mỏi. Nước mát rượi, âm thanh róc rách rất thư giãn. Tiếc là hơi đông vào cuối tuần, nhưng cảnh đẹp bù đắp tất cả! Nên đi vào ngày thường nếu muốn yên tĩnh hơn.</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>một tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'reviews': 8, 'photos': 90}</t>
         </is>
       </c>
-      <c r="B44" t="n">
+      <c r="B47" t="n">
         <v>4</v>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>11 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 151, 'photos': 1281}</t>
         </is>
       </c>
-      <c r="B45" t="n">
+      <c r="B48" t="n">
         <v>4</v>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Thác nhỏ cũng đẹp nhưng được trang trí dành cho du lịch rồi về độ rộng nhiều tầng và thiên nhiên thì không bằng thác Nàng Tiên hoặc thác Chiềng Khoa.
 Thác Dải Yếm được đầu tư khang trang nhưng đi bộ từ bãi gửi xe vào thác hơi bị xa (vé gửi xe 30k), đường đi vào và khu thác bên trong nhiều khu chụp ảnh checkin được trang trí chụp ảnh đẹp mắt. Giá vé tháng 1/2024 là 80k/ người vào cổng nhưng đến 30/4/2024 tăng lên 100k/ng giá vé hơi cao với việc vào ngắm thác.
@@ -1425,27 +1485,27 @@
 - Bản thân mình cảm nhận thì cũng bình thường thác không cao không rộng dài đẹp nhiều tầng bằng thác Nàng Tiên hoặc Chiềng Khoa. Nói chung đi du lịch Mộc Châu ghé qua cho biết thôi. Chứ để quay lại thì ít khả năng.</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>2 năm trước</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 138, 'photos': 564}</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 139, 'photos': 564}</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
         <v>4</v>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>View đẹp, chỉ tiếc là ghé hồi tháng 5 lúc đang mùa mưa, nên không được đi trải nghiệm nhiều.</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>11 tháng trước</t>
         </is>

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,7 +520,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 369, 'photos': 2614}</t>
+          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 369, 'photos': 2632}</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -565,7 +565,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>{'name': 'THANH NGUYEN', 'link': 'https://www.google.com/maps/contrib/110418688752170937071?hl=vi', 'contributor_id': '110418688752170937071', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIBtT-SxDlGGJM5jA47OmxpGvFdaG6EOeSswcBwx4VuXgnOdQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 70, 'photos': 207}</t>
+          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 299, 'photos': 3605}</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -573,19 +573,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>thác đẹp nhưng nên đi vào mùa nước sẽ thấy sự khác biệt hơn nhiều</t>
+          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7 tháng trước</t>
+          <t>4 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>{'name': 'Cửu Quang Nguyễn', 'link': 'https://www.google.com/maps/contrib/107704339232071144994?hl=vi', 'contributor_id': '107704339232071144994', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV2_oJLqzlVCtXNV77ConxSPDhhMhFP-czjeCf6uCm7cabO88k=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 77, 'photos': 349}</t>
+          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 25}</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -593,147 +593,87 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm nằm trong khu du lịch sinh thái thác Dải Yếm, đường đi khá tiện lợi để ghé vào, tuy nhiên cần chú ý lối vào có khúc cua dốc khá ngoặt. Vé vào là 150k/người, bên trong có khá nhiều vị trí để du ngoạn và ngắm cảnh, đặc biệt là khu vực thác nước rất hùng vĩ và mát mẻ, có cầu dẫn vào nhìn rất thơ mộng và tuyệt vời. Nếu có dịp ghé lên Mộc Châu thì nên ghé vào đây chơi 1 lần để du ngoạn thắng cảnh thiên nhiên tại nơi đây.</t>
+          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5 tháng trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Anh Quân', 'link': 'https://www.google.com/maps/contrib/111631093743063403454?hl=vi', 'contributor_id': '111631093743063403454', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIy-NjGEZ7ggp1yhLvVSe2iSDFAUAF4AILlK1IHBmSbkPzlKg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 9, 'photos': 24}</t>
+          <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'reviews': 16, 'photos': 114}</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>5</v>
       </c>
       <c r="C9" t="inlineStr">
-        <is>
-          <t>Cảnh đẹp, nhưng xu là đi ngay lúc mưa nên thác có nước như cf</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>một tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 299, 'photos': 3602}</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>4 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 25}</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>5 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'reviews': 16, 'photos': 114}</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" t="inlineStr">
         <is>
           <t>Đi tầm trưa nắng đẹp
 Thác nhỏ, đi cũng không mất quá nhiều thời gian
 Có cầu kính</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>{'name': 'Nghĩa Nguyễn Trung', 'link': 'https://www.google.com/maps/contrib/107253778101970197900?hl=vi', 'contributor_id': '107253778101970197900', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUNLHg5XlpgtWVVTp_oJKOYAejqmQORtgQ_Oe2vusE5W_sQoZc5=s120-c-rp-mo-ba12-br100', 'reviews': 275, 'photos': 1279}</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>Khu vực thác nước đẹp, nhiều cảnh quan, nhiều góc chụp đẹp.</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>2 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>{'name': 'Frugal Flow', 'link': 'https://www.google.com/maps/contrib/107453311426556875441?hl=vi', 'contributor_id': '107453311426556875441', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUspWRVGEEQ_LyS16qRB57xWZ-kgNRIjgdLPY8T7HzvNMFlILCV=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 85}</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>Đi vào một ngày nắng. Nắng hắt lên mặt nước long lanh nên xinh xắn hẳn:&gt; Chỉ là thác nay có vẻ hơi ít nc nên không như mình tưởng tượng.</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>6 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'reviews': 219, 'photos': 307}</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B12" t="n">
         <v>3</v>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Trải nghiệm vừa phải
 Giá vé theo trải nghiệm đi nhiều thác khác nhau của mình thì là khá cao so với các nơi khác, mình đi vào dịp tết nên thác ít nước.
@@ -741,64 +681,64 @@
 Cá nhân nếu quay lại Mộc Châu sẽ không đến thác này lần nào nữa</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>{'name': 'La Meu', 'link': 'https://www.google.com/maps/contrib/108858956358165703026?hl=vi', 'contributor_id': '108858956358165703026', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVKW-aZD0iBs1KBFQlmzfMiMTfjpd4PfUn4GO-K2tEt1PLpZ3YY=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 117}</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>5</v>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Thác Dải Yếm là điểm du lịch rất đáng đi. Đường đi dễ, xe máy hay ô tô đều thuận tiện. Không gian mát mẻ, thiên nhiên đẹp và trong lành.
 Nước thác xanh biếc, chảy mạnh nhưng nhìn rất êm và thơ mộng, chụp hình lên đẹp lắm. Khu vực được làm lối đi khá an toàn, dễ tham quan.
 Nhân viên ở đây dễ thương, nhiệt tình, hướng dẫn khách rất chu đáo và thân thiện. Phù hợp đi chơi cùng gia đình hoặc bạn bè để thư giãn, nghỉ ngơi.</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>9 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'reviews': 24, 'photos': 255}</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>5</v>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>{'name': 'Thái Nguyễn', 'link': 'https://www.google.com/maps/contrib/105517365260915933657?hl=vi', 'contributor_id': '105517365260915933657', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXLOkY3FUSH3Mz-aapJXPQUgoCFlQP20PICWZGzVI3cPkRkBIt_ew=s120-c-rp-mo-ba12-br100', 'reviews': 65, 'photos': 175}</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>5</v>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Nếu đi cùng Lover sẽ đẹp hơn.
 Nếu tự nhìn lại
@@ -866,56 +806,116 @@
 Hơn cả tới thiên đường</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 90, 'photos': 1080}</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 143, 'photos': 325}</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
+          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
+          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 90, 'photos': 1080}</t>
+          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
+          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>3 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 143, 'photos': 325}</t>
+          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 115, 'photos': 84}</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -923,59 +923,59 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
+          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
+          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 3220}</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
+          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2 tháng trước</t>
+          <t>10 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
+          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 251, 'photos': 5006}</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
+          <t>Cảnh quan đẹp, ng dân thân thiện</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3 tháng trước</t>
+          <t>5 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 115, 'photos': 84}</t>
+          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -983,85 +983,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
+          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>9 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 3220}</t>
+          <t>{'name': 'Linh Nguyễn', 'link': 'https://www.google.com/maps/contrib/109820275513447282944?hl=vi', 'contributor_id': '109820275513447282944', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVpZ-SNyOn6byhXW5cnkMUzIYl8pLeo3scME3-VG4n2ps2S2tYx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 992}</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" t="inlineStr">
-        <is>
-          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>10 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 251, 'photos': 5006}</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>5</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Cảnh quan đẹp, ng dân thân thiện</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>5 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>5</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>9 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>{'name': 'Linh Nguyễn', 'link': 'https://www.google.com/maps/contrib/109820275513447282944?hl=vi', 'contributor_id': '109820275513447282944', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVpZ-SNyOn6byhXW5cnkMUzIYl8pLeo3scME3-VG4n2ps2S2tYx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 992}</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>5</v>
-      </c>
-      <c r="C28" t="inlineStr">
         <is>
           <t>Thác đẹp, suối nước tự nhiên, đường đi dọc suối sạch sẽ
 Một số địa điểm du lịch ở Mộc Châu mọi người có thể tham khảo
@@ -1074,16 +1014,76 @@
 2. Cá Hồi Thanh Bảy</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 81, 'photos': 188}</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>7 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 72, 'photos': 501}</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2 năm trước</t>
+          <t>4 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 81, 'photos': 188}</t>
+          <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'reviews': 78, 'photos': 260}</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1091,27 +1091,28 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
+          <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
+Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
+          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 532, 'photos': 4109}</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
+          <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1123,74 +1124,13 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 72, 'photos': 501}</t>
+          <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 574}</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>5</v>
       </c>
       <c r="C31" t="inlineStr">
-        <is>
-          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>4 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'reviews': 78, 'photos': 260}</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>4</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
-Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 532, 'photos': 4109}</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>4</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 574}</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>5</v>
-      </c>
-      <c r="C34" t="inlineStr">
         <is>
           <t>Đúng tên gọi của nó. Thác cũng rất đẹp. Nếu vào mùa nước chắc còn đẹp hơn.
 Cảnh quan cũng rất sạch đẹp.
@@ -1199,6 +1139,66 @@
 - vé vào cổng giá phù hợp</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4192}</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Thời gian chỉnh sửa: 2 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 518}</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>một năm trước</t>
@@ -1208,7 +1208,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4192}</t>
+          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1216,19 +1216,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
+          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Thời gian chỉnh sửa: 2 năm trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 518}</t>
+          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 1623}</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1236,19 +1236,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
+          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>9 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
+          <t>{'name': 'ninh Men', 'link': 'https://www.google.com/maps/contrib/103025469094717120638?hl=vi', 'contributor_id': '103025469094717120638', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJr8a3WVJHmayMF2FvRRdJjmyVlo0gmvjXedEtF6z5_xuOtxg=s120-c-rp-mo-ba12-br100', 'reviews': 29, 'photos': 168}</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1256,27 +1256,28 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
+          <t>Đi Thác Dải Yếm đúng hôm… uống trà sữa trân châu. 😭
+Vé 150k/người nhưng cá nhân mình thấy hơi hụt hẫng. Thác không quá đặc biệt, đi một vòng là hết, chủ yếu là chụp ảnh. Nếu không thích check-in thì chắc sẽ thấy hơi “không có gì” so với giá vé.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>một tháng trước</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
+          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 49, 'photos': 144}</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
+          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1288,7 +1289,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 1623}</t>
+          <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWyzcZkQykW_QPymZ2fTMwerDVUm-XhQ6WZ0NqbjNzbEznIxcF7AQ=s120-c-rp-mo-ba12-br100', 'reviews': 149, 'photos': 3873}</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1296,19 +1297,20 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+          <t>Thác Dải Yếm, còn được gọi là thác Nàng, thác Bản Vặt, là một thác nước hùng vĩ nằm ở xã Mường Sang, huyện Mộc Châu, tỉnh Sơn La. Thác có chiều cao khoảng 100m, chia thành hai dòng thác chính, trông giống như một dải yếm đào mềm mại uốn lượn quanh vách núi.
+Thác Dải Yếm là một địa điểm du lịch hấp dẫn, thu hút khách du lịch trong và ngoài nước. Đây là nơi du khách có thể chiêm ngưỡng vẻ đẹp hùng vĩ của thác nước và tìm hiểu về truyền thuyết về thác.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>2 năm trước</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>{'name': 'ninh Men', 'link': 'https://www.google.com/maps/contrib/103025469094717120638?hl=vi', 'contributor_id': '103025469094717120638', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJr8a3WVJHmayMF2FvRRdJjmyVlo0gmvjXedEtF6z5_xuOtxg=s120-c-rp-mo-ba12-br100', 'reviews': 29, 'photos': 168}</t>
+          <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'reviews': 97, 'photos': 178}</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1316,20 +1318,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Đi Thác Dải Yếm đúng hôm… uống trà sữa trân châu. 😭
-Vé 150k/người nhưng cá nhân mình thấy hơi hụt hẫng. Thác không quá đặc biệt, đi một vòng là hết, chủ yếu là chụp ảnh. Nếu không thích check-in thì chắc sẽ thấy hơi “không có gì” so với giá vé.</t>
+          <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>một tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 49, 'photos': 144}</t>
+          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'reviews': 27, 'photos': 260}</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1337,7 +1338,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
+          <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1349,48 +1350,48 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWyzcZkQykW_QPymZ2fTMwerDVUm-XhQ6WZ0NqbjNzbEznIxcF7AQ=s120-c-rp-mo-ba12-br100', 'reviews': 149, 'photos': 3873}</t>
+          <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'reviews': 75, 'photos': 503}</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm, còn được gọi là thác Nàng, thác Bản Vặt, là một thác nước hùng vĩ nằm ở xã Mường Sang, huyện Mộc Châu, tỉnh Sơn La. Thác có chiều cao khoảng 100m, chia thành hai dòng thác chính, trông giống như một dải yếm đào mềm mại uốn lượn quanh vách núi.
-Thác Dải Yếm là một địa điểm du lịch hấp dẫn, thu hút khách du lịch trong và ngoài nước. Đây là nơi du khách có thể chiêm ngưỡng vẻ đẹp hùng vĩ của thác nước và tìm hiểu về truyền thuyết về thác.</t>
+          <t>Thác Dải Yếm nằm trên dòng suối Vặt khởi nguồn từ hai khe nước Bó Co Lắm và Bo Tá Cháu ở đầu bản Vặt, một bản của người Thái có lịch sử lâu đời. Suối Vặt chảy được 5 km đổ vào suối Bó Sập, một dòng suối lớn bắt nguồn từ bản Bó Sập giáp biên giới Việt Lào rồi chảy về đất Yên Châu. Tại nơi hợp lưu của hai suối, dòng nước gặp một vùng đá vôi và đổ xuống phía dưới tạo thành thác Dải Yếm.[5]
+Thác Dải Yếm bao gồm hai phần, thác nước phía trên rộng 70 mét, thác nước phía dưới nằm cách đó 150-200 mét. Vào mùa khô, thác phía dưới chỉ có một dòng chảy từ độ cao 50 m xuống triền đá ở dưới. hai thác đổ xuống với tổng chiều cao 100m, một bên được chia làm 9 tầng, bên còn lại 5 tầng. Cách giữa hai phần thác là một bãi đất phẳng thuận tiện cho việc tham quan của du khách. Thảm thực vật trên đỉnh thác cũng khá phong phú.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2 năm trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'reviews': 97, 'photos': 178}</t>
+          <t>{'name': 'Chi Ho', 'link': 'https://www.google.com/maps/contrib/102731288821463748765?hl=vi', 'contributor_id': '102731288821463748765', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWV3y9KiqGo7jILq-ZzBkSw28LDZHnwKXBhstpTEeRvr9jffKE=s120-c-rp-mo-ba12-br100', 'reviews': 85, 'photos': 1540}</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
+          <t>Thác Dải Yếm đẹp và hùng vĩ, xứng đáng cho chuyến picnic cuối tuần. Đường đi hơi gập ghềnh nhưng đến nơi thì quên hết mệt mỏi. Nước mát rượi, âm thanh róc rách rất thư giãn. Tiếc là hơi đông vào cuối tuần, nhưng cảnh đẹp bù đắp tất cả! Nên đi vào ngày thường nếu muốn yên tĩnh hơn.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>một tháng trước</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'reviews': 27, 'photos': 260}</t>
+          <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'reviews': 8, 'photos': 90}</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1398,86 +1399,25 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
+          <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>11 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'reviews': 75, 'photos': 503}</t>
+          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 151, 'photos': 1281}</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>4</v>
       </c>
       <c r="C45" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm nằm trên dòng suối Vặt khởi nguồn từ hai khe nước Bó Co Lắm và Bo Tá Cháu ở đầu bản Vặt, một bản của người Thái có lịch sử lâu đời. Suối Vặt chảy được 5 km đổ vào suối Bó Sập, một dòng suối lớn bắt nguồn từ bản Bó Sập giáp biên giới Việt Lào rồi chảy về đất Yên Châu. Tại nơi hợp lưu của hai suối, dòng nước gặp một vùng đá vôi và đổ xuống phía dưới tạo thành thác Dải Yếm.[5]
-Thác Dải Yếm bao gồm hai phần, thác nước phía trên rộng 70 mét, thác nước phía dưới nằm cách đó 150-200 mét. Vào mùa khô, thác phía dưới chỉ có một dòng chảy từ độ cao 50 m xuống triền đá ở dưới. hai thác đổ xuống với tổng chiều cao 100m, một bên được chia làm 9 tầng, bên còn lại 5 tầng. Cách giữa hai phần thác là một bãi đất phẳng thuận tiện cho việc tham quan của du khách. Thảm thực vật trên đỉnh thác cũng khá phong phú.</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>{'name': 'Chi Ho', 'link': 'https://www.google.com/maps/contrib/102731288821463748765?hl=vi', 'contributor_id': '102731288821463748765', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWV3y9KiqGo7jILq-ZzBkSw28LDZHnwKXBhstpTEeRvr9jffKE=s120-c-rp-mo-ba12-br100', 'reviews': 85, 'photos': 1540}</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>5</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm đẹp và hùng vĩ, xứng đáng cho chuyến picnic cuối tuần. Đường đi hơi gập ghềnh nhưng đến nơi thì quên hết mệt mỏi. Nước mát rượi, âm thanh róc rách rất thư giãn. Tiếc là hơi đông vào cuối tuần, nhưng cảnh đẹp bù đắp tất cả! Nên đi vào ngày thường nếu muốn yên tĩnh hơn.</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>một tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'reviews': 8, 'photos': 90}</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>4</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>11 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 151, 'photos': 1281}</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>4</v>
-      </c>
-      <c r="C48" t="inlineStr">
         <is>
           <t>Thác nhỏ cũng đẹp nhưng được trang trí dành cho du lịch rồi về độ rộng nhiều tầng và thiên nhiên thì không bằng thác Nàng Tiên hoặc thác Chiềng Khoa.
 Thác Dải Yếm được đầu tư khang trang nhưng đi bộ từ bãi gửi xe vào thác hơi bị xa (vé gửi xe 30k), đường đi vào và khu thác bên trong nhiều khu chụp ảnh checkin được trang trí chụp ảnh đẹp mắt. Giá vé tháng 1/2024 là 80k/ người vào cổng nhưng đến 30/4/2024 tăng lên 100k/ng giá vé hơi cao với việc vào ngắm thác.
@@ -1485,27 +1425,27 @@
 - Bản thân mình cảm nhận thì cũng bình thường thác không cao không rộng dài đẹp nhiều tầng bằng thác Nàng Tiên hoặc Chiềng Khoa. Nói chung đi du lịch Mộc Châu ghé qua cho biết thôi. Chứ để quay lại thì ít khả năng.</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>2 năm trước</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 139, 'photos': 564}</t>
         </is>
       </c>
-      <c r="B49" t="n">
+      <c r="B46" t="n">
         <v>4</v>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>View đẹp, chỉ tiếc là ghé hồi tháng 5 lúc đang mùa mưa, nên không được đi trải nghiệm nhiều.</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>11 tháng trước</t>
         </is>

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -473,7 +473,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>{'name': 'Hưng Nguyễn Duy (Hưng Photo)', 'link': 'https://www.google.com/maps/contrib/110173941936897044295?hl=vi', 'contributor_id': '110173941936897044295', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXshx7xq3ntsswbv03kbw9Z9KIntVjsKdM747CeNwqebP-xH_RO=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 191, 'photos': 2169}</t>
+          <t>{'name': 'Hưng Nguyễn Duy (Hưng Photo)', 'link': 'https://www.google.com/maps/contrib/110173941936897044295?hl=vi', 'contributor_id': '110173941936897044295', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXshx7xq3ntsswbv03kbw9Z9KIntVjsKdM747CeNwqebP-xH_RO=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 191, 'photos': 2197}</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -520,7 +520,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 369, 'photos': 2632}</t>
+          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 370, 'photos': 2637}</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Thời gian chỉnh sửa: 5 tháng trước</t>
+          <t>Thời gian chỉnh sửa: 6 tháng trước</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>7 tháng trước</t>
         </is>
       </c>
     </row>

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3 tuần trước</t>
+          <t>4 tuần trước</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4 tháng trước</t>
+          <t>5 tháng trước</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>một tháng trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,7 +565,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 299, 'photos': 3605}</t>
+          <t>{'name': 'THANH NGUYEN', 'link': 'https://www.google.com/maps/contrib/110418688752170937071?hl=vi', 'contributor_id': '110418688752170937071', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIBtT-SxDlGGJM5jA47OmxpGvFdaG6EOeSswcBwx4VuXgnOdQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 70, 'photos': 207}</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -573,19 +573,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
+          <t>thác đẹp nhưng nên đi vào mùa nước sẽ thấy sự khác biệt hơn nhiều</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4 tháng trước</t>
+          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 25}</t>
+          <t>{'name': 'Cửu Quang Nguyễn', 'link': 'https://www.google.com/maps/contrib/107704339232071144994?hl=vi', 'contributor_id': '107704339232071144994', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV2_oJLqzlVCtXNV77ConxSPDhhMhFP-czjeCf6uCm7cabO88k=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 78, 'photos': 349}</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -593,87 +593,147 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
+          <t>Thác Dải Yếm nằm trong khu du lịch sinh thái thác Dải Yếm, đường đi khá tiện lợi để ghé vào, tuy nhiên cần chú ý lối vào có khúc cua dốc khá ngoặt. Vé vào là 150k/người, bên trong có khá nhiều vị trí để du ngoạn và ngắm cảnh, đặc biệt là khu vực thác nước rất hùng vĩ và mát mẻ, có cầu dẫn vào nhìn rất thơ mộng và tuyệt vời. Nếu có dịp ghé lên Mộc Châu thì nên ghé vào đây chơi 1 lần để du ngoạn thắng cảnh thiên nhiên tại nơi đây.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>5 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>{'name': 'Nguyễn Anh Quân', 'link': 'https://www.google.com/maps/contrib/111631093743063403454?hl=vi', 'contributor_id': '111631093743063403454', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIy-NjGEZ7ggp1yhLvVSe2iSDFAUAF4AILlK1IHBmSbkPzlKg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 9, 'photos': 24}</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Cảnh đẹp, nhưng xu là đi ngay lúc mưa nên thác có nước như cf</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>một tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 299, 'photos': 3605}</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>4 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 25}</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>6 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'reviews': 16, 'photos': 114}</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Đi tầm trưa nắng đẹp
 Thác nhỏ, đi cũng không mất quá nhiều thời gian
 Có cầu kính</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>{'name': 'Nghĩa Nguyễn Trung', 'link': 'https://www.google.com/maps/contrib/107253778101970197900?hl=vi', 'contributor_id': '107253778101970197900', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUNLHg5XlpgtWVVTp_oJKOYAejqmQORtgQ_Oe2vusE5W_sQoZc5=s120-c-rp-mo-ba12-br100', 'reviews': 275, 'photos': 1279}</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Khu vực thác nước đẹp, nhiều cảnh quan, nhiều góc chụp đẹp.</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>2 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>{'name': 'Frugal Flow', 'link': 'https://www.google.com/maps/contrib/107453311426556875441?hl=vi', 'contributor_id': '107453311426556875441', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUspWRVGEEQ_LyS16qRB57xWZ-kgNRIjgdLPY8T7HzvNMFlILCV=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 85}</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Đi vào một ngày nắng. Nắng hắt lên mặt nước long lanh nên xinh xắn hẳn:&gt; Chỉ là thác nay có vẻ hơi ít nc nên không như mình tưởng tượng.</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'reviews': 219, 'photos': 307}</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B15" t="n">
         <v>3</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Trải nghiệm vừa phải
 Giá vé theo trải nghiệm đi nhiều thác khác nhau của mình thì là khá cao so với các nơi khác, mình đi vào dịp tết nên thác ít nước.
@@ -681,64 +741,64 @@
 Cá nhân nếu quay lại Mộc Châu sẽ không đến thác này lần nào nữa</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>{'name': 'La Meu', 'link': 'https://www.google.com/maps/contrib/108858956358165703026?hl=vi', 'contributor_id': '108858956358165703026', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVKW-aZD0iBs1KBFQlmzfMiMTfjpd4PfUn4GO-K2tEt1PLpZ3YY=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 117}</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>Thác Dải Yếm là điểm du lịch rất đáng đi. Đường đi dễ, xe máy hay ô tô đều thuận tiện. Không gian mát mẻ, thiên nhiên đẹp và trong lành.
 Nước thác xanh biếc, chảy mạnh nhưng nhìn rất êm và thơ mộng, chụp hình lên đẹp lắm. Khu vực được làm lối đi khá an toàn, dễ tham quan.
 Nhân viên ở đây dễ thương, nhiệt tình, hướng dẫn khách rất chu đáo và thân thiện. Phù hợp đi chơi cùng gia đình hoặc bạn bè để thư giãn, nghỉ ngơi.</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>9 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'reviews': 24, 'photos': 255}</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>{'name': 'Thái Nguyễn', 'link': 'https://www.google.com/maps/contrib/105517365260915933657?hl=vi', 'contributor_id': '105517365260915933657', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXLOkY3FUSH3Mz-aapJXPQUgoCFlQP20PICWZGzVI3cPkRkBIt_ew=s120-c-rp-mo-ba12-br100', 'reviews': 65, 'photos': 175}</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>5</v>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>Nếu đi cùng Lover sẽ đẹp hơn.
 Nếu tự nhìn lại
@@ -806,116 +866,56 @@
 Hơn cả tới thiên đường</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>8 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>8 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 90, 'photos': 1080}</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>5</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 143, 'photos': 325}</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>5</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
+          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
+          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2 tháng trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
+          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 90, 'photos': 1080}</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
+          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 115, 'photos': 84}</t>
+          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 143, 'photos': 325}</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -923,59 +923,59 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
+          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 3220}</t>
+          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
+          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10 tháng trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 251, 'photos': 5006}</t>
+          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cảnh quan đẹp, ng dân thân thiện</t>
+          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5 tháng trước</t>
+          <t>3 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
+          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 115, 'photos': 84}</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -983,25 +983,85 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
+          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 3220}</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>10 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 251, 'photos': 5006}</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Cảnh quan đẹp, ng dân thân thiện</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>5 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>9 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>{'name': 'Linh Nguyễn', 'link': 'https://www.google.com/maps/contrib/109820275513447282944?hl=vi', 'contributor_id': '109820275513447282944', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVpZ-SNyOn6byhXW5cnkMUzIYl8pLeo3scME3-VG4n2ps2S2tYx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 992}</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>5</v>
-      </c>
-      <c r="C25" t="inlineStr">
+      <c r="B28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>Thác đẹp, suối nước tự nhiên, đường đi dọc suối sạch sẽ
 Một số địa điểm du lịch ở Mộc Châu mọi người có thể tham khảo
@@ -1014,76 +1074,16 @@
 2. Cá Hồi Thanh Bảy</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>2 năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 81, 'photos': 188}</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>4</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>7 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>5</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 72, 'photos': 501}</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>5</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>4 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'reviews': 78, 'photos': 260}</t>
+          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 81, 'photos': 188}</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1091,46 +1091,106 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>7 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 72, 'photos': 501}</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>4 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'reviews': 78, 'photos': 260}</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
 Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 532, 'photos': 4109}</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B33" t="n">
         <v>4</v>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 574}</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>5</v>
-      </c>
-      <c r="C31" t="inlineStr">
+      <c r="B34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>Đúng tên gọi của nó. Thác cũng rất đẹp. Nếu vào mùa nước chắc còn đẹp hơn.
 Cảnh quan cũng rất sạch đẹp.
@@ -1139,66 +1199,6 @@
 - vé vào cổng giá phù hợp</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4192}</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>5</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Thời gian chỉnh sửa: 2 năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 518}</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>5</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>4</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
-        </is>
-      </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>một năm trước</t>
@@ -1208,7 +1208,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
+          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4192}</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1216,19 +1216,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
+          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>Thời gian chỉnh sửa: 2 năm trước</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 1623}</t>
+          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 518}</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1236,19 +1236,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>{'name': 'ninh Men', 'link': 'https://www.google.com/maps/contrib/103025469094717120638?hl=vi', 'contributor_id': '103025469094717120638', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJr8a3WVJHmayMF2FvRRdJjmyVlo0gmvjXedEtF6z5_xuOtxg=s120-c-rp-mo-ba12-br100', 'reviews': 29, 'photos': 168}</t>
+          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1256,168 +1256,228 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>5</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 1623}</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>5</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>9 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>{'name': 'ninh Men', 'link': 'https://www.google.com/maps/contrib/103025469094717120638?hl=vi', 'contributor_id': '103025469094717120638', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJr8a3WVJHmayMF2FvRRdJjmyVlo0gmvjXedEtF6z5_xuOtxg=s120-c-rp-mo-ba12-br100', 'reviews': 29, 'photos': 168}</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>4</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
           <t>Đi Thác Dải Yếm đúng hôm… uống trà sữa trân châu. 😭
 Vé 150k/người nhưng cá nhân mình thấy hơi hụt hẫng. Thác không quá đặc biệt, đi một vòng là hết, chủ yếu là chụp ảnh. Nếu không thích check-in thì chắc sẽ thấy hơi “không có gì” so với giá vé.</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>một tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 49, 'photos': 144}</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B41" t="n">
         <v>4</v>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWyzcZkQykW_QPymZ2fTMwerDVUm-XhQ6WZ0NqbjNzbEznIxcF7AQ=s120-c-rp-mo-ba12-br100', 'reviews': 149, 'photos': 3873}</t>
         </is>
       </c>
-      <c r="B39" t="n">
-        <v>5</v>
-      </c>
-      <c r="C39" t="inlineStr">
+      <c r="B42" t="n">
+        <v>5</v>
+      </c>
+      <c r="C42" t="inlineStr">
         <is>
           <t>Thác Dải Yếm, còn được gọi là thác Nàng, thác Bản Vặt, là một thác nước hùng vĩ nằm ở xã Mường Sang, huyện Mộc Châu, tỉnh Sơn La. Thác có chiều cao khoảng 100m, chia thành hai dòng thác chính, trông giống như một dải yếm đào mềm mại uốn lượn quanh vách núi.
 Thác Dải Yếm là một địa điểm du lịch hấp dẫn, thu hút khách du lịch trong và ngoài nước. Đây là nơi du khách có thể chiêm ngưỡng vẻ đẹp hùng vĩ của thác nước và tìm hiểu về truyền thuyết về thác.</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>2 năm trước</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'reviews': 97, 'photos': 178}</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="B43" t="n">
         <v>4</v>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'reviews': 27, 'photos': 260}</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="B44" t="n">
         <v>4</v>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'reviews': 75, 'photos': 503}</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B45" t="n">
         <v>4</v>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Thác Dải Yếm nằm trên dòng suối Vặt khởi nguồn từ hai khe nước Bó Co Lắm và Bo Tá Cháu ở đầu bản Vặt, một bản của người Thái có lịch sử lâu đời. Suối Vặt chảy được 5 km đổ vào suối Bó Sập, một dòng suối lớn bắt nguồn từ bản Bó Sập giáp biên giới Việt Lào rồi chảy về đất Yên Châu. Tại nơi hợp lưu của hai suối, dòng nước gặp một vùng đá vôi và đổ xuống phía dưới tạo thành thác Dải Yếm.[5]
 Thác Dải Yếm bao gồm hai phần, thác nước phía trên rộng 70 mét, thác nước phía dưới nằm cách đó 150-200 mét. Vào mùa khô, thác phía dưới chỉ có một dòng chảy từ độ cao 50 m xuống triền đá ở dưới. hai thác đổ xuống với tổng chiều cao 100m, một bên được chia làm 9 tầng, bên còn lại 5 tầng. Cách giữa hai phần thác là một bãi đất phẳng thuận tiện cho việc tham quan của du khách. Thảm thực vật trên đỉnh thác cũng khá phong phú.</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>{'name': 'Chi Ho', 'link': 'https://www.google.com/maps/contrib/102731288821463748765?hl=vi', 'contributor_id': '102731288821463748765', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWV3y9KiqGo7jILq-ZzBkSw28LDZHnwKXBhstpTEeRvr9jffKE=s120-c-rp-mo-ba12-br100', 'reviews': 85, 'photos': 1540}</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>5</v>
-      </c>
-      <c r="C43" t="inlineStr">
+      <c r="B46" t="n">
+        <v>5</v>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>Thác Dải Yếm đẹp và hùng vĩ, xứng đáng cho chuyến picnic cuối tuần. Đường đi hơi gập ghềnh nhưng đến nơi thì quên hết mệt mỏi. Nước mát rượi, âm thanh róc rách rất thư giãn. Tiếc là hơi đông vào cuối tuần, nhưng cảnh đẹp bù đắp tất cả! Nên đi vào ngày thường nếu muốn yên tĩnh hơn.</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>2 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'reviews': 8, 'photos': 90}</t>
         </is>
       </c>
-      <c r="B44" t="n">
+      <c r="B47" t="n">
         <v>4</v>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>11 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 151, 'photos': 1281}</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 151, 'photos': 1298}</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
         <v>4</v>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Thác nhỏ cũng đẹp nhưng được trang trí dành cho du lịch rồi về độ rộng nhiều tầng và thiên nhiên thì không bằng thác Nàng Tiên hoặc thác Chiềng Khoa.
 Thác Dải Yếm được đầu tư khang trang nhưng đi bộ từ bãi gửi xe vào thác hơi bị xa (vé gửi xe 30k), đường đi vào và khu thác bên trong nhiều khu chụp ảnh checkin được trang trí chụp ảnh đẹp mắt. Giá vé tháng 1/2024 là 80k/ người vào cổng nhưng đến 30/4/2024 tăng lên 100k/ng giá vé hơi cao với việc vào ngắm thác.
@@ -1425,27 +1485,27 @@
 - Bản thân mình cảm nhận thì cũng bình thường thác không cao không rộng dài đẹp nhiều tầng bằng thác Nàng Tiên hoặc Chiềng Khoa. Nói chung đi du lịch Mộc Châu ghé qua cho biết thôi. Chứ để quay lại thì ít khả năng.</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>2 năm trước</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 139, 'photos': 564}</t>
         </is>
       </c>
-      <c r="B46" t="n">
+      <c r="B49" t="n">
         <v>4</v>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>View đẹp, chỉ tiếc là ghé hồi tháng 5 lúc đang mùa mưa, nên không được đi trải nghiệm nhiều.</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>11 tháng trước</t>
         </is>

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -520,7 +520,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 370, 'photos': 2637}</t>
+          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 370, 'photos': 2638}</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -700,7 +700,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2 tháng trước</t>
+          <t>3 tháng trước</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'reviews': 24, 'photos': 255}</t>
+          <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'reviews': 24, 'photos': 256}</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -948,7 +948,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2 tháng trước</t>
+          <t>3 tháng trước</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 151, 'photos': 1298}</t>
+          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 151, 'photos': 1299}</t>
         </is>
       </c>
       <c r="B48" t="n">

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -466,14 +466,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4 tuần trước</t>
+          <t>một tháng trước</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>{'name': 'Hưng Nguyễn Duy (Hưng Photo)', 'link': 'https://www.google.com/maps/contrib/110173941936897044295?hl=vi', 'contributor_id': '110173941936897044295', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXshx7xq3ntsswbv03kbw9Z9KIntVjsKdM747CeNwqebP-xH_RO=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 191, 'photos': 2197}</t>
+          <t>{'name': 'Hưng Nguyễn Duy (Hưng Photo)', 'link': 'https://www.google.com/maps/contrib/110173941936897044295?hl=vi', 'contributor_id': '110173941936897044295', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXshx7xq3ntsswbv03kbw9Z9KIntVjsKdM747CeNwqebP-xH_RO=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 192, 'photos': 2197}</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -520,7 +520,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 370, 'photos': 2638}</t>
+          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 371, 'photos': 2638}</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -565,7 +565,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>{'name': 'THANH NGUYEN', 'link': 'https://www.google.com/maps/contrib/110418688752170937071?hl=vi', 'contributor_id': '110418688752170937071', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIBtT-SxDlGGJM5jA47OmxpGvFdaG6EOeSswcBwx4VuXgnOdQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 70, 'photos': 207}</t>
+          <t>{'name': 'THANH NGUYEN', 'link': 'https://www.google.com/maps/contrib/110418688752170937071?hl=vi', 'contributor_id': '110418688752170937071', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIBtT-SxDlGGJM5jA47OmxpGvFdaG6EOeSswcBwx4VuXgnOdQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 71, 'photos': 238}</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4 tháng trước</t>
+          <t>5 tháng trước</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 532, 'photos': 4109}</t>
+          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 534, 'photos': 4138}</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1390,7 +1390,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'reviews': 27, 'photos': 260}</t>
+          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'reviews': 28, 'photos': 264}</t>
         </is>
       </c>
       <c r="B44" t="n">

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,7 +520,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 371, 'photos': 2638}</t>
+          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 371, 'photos': 2642}</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -565,7 +565,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>{'name': 'THANH NGUYEN', 'link': 'https://www.google.com/maps/contrib/110418688752170937071?hl=vi', 'contributor_id': '110418688752170937071', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIBtT-SxDlGGJM5jA47OmxpGvFdaG6EOeSswcBwx4VuXgnOdQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 71, 'photos': 238}</t>
+          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 299, 'photos': 3605}</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -573,19 +573,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>thác đẹp nhưng nên đi vào mùa nước sẽ thấy sự khác biệt hơn nhiều</t>
+          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7 tháng trước</t>
+          <t>5 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>{'name': 'Cửu Quang Nguyễn', 'link': 'https://www.google.com/maps/contrib/107704339232071144994?hl=vi', 'contributor_id': '107704339232071144994', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV2_oJLqzlVCtXNV77ConxSPDhhMhFP-czjeCf6uCm7cabO88k=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 78, 'photos': 349}</t>
+          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 25}</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -593,147 +593,87 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm nằm trong khu du lịch sinh thái thác Dải Yếm, đường đi khá tiện lợi để ghé vào, tuy nhiên cần chú ý lối vào có khúc cua dốc khá ngoặt. Vé vào là 150k/người, bên trong có khá nhiều vị trí để du ngoạn và ngắm cảnh, đặc biệt là khu vực thác nước rất hùng vĩ và mát mẻ, có cầu dẫn vào nhìn rất thơ mộng và tuyệt vời. Nếu có dịp ghé lên Mộc Châu thì nên ghé vào đây chơi 1 lần để du ngoạn thắng cảnh thiên nhiên tại nơi đây.</t>
+          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5 tháng trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Anh Quân', 'link': 'https://www.google.com/maps/contrib/111631093743063403454?hl=vi', 'contributor_id': '111631093743063403454', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIy-NjGEZ7ggp1yhLvVSe2iSDFAUAF4AILlK1IHBmSbkPzlKg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 9, 'photos': 24}</t>
+          <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'reviews': 16, 'photos': 114}</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>5</v>
       </c>
       <c r="C9" t="inlineStr">
-        <is>
-          <t>Cảnh đẹp, nhưng xu là đi ngay lúc mưa nên thác có nước như cf</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>một tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 299, 'photos': 3605}</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>5 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 25}</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>6 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'reviews': 16, 'photos': 114}</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" t="inlineStr">
         <is>
           <t>Đi tầm trưa nắng đẹp
 Thác nhỏ, đi cũng không mất quá nhiều thời gian
 Có cầu kính</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>{'name': 'Nghĩa Nguyễn Trung', 'link': 'https://www.google.com/maps/contrib/107253778101970197900?hl=vi', 'contributor_id': '107253778101970197900', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUNLHg5XlpgtWVVTp_oJKOYAejqmQORtgQ_Oe2vusE5W_sQoZc5=s120-c-rp-mo-ba12-br100', 'reviews': 275, 'photos': 1279}</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>Khu vực thác nước đẹp, nhiều cảnh quan, nhiều góc chụp đẹp.</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>3 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>{'name': 'Frugal Flow', 'link': 'https://www.google.com/maps/contrib/107453311426556875441?hl=vi', 'contributor_id': '107453311426556875441', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUspWRVGEEQ_LyS16qRB57xWZ-kgNRIjgdLPY8T7HzvNMFlILCV=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 85}</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>Đi vào một ngày nắng. Nắng hắt lên mặt nước long lanh nên xinh xắn hẳn:&gt; Chỉ là thác nay có vẻ hơi ít nc nên không như mình tưởng tượng.</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'reviews': 219, 'photos': 307}</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B12" t="n">
         <v>3</v>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Trải nghiệm vừa phải
 Giá vé theo trải nghiệm đi nhiều thác khác nhau của mình thì là khá cao so với các nơi khác, mình đi vào dịp tết nên thác ít nước.
@@ -741,64 +681,64 @@
 Cá nhân nếu quay lại Mộc Châu sẽ không đến thác này lần nào nữa</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>{'name': 'La Meu', 'link': 'https://www.google.com/maps/contrib/108858956358165703026?hl=vi', 'contributor_id': '108858956358165703026', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVKW-aZD0iBs1KBFQlmzfMiMTfjpd4PfUn4GO-K2tEt1PLpZ3YY=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 117}</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>5</v>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Thác Dải Yếm là điểm du lịch rất đáng đi. Đường đi dễ, xe máy hay ô tô đều thuận tiện. Không gian mát mẻ, thiên nhiên đẹp và trong lành.
 Nước thác xanh biếc, chảy mạnh nhưng nhìn rất êm và thơ mộng, chụp hình lên đẹp lắm. Khu vực được làm lối đi khá an toàn, dễ tham quan.
 Nhân viên ở đây dễ thương, nhiệt tình, hướng dẫn khách rất chu đáo và thân thiện. Phù hợp đi chơi cùng gia đình hoặc bạn bè để thư giãn, nghỉ ngơi.</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>9 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'reviews': 24, 'photos': 256}</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>5</v>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>{'name': 'Thái Nguyễn', 'link': 'https://www.google.com/maps/contrib/105517365260915933657?hl=vi', 'contributor_id': '105517365260915933657', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXLOkY3FUSH3Mz-aapJXPQUgoCFlQP20PICWZGzVI3cPkRkBIt_ew=s120-c-rp-mo-ba12-br100', 'reviews': 65, 'photos': 175}</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>5</v>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Nếu đi cùng Lover sẽ đẹp hơn.
 Nếu tự nhìn lại
@@ -866,56 +806,116 @@
 Hơn cả tới thiên đường</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 90, 'photos': 1087}</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 143, 'photos': 325}</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
+          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
+          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>3 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 90, 'photos': 1080}</t>
+          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
+          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>3 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 143, 'photos': 325}</t>
+          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 115, 'photos': 84}</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -923,59 +923,59 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
+          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7 tháng trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
+          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 3220}</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
+          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3 tháng trước</t>
+          <t>10 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
+          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 251, 'photos': 5006}</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
+          <t>Cảnh quan đẹp, ng dân thân thiện</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3 tháng trước</t>
+          <t>5 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 115, 'photos': 84}</t>
+          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -983,85 +983,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
+          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>9 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 3220}</t>
+          <t>{'name': 'Linh Nguyễn', 'link': 'https://www.google.com/maps/contrib/109820275513447282944?hl=vi', 'contributor_id': '109820275513447282944', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVpZ-SNyOn6byhXW5cnkMUzIYl8pLeo3scME3-VG4n2ps2S2tYx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 992}</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" t="inlineStr">
-        <is>
-          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>10 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 251, 'photos': 5006}</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>5</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Cảnh quan đẹp, ng dân thân thiện</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>5 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>5</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>9 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>{'name': 'Linh Nguyễn', 'link': 'https://www.google.com/maps/contrib/109820275513447282944?hl=vi', 'contributor_id': '109820275513447282944', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVpZ-SNyOn6byhXW5cnkMUzIYl8pLeo3scME3-VG4n2ps2S2tYx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 992}</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>5</v>
-      </c>
-      <c r="C28" t="inlineStr">
         <is>
           <t>Thác đẹp, suối nước tự nhiên, đường đi dọc suối sạch sẽ
 Một số địa điểm du lịch ở Mộc Châu mọi người có thể tham khảo
@@ -1074,16 +1014,76 @@
 2. Cá Hồi Thanh Bảy</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 81, 'photos': 188}</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>7 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 72, 'photos': 501}</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2 năm trước</t>
+          <t>4 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 81, 'photos': 188}</t>
+          <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'reviews': 78, 'photos': 260}</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1091,27 +1091,28 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
+          <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
+Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
+          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 534, 'photos': 4138}</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
+          <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1123,74 +1124,13 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 72, 'photos': 501}</t>
+          <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 574}</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>5</v>
       </c>
       <c r="C31" t="inlineStr">
-        <is>
-          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>4 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'reviews': 78, 'photos': 260}</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>4</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
-Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 534, 'photos': 4138}</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>4</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 574}</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>5</v>
-      </c>
-      <c r="C34" t="inlineStr">
         <is>
           <t>Đúng tên gọi của nó. Thác cũng rất đẹp. Nếu vào mùa nước chắc còn đẹp hơn.
 Cảnh quan cũng rất sạch đẹp.
@@ -1199,6 +1139,66 @@
 - vé vào cổng giá phù hợp</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4192}</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Thời gian chỉnh sửa: 2 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 518}</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>một năm trước</t>
@@ -1208,7 +1208,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4192}</t>
+          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1216,19 +1216,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
+          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Thời gian chỉnh sửa: 2 năm trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 518}</t>
+          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 1623}</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1236,19 +1236,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
+          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>9 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
+          <t>{'name': 'ninh Men', 'link': 'https://www.google.com/maps/contrib/103025469094717120638?hl=vi', 'contributor_id': '103025469094717120638', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJr8a3WVJHmayMF2FvRRdJjmyVlo0gmvjXedEtF6z5_xuOtxg=s120-c-rp-mo-ba12-br100', 'reviews': 29, 'photos': 168}</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1256,27 +1256,28 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
+          <t>Đi Thác Dải Yếm đúng hôm… uống trà sữa trân châu. 😭
+Vé 150k/người nhưng cá nhân mình thấy hơi hụt hẫng. Thác không quá đặc biệt, đi một vòng là hết, chủ yếu là chụp ảnh. Nếu không thích check-in thì chắc sẽ thấy hơi “không có gì” so với giá vé.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>một tháng trước</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
+          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 49, 'photos': 144}</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
+          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1288,7 +1289,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 1623}</t>
+          <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWyzcZkQykW_QPymZ2fTMwerDVUm-XhQ6WZ0NqbjNzbEznIxcF7AQ=s120-c-rp-mo-ba12-br100', 'reviews': 149, 'photos': 3873}</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1296,19 +1297,20 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+          <t>Thác Dải Yếm, còn được gọi là thác Nàng, thác Bản Vặt, là một thác nước hùng vĩ nằm ở xã Mường Sang, huyện Mộc Châu, tỉnh Sơn La. Thác có chiều cao khoảng 100m, chia thành hai dòng thác chính, trông giống như một dải yếm đào mềm mại uốn lượn quanh vách núi.
+Thác Dải Yếm là một địa điểm du lịch hấp dẫn, thu hút khách du lịch trong và ngoài nước. Đây là nơi du khách có thể chiêm ngưỡng vẻ đẹp hùng vĩ của thác nước và tìm hiểu về truyền thuyết về thác.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>2 năm trước</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>{'name': 'ninh Men', 'link': 'https://www.google.com/maps/contrib/103025469094717120638?hl=vi', 'contributor_id': '103025469094717120638', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJr8a3WVJHmayMF2FvRRdJjmyVlo0gmvjXedEtF6z5_xuOtxg=s120-c-rp-mo-ba12-br100', 'reviews': 29, 'photos': 168}</t>
+          <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'reviews': 97, 'photos': 178}</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1316,20 +1318,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Đi Thác Dải Yếm đúng hôm… uống trà sữa trân châu. 😭
-Vé 150k/người nhưng cá nhân mình thấy hơi hụt hẫng. Thác không quá đặc biệt, đi một vòng là hết, chủ yếu là chụp ảnh. Nếu không thích check-in thì chắc sẽ thấy hơi “không có gì” so với giá vé.</t>
+          <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>một tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 49, 'photos': 144}</t>
+          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'reviews': 28, 'photos': 264}</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1337,7 +1338,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
+          <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1349,48 +1350,48 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWyzcZkQykW_QPymZ2fTMwerDVUm-XhQ6WZ0NqbjNzbEznIxcF7AQ=s120-c-rp-mo-ba12-br100', 'reviews': 149, 'photos': 3873}</t>
+          <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'reviews': 75, 'photos': 503}</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm, còn được gọi là thác Nàng, thác Bản Vặt, là một thác nước hùng vĩ nằm ở xã Mường Sang, huyện Mộc Châu, tỉnh Sơn La. Thác có chiều cao khoảng 100m, chia thành hai dòng thác chính, trông giống như một dải yếm đào mềm mại uốn lượn quanh vách núi.
-Thác Dải Yếm là một địa điểm du lịch hấp dẫn, thu hút khách du lịch trong và ngoài nước. Đây là nơi du khách có thể chiêm ngưỡng vẻ đẹp hùng vĩ của thác nước và tìm hiểu về truyền thuyết về thác.</t>
+          <t>Thác Dải Yếm nằm trên dòng suối Vặt khởi nguồn từ hai khe nước Bó Co Lắm và Bo Tá Cháu ở đầu bản Vặt, một bản của người Thái có lịch sử lâu đời. Suối Vặt chảy được 5 km đổ vào suối Bó Sập, một dòng suối lớn bắt nguồn từ bản Bó Sập giáp biên giới Việt Lào rồi chảy về đất Yên Châu. Tại nơi hợp lưu của hai suối, dòng nước gặp một vùng đá vôi và đổ xuống phía dưới tạo thành thác Dải Yếm.[5]
+Thác Dải Yếm bao gồm hai phần, thác nước phía trên rộng 70 mét, thác nước phía dưới nằm cách đó 150-200 mét. Vào mùa khô, thác phía dưới chỉ có một dòng chảy từ độ cao 50 m xuống triền đá ở dưới. hai thác đổ xuống với tổng chiều cao 100m, một bên được chia làm 9 tầng, bên còn lại 5 tầng. Cách giữa hai phần thác là một bãi đất phẳng thuận tiện cho việc tham quan của du khách. Thảm thực vật trên đỉnh thác cũng khá phong phú.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2 năm trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'reviews': 97, 'photos': 178}</t>
+          <t>{'name': 'Chi Ho', 'link': 'https://www.google.com/maps/contrib/102731288821463748765?hl=vi', 'contributor_id': '102731288821463748765', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWV3y9KiqGo7jILq-ZzBkSw28LDZHnwKXBhstpTEeRvr9jffKE=s120-c-rp-mo-ba12-br100', 'reviews': 85, 'photos': 1540}</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
+          <t>Thác Dải Yếm đẹp và hùng vĩ, xứng đáng cho chuyến picnic cuối tuần. Đường đi hơi gập ghềnh nhưng đến nơi thì quên hết mệt mỏi. Nước mát rượi, âm thanh róc rách rất thư giãn. Tiếc là hơi đông vào cuối tuần, nhưng cảnh đẹp bù đắp tất cả! Nên đi vào ngày thường nếu muốn yên tĩnh hơn.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'reviews': 28, 'photos': 264}</t>
+          <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'reviews': 8, 'photos': 90}</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1398,86 +1399,25 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
+          <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>11 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'reviews': 75, 'photos': 503}</t>
+          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 151, 'photos': 1299}</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>4</v>
       </c>
       <c r="C45" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm nằm trên dòng suối Vặt khởi nguồn từ hai khe nước Bó Co Lắm và Bo Tá Cháu ở đầu bản Vặt, một bản của người Thái có lịch sử lâu đời. Suối Vặt chảy được 5 km đổ vào suối Bó Sập, một dòng suối lớn bắt nguồn từ bản Bó Sập giáp biên giới Việt Lào rồi chảy về đất Yên Châu. Tại nơi hợp lưu của hai suối, dòng nước gặp một vùng đá vôi và đổ xuống phía dưới tạo thành thác Dải Yếm.[5]
-Thác Dải Yếm bao gồm hai phần, thác nước phía trên rộng 70 mét, thác nước phía dưới nằm cách đó 150-200 mét. Vào mùa khô, thác phía dưới chỉ có một dòng chảy từ độ cao 50 m xuống triền đá ở dưới. hai thác đổ xuống với tổng chiều cao 100m, một bên được chia làm 9 tầng, bên còn lại 5 tầng. Cách giữa hai phần thác là một bãi đất phẳng thuận tiện cho việc tham quan của du khách. Thảm thực vật trên đỉnh thác cũng khá phong phú.</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>{'name': 'Chi Ho', 'link': 'https://www.google.com/maps/contrib/102731288821463748765?hl=vi', 'contributor_id': '102731288821463748765', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWV3y9KiqGo7jILq-ZzBkSw28LDZHnwKXBhstpTEeRvr9jffKE=s120-c-rp-mo-ba12-br100', 'reviews': 85, 'photos': 1540}</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>5</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm đẹp và hùng vĩ, xứng đáng cho chuyến picnic cuối tuần. Đường đi hơi gập ghềnh nhưng đến nơi thì quên hết mệt mỏi. Nước mát rượi, âm thanh róc rách rất thư giãn. Tiếc là hơi đông vào cuối tuần, nhưng cảnh đẹp bù đắp tất cả! Nên đi vào ngày thường nếu muốn yên tĩnh hơn.</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'reviews': 8, 'photos': 90}</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>4</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>11 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 151, 'photos': 1299}</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>4</v>
-      </c>
-      <c r="C48" t="inlineStr">
         <is>
           <t>Thác nhỏ cũng đẹp nhưng được trang trí dành cho du lịch rồi về độ rộng nhiều tầng và thiên nhiên thì không bằng thác Nàng Tiên hoặc thác Chiềng Khoa.
 Thác Dải Yếm được đầu tư khang trang nhưng đi bộ từ bãi gửi xe vào thác hơi bị xa (vé gửi xe 30k), đường đi vào và khu thác bên trong nhiều khu chụp ảnh checkin được trang trí chụp ảnh đẹp mắt. Giá vé tháng 1/2024 là 80k/ người vào cổng nhưng đến 30/4/2024 tăng lên 100k/ng giá vé hơi cao với việc vào ngắm thác.
@@ -1485,27 +1425,27 @@
 - Bản thân mình cảm nhận thì cũng bình thường thác không cao không rộng dài đẹp nhiều tầng bằng thác Nàng Tiên hoặc Chiềng Khoa. Nói chung đi du lịch Mộc Châu ghé qua cho biết thôi. Chứ để quay lại thì ít khả năng.</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>2 năm trước</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 139, 'photos': 564}</t>
         </is>
       </c>
-      <c r="B49" t="n">
+      <c r="B46" t="n">
         <v>4</v>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>View đẹp, chỉ tiếc là ghé hồi tháng 5 lúc đang mùa mưa, nên không được đi trải nghiệm nhiều.</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>11 tháng trước</t>
         </is>

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -520,7 +520,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 371, 'photos': 2642}</t>
+          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 372, 'photos': 2644}</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -565,7 +565,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 299, 'photos': 3605}</t>
+          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 300, 'photos': 3612}</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -855,7 +855,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 143, 'photos': 325}</t>
+          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 143, 'photos': 329}</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -955,7 +955,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 251, 'photos': 5006}</t>
+          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 252, 'photos': 5012}</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1104,7 +1104,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 534, 'photos': 4138}</t>
+          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 536, 'photos': 4147}</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>một tháng trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 151, 'photos': 1299}</t>
+          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 152, 'photos': 1299}</t>
         </is>
       </c>
       <c r="B45" t="n">

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,14 +513,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 372, 'photos': 2644}</t>
+          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 373, 'photos': 2644}</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -565,7 +565,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 300, 'photos': 3612}</t>
+          <t>{'name': 'THANH NGUYEN', 'link': 'https://www.google.com/maps/contrib/110418688752170937071?hl=vi', 'contributor_id': '110418688752170937071', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIBtT-SxDlGGJM5jA47OmxpGvFdaG6EOeSswcBwx4VuXgnOdQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 71, 'photos': 238}</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -573,19 +573,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
+          <t>thác đẹp nhưng nên đi vào mùa nước sẽ thấy sự khác biệt hơn nhiều</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5 tháng trước</t>
+          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 25}</t>
+          <t>{'name': 'Cửu Quang Nguyễn', 'link': 'https://www.google.com/maps/contrib/107704339232071144994?hl=vi', 'contributor_id': '107704339232071144994', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV2_oJLqzlVCtXNV77ConxSPDhhMhFP-czjeCf6uCm7cabO88k=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 78, 'photos': 349}</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -593,87 +593,147 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
+          <t>Thác Dải Yếm nằm trong khu du lịch sinh thái thác Dải Yếm, đường đi khá tiện lợi để ghé vào, tuy nhiên cần chú ý lối vào có khúc cua dốc khá ngoặt. Vé vào là 150k/người, bên trong có khá nhiều vị trí để du ngoạn và ngắm cảnh, đặc biệt là khu vực thác nước rất hùng vĩ và mát mẻ, có cầu dẫn vào nhìn rất thơ mộng và tuyệt vời. Nếu có dịp ghé lên Mộc Châu thì nên ghé vào đây chơi 1 lần để du ngoạn thắng cảnh thiên nhiên tại nơi đây.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>5 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>{'name': 'Nguyễn Anh Quân', 'link': 'https://www.google.com/maps/contrib/111631093743063403454?hl=vi', 'contributor_id': '111631093743063403454', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIy-NjGEZ7ggp1yhLvVSe2iSDFAUAF4AILlK1IHBmSbkPzlKg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 9, 'photos': 24}</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Cảnh đẹp, nhưng xu là đi ngay lúc mưa nên thác có nước như cf</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 300, 'photos': 3612}</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>5 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 25}</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>6 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'reviews': 16, 'photos': 114}</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Đi tầm trưa nắng đẹp
 Thác nhỏ, đi cũng không mất quá nhiều thời gian
 Có cầu kính</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>{'name': 'Nghĩa Nguyễn Trung', 'link': 'https://www.google.com/maps/contrib/107253778101970197900?hl=vi', 'contributor_id': '107253778101970197900', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUNLHg5XlpgtWVVTp_oJKOYAejqmQORtgQ_Oe2vusE5W_sQoZc5=s120-c-rp-mo-ba12-br100', 'reviews': 275, 'photos': 1279}</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Khu vực thác nước đẹp, nhiều cảnh quan, nhiều góc chụp đẹp.</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>3 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>{'name': 'Frugal Flow', 'link': 'https://www.google.com/maps/contrib/107453311426556875441?hl=vi', 'contributor_id': '107453311426556875441', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUspWRVGEEQ_LyS16qRB57xWZ-kgNRIjgdLPY8T7HzvNMFlILCV=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 85}</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Đi vào một ngày nắng. Nắng hắt lên mặt nước long lanh nên xinh xắn hẳn:&gt; Chỉ là thác nay có vẻ hơi ít nc nên không như mình tưởng tượng.</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'reviews': 219, 'photos': 307}</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B15" t="n">
         <v>3</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Trải nghiệm vừa phải
 Giá vé theo trải nghiệm đi nhiều thác khác nhau của mình thì là khá cao so với các nơi khác, mình đi vào dịp tết nên thác ít nước.
@@ -681,64 +741,64 @@
 Cá nhân nếu quay lại Mộc Châu sẽ không đến thác này lần nào nữa</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>{'name': 'La Meu', 'link': 'https://www.google.com/maps/contrib/108858956358165703026?hl=vi', 'contributor_id': '108858956358165703026', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVKW-aZD0iBs1KBFQlmzfMiMTfjpd4PfUn4GO-K2tEt1PLpZ3YY=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 117}</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>Thác Dải Yếm là điểm du lịch rất đáng đi. Đường đi dễ, xe máy hay ô tô đều thuận tiện. Không gian mát mẻ, thiên nhiên đẹp và trong lành.
 Nước thác xanh biếc, chảy mạnh nhưng nhìn rất êm và thơ mộng, chụp hình lên đẹp lắm. Khu vực được làm lối đi khá an toàn, dễ tham quan.
 Nhân viên ở đây dễ thương, nhiệt tình, hướng dẫn khách rất chu đáo và thân thiện. Phù hợp đi chơi cùng gia đình hoặc bạn bè để thư giãn, nghỉ ngơi.</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>9 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'reviews': 24, 'photos': 256}</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 256}</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>{'name': 'Thái Nguyễn', 'link': 'https://www.google.com/maps/contrib/105517365260915933657?hl=vi', 'contributor_id': '105517365260915933657', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXLOkY3FUSH3Mz-aapJXPQUgoCFlQP20PICWZGzVI3cPkRkBIt_ew=s120-c-rp-mo-ba12-br100', 'reviews': 65, 'photos': 175}</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>5</v>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>Nếu đi cùng Lover sẽ đẹp hơn.
 Nếu tự nhìn lại
@@ -806,116 +866,56 @@
 Hơn cả tới thiên đường</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>8 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>8 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 90, 'photos': 1087}</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>5</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 143, 'photos': 329}</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>5</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
+          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
+          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3 tháng trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
+          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 1087}</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
+          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 115, 'photos': 84}</t>
+          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 329}</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -923,59 +923,59 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
+          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 3220}</t>
+          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
+          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10 tháng trước</t>
+          <t>3 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 252, 'photos': 5012}</t>
+          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cảnh quan đẹp, ng dân thân thiện</t>
+          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5 tháng trước</t>
+          <t>3 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
+          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 115, 'photos': 83}</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -983,25 +983,85 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
+          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 191, 'photos': 3220}</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>10 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 252, 'photos': 5012}</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Cảnh quan đẹp, ng dân thân thiện</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>6 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>9 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>{'name': 'Linh Nguyễn', 'link': 'https://www.google.com/maps/contrib/109820275513447282944?hl=vi', 'contributor_id': '109820275513447282944', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVpZ-SNyOn6byhXW5cnkMUzIYl8pLeo3scME3-VG4n2ps2S2tYx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 992}</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>5</v>
-      </c>
-      <c r="C25" t="inlineStr">
+      <c r="B28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>Thác đẹp, suối nước tự nhiên, đường đi dọc suối sạch sẽ
 Một số địa điểm du lịch ở Mộc Châu mọi người có thể tham khảo
@@ -1014,76 +1074,16 @@
 2. Cá Hồi Thanh Bảy</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>2 năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 81, 'photos': 188}</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>4</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>7 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>5</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 72, 'photos': 501}</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>5</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>4 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'reviews': 78, 'photos': 260}</t>
+          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 81, 'photos': 188}</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1091,46 +1091,106 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>7 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 72, 'photos': 501}</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>4 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'reviews': 78, 'photos': 260}</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
 Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 536, 'photos': 4147}</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B33" t="n">
         <v>4</v>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 574}</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>5</v>
-      </c>
-      <c r="C31" t="inlineStr">
+      <c r="B34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>Đúng tên gọi của nó. Thác cũng rất đẹp. Nếu vào mùa nước chắc còn đẹp hơn.
 Cảnh quan cũng rất sạch đẹp.
@@ -1139,66 +1199,6 @@
 - vé vào cổng giá phù hợp</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4192}</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>5</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Thời gian chỉnh sửa: 2 năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 518}</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>5</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>4</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
-        </is>
-      </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>một năm trước</t>
@@ -1208,7 +1208,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
+          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4192}</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1216,19 +1216,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
+          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>Thời gian chỉnh sửa: 2 năm trước</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 1623}</t>
+          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 518}</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1236,19 +1236,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>{'name': 'ninh Men', 'link': 'https://www.google.com/maps/contrib/103025469094717120638?hl=vi', 'contributor_id': '103025469094717120638', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJr8a3WVJHmayMF2FvRRdJjmyVlo0gmvjXedEtF6z5_xuOtxg=s120-c-rp-mo-ba12-br100', 'reviews': 29, 'photos': 168}</t>
+          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1256,168 +1256,228 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>5</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 1623}</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>5</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>9 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>{'name': 'ninh Men', 'link': 'https://www.google.com/maps/contrib/103025469094717120638?hl=vi', 'contributor_id': '103025469094717120638', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJr8a3WVJHmayMF2FvRRdJjmyVlo0gmvjXedEtF6z5_xuOtxg=s120-c-rp-mo-ba12-br100', 'reviews': 29, 'photos': 168}</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>4</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
           <t>Đi Thác Dải Yếm đúng hôm… uống trà sữa trân châu. 😭
 Vé 150k/người nhưng cá nhân mình thấy hơi hụt hẫng. Thác không quá đặc biệt, đi một vòng là hết, chủ yếu là chụp ảnh. Nếu không thích check-in thì chắc sẽ thấy hơi “không có gì” so với giá vé.</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>2 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 49, 'photos': 144}</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B41" t="n">
         <v>4</v>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWyzcZkQykW_QPymZ2fTMwerDVUm-XhQ6WZ0NqbjNzbEznIxcF7AQ=s120-c-rp-mo-ba12-br100', 'reviews': 149, 'photos': 3873}</t>
         </is>
       </c>
-      <c r="B39" t="n">
-        <v>5</v>
-      </c>
-      <c r="C39" t="inlineStr">
+      <c r="B42" t="n">
+        <v>5</v>
+      </c>
+      <c r="C42" t="inlineStr">
         <is>
           <t>Thác Dải Yếm, còn được gọi là thác Nàng, thác Bản Vặt, là một thác nước hùng vĩ nằm ở xã Mường Sang, huyện Mộc Châu, tỉnh Sơn La. Thác có chiều cao khoảng 100m, chia thành hai dòng thác chính, trông giống như một dải yếm đào mềm mại uốn lượn quanh vách núi.
 Thác Dải Yếm là một địa điểm du lịch hấp dẫn, thu hút khách du lịch trong và ngoài nước. Đây là nơi du khách có thể chiêm ngưỡng vẻ đẹp hùng vĩ của thác nước và tìm hiểu về truyền thuyết về thác.</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>2 năm trước</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'reviews': 97, 'photos': 178}</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="B43" t="n">
         <v>4</v>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'reviews': 28, 'photos': 264}</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="B44" t="n">
         <v>4</v>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'reviews': 75, 'photos': 503}</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B45" t="n">
         <v>4</v>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Thác Dải Yếm nằm trên dòng suối Vặt khởi nguồn từ hai khe nước Bó Co Lắm và Bo Tá Cháu ở đầu bản Vặt, một bản của người Thái có lịch sử lâu đời. Suối Vặt chảy được 5 km đổ vào suối Bó Sập, một dòng suối lớn bắt nguồn từ bản Bó Sập giáp biên giới Việt Lào rồi chảy về đất Yên Châu. Tại nơi hợp lưu của hai suối, dòng nước gặp một vùng đá vôi và đổ xuống phía dưới tạo thành thác Dải Yếm.[5]
 Thác Dải Yếm bao gồm hai phần, thác nước phía trên rộng 70 mét, thác nước phía dưới nằm cách đó 150-200 mét. Vào mùa khô, thác phía dưới chỉ có một dòng chảy từ độ cao 50 m xuống triền đá ở dưới. hai thác đổ xuống với tổng chiều cao 100m, một bên được chia làm 9 tầng, bên còn lại 5 tầng. Cách giữa hai phần thác là một bãi đất phẳng thuận tiện cho việc tham quan của du khách. Thảm thực vật trên đỉnh thác cũng khá phong phú.</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>{'name': 'Chi Ho', 'link': 'https://www.google.com/maps/contrib/102731288821463748765?hl=vi', 'contributor_id': '102731288821463748765', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWV3y9KiqGo7jILq-ZzBkSw28LDZHnwKXBhstpTEeRvr9jffKE=s120-c-rp-mo-ba12-br100', 'reviews': 85, 'photos': 1540}</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>5</v>
-      </c>
-      <c r="C43" t="inlineStr">
+      <c r="B46" t="n">
+        <v>5</v>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>Thác Dải Yếm đẹp và hùng vĩ, xứng đáng cho chuyến picnic cuối tuần. Đường đi hơi gập ghềnh nhưng đến nơi thì quên hết mệt mỏi. Nước mát rượi, âm thanh róc rách rất thư giãn. Tiếc là hơi đông vào cuối tuần, nhưng cảnh đẹp bù đắp tất cả! Nên đi vào ngày thường nếu muốn yên tĩnh hơn.</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>2 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'reviews': 8, 'photos': 90}</t>
         </is>
       </c>
-      <c r="B44" t="n">
+      <c r="B47" t="n">
         <v>4</v>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>11 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 152, 'photos': 1299}</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 152, 'photos': 1307}</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
         <v>4</v>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Thác nhỏ cũng đẹp nhưng được trang trí dành cho du lịch rồi về độ rộng nhiều tầng và thiên nhiên thì không bằng thác Nàng Tiên hoặc thác Chiềng Khoa.
 Thác Dải Yếm được đầu tư khang trang nhưng đi bộ từ bãi gửi xe vào thác hơi bị xa (vé gửi xe 30k), đường đi vào và khu thác bên trong nhiều khu chụp ảnh checkin được trang trí chụp ảnh đẹp mắt. Giá vé tháng 1/2024 là 80k/ người vào cổng nhưng đến 30/4/2024 tăng lên 100k/ng giá vé hơi cao với việc vào ngắm thác.
@@ -1425,27 +1485,27 @@
 - Bản thân mình cảm nhận thì cũng bình thường thác không cao không rộng dài đẹp nhiều tầng bằng thác Nàng Tiên hoặc Chiềng Khoa. Nói chung đi du lịch Mộc Châu ghé qua cho biết thôi. Chứ để quay lại thì ít khả năng.</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>2 năm trước</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 139, 'photos': 564}</t>
         </is>
       </c>
-      <c r="B46" t="n">
+      <c r="B49" t="n">
         <v>4</v>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>View đẹp, chỉ tiếc là ghé hồi tháng 5 lúc đang mùa mưa, nên không được đi trải nghiệm nhiều.</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>11 tháng trước</t>
         </is>

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>{'name': 'ZjmLee YTBer', 'link': 'https://www.google.com/maps/contrib/100979561872983589256?hl=vi', 'contributor_id': '100979561872983589256', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU6i9poRXPBKYv-WgZHmB9chW6jRPCOh3klZ1Z7Yv_DOaukn4g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 79, 'photos': 1243}</t>
+          <t>{'name': 'ZjmLee YTBer', 'link': 'https://www.google.com/maps/contrib/100979561872983589256?hl=vi', 'contributor_id': '100979561872983589256', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU6i9poRXPBKYv-WgZHmB9chW6jRPCOh3klZ1Z7Yv_DOaukn4g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 79, 'photos': 1252}</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -520,7 +520,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 373, 'photos': 2644}</t>
+          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 374, 'photos': 2644}</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -975,7 +975,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 115, 'photos': 83}</t>
+          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 114, 'photos': 83}</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1464,14 +1464,14 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>11 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 152, 'photos': 1307}</t>
+          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 153, 'photos': 1307}</t>
         </is>
       </c>
       <c r="B48" t="n">

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -473,7 +473,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>{'name': 'Hưng Nguyễn Duy (Hưng Photo)', 'link': 'https://www.google.com/maps/contrib/110173941936897044295?hl=vi', 'contributor_id': '110173941936897044295', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXshx7xq3ntsswbv03kbw9Z9KIntVjsKdM747CeNwqebP-xH_RO=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 192, 'photos': 2197}</t>
+          <t>{'name': 'Hưng Nguyễn Duy (Hưng Photo)', 'link': 'https://www.google.com/maps/contrib/110173941936897044295?hl=vi', 'contributor_id': '110173941936897044295', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXshx7xq3ntsswbv03kbw9Z9KIntVjsKdM747CeNwqebP-xH_RO=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 192, 'photos': 2205}</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>{'name': 'ZjmLee YTBer', 'link': 'https://www.google.com/maps/contrib/100979561872983589256?hl=vi', 'contributor_id': '100979561872983589256', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU6i9poRXPBKYv-WgZHmB9chW6jRPCOh3klZ1Z7Yv_DOaukn4g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 79, 'photos': 1252}</t>
+          <t>{'name': 'ZjmLee YTBer', 'link': 'https://www.google.com/maps/contrib/100979561872983589256?hl=vi', 'contributor_id': '100979561872983589256', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU6i9poRXPBKYv-WgZHmB9chW6jRPCOh3klZ1Z7Yv_DOaukn4g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 80, 'photos': 1252}</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1329,7 +1329,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 49, 'photos': 144}</t>
+          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 50, 'photos': 144}</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1494,7 +1494,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 139, 'photos': 564}</t>
+          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 139, 'photos': 569}</t>
         </is>
       </c>
       <c r="B49" t="n">

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,7 +565,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>{'name': 'THANH NGUYEN', 'link': 'https://www.google.com/maps/contrib/110418688752170937071?hl=vi', 'contributor_id': '110418688752170937071', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIBtT-SxDlGGJM5jA47OmxpGvFdaG6EOeSswcBwx4VuXgnOdQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 71, 'photos': 238}</t>
+          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 300, 'photos': 3612}</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -573,19 +573,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>thác đẹp nhưng nên đi vào mùa nước sẽ thấy sự khác biệt hơn nhiều</t>
+          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7 tháng trước</t>
+          <t>5 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>{'name': 'Cửu Quang Nguyễn', 'link': 'https://www.google.com/maps/contrib/107704339232071144994?hl=vi', 'contributor_id': '107704339232071144994', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV2_oJLqzlVCtXNV77ConxSPDhhMhFP-czjeCf6uCm7cabO88k=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 78, 'photos': 349}</t>
+          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 25}</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -593,147 +593,87 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm nằm trong khu du lịch sinh thái thác Dải Yếm, đường đi khá tiện lợi để ghé vào, tuy nhiên cần chú ý lối vào có khúc cua dốc khá ngoặt. Vé vào là 150k/người, bên trong có khá nhiều vị trí để du ngoạn và ngắm cảnh, đặc biệt là khu vực thác nước rất hùng vĩ và mát mẻ, có cầu dẫn vào nhìn rất thơ mộng và tuyệt vời. Nếu có dịp ghé lên Mộc Châu thì nên ghé vào đây chơi 1 lần để du ngoạn thắng cảnh thiên nhiên tại nơi đây.</t>
+          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5 tháng trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Anh Quân', 'link': 'https://www.google.com/maps/contrib/111631093743063403454?hl=vi', 'contributor_id': '111631093743063403454', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIy-NjGEZ7ggp1yhLvVSe2iSDFAUAF4AILlK1IHBmSbkPzlKg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 9, 'photos': 24}</t>
+          <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'reviews': 16, 'photos': 114}</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>5</v>
       </c>
       <c r="C9" t="inlineStr">
-        <is>
-          <t>Cảnh đẹp, nhưng xu là đi ngay lúc mưa nên thác có nước như cf</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 300, 'photos': 3612}</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>5 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 25}</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>6 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'reviews': 16, 'photos': 114}</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" t="inlineStr">
         <is>
           <t>Đi tầm trưa nắng đẹp
 Thác nhỏ, đi cũng không mất quá nhiều thời gian
 Có cầu kính</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>{'name': 'Nghĩa Nguyễn Trung', 'link': 'https://www.google.com/maps/contrib/107253778101970197900?hl=vi', 'contributor_id': '107253778101970197900', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUNLHg5XlpgtWVVTp_oJKOYAejqmQORtgQ_Oe2vusE5W_sQoZc5=s120-c-rp-mo-ba12-br100', 'reviews': 275, 'photos': 1279}</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>Khu vực thác nước đẹp, nhiều cảnh quan, nhiều góc chụp đẹp.</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>3 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>{'name': 'Frugal Flow', 'link': 'https://www.google.com/maps/contrib/107453311426556875441?hl=vi', 'contributor_id': '107453311426556875441', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUspWRVGEEQ_LyS16qRB57xWZ-kgNRIjgdLPY8T7HzvNMFlILCV=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 85}</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>Đi vào một ngày nắng. Nắng hắt lên mặt nước long lanh nên xinh xắn hẳn:&gt; Chỉ là thác nay có vẻ hơi ít nc nên không như mình tưởng tượng.</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'reviews': 219, 'photos': 307}</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B12" t="n">
         <v>3</v>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Trải nghiệm vừa phải
 Giá vé theo trải nghiệm đi nhiều thác khác nhau của mình thì là khá cao so với các nơi khác, mình đi vào dịp tết nên thác ít nước.
@@ -741,64 +681,64 @@
 Cá nhân nếu quay lại Mộc Châu sẽ không đến thác này lần nào nữa</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>{'name': 'La Meu', 'link': 'https://www.google.com/maps/contrib/108858956358165703026?hl=vi', 'contributor_id': '108858956358165703026', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVKW-aZD0iBs1KBFQlmzfMiMTfjpd4PfUn4GO-K2tEt1PLpZ3YY=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 117}</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>5</v>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Thác Dải Yếm là điểm du lịch rất đáng đi. Đường đi dễ, xe máy hay ô tô đều thuận tiện. Không gian mát mẻ, thiên nhiên đẹp và trong lành.
 Nước thác xanh biếc, chảy mạnh nhưng nhìn rất êm và thơ mộng, chụp hình lên đẹp lắm. Khu vực được làm lối đi khá an toàn, dễ tham quan.
 Nhân viên ở đây dễ thương, nhiệt tình, hướng dẫn khách rất chu đáo và thân thiện. Phù hợp đi chơi cùng gia đình hoặc bạn bè để thư giãn, nghỉ ngơi.</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>9 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 256}</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>5</v>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>{'name': 'Thái Nguyễn', 'link': 'https://www.google.com/maps/contrib/105517365260915933657?hl=vi', 'contributor_id': '105517365260915933657', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXLOkY3FUSH3Mz-aapJXPQUgoCFlQP20PICWZGzVI3cPkRkBIt_ew=s120-c-rp-mo-ba12-br100', 'reviews': 65, 'photos': 175}</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>5</v>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Nếu đi cùng Lover sẽ đẹp hơn.
 Nếu tự nhìn lại
@@ -866,56 +806,116 @@
 Hơn cả tới thiên đường</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 1103}</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 330}</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
+          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
+          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>3 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 1087}</t>
+          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
+          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>3 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 329}</t>
+          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 114, 'photos': 83}</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -923,59 +923,59 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
+          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7 tháng trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
+          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 191, 'photos': 3220}</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
+          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3 tháng trước</t>
+          <t>10 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
+          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 252, 'photos': 5012}</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
+          <t>Cảnh quan đẹp, ng dân thân thiện</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3 tháng trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 114, 'photos': 83}</t>
+          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -983,85 +983,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
+          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>9 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 191, 'photos': 3220}</t>
+          <t>{'name': 'Linh Nguyễn', 'link': 'https://www.google.com/maps/contrib/109820275513447282944?hl=vi', 'contributor_id': '109820275513447282944', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVpZ-SNyOn6byhXW5cnkMUzIYl8pLeo3scME3-VG4n2ps2S2tYx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 992}</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" t="inlineStr">
-        <is>
-          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>10 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 252, 'photos': 5012}</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>5</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Cảnh quan đẹp, ng dân thân thiện</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>6 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>5</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>9 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>{'name': 'Linh Nguyễn', 'link': 'https://www.google.com/maps/contrib/109820275513447282944?hl=vi', 'contributor_id': '109820275513447282944', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVpZ-SNyOn6byhXW5cnkMUzIYl8pLeo3scME3-VG4n2ps2S2tYx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 992}</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>5</v>
-      </c>
-      <c r="C28" t="inlineStr">
         <is>
           <t>Thác đẹp, suối nước tự nhiên, đường đi dọc suối sạch sẽ
 Một số địa điểm du lịch ở Mộc Châu mọi người có thể tham khảo
@@ -1074,16 +1014,76 @@
 2. Cá Hồi Thanh Bảy</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 81, 'photos': 188}</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>7 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 72, 'photos': 501}</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2 năm trước</t>
+          <t>4 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 81, 'photos': 188}</t>
+          <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'reviews': 78, 'photos': 260}</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1091,27 +1091,28 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
+          <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
+Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
+          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 536, 'photos': 4147}</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
+          <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1123,74 +1124,13 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 72, 'photos': 501}</t>
+          <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 574}</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>5</v>
       </c>
       <c r="C31" t="inlineStr">
-        <is>
-          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>4 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'reviews': 78, 'photos': 260}</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>4</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
-Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 536, 'photos': 4147}</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>4</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 574}</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>5</v>
-      </c>
-      <c r="C34" t="inlineStr">
         <is>
           <t>Đúng tên gọi của nó. Thác cũng rất đẹp. Nếu vào mùa nước chắc còn đẹp hơn.
 Cảnh quan cũng rất sạch đẹp.
@@ -1199,6 +1139,66 @@
 - vé vào cổng giá phù hợp</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4192}</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Thời gian chỉnh sửa: 2 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 518}</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>một năm trước</t>
@@ -1208,7 +1208,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4192}</t>
+          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1216,19 +1216,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
+          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Thời gian chỉnh sửa: 2 năm trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 518}</t>
+          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 1623}</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1236,19 +1236,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
+          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>10 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
+          <t>{'name': 'ninh Men', 'link': 'https://www.google.com/maps/contrib/103025469094717120638?hl=vi', 'contributor_id': '103025469094717120638', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJr8a3WVJHmayMF2FvRRdJjmyVlo0gmvjXedEtF6z5_xuOtxg=s120-c-rp-mo-ba12-br100', 'reviews': 29, 'photos': 168}</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1256,27 +1256,28 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
+          <t>Đi Thác Dải Yếm đúng hôm… uống trà sữa trân châu. 😭
+Vé 150k/người nhưng cá nhân mình thấy hơi hụt hẫng. Thác không quá đặc biệt, đi một vòng là hết, chủ yếu là chụp ảnh. Nếu không thích check-in thì chắc sẽ thấy hơi “không có gì” so với giá vé.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
+          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 50, 'photos': 144}</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
+          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1288,7 +1289,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 1623}</t>
+          <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWyzcZkQykW_QPymZ2fTMwerDVUm-XhQ6WZ0NqbjNzbEznIxcF7AQ=s120-c-rp-mo-ba12-br100', 'reviews': 149, 'photos': 3873}</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1296,19 +1297,20 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+          <t>Thác Dải Yếm, còn được gọi là thác Nàng, thác Bản Vặt, là một thác nước hùng vĩ nằm ở xã Mường Sang, huyện Mộc Châu, tỉnh Sơn La. Thác có chiều cao khoảng 100m, chia thành hai dòng thác chính, trông giống như một dải yếm đào mềm mại uốn lượn quanh vách núi.
+Thác Dải Yếm là một địa điểm du lịch hấp dẫn, thu hút khách du lịch trong và ngoài nước. Đây là nơi du khách có thể chiêm ngưỡng vẻ đẹp hùng vĩ của thác nước và tìm hiểu về truyền thuyết về thác.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>2 năm trước</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>{'name': 'ninh Men', 'link': 'https://www.google.com/maps/contrib/103025469094717120638?hl=vi', 'contributor_id': '103025469094717120638', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJr8a3WVJHmayMF2FvRRdJjmyVlo0gmvjXedEtF6z5_xuOtxg=s120-c-rp-mo-ba12-br100', 'reviews': 29, 'photos': 168}</t>
+          <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'reviews': 97, 'photos': 178}</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1316,20 +1318,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Đi Thác Dải Yếm đúng hôm… uống trà sữa trân châu. 😭
-Vé 150k/người nhưng cá nhân mình thấy hơi hụt hẫng. Thác không quá đặc biệt, đi một vòng là hết, chủ yếu là chụp ảnh. Nếu không thích check-in thì chắc sẽ thấy hơi “không có gì” so với giá vé.</t>
+          <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 50, 'photos': 144}</t>
+          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'reviews': 28, 'photos': 264}</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1337,7 +1338,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
+          <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1349,48 +1350,48 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWyzcZkQykW_QPymZ2fTMwerDVUm-XhQ6WZ0NqbjNzbEznIxcF7AQ=s120-c-rp-mo-ba12-br100', 'reviews': 149, 'photos': 3873}</t>
+          <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'reviews': 75, 'photos': 503}</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm, còn được gọi là thác Nàng, thác Bản Vặt, là một thác nước hùng vĩ nằm ở xã Mường Sang, huyện Mộc Châu, tỉnh Sơn La. Thác có chiều cao khoảng 100m, chia thành hai dòng thác chính, trông giống như một dải yếm đào mềm mại uốn lượn quanh vách núi.
-Thác Dải Yếm là một địa điểm du lịch hấp dẫn, thu hút khách du lịch trong và ngoài nước. Đây là nơi du khách có thể chiêm ngưỡng vẻ đẹp hùng vĩ của thác nước và tìm hiểu về truyền thuyết về thác.</t>
+          <t>Thác Dải Yếm nằm trên dòng suối Vặt khởi nguồn từ hai khe nước Bó Co Lắm và Bo Tá Cháu ở đầu bản Vặt, một bản của người Thái có lịch sử lâu đời. Suối Vặt chảy được 5 km đổ vào suối Bó Sập, một dòng suối lớn bắt nguồn từ bản Bó Sập giáp biên giới Việt Lào rồi chảy về đất Yên Châu. Tại nơi hợp lưu của hai suối, dòng nước gặp một vùng đá vôi và đổ xuống phía dưới tạo thành thác Dải Yếm.[5]
+Thác Dải Yếm bao gồm hai phần, thác nước phía trên rộng 70 mét, thác nước phía dưới nằm cách đó 150-200 mét. Vào mùa khô, thác phía dưới chỉ có một dòng chảy từ độ cao 50 m xuống triền đá ở dưới. hai thác đổ xuống với tổng chiều cao 100m, một bên được chia làm 9 tầng, bên còn lại 5 tầng. Cách giữa hai phần thác là một bãi đất phẳng thuận tiện cho việc tham quan của du khách. Thảm thực vật trên đỉnh thác cũng khá phong phú.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2 năm trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'reviews': 97, 'photos': 178}</t>
+          <t>{'name': 'Chi Ho', 'link': 'https://www.google.com/maps/contrib/102731288821463748765?hl=vi', 'contributor_id': '102731288821463748765', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWV3y9KiqGo7jILq-ZzBkSw28LDZHnwKXBhstpTEeRvr9jffKE=s120-c-rp-mo-ba12-br100', 'reviews': 85, 'photos': 1540}</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
+          <t>Thác Dải Yếm đẹp và hùng vĩ, xứng đáng cho chuyến picnic cuối tuần. Đường đi hơi gập ghềnh nhưng đến nơi thì quên hết mệt mỏi. Nước mát rượi, âm thanh róc rách rất thư giãn. Tiếc là hơi đông vào cuối tuần, nhưng cảnh đẹp bù đắp tất cả! Nên đi vào ngày thường nếu muốn yên tĩnh hơn.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'reviews': 28, 'photos': 264}</t>
+          <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'reviews': 8, 'photos': 90}</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1398,7 +1399,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
+          <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1410,74 +1411,13 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'reviews': 75, 'photos': 503}</t>
+          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 153, 'photos': 1307}</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>4</v>
       </c>
       <c r="C45" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm nằm trên dòng suối Vặt khởi nguồn từ hai khe nước Bó Co Lắm và Bo Tá Cháu ở đầu bản Vặt, một bản của người Thái có lịch sử lâu đời. Suối Vặt chảy được 5 km đổ vào suối Bó Sập, một dòng suối lớn bắt nguồn từ bản Bó Sập giáp biên giới Việt Lào rồi chảy về đất Yên Châu. Tại nơi hợp lưu của hai suối, dòng nước gặp một vùng đá vôi và đổ xuống phía dưới tạo thành thác Dải Yếm.[5]
-Thác Dải Yếm bao gồm hai phần, thác nước phía trên rộng 70 mét, thác nước phía dưới nằm cách đó 150-200 mét. Vào mùa khô, thác phía dưới chỉ có một dòng chảy từ độ cao 50 m xuống triền đá ở dưới. hai thác đổ xuống với tổng chiều cao 100m, một bên được chia làm 9 tầng, bên còn lại 5 tầng. Cách giữa hai phần thác là một bãi đất phẳng thuận tiện cho việc tham quan của du khách. Thảm thực vật trên đỉnh thác cũng khá phong phú.</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>{'name': 'Chi Ho', 'link': 'https://www.google.com/maps/contrib/102731288821463748765?hl=vi', 'contributor_id': '102731288821463748765', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWV3y9KiqGo7jILq-ZzBkSw28LDZHnwKXBhstpTEeRvr9jffKE=s120-c-rp-mo-ba12-br100', 'reviews': 85, 'photos': 1540}</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>5</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm đẹp và hùng vĩ, xứng đáng cho chuyến picnic cuối tuần. Đường đi hơi gập ghềnh nhưng đến nơi thì quên hết mệt mỏi. Nước mát rượi, âm thanh róc rách rất thư giãn. Tiếc là hơi đông vào cuối tuần, nhưng cảnh đẹp bù đắp tất cả! Nên đi vào ngày thường nếu muốn yên tĩnh hơn.</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'reviews': 8, 'photos': 90}</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>4</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 153, 'photos': 1307}</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>4</v>
-      </c>
-      <c r="C48" t="inlineStr">
         <is>
           <t>Thác nhỏ cũng đẹp nhưng được trang trí dành cho du lịch rồi về độ rộng nhiều tầng và thiên nhiên thì không bằng thác Nàng Tiên hoặc thác Chiềng Khoa.
 Thác Dải Yếm được đầu tư khang trang nhưng đi bộ từ bãi gửi xe vào thác hơi bị xa (vé gửi xe 30k), đường đi vào và khu thác bên trong nhiều khu chụp ảnh checkin được trang trí chụp ảnh đẹp mắt. Giá vé tháng 1/2024 là 80k/ người vào cổng nhưng đến 30/4/2024 tăng lên 100k/ng giá vé hơi cao với việc vào ngắm thác.
@@ -1485,27 +1425,27 @@
 - Bản thân mình cảm nhận thì cũng bình thường thác không cao không rộng dài đẹp nhiều tầng bằng thác Nàng Tiên hoặc Chiềng Khoa. Nói chung đi du lịch Mộc Châu ghé qua cho biết thôi. Chứ để quay lại thì ít khả năng.</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>2 năm trước</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 139, 'photos': 569}</t>
         </is>
       </c>
-      <c r="B49" t="n">
+      <c r="B46" t="n">
         <v>4</v>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>View đẹp, chỉ tiếc là ghé hồi tháng 5 lúc đang mùa mưa, nên không được đi trải nghiệm nhiều.</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>11 tháng trước</t>
         </is>

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -473,7 +473,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>{'name': 'Hưng Nguyễn Duy (Hưng Photo)', 'link': 'https://www.google.com/maps/contrib/110173941936897044295?hl=vi', 'contributor_id': '110173941936897044295', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXshx7xq3ntsswbv03kbw9Z9KIntVjsKdM747CeNwqebP-xH_RO=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 192, 'photos': 2205}</t>
+          <t>{'name': 'Hưng Nguyễn Duy (Hưng Photo)', 'link': 'https://www.google.com/maps/contrib/110173941936897044295?hl=vi', 'contributor_id': '110173941936897044295', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXshx7xq3ntsswbv03kbw9Z9KIntVjsKdM747CeNwqebP-xH_RO=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 194, 'photos': 2205}</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -565,7 +565,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 300, 'photos': 3612}</t>
+          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 302, 'photos': 3612}</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -667,7 +667,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'reviews': 219, 'photos': 307}</t>
+          <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'reviews': 220, 'photos': 307}</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -828,14 +828,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>9 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 1103}</t>
+          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 92, 'photos': 1103}</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1104,7 +1104,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 536, 'photos': 4147}</t>
+          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 537, 'photos': 4147}</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1148,7 +1148,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4192}</t>
+          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 653, 'photos': 4192}</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1228,7 +1228,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 189, 'photos': 1623}</t>
+          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 1623}</t>
         </is>
       </c>
       <c r="B36" t="n">

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -835,7 +835,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 92, 'photos': 1103}</t>
+          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 93, 'photos': 1103}</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -855,7 +855,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 330}</t>
+          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 145, 'photos': 330}</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -935,7 +935,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 191, 'photos': 3220}</t>
+          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 3220}</t>
         </is>
       </c>
       <c r="B22" t="n">

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,7 +565,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 302, 'photos': 3612}</t>
+          <t>{'name': 'THANH NGUYEN', 'link': 'https://www.google.com/maps/contrib/110418688752170937071?hl=vi', 'contributor_id': '110418688752170937071', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIBtT-SxDlGGJM5jA47OmxpGvFdaG6EOeSswcBwx4VuXgnOdQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 71, 'photos': 238}</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -573,19 +573,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
+          <t>thác đẹp nhưng nên đi vào mùa nước sẽ thấy sự khác biệt hơn nhiều</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5 tháng trước</t>
+          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 25}</t>
+          <t>{'name': 'Cửu Quang Nguyễn', 'link': 'https://www.google.com/maps/contrib/107704339232071144994?hl=vi', 'contributor_id': '107704339232071144994', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV2_oJLqzlVCtXNV77ConxSPDhhMhFP-czjeCf6uCm7cabO88k=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 79, 'photos': 359}</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -593,87 +593,147 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
+          <t>Thác Dải Yếm nằm trong khu du lịch sinh thái thác Dải Yếm, đường đi khá tiện lợi để ghé vào, tuy nhiên cần chú ý lối vào có khúc cua dốc khá ngoặt. Vé vào là 150k/người, bên trong có khá nhiều vị trí để du ngoạn và ngắm cảnh, đặc biệt là khu vực thác nước rất hùng vĩ và mát mẻ, có cầu dẫn vào nhìn rất thơ mộng và tuyệt vời. Nếu có dịp ghé lên Mộc Châu thì nên ghé vào đây chơi 1 lần để du ngoạn thắng cảnh thiên nhiên tại nơi đây.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>5 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>{'name': 'Nguyễn Anh Quân', 'link': 'https://www.google.com/maps/contrib/111631093743063403454?hl=vi', 'contributor_id': '111631093743063403454', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIy-NjGEZ7ggp1yhLvVSe2iSDFAUAF4AILlK1IHBmSbkPzlKg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 9, 'photos': 24}</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Cảnh đẹp, nhưng xu là đi ngay lúc mưa nên thác có nước như cf</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 302, 'photos': 3616}</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>5 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 25}</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>6 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'reviews': 16, 'photos': 114}</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Đi tầm trưa nắng đẹp
 Thác nhỏ, đi cũng không mất quá nhiều thời gian
 Có cầu kính</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>{'name': 'Nghĩa Nguyễn Trung', 'link': 'https://www.google.com/maps/contrib/107253778101970197900?hl=vi', 'contributor_id': '107253778101970197900', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUNLHg5XlpgtWVVTp_oJKOYAejqmQORtgQ_Oe2vusE5W_sQoZc5=s120-c-rp-mo-ba12-br100', 'reviews': 275, 'photos': 1279}</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Khu vực thác nước đẹp, nhiều cảnh quan, nhiều góc chụp đẹp.</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>3 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>{'name': 'Frugal Flow', 'link': 'https://www.google.com/maps/contrib/107453311426556875441?hl=vi', 'contributor_id': '107453311426556875441', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUspWRVGEEQ_LyS16qRB57xWZ-kgNRIjgdLPY8T7HzvNMFlILCV=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 85}</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Đi vào một ngày nắng. Nắng hắt lên mặt nước long lanh nên xinh xắn hẳn:&gt; Chỉ là thác nay có vẻ hơi ít nc nên không như mình tưởng tượng.</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'reviews': 220, 'photos': 307}</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B15" t="n">
         <v>3</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Trải nghiệm vừa phải
 Giá vé theo trải nghiệm đi nhiều thác khác nhau của mình thì là khá cao so với các nơi khác, mình đi vào dịp tết nên thác ít nước.
@@ -681,64 +741,64 @@
 Cá nhân nếu quay lại Mộc Châu sẽ không đến thác này lần nào nữa</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>{'name': 'La Meu', 'link': 'https://www.google.com/maps/contrib/108858956358165703026?hl=vi', 'contributor_id': '108858956358165703026', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVKW-aZD0iBs1KBFQlmzfMiMTfjpd4PfUn4GO-K2tEt1PLpZ3YY=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 117}</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>Thác Dải Yếm là điểm du lịch rất đáng đi. Đường đi dễ, xe máy hay ô tô đều thuận tiện. Không gian mát mẻ, thiên nhiên đẹp và trong lành.
 Nước thác xanh biếc, chảy mạnh nhưng nhìn rất êm và thơ mộng, chụp hình lên đẹp lắm. Khu vực được làm lối đi khá an toàn, dễ tham quan.
 Nhân viên ở đây dễ thương, nhiệt tình, hướng dẫn khách rất chu đáo và thân thiện. Phù hợp đi chơi cùng gia đình hoặc bạn bè để thư giãn, nghỉ ngơi.</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>9 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 256}</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>{'name': 'Thái Nguyễn', 'link': 'https://www.google.com/maps/contrib/105517365260915933657?hl=vi', 'contributor_id': '105517365260915933657', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXLOkY3FUSH3Mz-aapJXPQUgoCFlQP20PICWZGzVI3cPkRkBIt_ew=s120-c-rp-mo-ba12-br100', 'reviews': 65, 'photos': 175}</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>5</v>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>Nếu đi cùng Lover sẽ đẹp hơn.
 Nếu tự nhìn lại
@@ -806,116 +866,56 @@
 Hơn cả tới thiên đường</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>8 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>9 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 93, 'photos': 1103}</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>5</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 145, 'photos': 330}</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>5</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
+          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
+          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3 tháng trước</t>
+          <t>9 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
+          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 93, 'photos': 1103}</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
+          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 114, 'photos': 83}</t>
+          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 145, 'photos': 330}</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -923,59 +923,59 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
+          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 3220}</t>
+          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
+          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10 tháng trước</t>
+          <t>3 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 252, 'photos': 5012}</t>
+          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cảnh quan đẹp, ng dân thân thiện</t>
+          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>3 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
+          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 114, 'photos': 83}</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -983,25 +983,85 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
+          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 3220}</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>10 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 252, 'photos': 5012}</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Cảnh quan đẹp, ng dân thân thiện</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>6 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>9 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>{'name': 'Linh Nguyễn', 'link': 'https://www.google.com/maps/contrib/109820275513447282944?hl=vi', 'contributor_id': '109820275513447282944', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVpZ-SNyOn6byhXW5cnkMUzIYl8pLeo3scME3-VG4n2ps2S2tYx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 992}</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>5</v>
-      </c>
-      <c r="C25" t="inlineStr">
+      <c r="B28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>Thác đẹp, suối nước tự nhiên, đường đi dọc suối sạch sẽ
 Một số địa điểm du lịch ở Mộc Châu mọi người có thể tham khảo
@@ -1014,76 +1074,16 @@
 2. Cá Hồi Thanh Bảy</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>2 năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 81, 'photos': 188}</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>4</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>7 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>5</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 72, 'photos': 501}</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>5</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>4 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'reviews': 78, 'photos': 260}</t>
+          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 81, 'photos': 188}</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1091,46 +1091,106 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>7 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 72, 'photos': 501}</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>5 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'reviews': 78, 'photos': 260}</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
 Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 537, 'photos': 4147}</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B33" t="n">
         <v>4</v>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 574}</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>5</v>
-      </c>
-      <c r="C31" t="inlineStr">
+      <c r="B34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>Đúng tên gọi của nó. Thác cũng rất đẹp. Nếu vào mùa nước chắc còn đẹp hơn.
 Cảnh quan cũng rất sạch đẹp.
@@ -1139,66 +1199,6 @@
 - vé vào cổng giá phù hợp</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 653, 'photos': 4192}</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>5</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Thời gian chỉnh sửa: 2 năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 518}</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>5</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>4</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
-        </is>
-      </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>một năm trước</t>
@@ -1208,7 +1208,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
+          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 653, 'photos': 4198}</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1216,19 +1216,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
+          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>Thời gian chỉnh sửa: 2 năm trước</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 1623}</t>
+          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 517}</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1236,19 +1236,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>10 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>{'name': 'ninh Men', 'link': 'https://www.google.com/maps/contrib/103025469094717120638?hl=vi', 'contributor_id': '103025469094717120638', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJr8a3WVJHmayMF2FvRRdJjmyVlo0gmvjXedEtF6z5_xuOtxg=s120-c-rp-mo-ba12-br100', 'reviews': 29, 'photos': 168}</t>
+          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1256,168 +1256,228 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>5</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 1641}</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>5</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>10 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>{'name': 'ninh Men', 'link': 'https://www.google.com/maps/contrib/103025469094717120638?hl=vi', 'contributor_id': '103025469094717120638', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJr8a3WVJHmayMF2FvRRdJjmyVlo0gmvjXedEtF6z5_xuOtxg=s120-c-rp-mo-ba12-br100', 'reviews': 29, 'photos': 168}</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>4</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
           <t>Đi Thác Dải Yếm đúng hôm… uống trà sữa trân châu. 😭
 Vé 150k/người nhưng cá nhân mình thấy hơi hụt hẫng. Thác không quá đặc biệt, đi một vòng là hết, chủ yếu là chụp ảnh. Nếu không thích check-in thì chắc sẽ thấy hơi “không có gì” so với giá vé.</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>2 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 50, 'photos': 144}</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B41" t="n">
         <v>4</v>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWyzcZkQykW_QPymZ2fTMwerDVUm-XhQ6WZ0NqbjNzbEznIxcF7AQ=s120-c-rp-mo-ba12-br100', 'reviews': 149, 'photos': 3873}</t>
         </is>
       </c>
-      <c r="B39" t="n">
-        <v>5</v>
-      </c>
-      <c r="C39" t="inlineStr">
+      <c r="B42" t="n">
+        <v>5</v>
+      </c>
+      <c r="C42" t="inlineStr">
         <is>
           <t>Thác Dải Yếm, còn được gọi là thác Nàng, thác Bản Vặt, là một thác nước hùng vĩ nằm ở xã Mường Sang, huyện Mộc Châu, tỉnh Sơn La. Thác có chiều cao khoảng 100m, chia thành hai dòng thác chính, trông giống như một dải yếm đào mềm mại uốn lượn quanh vách núi.
 Thác Dải Yếm là một địa điểm du lịch hấp dẫn, thu hút khách du lịch trong và ngoài nước. Đây là nơi du khách có thể chiêm ngưỡng vẻ đẹp hùng vĩ của thác nước và tìm hiểu về truyền thuyết về thác.</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>2 năm trước</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'reviews': 97, 'photos': 178}</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="B43" t="n">
         <v>4</v>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'reviews': 28, 'photos': 264}</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="B44" t="n">
         <v>4</v>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'reviews': 75, 'photos': 503}</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B45" t="n">
         <v>4</v>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Thác Dải Yếm nằm trên dòng suối Vặt khởi nguồn từ hai khe nước Bó Co Lắm và Bo Tá Cháu ở đầu bản Vặt, một bản của người Thái có lịch sử lâu đời. Suối Vặt chảy được 5 km đổ vào suối Bó Sập, một dòng suối lớn bắt nguồn từ bản Bó Sập giáp biên giới Việt Lào rồi chảy về đất Yên Châu. Tại nơi hợp lưu của hai suối, dòng nước gặp một vùng đá vôi và đổ xuống phía dưới tạo thành thác Dải Yếm.[5]
 Thác Dải Yếm bao gồm hai phần, thác nước phía trên rộng 70 mét, thác nước phía dưới nằm cách đó 150-200 mét. Vào mùa khô, thác phía dưới chỉ có một dòng chảy từ độ cao 50 m xuống triền đá ở dưới. hai thác đổ xuống với tổng chiều cao 100m, một bên được chia làm 9 tầng, bên còn lại 5 tầng. Cách giữa hai phần thác là một bãi đất phẳng thuận tiện cho việc tham quan của du khách. Thảm thực vật trên đỉnh thác cũng khá phong phú.</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>{'name': 'Chi Ho', 'link': 'https://www.google.com/maps/contrib/102731288821463748765?hl=vi', 'contributor_id': '102731288821463748765', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWV3y9KiqGo7jILq-ZzBkSw28LDZHnwKXBhstpTEeRvr9jffKE=s120-c-rp-mo-ba12-br100', 'reviews': 85, 'photos': 1540}</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>5</v>
-      </c>
-      <c r="C43" t="inlineStr">
+      <c r="B46" t="n">
+        <v>5</v>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>Thác Dải Yếm đẹp và hùng vĩ, xứng đáng cho chuyến picnic cuối tuần. Đường đi hơi gập ghềnh nhưng đến nơi thì quên hết mệt mỏi. Nước mát rượi, âm thanh róc rách rất thư giãn. Tiếc là hơi đông vào cuối tuần, nhưng cảnh đẹp bù đắp tất cả! Nên đi vào ngày thường nếu muốn yên tĩnh hơn.</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>2 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'reviews': 8, 'photos': 90}</t>
         </is>
       </c>
-      <c r="B44" t="n">
+      <c r="B47" t="n">
         <v>4</v>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>một năm trước</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 153, 'photos': 1307}</t>
         </is>
       </c>
-      <c r="B45" t="n">
+      <c r="B48" t="n">
         <v>4</v>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Thác nhỏ cũng đẹp nhưng được trang trí dành cho du lịch rồi về độ rộng nhiều tầng và thiên nhiên thì không bằng thác Nàng Tiên hoặc thác Chiềng Khoa.
 Thác Dải Yếm được đầu tư khang trang nhưng đi bộ từ bãi gửi xe vào thác hơi bị xa (vé gửi xe 30k), đường đi vào và khu thác bên trong nhiều khu chụp ảnh checkin được trang trí chụp ảnh đẹp mắt. Giá vé tháng 1/2024 là 80k/ người vào cổng nhưng đến 30/4/2024 tăng lên 100k/ng giá vé hơi cao với việc vào ngắm thác.
@@ -1425,27 +1485,27 @@
 - Bản thân mình cảm nhận thì cũng bình thường thác không cao không rộng dài đẹp nhiều tầng bằng thác Nàng Tiên hoặc Chiềng Khoa. Nói chung đi du lịch Mộc Châu ghé qua cho biết thôi. Chứ để quay lại thì ít khả năng.</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>2 năm trước</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 139, 'photos': 569}</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 139, 'photos': 560}</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
         <v>4</v>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>View đẹp, chỉ tiếc là ghé hồi tháng 5 lúc đang mùa mưa, nên không được đi trải nghiệm nhiều.</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>11 tháng trước</t>
         </is>

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,7 +565,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>{'name': 'THANH NGUYEN', 'link': 'https://www.google.com/maps/contrib/110418688752170937071?hl=vi', 'contributor_id': '110418688752170937071', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIBtT-SxDlGGJM5jA47OmxpGvFdaG6EOeSswcBwx4VuXgnOdQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 71, 'photos': 238}</t>
+          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 302, 'photos': 3616}</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -573,19 +573,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>thác đẹp nhưng nên đi vào mùa nước sẽ thấy sự khác biệt hơn nhiều</t>
+          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7 tháng trước</t>
+          <t>5 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>{'name': 'Cửu Quang Nguyễn', 'link': 'https://www.google.com/maps/contrib/107704339232071144994?hl=vi', 'contributor_id': '107704339232071144994', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV2_oJLqzlVCtXNV77ConxSPDhhMhFP-czjeCf6uCm7cabO88k=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 79, 'photos': 359}</t>
+          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 25}</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -593,147 +593,87 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm nằm trong khu du lịch sinh thái thác Dải Yếm, đường đi khá tiện lợi để ghé vào, tuy nhiên cần chú ý lối vào có khúc cua dốc khá ngoặt. Vé vào là 150k/người, bên trong có khá nhiều vị trí để du ngoạn và ngắm cảnh, đặc biệt là khu vực thác nước rất hùng vĩ và mát mẻ, có cầu dẫn vào nhìn rất thơ mộng và tuyệt vời. Nếu có dịp ghé lên Mộc Châu thì nên ghé vào đây chơi 1 lần để du ngoạn thắng cảnh thiên nhiên tại nơi đây.</t>
+          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5 tháng trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Anh Quân', 'link': 'https://www.google.com/maps/contrib/111631093743063403454?hl=vi', 'contributor_id': '111631093743063403454', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIy-NjGEZ7ggp1yhLvVSe2iSDFAUAF4AILlK1IHBmSbkPzlKg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 9, 'photos': 24}</t>
+          <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'reviews': 16, 'photos': 114}</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>5</v>
       </c>
       <c r="C9" t="inlineStr">
-        <is>
-          <t>Cảnh đẹp, nhưng xu là đi ngay lúc mưa nên thác có nước như cf</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'reviews': 302, 'photos': 3616}</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>5 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 25}</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>6 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'reviews': 16, 'photos': 114}</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" t="inlineStr">
         <is>
           <t>Đi tầm trưa nắng đẹp
 Thác nhỏ, đi cũng không mất quá nhiều thời gian
 Có cầu kính</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>{'name': 'Nghĩa Nguyễn Trung', 'link': 'https://www.google.com/maps/contrib/107253778101970197900?hl=vi', 'contributor_id': '107253778101970197900', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUNLHg5XlpgtWVVTp_oJKOYAejqmQORtgQ_Oe2vusE5W_sQoZc5=s120-c-rp-mo-ba12-br100', 'reviews': 275, 'photos': 1279}</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>Khu vực thác nước đẹp, nhiều cảnh quan, nhiều góc chụp đẹp.</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>3 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>{'name': 'Frugal Flow', 'link': 'https://www.google.com/maps/contrib/107453311426556875441?hl=vi', 'contributor_id': '107453311426556875441', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUspWRVGEEQ_LyS16qRB57xWZ-kgNRIjgdLPY8T7HzvNMFlILCV=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 85}</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>Đi vào một ngày nắng. Nắng hắt lên mặt nước long lanh nên xinh xắn hẳn:&gt; Chỉ là thác nay có vẻ hơi ít nc nên không như mình tưởng tượng.</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'reviews': 220, 'photos': 307}</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B12" t="n">
         <v>3</v>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Trải nghiệm vừa phải
 Giá vé theo trải nghiệm đi nhiều thác khác nhau của mình thì là khá cao so với các nơi khác, mình đi vào dịp tết nên thác ít nước.
@@ -741,64 +681,64 @@
 Cá nhân nếu quay lại Mộc Châu sẽ không đến thác này lần nào nữa</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>{'name': 'La Meu', 'link': 'https://www.google.com/maps/contrib/108858956358165703026?hl=vi', 'contributor_id': '108858956358165703026', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVKW-aZD0iBs1KBFQlmzfMiMTfjpd4PfUn4GO-K2tEt1PLpZ3YY=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 117}</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>5</v>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Thác Dải Yếm là điểm du lịch rất đáng đi. Đường đi dễ, xe máy hay ô tô đều thuận tiện. Không gian mát mẻ, thiên nhiên đẹp và trong lành.
 Nước thác xanh biếc, chảy mạnh nhưng nhìn rất êm và thơ mộng, chụp hình lên đẹp lắm. Khu vực được làm lối đi khá an toàn, dễ tham quan.
 Nhân viên ở đây dễ thương, nhiệt tình, hướng dẫn khách rất chu đáo và thân thiện. Phù hợp đi chơi cùng gia đình hoặc bạn bè để thư giãn, nghỉ ngơi.</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>9 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'reviews': 25, 'photos': 256}</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>5</v>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>{'name': 'Thái Nguyễn', 'link': 'https://www.google.com/maps/contrib/105517365260915933657?hl=vi', 'contributor_id': '105517365260915933657', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXLOkY3FUSH3Mz-aapJXPQUgoCFlQP20PICWZGzVI3cPkRkBIt_ew=s120-c-rp-mo-ba12-br100', 'reviews': 65, 'photos': 175}</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>5</v>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Nếu đi cùng Lover sẽ đẹp hơn.
 Nếu tự nhìn lại
@@ -866,56 +806,116 @@
 Hơn cả tới thiên đường</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>9 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 93, 'photos': 1103}</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 145, 'photos': 330}</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'reviews': 57, 'photos': 1245}</t>
+          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
+          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>3 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 93, 'photos': 1103}</t>
+          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
+          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>3 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 145, 'photos': 330}</t>
+          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 114, 'photos': 83}</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -923,59 +923,59 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
+          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7 tháng trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'reviews': 38, 'photos': 73}</t>
+          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 3220}</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
+          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3 tháng trước</t>
+          <t>10 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'reviews': 34, 'photos': 79}</t>
+          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 252, 'photos': 5012}</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
+          <t>Cảnh quan đẹp, ng dân thân thiện</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3 tháng trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'reviews': 114, 'photos': 83}</t>
+          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -983,85 +983,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
+          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>9 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 3220}</t>
+          <t>{'name': 'Linh Nguyễn', 'link': 'https://www.google.com/maps/contrib/109820275513447282944?hl=vi', 'contributor_id': '109820275513447282944', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVpZ-SNyOn6byhXW5cnkMUzIYl8pLeo3scME3-VG4n2ps2S2tYx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 992}</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" t="inlineStr">
-        <is>
-          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>10 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'reviews': 252, 'photos': 5012}</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>5</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Cảnh quan đẹp, ng dân thân thiện</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>6 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 41}</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>5</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>9 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>{'name': 'Linh Nguyễn', 'link': 'https://www.google.com/maps/contrib/109820275513447282944?hl=vi', 'contributor_id': '109820275513447282944', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVpZ-SNyOn6byhXW5cnkMUzIYl8pLeo3scME3-VG4n2ps2S2tYx=s120-c-rp-mo-ba12-br100', 'reviews': 144, 'photos': 992}</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>5</v>
-      </c>
-      <c r="C28" t="inlineStr">
         <is>
           <t>Thác đẹp, suối nước tự nhiên, đường đi dọc suối sạch sẽ
 Một số địa điểm du lịch ở Mộc Châu mọi người có thể tham khảo
@@ -1074,16 +1014,76 @@
 2. Cá Hồi Thanh Bảy</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 81, 'photos': 188}</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>7 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 72, 'photos': 501}</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2 năm trước</t>
+          <t>5 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'reviews': 81, 'photos': 188}</t>
+          <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'reviews': 78, 'photos': 260}</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1091,27 +1091,28 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
+          <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
+Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'reviews': 12, 'photos': 65}</t>
+          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 537, 'photos': 4147}</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
+          <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1123,74 +1124,13 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'reviews': 72, 'photos': 501}</t>
+          <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 574}</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>5</v>
       </c>
       <c r="C31" t="inlineStr">
-        <is>
-          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>5 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'reviews': 78, 'photos': 260}</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>4</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
-Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 537, 'photos': 4147}</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>4</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'reviews': 91, 'photos': 574}</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>5</v>
-      </c>
-      <c r="C34" t="inlineStr">
         <is>
           <t>Đúng tên gọi của nó. Thác cũng rất đẹp. Nếu vào mùa nước chắc còn đẹp hơn.
 Cảnh quan cũng rất sạch đẹp.
@@ -1199,6 +1139,66 @@
 - vé vào cổng giá phù hợp</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 653, 'photos': 4198}</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Thời gian chỉnh sửa: 2 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 517}</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>một năm trước</t>
@@ -1208,7 +1208,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 653, 'photos': 4198}</t>
+          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1216,19 +1216,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
+          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Thời gian chỉnh sửa: 2 năm trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 517}</t>
+          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 1641}</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1236,19 +1236,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
+          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>10 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
+          <t>{'name': 'ninh Men', 'link': 'https://www.google.com/maps/contrib/103025469094717120638?hl=vi', 'contributor_id': '103025469094717120638', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJr8a3WVJHmayMF2FvRRdJjmyVlo0gmvjXedEtF6z5_xuOtxg=s120-c-rp-mo-ba12-br100', 'reviews': 29, 'photos': 168}</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1256,27 +1256,28 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
+          <t>Đi Thác Dải Yếm đúng hôm… uống trà sữa trân châu. 😭
+Vé 150k/người nhưng cá nhân mình thấy hơi hụt hẫng. Thác không quá đặc biệt, đi một vòng là hết, chủ yếu là chụp ảnh. Nếu không thích check-in thì chắc sẽ thấy hơi “không có gì” so với giá vé.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
+          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 50, 'photos': 144}</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
+          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1288,7 +1289,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 1641}</t>
+          <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWyzcZkQykW_QPymZ2fTMwerDVUm-XhQ6WZ0NqbjNzbEznIxcF7AQ=s120-c-rp-mo-ba12-br100', 'reviews': 149, 'photos': 3873}</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1296,19 +1297,20 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+          <t>Thác Dải Yếm, còn được gọi là thác Nàng, thác Bản Vặt, là một thác nước hùng vĩ nằm ở xã Mường Sang, huyện Mộc Châu, tỉnh Sơn La. Thác có chiều cao khoảng 100m, chia thành hai dòng thác chính, trông giống như một dải yếm đào mềm mại uốn lượn quanh vách núi.
+Thác Dải Yếm là một địa điểm du lịch hấp dẫn, thu hút khách du lịch trong và ngoài nước. Đây là nơi du khách có thể chiêm ngưỡng vẻ đẹp hùng vĩ của thác nước và tìm hiểu về truyền thuyết về thác.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>10 tháng trước</t>
+          <t>2 năm trước</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>{'name': 'ninh Men', 'link': 'https://www.google.com/maps/contrib/103025469094717120638?hl=vi', 'contributor_id': '103025469094717120638', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJr8a3WVJHmayMF2FvRRdJjmyVlo0gmvjXedEtF6z5_xuOtxg=s120-c-rp-mo-ba12-br100', 'reviews': 29, 'photos': 168}</t>
+          <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'reviews': 97, 'photos': 178}</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1316,20 +1318,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Đi Thác Dải Yếm đúng hôm… uống trà sữa trân châu. 😭
-Vé 150k/người nhưng cá nhân mình thấy hơi hụt hẫng. Thác không quá đặc biệt, đi một vòng là hết, chủ yếu là chụp ảnh. Nếu không thích check-in thì chắc sẽ thấy hơi “không có gì” so với giá vé.</t>
+          <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'reviews': 50, 'photos': 144}</t>
+          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'reviews': 28, 'photos': 264}</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1337,7 +1338,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
+          <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1349,48 +1350,48 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWyzcZkQykW_QPymZ2fTMwerDVUm-XhQ6WZ0NqbjNzbEznIxcF7AQ=s120-c-rp-mo-ba12-br100', 'reviews': 149, 'photos': 3873}</t>
+          <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'reviews': 75, 'photos': 503}</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm, còn được gọi là thác Nàng, thác Bản Vặt, là một thác nước hùng vĩ nằm ở xã Mường Sang, huyện Mộc Châu, tỉnh Sơn La. Thác có chiều cao khoảng 100m, chia thành hai dòng thác chính, trông giống như một dải yếm đào mềm mại uốn lượn quanh vách núi.
-Thác Dải Yếm là một địa điểm du lịch hấp dẫn, thu hút khách du lịch trong và ngoài nước. Đây là nơi du khách có thể chiêm ngưỡng vẻ đẹp hùng vĩ của thác nước và tìm hiểu về truyền thuyết về thác.</t>
+          <t>Thác Dải Yếm nằm trên dòng suối Vặt khởi nguồn từ hai khe nước Bó Co Lắm và Bo Tá Cháu ở đầu bản Vặt, một bản của người Thái có lịch sử lâu đời. Suối Vặt chảy được 5 km đổ vào suối Bó Sập, một dòng suối lớn bắt nguồn từ bản Bó Sập giáp biên giới Việt Lào rồi chảy về đất Yên Châu. Tại nơi hợp lưu của hai suối, dòng nước gặp một vùng đá vôi và đổ xuống phía dưới tạo thành thác Dải Yếm.[5]
+Thác Dải Yếm bao gồm hai phần, thác nước phía trên rộng 70 mét, thác nước phía dưới nằm cách đó 150-200 mét. Vào mùa khô, thác phía dưới chỉ có một dòng chảy từ độ cao 50 m xuống triền đá ở dưới. hai thác đổ xuống với tổng chiều cao 100m, một bên được chia làm 9 tầng, bên còn lại 5 tầng. Cách giữa hai phần thác là một bãi đất phẳng thuận tiện cho việc tham quan của du khách. Thảm thực vật trên đỉnh thác cũng khá phong phú.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2 năm trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'reviews': 97, 'photos': 178}</t>
+          <t>{'name': 'Chi Ho', 'link': 'https://www.google.com/maps/contrib/102731288821463748765?hl=vi', 'contributor_id': '102731288821463748765', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWV3y9KiqGo7jILq-ZzBkSw28LDZHnwKXBhstpTEeRvr9jffKE=s120-c-rp-mo-ba12-br100', 'reviews': 85, 'photos': 1540}</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
+          <t>Thác Dải Yếm đẹp và hùng vĩ, xứng đáng cho chuyến picnic cuối tuần. Đường đi hơi gập ghềnh nhưng đến nơi thì quên hết mệt mỏi. Nước mát rượi, âm thanh róc rách rất thư giãn. Tiếc là hơi đông vào cuối tuần, nhưng cảnh đẹp bù đắp tất cả! Nên đi vào ngày thường nếu muốn yên tĩnh hơn.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'reviews': 28, 'photos': 264}</t>
+          <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'reviews': 8, 'photos': 90}</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1398,7 +1399,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
+          <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1410,74 +1411,13 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'reviews': 75, 'photos': 503}</t>
+          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 153, 'photos': 1307}</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>4</v>
       </c>
       <c r="C45" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm nằm trên dòng suối Vặt khởi nguồn từ hai khe nước Bó Co Lắm và Bo Tá Cháu ở đầu bản Vặt, một bản của người Thái có lịch sử lâu đời. Suối Vặt chảy được 5 km đổ vào suối Bó Sập, một dòng suối lớn bắt nguồn từ bản Bó Sập giáp biên giới Việt Lào rồi chảy về đất Yên Châu. Tại nơi hợp lưu của hai suối, dòng nước gặp một vùng đá vôi và đổ xuống phía dưới tạo thành thác Dải Yếm.[5]
-Thác Dải Yếm bao gồm hai phần, thác nước phía trên rộng 70 mét, thác nước phía dưới nằm cách đó 150-200 mét. Vào mùa khô, thác phía dưới chỉ có một dòng chảy từ độ cao 50 m xuống triền đá ở dưới. hai thác đổ xuống với tổng chiều cao 100m, một bên được chia làm 9 tầng, bên còn lại 5 tầng. Cách giữa hai phần thác là một bãi đất phẳng thuận tiện cho việc tham quan của du khách. Thảm thực vật trên đỉnh thác cũng khá phong phú.</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>{'name': 'Chi Ho', 'link': 'https://www.google.com/maps/contrib/102731288821463748765?hl=vi', 'contributor_id': '102731288821463748765', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWV3y9KiqGo7jILq-ZzBkSw28LDZHnwKXBhstpTEeRvr9jffKE=s120-c-rp-mo-ba12-br100', 'reviews': 85, 'photos': 1540}</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>5</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm đẹp và hùng vĩ, xứng đáng cho chuyến picnic cuối tuần. Đường đi hơi gập ghềnh nhưng đến nơi thì quên hết mệt mỏi. Nước mát rượi, âm thanh róc rách rất thư giãn. Tiếc là hơi đông vào cuối tuần, nhưng cảnh đẹp bù đắp tất cả! Nên đi vào ngày thường nếu muốn yên tĩnh hơn.</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'reviews': 8, 'photos': 90}</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>4</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 153, 'photos': 1307}</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>4</v>
-      </c>
-      <c r="C48" t="inlineStr">
         <is>
           <t>Thác nhỏ cũng đẹp nhưng được trang trí dành cho du lịch rồi về độ rộng nhiều tầng và thiên nhiên thì không bằng thác Nàng Tiên hoặc thác Chiềng Khoa.
 Thác Dải Yếm được đầu tư khang trang nhưng đi bộ từ bãi gửi xe vào thác hơi bị xa (vé gửi xe 30k), đường đi vào và khu thác bên trong nhiều khu chụp ảnh checkin được trang trí chụp ảnh đẹp mắt. Giá vé tháng 1/2024 là 80k/ người vào cổng nhưng đến 30/4/2024 tăng lên 100k/ng giá vé hơi cao với việc vào ngắm thác.
@@ -1485,27 +1425,27 @@
 - Bản thân mình cảm nhận thì cũng bình thường thác không cao không rộng dài đẹp nhiều tầng bằng thác Nàng Tiên hoặc Chiềng Khoa. Nói chung đi du lịch Mộc Châu ghé qua cho biết thôi. Chứ để quay lại thì ít khả năng.</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>2 năm trước</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 139, 'photos': 560}</t>
         </is>
       </c>
-      <c r="B49" t="n">
+      <c r="B46" t="n">
         <v>4</v>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>View đẹp, chỉ tiếc là ghé hồi tháng 5 lúc đang mùa mưa, nên không được đi trải nghiệm nhiều.</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>11 tháng trước</t>
         </is>

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -520,7 +520,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 374, 'photos': 2644}</t>
+          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 374, 'photos': 2645}</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -835,7 +835,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 93, 'photos': 1103}</t>
+          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 93, 'photos': 1120}</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1168,7 +1168,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 148, 'photos': 517}</t>
+          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'reviews': 147, 'photos': 517}</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1188,7 +1188,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 227}</t>
+          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 233}</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1434,7 +1434,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 139, 'photos': 560}</t>
+          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 138, 'photos': 560}</t>
         </is>
       </c>
       <c r="B46" t="n">

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>{'name': 'ZjmLee YTBer', 'link': 'https://www.google.com/maps/contrib/100979561872983589256?hl=vi', 'contributor_id': '100979561872983589256', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU6i9poRXPBKYv-WgZHmB9chW6jRPCOh3klZ1Z7Yv_DOaukn4g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 80, 'photos': 1252}</t>
+          <t>{'name': 'ZjmLee YTBer', 'link': 'https://www.google.com/maps/contrib/100979561872983589256?hl=vi', 'contributor_id': '100979561872983589256', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU6i9poRXPBKYv-WgZHmB9chW6jRPCOh3klZ1Z7Yv_DOaukn4g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 79, 'photos': 1213}</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -542,7 +542,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>{'name': 'Vĩ Lê Bá', 'link': 'https://www.google.com/maps/contrib/115860838984920745696?hl=vi', 'contributor_id': '115860838984920745696', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7wdRrYJWeEmKs7YInZz_FDg-T90l2ImigSwJKL2hWmQu75bzm=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 60, 'photos': 94}</t>
+          <t>{'name': 'Vĩ Lê Bá', 'link': 'https://www.google.com/maps/contrib/115860838984920745696?hl=vi', 'contributor_id': '115860838984920745696', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7wdRrYJWeEmKs7YInZz_FDg-T90l2ImigSwJKL2hWmQu75bzm=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 60, 'photos': 96}</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -835,7 +835,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 93, 'photos': 1120}</t>
+          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'reviews': 94, 'photos': 1120}</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1188,7 +1188,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 162, 'photos': 233}</t>
+          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'reviews': 164, 'photos': 233}</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1434,7 +1434,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 138, 'photos': 560}</t>
+          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 138, 'photos': 561}</t>
         </is>
       </c>
       <c r="B46" t="n">

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -542,7 +542,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>{'name': 'Vĩ Lê Bá', 'link': 'https://www.google.com/maps/contrib/115860838984920745696?hl=vi', 'contributor_id': '115860838984920745696', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7wdRrYJWeEmKs7YInZz_FDg-T90l2ImigSwJKL2hWmQu75bzm=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 60, 'photos': 96}</t>
+          <t>{'name': 'Vĩ Lê Bá', 'link': 'https://www.google.com/maps/contrib/115860838984920745696?hl=vi', 'contributor_id': '115860838984920745696', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7wdRrYJWeEmKs7YInZz_FDg-T90l2ImigSwJKL2hWmQu75bzm=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 61, 'photos': 96}</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1148,7 +1148,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 653, 'photos': 4198}</t>
+          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 653, 'photos': 4196}</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1208,7 +1208,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 250}</t>
+          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 248}</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1411,7 +1411,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 153, 'photos': 1307}</t>
+          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 153, 'photos': 1294}</t>
         </is>
       </c>
       <c r="B45" t="n">

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -667,7 +667,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'reviews': 220, 'photos': 307}</t>
+          <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'reviews': 220, 'photos': 316}</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -705,7 +705,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>10 tháng trước</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>9 tháng trước</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 190, 'photos': 3220}</t>
+          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'reviews': 191, 'photos': 3220}</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1104,7 +1104,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 537, 'photos': 4147}</t>
+          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'reviews': 536, 'photos': 4147}</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1148,7 +1148,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 653, 'photos': 4196}</t>
+          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'reviews': 652, 'photos': 4196}</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1208,7 +1208,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 136, 'photos': 248}</t>
+          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'reviews': 134, 'photos': 248}</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1411,7 +1411,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 153, 'photos': 1294}</t>
+          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'reviews': 152, 'photos': 1294}</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1434,7 +1434,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 138, 'photos': 561}</t>
+          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'reviews': 139, 'photos': 561}</t>
         </is>
       </c>
       <c r="B46" t="n">

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -667,7 +667,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'reviews': 220, 'photos': 316}</t>
+          <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'reviews': 222, 'photos': 316}</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -855,7 +855,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 145, 'photos': 330}</t>
+          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'reviews': 146, 'photos': 330}</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1289,7 +1289,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWyzcZkQykW_QPymZ2fTMwerDVUm-XhQ6WZ0NqbjNzbEznIxcF7AQ=s120-c-rp-mo-ba12-br100', 'reviews': 149, 'photos': 3873}</t>
+          <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVOAB-25PMt-dfRNT-0Cxi6yv3ndR1rsuSnkmcbVorHpLvMDfzp2g=s120-c-rp-mo-ba12-br100', 'reviews': 149, 'photos': 3873}</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1371,7 +1371,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>{'name': 'Chi Ho', 'link': 'https://www.google.com/maps/contrib/102731288821463748765?hl=vi', 'contributor_id': '102731288821463748765', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWV3y9KiqGo7jILq-ZzBkSw28LDZHnwKXBhstpTEeRvr9jffKE=s120-c-rp-mo-ba12-br100', 'reviews': 85, 'photos': 1540}</t>
+          <t>{'name': 'Chi Ho', 'link': 'https://www.google.com/maps/contrib/102731288821463748765?hl=vi', 'contributor_id': '102731288821463748765', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWV3y9KiqGo7jILq-ZzBkSw28LDZHnwKXBhstpTEeRvr9jffKE=s120-c-rp-mo-ba12-br100', 'reviews': 85, 'photos': 1545}</t>
         </is>
       </c>
       <c r="B43" t="n">

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -520,7 +520,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 374, 'photos': 2645}</t>
+          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 374, 'photos': 2657}</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -558,7 +558,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>{'name': 'Chi Ho', 'link': 'https://www.google.com/maps/contrib/102731288821463748765?hl=vi', 'contributor_id': '102731288821463748765', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWV3y9KiqGo7jILq-ZzBkSw28LDZHnwKXBhstpTEeRvr9jffKE=s120-c-rp-mo-ba12-br100', 'reviews': 85, 'photos': 1545}</t>
+          <t>{'name': 'Chi Ho', 'link': 'https://www.google.com/maps/contrib/102731288821463748765?hl=vi', 'contributor_id': '102731288821463748765', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWV3y9KiqGo7jILq-ZzBkSw28LDZHnwKXBhstpTEeRvr9jffKE=s120-c-rp-mo-ba12-br100', 'reviews': 85, 'photos': 1557}</t>
         </is>
       </c>
       <c r="B43" t="n">

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -520,7 +520,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 374, 'photos': 2657}</t>
+          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 377, 'photos': 2657}</t>
         </is>
       </c>
       <c r="B5" t="n">

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,6 +562,995 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>{'name': 'THANH NGUYEN', 'link': 'https://www.google.com/maps/contrib/110418688752170937071?hl=vi', 'contributor_id': '110418688752170937071', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIBtT-SxDlGGJM5jA47OmxpGvFdaG6EOeSswcBwx4VuXgnOdQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 71, 'photos': 238}</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>thác đẹp nhưng nên đi vào mùa nước sẽ thấy sự khác biệt hơn nhiều</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>{'name': 'Cửu Quang Nguyễn', 'link': 'https://www.google.com/maps/contrib/107704339232071144994?hl=vi', 'contributor_id': '107704339232071144994', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV2_oJLqzlVCtXNV77ConxSPDhhMhFP-czjeCf6uCm7cabO88k=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 79, 'photos': 359}</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Thác Dải Yếm nằm trong khu du lịch sinh thái thác Dải Yếm, đường đi khá tiện lợi để ghé vào, tuy nhiên cần chú ý lối vào có khúc cua dốc khá ngoặt. Vé vào là 150k/người, bên trong có khá nhiều vị trí để du ngoạn và ngắm cảnh, đặc biệt là khu vực thác nước rất hùng vĩ và mát mẻ, có cầu dẫn vào nhìn rất thơ mộng và tuyệt vời. Nếu có dịp ghé lên Mộc Châu thì nên ghé vào đây chơi 1 lần để du ngoạn thắng cảnh thiên nhiên tại nơi đây.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>{'name': 'Nguyễn Anh Quân', 'link': 'https://www.google.com/maps/contrib/111631093743063403454?hl=vi', 'contributor_id': '111631093743063403454', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIy-NjGEZ7ggp1yhLvVSe2iSDFAUAF4AILlK1IHBmSbkPzlKg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 9, 'photos': 24}</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Cảnh đẹp, nhưng xu là đi ngay lúc mưa nên thác có nước như cf</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 302, 'photos': 3616}</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>5 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 12, 'photos': 25}</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>6 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 16, 'photos': 114}</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Đi tầm trưa nắng đẹp
+Thác nhỏ, đi cũng không mất quá nhiều thời gian
+Có cầu kính</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>7 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>{'name': 'Nghĩa Nguyễn Trung', 'link': 'https://www.google.com/maps/contrib/107253778101970197900?hl=vi', 'contributor_id': '107253778101970197900', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUNLHg5XlpgtWVVTp_oJKOYAejqmQORtgQ_Oe2vusE5W_sQoZc5=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 275, 'photos': 1279}</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Khu vực thác nước đẹp, nhiều cảnh quan, nhiều góc chụp đẹp.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>{'name': 'Frugal Flow', 'link': 'https://www.google.com/maps/contrib/107453311426556875441?hl=vi', 'contributor_id': '107453311426556875441', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUspWRVGEEQ_LyS16qRB57xWZ-kgNRIjgdLPY8T7HzvNMFlILCV=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 25, 'photos': 85}</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Đi vào một ngày nắng. Nắng hắt lên mặt nước long lanh nên xinh xắn hẳn:&gt; Chỉ là thác nay có vẻ hơi ít nc nên không như mình tưởng tượng.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>7 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 222, 'photos': 316}</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Trải nghiệm vừa phải
+Giá vé theo trải nghiệm đi nhiều thác khác nhau của mình thì là khá cao so với các nơi khác, mình đi vào dịp tết nên thác ít nước.
+Cảnh quan xung quanh thác ở mức bình thường.
+Cá nhân nếu quay lại Mộc Châu sẽ không đến thác này lần nào nữa</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>{'name': 'La Meu', 'link': 'https://www.google.com/maps/contrib/108858956358165703026?hl=vi', 'contributor_id': '108858956358165703026', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVKW-aZD0iBs1KBFQlmzfMiMTfjpd4PfUn4GO-K2tEt1PLpZ3YY=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 25, 'photos': 117}</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Thác Dải Yếm là điểm du lịch rất đáng đi. Đường đi dễ, xe máy hay ô tô đều thuận tiện. Không gian mát mẻ, thiên nhiên đẹp và trong lành.
+Nước thác xanh biếc, chảy mạnh nhưng nhìn rất êm và thơ mộng, chụp hình lên đẹp lắm. Khu vực được làm lối đi khá an toàn, dễ tham quan.
+Nhân viên ở đây dễ thương, nhiệt tình, hướng dẫn khách rất chu đáo và thân thiện. Phù hợp đi chơi cùng gia đình hoặc bạn bè để thư giãn, nghỉ ngơi.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>10 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 25, 'photos': 256}</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>8 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>{'name': 'Thái Nguyễn', 'link': 'https://www.google.com/maps/contrib/105517365260915933657?hl=vi', 'contributor_id': '105517365260915933657', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXLOkY3FUSH3Mz-aapJXPQUgoCFlQP20PICWZGzVI3cPkRkBIt_ew=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 65, 'photos': 175}</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Nếu đi cùng Lover sẽ đẹp hơn.
+Nếu tự nhìn lại
+Quãng thời gian qua
+Đã có lúc nước mắt anh
+Nuốt ngược vào trong
+Cay đắng
+Tự mình trách
+Vì không trói được tiếng yêu
+Vì anh muốn quan tâm em
+Bằng tất cả những yêu thương
+Bao năm anh có được
+Mà sao mắt môi em
+Vẫn chưa khi nào bằng lòng
+Giờ thì anh đã can đảm
+Để rời xa em rồi
+Đừng khóc nhé em người ơi
+Dù rằng đường mình chung đôi
+Anh từng ngỡ sẽ dài
+Người ta yêu
+Nào đâu cứ phải
+Bên nhau đến cùng
+Giờ thì anh đã can đảm
+Để nhìn em mỉm cười
+Và cám ơn em ngày qua
+Dù điều này làm anh đau
+Hơn cả tới thiên đường
+Sẽ còn mình anh
+Với nỗi bất an
+Sẽ chẳng biết phải khóc hay cười
+Những khi nhớ em
+Rồi lo lắng
+Ổn không nếu em thiếu anh
+Ngủ ngoan nhé
+Em thân yêu của anh
+Đừng bắt màn đêm
+Len vào đôi mắt tròn
+Vào buổi sáng hôm sau
+Bình yên như chưa yêu nhau
+Giờ thì anh đã can đảm
+Để rời xa em rồi
+Đừng khóc nhé em người ơi
+Dù rằng đường mình chung đôi
+Anh từng ngỡ sẽ dài
+Người ta yêu
+Nào đâu cứ phải
+Bên nhau đến cùng
+Giờ thì anh đã can đảm
+Để nhìn em mỉm cười
+Và cám ơn em ngày qua
+Dù điều này làm anh đau
+Hơn cả tới thiên đường
+Giờ thì anh đã can đảm
+Để rời xa em rồi
+Đừng khóc nhé em người ơi
+Dù rằng đường mình chung đôi
+Anh từng ngỡ sẽ dài
+Người ta yêu
+Nào đâu cứ phải
+Bên nhau đến cùng
+Giờ thì anh đã can đảm
+Để nhìn em mỉm cười
+Và cám ơn em ngày qua
+Dù điều này làm anh đau
+Hơn cả tới thiên đường</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>9 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 57, 'photos': 1245}</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>9 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 94, 'photos': 1120}</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 146, 'photos': 330}</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>7 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 38, 'photos': 73}</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>3 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 34, 'photos': 79}</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>3 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 114, 'photos': 83}</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>9 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 191, 'photos': 3220}</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>11 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 252, 'photos': 5012}</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Cảnh quan đẹp, ng dân thân thiện</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>6 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 12, 'photos': 41}</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>9 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>{'name': 'Linh Nguyễn', 'link': 'https://www.google.com/maps/contrib/109820275513447282944?hl=vi', 'contributor_id': '109820275513447282944', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVpZ-SNyOn6byhXW5cnkMUzIYl8pLeo3scME3-VG4n2ps2S2tYx=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 144, 'photos': 992}</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Thác đẹp, suối nước tự nhiên, đường đi dọc suối sạch sẽ
+Một số địa điểm du lịch ở Mộc Châu mọi người có thể tham khảo
+1. Phố đi bộ Mộc Châu: bên trong có nhiều cửa hàng bán đặc sản, đồ thổ cẩm, có bán đồ ăn, có hoạt động văn nghệ, phun tuyết… vé vào cổng 50k/ người
+2. Rừng thông bản Áng: khu du lịch rộng, đi dạo bộ quanh hồ, ngắm rừng thông. Bên trong có quán cafe, quán ăn. Lúc mình đi thấy đang sửa chữa mở rộng thêm
+3. Đồi chè trái tim
+4. Thác dải yếm: chỗ thác nước và đường đi men suối đẹp nha, có luôn cầu kính ( đi cầu kính mua vé riêng). Mình đi dịp trước tết hoa đào nở nhiều đẹp lắm
+Quán ăn
+1. Ẩm thực Tuấn Gù
+2. Cá Hồi Thanh Bảy</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 81, 'photos': 188}</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>8 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 12, 'photos': 65}</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 72, 'photos': 501}</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>5 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 78, 'photos': 260}</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
+Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 537, 'photos': 4147}</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 91, 'photos': 574}</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Đúng tên gọi của nó. Thác cũng rất đẹp. Nếu vào mùa nước chắc còn đẹp hơn.
+Cảnh quan cũng rất sạch đẹp.
+- Vào mùa hè nếu bạn ngồi ngâm chân tại thác số 1 thì không khác gì ngâm chân tại Seoul - Mugyo dong …. mát lạnh sảng khoái.
+- về cảnh quan: lúc đầu vào cổng mình cữ ngỡ khung cảnh của đảo Nami Hàn quốc.😍. Rất nhiều hoa và cây xanh. Nếu bạn đi đúng mùa hoa thì thật tuyệt với.
+- vé vào cổng giá phù hợp</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 653, 'photos': 4196}</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>5</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Thời gian chỉnh sửa: 2 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 147, 'photos': 517}</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>5</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 164, 'photos': 234}</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>4</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 135, 'photos': 248}</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>5</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 190, 'photos': 1641}</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>5</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>10 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>{'name': 'ninh Men', 'link': 'https://www.google.com/maps/contrib/103025469094717120638?hl=vi', 'contributor_id': '103025469094717120638', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJr8a3WVJHmayMF2FvRRdJjmyVlo0gmvjXedEtF6z5_xuOtxg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 29, 'photos': 168}</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>4</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Đi Thác Dải Yếm đúng hôm… uống trà sữa trân châu. 😭
+Vé 150k/người nhưng cá nhân mình thấy hơi hụt hẫng. Thác không quá đặc biệt, đi một vòng là hết, chủ yếu là chụp ảnh. Nếu không thích check-in thì chắc sẽ thấy hơi “không có gì” so với giá vé.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 50, 'photos': 144}</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVOAB-25PMt-dfRNT-0Cxi6yv3ndR1rsuSnkmcbVorHpLvMDfzp2g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 149, 'photos': 3873}</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>5</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Thác Dải Yếm, còn được gọi là thác Nàng, thác Bản Vặt, là một thác nước hùng vĩ nằm ở xã Mường Sang, huyện Mộc Châu, tỉnh Sơn La. Thác có chiều cao khoảng 100m, chia thành hai dòng thác chính, trông giống như một dải yếm đào mềm mại uốn lượn quanh vách núi.
+Thác Dải Yếm là một địa điểm du lịch hấp dẫn, thu hút khách du lịch trong và ngoài nước. Đây là nơi du khách có thể chiêm ngưỡng vẻ đẹp hùng vĩ của thác nước và tìm hiểu về truyền thuyết về thác.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 97, 'photos': 178}</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>4</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 28, 'photos': 264}</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>4</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 75, 'photos': 503}</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>4</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Thác Dải Yếm nằm trên dòng suối Vặt khởi nguồn từ hai khe nước Bó Co Lắm và Bo Tá Cháu ở đầu bản Vặt, một bản của người Thái có lịch sử lâu đời. Suối Vặt chảy được 5 km đổ vào suối Bó Sập, một dòng suối lớn bắt nguồn từ bản Bó Sập giáp biên giới Việt Lào rồi chảy về đất Yên Châu. Tại nơi hợp lưu của hai suối, dòng nước gặp một vùng đá vôi và đổ xuống phía dưới tạo thành thác Dải Yếm.[5]
+Thác Dải Yếm bao gồm hai phần, thác nước phía trên rộng 70 mét, thác nước phía dưới nằm cách đó 150-200 mét. Vào mùa khô, thác phía dưới chỉ có một dòng chảy từ độ cao 50 m xuống triền đá ở dưới. hai thác đổ xuống với tổng chiều cao 100m, một bên được chia làm 9 tầng, bên còn lại 5 tầng. Cách giữa hai phần thác là một bãi đất phẳng thuận tiện cho việc tham quan của du khách. Thảm thực vật trên đỉnh thác cũng khá phong phú.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>{'name': 'Chi Ho', 'link': 'https://www.google.com/maps/contrib/102731288821463748765?hl=vi', 'contributor_id': '102731288821463748765', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWV3y9KiqGo7jILq-ZzBkSw28LDZHnwKXBhstpTEeRvr9jffKE=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 85, 'photos': 1557}</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>5</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Thác Dải Yếm đẹp và hùng vĩ, xứng đáng cho chuyến picnic cuối tuần. Đường đi hơi gập ghềnh nhưng đến nơi thì quên hết mệt mỏi. Nước mát rượi, âm thanh róc rách rất thư giãn. Tiếc là hơi đông vào cuối tuần, nhưng cảnh đẹp bù đắp tất cả! Nên đi vào ngày thường nếu muốn yên tĩnh hơn.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 8, 'photos': 90}</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>4</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 152, 'photos': 1293}</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>4</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Thác nhỏ cũng đẹp nhưng được trang trí dành cho du lịch rồi về độ rộng nhiều tầng và thiên nhiên thì không bằng thác Nàng Tiên hoặc thác Chiềng Khoa.
+Thác Dải Yếm được đầu tư khang trang nhưng đi bộ từ bãi gửi xe vào thác hơi bị xa (vé gửi xe 30k), đường đi vào và khu thác bên trong nhiều khu chụp ảnh checkin được trang trí chụp ảnh đẹp mắt. Giá vé tháng 1/2024 là 80k/ người vào cổng nhưng đến 30/4/2024 tăng lên 100k/ng giá vé hơi cao với việc vào ngắm thác.
+Muốn lên cầu kính giá vé riêng 100k/người. Lên cầu kính chơi ngắm cảnh cũng ok. Từ cầu kính nhìn đi mấy quả đồi phía dưới bị đào bới làm đường nhìn không được thiên nhiên cho lắm.
+- Bản thân mình cảm nhận thì cũng bình thường thác không cao không rộng dài đẹp nhiều tầng bằng thác Nàng Tiên hoặc Chiềng Khoa. Nói chung đi du lịch Mộc Châu ghé qua cho biết thôi. Chứ để quay lại thì ít khả năng.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 139, 'photos': 561}</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>4</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>View đẹp, chỉ tiếc là ghé hồi tháng 5 lúc đang mùa mưa, nên không được đi trải nghiệm nhiều.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>11 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>{'name': 'Hung Tran', 'link': 'https://www.google.com/maps/contrib/111025160790635631721?hl=vi', 'contributor_id': '111025160790635631721', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXJvHNQsMohKHo9fo2c_guCokbfqlcHTDulcTBswdAfP6GIiZRa=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 120, 'photos': 1818}</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>5</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Mới đi Thác Dải Yếm mà thấy cảnh ở đây quá ấn tượng. Nước từ thác chảy xuống nhìn thôi đã mát cả mắt, mát hơn một phần do cái thời tiết mát mẻ nơi miền núi này. Đường đến thác hơi gồ ghề tí nên đi lại cẩn thận xíu nhưng được cái khung cảnh thiên nhiên trời ban, thấy cũng quá ổn. Có mấy gian hàng bán đặc sản địa phương, cứ thấy ghé thử, giá nơi này cũng dễ chịu. Mọi thứ rất thư thái, không đông đúc, thích hợp để đi vào ngày nghỉ. Thêm vài chỗ ngồi nghỉ ngơi thì tuyệt!</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>10 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>{'name': 'Nguyen Hung Son', 'link': 'https://www.google.com/maps/contrib/103602300698496865451?hl=vi', 'contributor_id': '103602300698496865451', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUZaCtGsEksmQHBlNq8Xrol7h098HYLQGNUZgSqhr55eCVudl46og=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 74, 'photos': 2146}</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>4</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Thác Dải Yếm dường như trở thành một công viên. Lối vào thác khi đi qua cổng và đến Suối Hẹn Hò, khách thăm quan có thể đi theo đường bê tông hoặc đi xuống suối hẹn hò men theo đường lát đá ven suối và núi. Đa phần cá cảnh quan ở đây đã được cải tạo. Các trò chơi như Cầu Kính, Zipline và có lẽ đặc biệt nhất vẫn là check-in tại Thác Dải Yếm khi đầy nước. Vé vào cửa 100k/người lớn, trẻ em 50k (&lt;1,2m). Vé cầu kính 100k, Zipline 50k.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2 năm trước</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{'name': 'Hanh Vu', 'link': 'https://www.google.com/maps/contrib/101916078015092582424?hl=vi', 'contributor_id': '101916078015092582424', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWKKa85i2VN2RSjhkp53oKKDcXbjK49YmqN3D2BpL8QOof8ZRlo=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 28, 'photos': 33}</t>
+          <t>{'name': 'Hanh Vu', 'link': 'https://www.google.com/maps/contrib/101916078015092582424?hl=vi', 'contributor_id': '101916078015092582424', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWKKa85i2VN2RSjhkp53oKKDcXbjK49YmqN3D2BpL8QOof8ZRlo=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 28, 'photos': 34}</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -645,7 +645,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 12, 'photos': 25}</t>
+          <t>{'name': 'Gia Hân Nhâm', 'link': 'https://www.google.com/maps/contrib/105260403784604064817?hl=vi', 'contributor_id': '105260403784604064817', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXW4Eq54WOYUlLcmPr0wFzcfgLQhMAImSwK6dXvpDOyeFlOocZZ7w=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 15, 'photos': 63}</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -653,61 +653,61 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
+          <t>Thác rất đẹp, bước vào thật sự bị ngộp khung cảnh hùng vĩ của Việt Nam mình. Mỗi nơi đi là mỗi trải nghiệm</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>một tháng trước</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 12, 'photos': 25}</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>6 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 16, 'photos': 114}</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Đi tầm trưa nắng đẹp
 Thác nhỏ, đi cũng không mất quá nhiều thời gian
 Có cầu kính</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>{'name': 'Nghĩa Nguyễn Trung', 'link': 'https://www.google.com/maps/contrib/107253778101970197900?hl=vi', 'contributor_id': '107253778101970197900', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUNLHg5XlpgtWVVTp_oJKOYAejqmQORtgQ_Oe2vusE5W_sQoZc5=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 275, 'photos': 1279}</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Khu vực thác nước đẹp, nhiều cảnh quan, nhiều góc chụp đẹp.</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>3 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>{'name': 'Frugal Flow', 'link': 'https://www.google.com/maps/contrib/107453311426556875441?hl=vi', 'contributor_id': '107453311426556875441', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUspWRVGEEQ_LyS16qRB57xWZ-kgNRIjgdLPY8T7HzvNMFlILCV=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 25, 'photos': 85}</t>
+          <t>{'name': 'Nghĩa Nguyễn Trung', 'link': 'https://www.google.com/maps/contrib/107253778101970197900?hl=vi', 'contributor_id': '107253778101970197900', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUNLHg5XlpgtWVVTp_oJKOYAejqmQORtgQ_Oe2vusE5W_sQoZc5=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 275, 'photos': 1279}</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -715,25 +715,45 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Đi vào một ngày nắng. Nắng hắt lên mặt nước long lanh nên xinh xắn hẳn:&gt; Chỉ là thác nay có vẻ hơi ít nc nên không như mình tưởng tượng.</t>
+          <t>Khu vực thác nước đẹp, nhiều cảnh quan, nhiều góc chụp đẹp.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7 tháng trước</t>
+          <t>3 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>{'name': 'Frugal Flow', 'link': 'https://www.google.com/maps/contrib/107453311426556875441?hl=vi', 'contributor_id': '107453311426556875441', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUspWRVGEEQ_LyS16qRB57xWZ-kgNRIjgdLPY8T7HzvNMFlILCV=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 25, 'photos': 85}</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Đi vào một ngày nắng. Nắng hắt lên mặt nước long lanh nên xinh xắn hẳn:&gt; Chỉ là thác nay có vẻ hơi ít nc nên không như mình tưởng tượng.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>7 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 222, 'photos': 316}</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B16" t="n">
         <v>3</v>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Trải nghiệm vừa phải
 Giá vé theo trải nghiệm đi nhiều thác khác nhau của mình thì là khá cao so với các nơi khác, mình đi vào dịp tết nên thác ít nước.
@@ -741,64 +761,64 @@
 Cá nhân nếu quay lại Mộc Châu sẽ không đến thác này lần nào nữa</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>8 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>{'name': 'La Meu', 'link': 'https://www.google.com/maps/contrib/108858956358165703026?hl=vi', 'contributor_id': '108858956358165703026', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVKW-aZD0iBs1KBFQlmzfMiMTfjpd4PfUn4GO-K2tEt1PLpZ3YY=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 25, 'photos': 117}</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>5</v>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Thác Dải Yếm là điểm du lịch rất đáng đi. Đường đi dễ, xe máy hay ô tô đều thuận tiện. Không gian mát mẻ, thiên nhiên đẹp và trong lành.
 Nước thác xanh biếc, chảy mạnh nhưng nhìn rất êm và thơ mộng, chụp hình lên đẹp lắm. Khu vực được làm lối đi khá an toàn, dễ tham quan.
 Nhân viên ở đây dễ thương, nhiệt tình, hướng dẫn khách rất chu đáo và thân thiện. Phù hợp đi chơi cùng gia đình hoặc bạn bè để thư giãn, nghỉ ngơi.</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>10 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 25, 'photos': 256}</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>5</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 25, 'photos': 256}</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>8 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>{'name': 'Thái Nguyễn', 'link': 'https://www.google.com/maps/contrib/105517365260915933657?hl=vi', 'contributor_id': '105517365260915933657', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXLOkY3FUSH3Mz-aapJXPQUgoCFlQP20PICWZGzVI3cPkRkBIt_ew=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 65, 'photos': 175}</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>5</v>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Nếu đi cùng Lover sẽ đẹp hơn.
 Nếu tự nhìn lại
@@ -866,26 +886,6 @@
 Hơn cả tới thiên đường</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>9 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 57, 'photos': 1245}</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>3</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
-        </is>
-      </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>9 tháng trước</t>
@@ -895,27 +895,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 94, 'photos': 1120}</t>
+          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 57, 'photos': 1245}</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
+          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>9 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 146, 'photos': 330}</t>
+          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 94, 'photos': 1120}</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -923,19 +923,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
+          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 38, 'photos': 73}</t>
+          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 146, 'photos': 330}</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -943,27 +943,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
+          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3 tháng trước</t>
+          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 34, 'photos': 79}</t>
+          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 38, 'photos': 73}</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
+          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -975,67 +975,67 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 114, 'photos': 83}</t>
+          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 34, 'photos': 79}</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
+          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>4 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 191, 'photos': 3220}</t>
+          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 114, 'photos': 83}</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
+          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>11 tháng trước</t>
+          <t>9 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 252, 'photos': 5012}</t>
+          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 191, 'photos': 3220}</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cảnh quan đẹp, ng dân thân thiện</t>
+          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>11 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 12, 'photos': 41}</t>
+          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 252, 'photos': 5012}</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1043,25 +1043,45 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
+          <t>Cảnh quan đẹp, ng dân thân thiện</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 12, 'photos': 41}</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>10 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>{'name': 'Linh Nguyễn', 'link': 'https://www.google.com/maps/contrib/109820275513447282944?hl=vi', 'contributor_id': '109820275513447282944', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVpZ-SNyOn6byhXW5cnkMUzIYl8pLeo3scME3-VG4n2ps2S2tYx=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 144, 'photos': 992}</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>5</v>
-      </c>
-      <c r="C28" t="inlineStr">
+      <c r="B29" t="n">
+        <v>5</v>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>Thác đẹp, suối nước tự nhiên, đường đi dọc suối sạch sẽ
 Một số địa điểm du lịch ở Mộc Châu mọi người có thể tham khảo
@@ -1074,56 +1094,36 @@
 2. Cá Hồi Thanh Bảy</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>2 năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 81, 'photos': 188}</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>4</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 12, 'photos': 65}</t>
+          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 81, 'photos': 188}</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
+          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 72, 'photos': 501}</t>
+          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 12, 'photos': 65}</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1131,50 +1131,50 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
+          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 72, 'photos': 501}</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>5 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 78, 'photos': 260}</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="B33" t="n">
         <v>4</v>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
 Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 537, 'photos': 4147}</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>4</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
-        </is>
-      </c>
       <c r="D33" t="inlineStr">
         <is>
           <t>một năm trước</t>
@@ -1184,13 +1184,33 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 537, 'photos': 4147}</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 91, 'photos': 574}</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>5</v>
-      </c>
-      <c r="C34" t="inlineStr">
+      <c r="B35" t="n">
+        <v>5</v>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>Đúng tên gọi của nó. Thác cũng rất đẹp. Nếu vào mùa nước chắc còn đẹp hơn.
 Cảnh quan cũng rất sạch đẹp.
@@ -1199,36 +1219,16 @@
 - vé vào cổng giá phù hợp</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 653, 'photos': 4196}</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>5</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Thời gian chỉnh sửa: 2 năm trước</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 147, 'photos': 517}</t>
+          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 653, 'photos': 4196}</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1236,27 +1236,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
+          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>Thời gian chỉnh sửa: 2 năm trước</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 164, 'photos': 234}</t>
+          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 147, 'photos': 517}</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
+          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1268,15 +1268,15 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 135, 'photos': 248}</t>
+          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 164, 'photos': 234}</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
+          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1288,7 +1288,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 190, 'photos': 1641}</t>
+          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 135, 'photos': 248}</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1296,101 +1296,101 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>10 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 190, 'photos': 1641}</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>5</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>10 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>{'name': 'ninh Men', 'link': 'https://www.google.com/maps/contrib/103025469094717120638?hl=vi', 'contributor_id': '103025469094717120638', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJr8a3WVJHmayMF2FvRRdJjmyVlo0gmvjXedEtF6z5_xuOtxg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 29, 'photos': 168}</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="B41" t="n">
         <v>4</v>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Đi Thác Dải Yếm đúng hôm… uống trà sữa trân châu. 😭
 Vé 150k/người nhưng cá nhân mình thấy hơi hụt hẫng. Thác không quá đặc biệt, đi một vòng là hết, chủ yếu là chụp ảnh. Nếu không thích check-in thì chắc sẽ thấy hơi “không có gì” so với giá vé.</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>2 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 50, 'photos': 144}</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>4</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 50, 'photos': 144}</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>4</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVOAB-25PMt-dfRNT-0Cxi6yv3ndR1rsuSnkmcbVorHpLvMDfzp2g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 149, 'photos': 3873}</t>
         </is>
       </c>
-      <c r="B42" t="n">
-        <v>5</v>
-      </c>
-      <c r="C42" t="inlineStr">
+      <c r="B43" t="n">
+        <v>5</v>
+      </c>
+      <c r="C43" t="inlineStr">
         <is>
           <t>Thác Dải Yếm, còn được gọi là thác Nàng, thác Bản Vặt, là một thác nước hùng vĩ nằm ở xã Mường Sang, huyện Mộc Châu, tỉnh Sơn La. Thác có chiều cao khoảng 100m, chia thành hai dòng thác chính, trông giống như một dải yếm đào mềm mại uốn lượn quanh vách núi.
 Thác Dải Yếm là một địa điểm du lịch hấp dẫn, thu hút khách du lịch trong và ngoài nước. Đây là nơi du khách có thể chiêm ngưỡng vẻ đẹp hùng vĩ của thác nước và tìm hiểu về truyền thuyết về thác.</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>2 năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 97, 'photos': 178}</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>4</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 28, 'photos': 264}</t>
+          <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 97, 'photos': 178}</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
+          <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1410,7 +1410,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 75, 'photos': 503}</t>
+          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 28, 'photos': 264}</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1418,66 +1418,86 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
+          <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 75, 'photos': 503}</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>4</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
           <t>Thác Dải Yếm nằm trên dòng suối Vặt khởi nguồn từ hai khe nước Bó Co Lắm và Bo Tá Cháu ở đầu bản Vặt, một bản của người Thái có lịch sử lâu đời. Suối Vặt chảy được 5 km đổ vào suối Bó Sập, một dòng suối lớn bắt nguồn từ bản Bó Sập giáp biên giới Việt Lào rồi chảy về đất Yên Châu. Tại nơi hợp lưu của hai suối, dòng nước gặp một vùng đá vôi và đổ xuống phía dưới tạo thành thác Dải Yếm.[5]
 Thác Dải Yếm bao gồm hai phần, thác nước phía trên rộng 70 mét, thác nước phía dưới nằm cách đó 150-200 mét. Vào mùa khô, thác phía dưới chỉ có một dòng chảy từ độ cao 50 m xuống triền đá ở dưới. hai thác đổ xuống với tổng chiều cao 100m, một bên được chia làm 9 tầng, bên còn lại 5 tầng. Cách giữa hai phần thác là một bãi đất phẳng thuận tiện cho việc tham quan của du khách. Thảm thực vật trên đỉnh thác cũng khá phong phú.</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>{'name': 'Chi Ho', 'link': 'https://www.google.com/maps/contrib/102731288821463748765?hl=vi', 'contributor_id': '102731288821463748765', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWV3y9KiqGo7jILq-ZzBkSw28LDZHnwKXBhstpTEeRvr9jffKE=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 85, 'photos': 1557}</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>5</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm đẹp và hùng vĩ, xứng đáng cho chuyến picnic cuối tuần. Đường đi hơi gập ghềnh nhưng đến nơi thì quên hết mệt mỏi. Nước mát rượi, âm thanh róc rách rất thư giãn. Tiếc là hơi đông vào cuối tuần, nhưng cảnh đẹp bù đắp tất cả! Nên đi vào ngày thường nếu muốn yên tĩnh hơn.</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 8, 'photos': 90}</t>
+          <t>{'name': 'Chi Ho', 'link': 'https://www.google.com/maps/contrib/102731288821463748765?hl=vi', 'contributor_id': '102731288821463748765', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWV3y9KiqGo7jILq-ZzBkSw28LDZHnwKXBhstpTEeRvr9jffKE=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 85, 'photos': 1557}</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
+          <t>Thác Dải Yếm đẹp và hùng vĩ, xứng đáng cho chuyến picnic cuối tuần. Đường đi hơi gập ghềnh nhưng đến nơi thì quên hết mệt mỏi. Nước mát rượi, âm thanh róc rách rất thư giãn. Tiếc là hơi đông vào cuối tuần, nhưng cảnh đẹp bù đắp tất cả! Nên đi vào ngày thường nếu muốn yên tĩnh hơn.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 152, 'photos': 1293}</t>
+          <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 8, 'photos': 90}</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>4</v>
       </c>
       <c r="C48" t="inlineStr">
+        <is>
+          <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 152, 'photos': 1293}</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>4</v>
+      </c>
+      <c r="C49" t="inlineStr">
         <is>
           <t>Thác nhỏ cũng đẹp nhưng được trang trí dành cho du lịch rồi về độ rộng nhiều tầng và thiên nhiên thì không bằng thác Nàng Tiên hoặc thác Chiềng Khoa.
 Thác Dải Yếm được đầu tư khang trang nhưng đi bộ từ bãi gửi xe vào thác hơi bị xa (vé gửi xe 30k), đường đi vào và khu thác bên trong nhiều khu chụp ảnh checkin được trang trí chụp ảnh đẹp mắt. Giá vé tháng 1/2024 là 80k/ người vào cổng nhưng đến 30/4/2024 tăng lên 100k/ng giá vé hơi cao với việc vào ngắm thác.
@@ -1485,69 +1505,49 @@
 - Bản thân mình cảm nhận thì cũng bình thường thác không cao không rộng dài đẹp nhiều tầng bằng thác Nàng Tiên hoặc Chiềng Khoa. Nói chung đi du lịch Mộc Châu ghé qua cho biết thôi. Chứ để quay lại thì ít khả năng.</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>2 năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 139, 'photos': 561}</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>4</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>View đẹp, chỉ tiếc là ghé hồi tháng 5 lúc đang mùa mưa, nên không được đi trải nghiệm nhiều.</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>11 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>{'name': 'Hung Tran', 'link': 'https://www.google.com/maps/contrib/111025160790635631721?hl=vi', 'contributor_id': '111025160790635631721', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXJvHNQsMohKHo9fo2c_guCokbfqlcHTDulcTBswdAfP6GIiZRa=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 120, 'photos': 1818}</t>
+          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 139, 'photos': 561}</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Mới đi Thác Dải Yếm mà thấy cảnh ở đây quá ấn tượng. Nước từ thác chảy xuống nhìn thôi đã mát cả mắt, mát hơn một phần do cái thời tiết mát mẻ nơi miền núi này. Đường đến thác hơi gồ ghề tí nên đi lại cẩn thận xíu nhưng được cái khung cảnh thiên nhiên trời ban, thấy cũng quá ổn. Có mấy gian hàng bán đặc sản địa phương, cứ thấy ghé thử, giá nơi này cũng dễ chịu. Mọi thứ rất thư thái, không đông đúc, thích hợp để đi vào ngày nghỉ. Thêm vài chỗ ngồi nghỉ ngơi thì tuyệt!</t>
+          <t>View đẹp, chỉ tiếc là ghé hồi tháng 5 lúc đang mùa mưa, nên không được đi trải nghiệm nhiều.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>10 tháng trước</t>
+          <t>11 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyen Hung Son', 'link': 'https://www.google.com/maps/contrib/103602300698496865451?hl=vi', 'contributor_id': '103602300698496865451', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUZaCtGsEksmQHBlNq8Xrol7h098HYLQGNUZgSqhr55eCVudl46og=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 74, 'photos': 2146}</t>
+          <t>{'name': 'Hung Tran', 'link': 'https://www.google.com/maps/contrib/111025160790635631721?hl=vi', 'contributor_id': '111025160790635631721', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXJvHNQsMohKHo9fo2c_guCokbfqlcHTDulcTBswdAfP6GIiZRa=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 120, 'photos': 1818}</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm dường như trở thành một công viên. Lối vào thác khi đi qua cổng và đến Suối Hẹn Hò, khách thăm quan có thể đi theo đường bê tông hoặc đi xuống suối hẹn hò men theo đường lát đá ven suối và núi. Đa phần cá cảnh quan ở đây đã được cải tạo. Các trò chơi như Cầu Kính, Zipline và có lẽ đặc biệt nhất vẫn là check-in tại Thác Dải Yếm khi đầy nước. Vé vào cửa 100k/người lớn, trẻ em 50k (&lt;1,2m). Vé cầu kính 100k, Zipline 50k.</t>
+          <t>Mới đi Thác Dải Yếm mà thấy cảnh ở đây quá ấn tượng. Nước từ thác chảy xuống nhìn thôi đã mát cả mắt, mát hơn một phần do cái thời tiết mát mẻ nơi miền núi này. Đường đến thác hơi gồ ghề tí nên đi lại cẩn thận xíu nhưng được cái khung cảnh thiên nhiên trời ban, thấy cũng quá ổn. Có mấy gian hàng bán đặc sản địa phương, cứ thấy ghé thử, giá nơi này cũng dễ chịu. Mọi thứ rất thư thái, không đông đúc, thích hợp để đi vào ngày nghỉ. Thêm vài chỗ ngồi nghỉ ngơi thì tuyệt!</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2 năm trước</t>
+          <t>10 tháng trước</t>
         </is>
       </c>
     </row>

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -453,33 +453,13 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{'name': 'Hanh Vu', 'link': 'https://www.google.com/maps/contrib/101916078015092582424?hl=vi', 'contributor_id': '101916078015092582424', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWKKa85i2VN2RSjhkp53oKKDcXbjK49YmqN3D2BpL8QOof8ZRlo=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 28, 'photos': 34}</t>
+          <t>{'name': 'Hưng Nguyễn Duy (Hưng Photo)', 'link': 'https://www.google.com/maps/contrib/110173941936897044295?hl=vi', 'contributor_id': '110173941936897044295', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXshx7xq3ntsswbv03kbw9Z9KIntVjsKdM747CeNwqebP-xH_RO=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 194, 'photos': 2205}</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm nằm trong khu du lịch sinh thái Thác Dải Yếm, vé vào 150k/người. Bên trong có thác nước nhưng nước khá đục nên không tắm được, có thêm cầu kính tình yêu để chụp ảnh. Mình thấy khu này không có quá nhiều điểm để tham quan, chủ yếu vào ngắm thác và chụp ảnh, nên nếu kỳ vọng có nhiều hoạt động thì sẽ hơi ít.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>một tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>{'name': 'Hưng Nguyễn Duy (Hưng Photo)', 'link': 'https://www.google.com/maps/contrib/110173941936897044295?hl=vi', 'contributor_id': '110173941936897044295', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXshx7xq3ntsswbv03kbw9Z9KIntVjsKdM747CeNwqebP-xH_RO=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 194, 'photos': 2205}</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C3" t="inlineStr">
         <is>
           <t>Địa điểm du lịch nổi tiếng nên khám phá khi tới Mộc Châu.
 Chỗ để xe rộng rãi (Phí gửi xe là 30N)
@@ -488,22 +468,22 @@
 Có bán nhiều đồ lưu niệm và đặc sản núi rừng Tây Bắc.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>5 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>{'name': 'ZjmLee YTBer', 'link': 'https://www.google.com/maps/contrib/100979561872983589256?hl=vi', 'contributor_id': '100979561872983589256', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU6i9poRXPBKYv-WgZHmB9chW6jRPCOh3klZ1Z7Yv_DOaukn4g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 79, 'photos': 1213}</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>Nghe người địa phương kể lại thì cái tên “Dải Yếm” xuất phát từ truyền thuyết của người Thái. Họ nói rằng dòng thác trắng xóa từ trên cao đổ xuống giống như dải yếm của người con gái, nên từ đó cái tên này được gọi luôn cho tới bây giờ. Nghe vậy nên đứng nhìn dòng thác cũng thấy có chút gì đó rất nên thơ.
 Đi bộ quanh khu thác khá dễ, có lối đi và bậc đá để xuống gần chân thác. Nếu đi vào mùa nước nhiều thì thác nhìn đẹp hơn, nước trắng xóa và tiếng thác nghe rất đã tai. Còn những ngày nắng nhẹ thì không khí ở đây khá chill, kiểu ngồi nghỉ một chút, nghe tiếng nước và nhìn rừng cây xung quanh cũng thấy thư giãn.
@@ -511,44 +491,44 @@
 Nếu đang đi du lịch tự túc ở Mộc Châu, thì Thác Dải Yếm là một nơi khá đáng ghé qua. Không cần quá nhiều thời gian, chỉ cần dành khoảng một tiếng dạo quanh thôi cũng đủ để cảm nhận được một góc thiên nhiên rất đặc trưng của vùng núi này.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 377, 'photos': 2657}</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C5" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 377, 'photos': 2666}</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>Nơi rất đáng để tham quan, trãi nghiệm chút it về cầu kính và kết hợp đi ngắm thác nước.
 Có nhiều nơi lên hình đẹp, cảnh đẹp. Có bán đặc sản Mộc Châu rất đa dạng.
 😍😍👍</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Thời gian chỉnh sửa: 6 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>{'name': 'Vĩ Lê Bá', 'link': 'https://www.google.com/maps/contrib/115860838984920745696?hl=vi', 'contributor_id': '115860838984920745696', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7wdRrYJWeEmKs7YInZz_FDg-T90l2ImigSwJKL2hWmQu75bzm=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 61, 'photos': 96}</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B5" t="n">
         <v>4</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Đẹp thì đẹp sơ sơ nhưng không gian vẫn khá là thoải mái
 Đi bộ oklea nhưng mà vẫn còn quá nhỏ, đi cỡ 30 phút là xong mất tiêu r
@@ -556,9 +536,29 @@
 Nói chung là vẫn okela</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>{'name': 'Hanh Vu', 'link': 'https://www.google.com/maps/contrib/101916078015092582424?hl=vi', 'contributor_id': '101916078015092582424', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWKKa85i2VN2RSjhkp53oKKDcXbjK49YmqN3D2BpL8QOof8ZRlo=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 29, 'photos': 34}</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Thác Dải Yếm nằm trong khu du lịch sinh thái Thác Dải Yếm, vé vào 150k/người. Bên trong có thác nước nhưng nước khá đục nên không tắm được, có thêm cầu kính tình yêu để chụp ảnh. Mình thấy khu này không có quá nhiều điểm để tham quan, chủ yếu vào ngắm thác và chụp ảnh, nên nếu kỳ vọng có nhiều hoạt động thì sẽ hơi ít.</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7 tháng trước</t>
+          <t>một tháng trước</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7 tháng trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 146, 'photos': 330}</t>
+          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 146, 'photos': 334}</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1123,7 +1123,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 12, 'photos': 65}</t>
+          <t>{'name': 'Nguyễn Tấn Thành', 'link': 'https://www.google.com/maps/contrib/117227534316521742646?hl=vi', 'contributor_id': '117227534316521742646', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUCPB87qD_q8UFnvBcCkGu3uE2AN4atMK6XrLGFH3fII6nWymikeg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 35, 'photos': 483}</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1131,19 +1131,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
+          <t>Cảnh ở thác rất là đẹp</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>một tháng trước</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 72, 'photos': 501}</t>
+          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 12, 'photos': 65}</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1151,50 +1151,50 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
+          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 72, 'photos': 501}</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>5 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 78, 'photos': 260}</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="B34" t="n">
         <v>4</v>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
 Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 537, 'photos': 4147}</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>4</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
-        </is>
-      </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>một năm trước</t>
@@ -1204,13 +1204,33 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 536, 'photos': 4147}</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 91, 'photos': 574}</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>5</v>
-      </c>
-      <c r="C35" t="inlineStr">
+      <c r="B36" t="n">
+        <v>5</v>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>Đúng tên gọi của nó. Thác cũng rất đẹp. Nếu vào mùa nước chắc còn đẹp hơn.
 Cảnh quan cũng rất sạch đẹp.
@@ -1219,36 +1239,16 @@
 - vé vào cổng giá phù hợp</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 653, 'photos': 4196}</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>5</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Thời gian chỉnh sửa: 2 năm trước</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 147, 'photos': 517}</t>
+          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 652, 'photos': 4196}</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1256,27 +1256,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
+          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>Thời gian chỉnh sửa: 2 năm trước</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 164, 'photos': 234}</t>
+          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 147, 'photos': 517}</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
+          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1288,15 +1288,15 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 135, 'photos': 248}</t>
+          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 164, 'photos': 234}</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
+          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1308,7 +1308,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 190, 'photos': 1641}</t>
+          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 134, 'photos': 248}</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1316,101 +1316,101 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>10 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 190, 'photos': 1641}</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>5</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>10 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>{'name': 'ninh Men', 'link': 'https://www.google.com/maps/contrib/103025469094717120638?hl=vi', 'contributor_id': '103025469094717120638', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJr8a3WVJHmayMF2FvRRdJjmyVlo0gmvjXedEtF6z5_xuOtxg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 29, 'photos': 168}</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="B42" t="n">
         <v>4</v>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Đi Thác Dải Yếm đúng hôm… uống trà sữa trân châu. 😭
 Vé 150k/người nhưng cá nhân mình thấy hơi hụt hẫng. Thác không quá đặc biệt, đi một vòng là hết, chủ yếu là chụp ảnh. Nếu không thích check-in thì chắc sẽ thấy hơi “không có gì” so với giá vé.</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>2 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 50, 'photos': 144}</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>4</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 50, 'photos': 144}</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>4</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVOAB-25PMt-dfRNT-0Cxi6yv3ndR1rsuSnkmcbVorHpLvMDfzp2g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 149, 'photos': 3873}</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>5</v>
-      </c>
-      <c r="C43" t="inlineStr">
+      <c r="B44" t="n">
+        <v>5</v>
+      </c>
+      <c r="C44" t="inlineStr">
         <is>
           <t>Thác Dải Yếm, còn được gọi là thác Nàng, thác Bản Vặt, là một thác nước hùng vĩ nằm ở xã Mường Sang, huyện Mộc Châu, tỉnh Sơn La. Thác có chiều cao khoảng 100m, chia thành hai dòng thác chính, trông giống như một dải yếm đào mềm mại uốn lượn quanh vách núi.
 Thác Dải Yếm là một địa điểm du lịch hấp dẫn, thu hút khách du lịch trong và ngoài nước. Đây là nơi du khách có thể chiêm ngưỡng vẻ đẹp hùng vĩ của thác nước và tìm hiểu về truyền thuyết về thác.</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>2 năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 97, 'photos': 178}</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>4</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 28, 'photos': 264}</t>
+          <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 97, 'photos': 178}</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
+          <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1430,7 +1430,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 75, 'photos': 503}</t>
+          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 28, 'photos': 264}</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1438,66 +1438,86 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 75, 'photos': 503}</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>4</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
           <t>Thác Dải Yếm nằm trên dòng suối Vặt khởi nguồn từ hai khe nước Bó Co Lắm và Bo Tá Cháu ở đầu bản Vặt, một bản của người Thái có lịch sử lâu đời. Suối Vặt chảy được 5 km đổ vào suối Bó Sập, một dòng suối lớn bắt nguồn từ bản Bó Sập giáp biên giới Việt Lào rồi chảy về đất Yên Châu. Tại nơi hợp lưu của hai suối, dòng nước gặp một vùng đá vôi và đổ xuống phía dưới tạo thành thác Dải Yếm.[5]
 Thác Dải Yếm bao gồm hai phần, thác nước phía trên rộng 70 mét, thác nước phía dưới nằm cách đó 150-200 mét. Vào mùa khô, thác phía dưới chỉ có một dòng chảy từ độ cao 50 m xuống triền đá ở dưới. hai thác đổ xuống với tổng chiều cao 100m, một bên được chia làm 9 tầng, bên còn lại 5 tầng. Cách giữa hai phần thác là một bãi đất phẳng thuận tiện cho việc tham quan của du khách. Thảm thực vật trên đỉnh thác cũng khá phong phú.</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>{'name': 'Chi Ho', 'link': 'https://www.google.com/maps/contrib/102731288821463748765?hl=vi', 'contributor_id': '102731288821463748765', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWV3y9KiqGo7jILq-ZzBkSw28LDZHnwKXBhstpTEeRvr9jffKE=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 85, 'photos': 1557}</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>5</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm đẹp và hùng vĩ, xứng đáng cho chuyến picnic cuối tuần. Đường đi hơi gập ghềnh nhưng đến nơi thì quên hết mệt mỏi. Nước mát rượi, âm thanh róc rách rất thư giãn. Tiếc là hơi đông vào cuối tuần, nhưng cảnh đẹp bù đắp tất cả! Nên đi vào ngày thường nếu muốn yên tĩnh hơn.</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 8, 'photos': 90}</t>
+          <t>{'name': 'Chi Ho', 'link': 'https://www.google.com/maps/contrib/102731288821463748765?hl=vi', 'contributor_id': '102731288821463748765', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWV3y9KiqGo7jILq-ZzBkSw28LDZHnwKXBhstpTEeRvr9jffKE=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 85, 'photos': 1557}</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
+          <t>Thác Dải Yếm đẹp và hùng vĩ, xứng đáng cho chuyến picnic cuối tuần. Đường đi hơi gập ghềnh nhưng đến nơi thì quên hết mệt mỏi. Nước mát rượi, âm thanh róc rách rất thư giãn. Tiếc là hơi đông vào cuối tuần, nhưng cảnh đẹp bù đắp tất cả! Nên đi vào ngày thường nếu muốn yên tĩnh hơn.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 152, 'photos': 1293}</t>
+          <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 8, 'photos': 90}</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>4</v>
       </c>
       <c r="C49" t="inlineStr">
+        <is>
+          <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 151, 'photos': 1293}</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C50" t="inlineStr">
         <is>
           <t>Thác nhỏ cũng đẹp nhưng được trang trí dành cho du lịch rồi về độ rộng nhiều tầng và thiên nhiên thì không bằng thác Nàng Tiên hoặc thác Chiềng Khoa.
 Thác Dải Yếm được đầu tư khang trang nhưng đi bộ từ bãi gửi xe vào thác hơi bị xa (vé gửi xe 30k), đường đi vào và khu thác bên trong nhiều khu chụp ảnh checkin được trang trí chụp ảnh đẹp mắt. Giá vé tháng 1/2024 là 80k/ người vào cổng nhưng đến 30/4/2024 tăng lên 100k/ng giá vé hơi cao với việc vào ngắm thác.
@@ -1505,49 +1525,29 @@
 - Bản thân mình cảm nhận thì cũng bình thường thác không cao không rộng dài đẹp nhiều tầng bằng thác Nàng Tiên hoặc Chiềng Khoa. Nói chung đi du lịch Mộc Châu ghé qua cho biết thôi. Chứ để quay lại thì ít khả năng.</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>2 năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 139, 'photos': 561}</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>4</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>View đẹp, chỉ tiếc là ghé hồi tháng 5 lúc đang mùa mưa, nên không được đi trải nghiệm nhiều.</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>11 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>{'name': 'Hung Tran', 'link': 'https://www.google.com/maps/contrib/111025160790635631721?hl=vi', 'contributor_id': '111025160790635631721', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXJvHNQsMohKHo9fo2c_guCokbfqlcHTDulcTBswdAfP6GIiZRa=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 120, 'photos': 1818}</t>
+          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 139, 'photos': 561}</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Mới đi Thác Dải Yếm mà thấy cảnh ở đây quá ấn tượng. Nước từ thác chảy xuống nhìn thôi đã mát cả mắt, mát hơn một phần do cái thời tiết mát mẻ nơi miền núi này. Đường đến thác hơi gồ ghề tí nên đi lại cẩn thận xíu nhưng được cái khung cảnh thiên nhiên trời ban, thấy cũng quá ổn. Có mấy gian hàng bán đặc sản địa phương, cứ thấy ghé thử, giá nơi này cũng dễ chịu. Mọi thứ rất thư thái, không đông đúc, thích hợp để đi vào ngày nghỉ. Thêm vài chỗ ngồi nghỉ ngơi thì tuyệt!</t>
+          <t>View đẹp, chỉ tiếc là ghé hồi tháng 5 lúc đang mùa mưa, nên không được đi trải nghiệm nhiều.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>10 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -477,58 +477,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>{'name': 'ZjmLee YTBer', 'link': 'https://www.google.com/maps/contrib/100979561872983589256?hl=vi', 'contributor_id': '100979561872983589256', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU6i9poRXPBKYv-WgZHmB9chW6jRPCOh3klZ1Z7Yv_DOaukn4g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 79, 'photos': 1213}</t>
+          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 377, 'photos': 2666}</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>5</v>
       </c>
       <c r="C3" t="inlineStr">
-        <is>
-          <t>Nghe người địa phương kể lại thì cái tên “Dải Yếm” xuất phát từ truyền thuyết của người Thái. Họ nói rằng dòng thác trắng xóa từ trên cao đổ xuống giống như dải yếm của người con gái, nên từ đó cái tên này được gọi luôn cho tới bây giờ. Nghe vậy nên đứng nhìn dòng thác cũng thấy có chút gì đó rất nên thơ.
-Đi bộ quanh khu thác khá dễ, có lối đi và bậc đá để xuống gần chân thác. Nếu đi vào mùa nước nhiều thì thác nhìn đẹp hơn, nước trắng xóa và tiếng thác nghe rất đã tai. Còn những ngày nắng nhẹ thì không khí ở đây khá chill, kiểu ngồi nghỉ một chút, nghe tiếng nước và nhìn rừng cây xung quanh cũng thấy thư giãn.
-Mình thấy Thác Dải Yếm hợp với kiểu du lịch nhẹ nhàng: dừng chân, đi bộ một vòng, chụp vài bức ảnh rồi tiếp tục hành trình khám phá Mộc Châu. Nó không phải kiểu điểm du lịch quá hoành tráng, nhưng lại có cái nét mộc mạc và dễ chịu đúng chất cao nguyên.
-Nếu đang đi du lịch tự túc ở Mộc Châu, thì Thác Dải Yếm là một nơi khá đáng ghé qua. Không cần quá nhiều thời gian, chỉ cần dành khoảng một tiếng dạo quanh thôi cũng đủ để cảm nhận được một góc thiên nhiên rất đặc trưng của vùng núi này.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>7 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 377, 'photos': 2666}</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C4" t="inlineStr">
         <is>
           <t>Nơi rất đáng để tham quan, trãi nghiệm chút it về cầu kính và kết hợp đi ngắm thác nước.
 Có nhiều nơi lên hình đẹp, cảnh đẹp. Có bán đặc sản Mộc Châu rất đa dạng.
 😍😍👍</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Thời gian chỉnh sửa: 6 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>{'name': 'Vĩ Lê Bá', 'link': 'https://www.google.com/maps/contrib/115860838984920745696?hl=vi', 'contributor_id': '115860838984920745696', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7wdRrYJWeEmKs7YInZz_FDg-T90l2ImigSwJKL2hWmQu75bzm=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 61, 'photos': 96}</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B4" t="n">
         <v>4</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Đẹp thì đẹp sơ sơ nhưng không gian vẫn khá là thoải mái
 Đi bộ oklea nhưng mà vẫn còn quá nhỏ, đi cỡ 30 phút là xong mất tiêu r
@@ -536,36 +513,56 @@
 Nói chung là vẫn okela</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>7 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>{'name': 'Hanh Vu', 'link': 'https://www.google.com/maps/contrib/101916078015092582424?hl=vi', 'contributor_id': '101916078015092582424', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWKKa85i2VN2RSjhkp53oKKDcXbjK49YmqN3D2BpL8QOof8ZRlo=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 29, 'photos': 34}</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Thác Dải Yếm nằm trong khu du lịch sinh thái Thác Dải Yếm, vé vào 150k/người. Bên trong có thác nước nhưng nước khá đục nên không tắm được, có thêm cầu kính tình yêu để chụp ảnh. Mình thấy khu này không có quá nhiều điểm để tham quan, chủ yếu vào ngắm thác và chụp ảnh, nên nếu kỳ vọng có nhiều hoạt động thì sẽ hơi ít.</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7 tháng trước</t>
+          <t>một tháng trước</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>{'name': 'Hanh Vu', 'link': 'https://www.google.com/maps/contrib/101916078015092582424?hl=vi', 'contributor_id': '101916078015092582424', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWKKa85i2VN2RSjhkp53oKKDcXbjK49YmqN3D2BpL8QOof8ZRlo=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 29, 'photos': 34}</t>
+          <t>{'name': 'THANH NGUYEN', 'link': 'https://www.google.com/maps/contrib/110418688752170937071?hl=vi', 'contributor_id': '110418688752170937071', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIBtT-SxDlGGJM5jA47OmxpGvFdaG6EOeSswcBwx4VuXgnOdQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 71, 'photos': 238}</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm nằm trong khu du lịch sinh thái Thác Dải Yếm, vé vào 150k/người. Bên trong có thác nước nhưng nước khá đục nên không tắm được, có thêm cầu kính tình yêu để chụp ảnh. Mình thấy khu này không có quá nhiều điểm để tham quan, chủ yếu vào ngắm thác và chụp ảnh, nên nếu kỳ vọng có nhiều hoạt động thì sẽ hơi ít.</t>
+          <t>thác đẹp nhưng nên đi vào mùa nước sẽ thấy sự khác biệt hơn nhiều</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>một tháng trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>{'name': 'THANH NGUYEN', 'link': 'https://www.google.com/maps/contrib/110418688752170937071?hl=vi', 'contributor_id': '110418688752170937071', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIBtT-SxDlGGJM5jA47OmxpGvFdaG6EOeSswcBwx4VuXgnOdQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 71, 'photos': 238}</t>
+          <t>{'name': 'Cửu Quang Nguyễn', 'link': 'https://www.google.com/maps/contrib/107704339232071144994?hl=vi', 'contributor_id': '107704339232071144994', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV2_oJLqzlVCtXNV77ConxSPDhhMhFP-czjeCf6uCm7cabO88k=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 79, 'photos': 359}</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -573,19 +570,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>thác đẹp nhưng nên đi vào mùa nước sẽ thấy sự khác biệt hơn nhiều</t>
+          <t>Thác Dải Yếm nằm trong khu du lịch sinh thái thác Dải Yếm, đường đi khá tiện lợi để ghé vào, tuy nhiên cần chú ý lối vào có khúc cua dốc khá ngoặt. Vé vào là 150k/người, bên trong có khá nhiều vị trí để du ngoạn và ngắm cảnh, đặc biệt là khu vực thác nước rất hùng vĩ và mát mẻ, có cầu dẫn vào nhìn rất thơ mộng và tuyệt vời. Nếu có dịp ghé lên Mộc Châu thì nên ghé vào đây chơi 1 lần để du ngoạn thắng cảnh thiên nhiên tại nơi đây.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>{'name': 'Cửu Quang Nguyễn', 'link': 'https://www.google.com/maps/contrib/107704339232071144994?hl=vi', 'contributor_id': '107704339232071144994', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV2_oJLqzlVCtXNV77ConxSPDhhMhFP-czjeCf6uCm7cabO88k=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 79, 'photos': 359}</t>
+          <t>{'name': 'Nguyễn Anh Quân', 'link': 'https://www.google.com/maps/contrib/111631093743063403454?hl=vi', 'contributor_id': '111631093743063403454', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIy-NjGEZ7ggp1yhLvVSe2iSDFAUAF4AILlK1IHBmSbkPzlKg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 9, 'photos': 24}</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -593,19 +590,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm nằm trong khu du lịch sinh thái thác Dải Yếm, đường đi khá tiện lợi để ghé vào, tuy nhiên cần chú ý lối vào có khúc cua dốc khá ngoặt. Vé vào là 150k/người, bên trong có khá nhiều vị trí để du ngoạn và ngắm cảnh, đặc biệt là khu vực thác nước rất hùng vĩ và mát mẻ, có cầu dẫn vào nhìn rất thơ mộng và tuyệt vời. Nếu có dịp ghé lên Mộc Châu thì nên ghé vào đây chơi 1 lần để du ngoạn thắng cảnh thiên nhiên tại nơi đây.</t>
+          <t>Cảnh đẹp, nhưng xu là đi ngay lúc mưa nên thác có nước như cf</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Anh Quân', 'link': 'https://www.google.com/maps/contrib/111631093743063403454?hl=vi', 'contributor_id': '111631093743063403454', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIy-NjGEZ7ggp1yhLvVSe2iSDFAUAF4AILlK1IHBmSbkPzlKg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 9, 'photos': 24}</t>
+          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 302, 'photos': 3616}</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -613,19 +610,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cảnh đẹp, nhưng xu là đi ngay lúc mưa nên thác có nước như cf</t>
+          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2 tháng trước</t>
+          <t>5 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 302, 'photos': 3616}</t>
+          <t>{'name': 'Gia Hân Nhâm', 'link': 'https://www.google.com/maps/contrib/105260403784604064817?hl=vi', 'contributor_id': '105260403784604064817', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXW4Eq54WOYUlLcmPr0wFzcfgLQhMAImSwK6dXvpDOyeFlOocZZ7w=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 15, 'photos': 63}</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -633,19 +630,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
+          <t>Thác rất đẹp, bước vào thật sự bị ngộp khung cảnh hùng vĩ của Việt Nam mình. Mỗi nơi đi là mỗi trải nghiệm</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5 tháng trước</t>
+          <t>một tháng trước</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>{'name': 'Gia Hân Nhâm', 'link': 'https://www.google.com/maps/contrib/105260403784604064817?hl=vi', 'contributor_id': '105260403784604064817', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXW4Eq54WOYUlLcmPr0wFzcfgLQhMAImSwK6dXvpDOyeFlOocZZ7w=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 15, 'photos': 63}</t>
+          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 12, 'photos': 25}</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -653,61 +650,61 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thác rất đẹp, bước vào thật sự bị ngộp khung cảnh hùng vĩ của Việt Nam mình. Mỗi nơi đi là mỗi trải nghiệm</t>
+          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>một tháng trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 12, 'photos': 25}</t>
+          <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 16, 'photos': 114}</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>5</v>
       </c>
       <c r="C12" t="inlineStr">
-        <is>
-          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>6 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 16, 'photos': 114}</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" t="inlineStr">
         <is>
           <t>Đi tầm trưa nắng đẹp
 Thác nhỏ, đi cũng không mất quá nhiều thời gian
 Có cầu kính</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>{'name': 'Nghĩa Nguyễn Trung', 'link': 'https://www.google.com/maps/contrib/107253778101970197900?hl=vi', 'contributor_id': '107253778101970197900', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUNLHg5XlpgtWVVTp_oJKOYAejqmQORtgQ_Oe2vusE5W_sQoZc5=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 275, 'photos': 1279}</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Khu vực thác nước đẹp, nhiều cảnh quan, nhiều góc chụp đẹp.</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>3 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>{'name': 'Nghĩa Nguyễn Trung', 'link': 'https://www.google.com/maps/contrib/107253778101970197900?hl=vi', 'contributor_id': '107253778101970197900', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUNLHg5XlpgtWVVTp_oJKOYAejqmQORtgQ_Oe2vusE5W_sQoZc5=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 275, 'photos': 1279}</t>
+          <t>{'name': 'Frugal Flow', 'link': 'https://www.google.com/maps/contrib/107453311426556875441?hl=vi', 'contributor_id': '107453311426556875441', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUspWRVGEEQ_LyS16qRB57xWZ-kgNRIjgdLPY8T7HzvNMFlILCV=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 25, 'photos': 85}</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -715,45 +712,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Khu vực thác nước đẹp, nhiều cảnh quan, nhiều góc chụp đẹp.</t>
+          <t>Đi vào một ngày nắng. Nắng hắt lên mặt nước long lanh nên xinh xắn hẳn:&gt; Chỉ là thác nay có vẻ hơi ít nc nên không như mình tưởng tượng.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3 tháng trước</t>
+          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>{'name': 'Frugal Flow', 'link': 'https://www.google.com/maps/contrib/107453311426556875441?hl=vi', 'contributor_id': '107453311426556875441', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUspWRVGEEQ_LyS16qRB57xWZ-kgNRIjgdLPY8T7HzvNMFlILCV=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 25, 'photos': 85}</t>
+          <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 222, 'photos': 316}</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C15" t="inlineStr">
-        <is>
-          <t>Đi vào một ngày nắng. Nắng hắt lên mặt nước long lanh nên xinh xắn hẳn:&gt; Chỉ là thác nay có vẻ hơi ít nc nên không như mình tưởng tượng.</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>7 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 222, 'photos': 316}</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" t="inlineStr">
         <is>
           <t>Trải nghiệm vừa phải
 Giá vé theo trải nghiệm đi nhiều thác khác nhau của mình thì là khá cao so với các nơi khác, mình đi vào dịp tết nên thác ít nước.
@@ -761,64 +738,64 @@
 Cá nhân nếu quay lại Mộc Châu sẽ không đến thác này lần nào nữa</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>8 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>{'name': 'La Meu', 'link': 'https://www.google.com/maps/contrib/108858956358165703026?hl=vi', 'contributor_id': '108858956358165703026', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVKW-aZD0iBs1KBFQlmzfMiMTfjpd4PfUn4GO-K2tEt1PLpZ3YY=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 25, 'photos': 117}</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>5</v>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>Thác Dải Yếm là điểm du lịch rất đáng đi. Đường đi dễ, xe máy hay ô tô đều thuận tiện. Không gian mát mẻ, thiên nhiên đẹp và trong lành.
 Nước thác xanh biếc, chảy mạnh nhưng nhìn rất êm và thơ mộng, chụp hình lên đẹp lắm. Khu vực được làm lối đi khá an toàn, dễ tham quan.
 Nhân viên ở đây dễ thương, nhiệt tình, hướng dẫn khách rất chu đáo và thân thiện. Phù hợp đi chơi cùng gia đình hoặc bạn bè để thư giãn, nghỉ ngơi.</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>10 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 25, 'photos': 256}</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>10 tháng trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 25, 'photos': 256}</t>
+          <t>{'name': 'Thái Nguyễn', 'link': 'https://www.google.com/maps/contrib/105517365260915933657?hl=vi', 'contributor_id': '105517365260915933657', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXLOkY3FUSH3Mz-aapJXPQUgoCFlQP20PICWZGzVI3cPkRkBIt_ew=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 65, 'photos': 175}</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>5</v>
       </c>
       <c r="C18" t="inlineStr">
-        <is>
-          <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>8 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>{'name': 'Thái Nguyễn', 'link': 'https://www.google.com/maps/contrib/105517365260915933657?hl=vi', 'contributor_id': '105517365260915933657', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXLOkY3FUSH3Mz-aapJXPQUgoCFlQP20PICWZGzVI3cPkRkBIt_ew=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 65, 'photos': 175}</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>5</v>
-      </c>
-      <c r="C19" t="inlineStr">
         <is>
           <t>Nếu đi cùng Lover sẽ đẹp hơn.
 Nếu tự nhìn lại
@@ -886,6 +863,26 @@
 Hơn cả tới thiên đường</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>9 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 57, 'photos': 1256}</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>9 tháng trước</t>
@@ -895,27 +892,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 57, 'photos': 1245}</t>
+          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 94, 'photos': 1120}</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
+          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 94, 'photos': 1120}</t>
+          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 38, 'photos': 73}</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -923,19 +920,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
+          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>3 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 146, 'photos': 334}</t>
+          <t>{'name': 'ZjmLee YTBer', 'link': 'https://www.google.com/maps/contrib/100979561872983589256?hl=vi', 'contributor_id': '100979561872983589256', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU6i9poRXPBKYv-WgZHmB9chW6jRPCOh3klZ1Z7Yv_DOaukn4g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 79, 'photos': 1213}</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -943,7 +940,10 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
+          <t>Nghe người địa phương kể lại thì cái tên “Dải Yếm” xuất phát từ truyền thuyết của người Thái. Họ nói rằng dòng thác trắng xóa từ trên cao đổ xuống giống như dải yếm của người con gái, nên từ đó cái tên này được gọi luôn cho tới bây giờ. Nghe vậy nên đứng nhìn dòng thác cũng thấy có chút gì đó rất nên thơ.
+Đi bộ quanh khu thác khá dễ, có lối đi và bậc đá để xuống gần chân thác. Nếu đi vào mùa nước nhiều thì thác nhìn đẹp hơn, nước trắng xóa và tiếng thác nghe rất đã tai. Còn những ngày nắng nhẹ thì không khí ở đây khá chill, kiểu ngồi nghỉ một chút, nghe tiếng nước và nhìn rừng cây xung quanh cũng thấy thư giãn.
+Mình thấy Thác Dải Yếm hợp với kiểu du lịch nhẹ nhàng: dừng chân, đi bộ một vòng, chụp vài bức ảnh rồi tiếp tục hành trình khám phá Mộc Châu. Nó không phải kiểu điểm du lịch quá hoành tráng, nhưng lại có cái nét mộc mạc và dễ chịu đúng chất cao nguyên.
+Nếu đang đi du lịch tự túc ở Mộc Châu, thì Thác Dải Yếm là một nơi khá đáng ghé qua. Không cần quá nhiều thời gian, chỉ cần dành khoảng một tiếng dạo quanh thôi cũng đủ để cảm nhận được một góc thiên nhiên rất đặc trưng của vùng núi này.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -955,87 +955,87 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 38, 'photos': 73}</t>
+          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 34, 'photos': 79}</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
+          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3 tháng trước</t>
+          <t>4 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 34, 'photos': 79}</t>
+          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 114, 'photos': 86}</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
+          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4 tháng trước</t>
+          <t>9 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 114, 'photos': 83}</t>
+          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 191, 'photos': 3220}</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
+          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>11 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 191, 'photos': 3220}</t>
+          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 12, 'photos': 41}</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
+          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>11 tháng trước</t>
+          <t>10 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>{'name': 'Tình Đinh Thanh', 'link': 'https://www.google.com/maps/contrib/104009497892966545965?hl=vi', 'contributor_id': '104009497892966545965', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXRIh8MI-mVHJP5dVjbSfCSpyUeIeQPmA9d5ORdOdkVmBdnnvg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 252, 'photos': 5012}</t>
+          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 148, 'photos': 334}</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1043,45 +1043,25 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cảnh quan đẹp, ng dân thân thiện</t>
+          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 12, 'photos': 41}</t>
+          <t>{'name': 'Linh Nguyễn', 'link': 'https://www.google.com/maps/contrib/109820275513447282944?hl=vi', 'contributor_id': '109820275513447282944', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVpZ-SNyOn6byhXW5cnkMUzIYl8pLeo3scME3-VG4n2ps2S2tYx=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 144, 'photos': 992}</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>5</v>
       </c>
       <c r="C28" t="inlineStr">
-        <is>
-          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>10 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>{'name': 'Linh Nguyễn', 'link': 'https://www.google.com/maps/contrib/109820275513447282944?hl=vi', 'contributor_id': '109820275513447282944', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVpZ-SNyOn6byhXW5cnkMUzIYl8pLeo3scME3-VG4n2ps2S2tYx=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 144, 'photos': 992}</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>5</v>
-      </c>
-      <c r="C29" t="inlineStr">
         <is>
           <t>Thác đẹp, suối nước tự nhiên, đường đi dọc suối sạch sẽ
 Một số địa điểm du lịch ở Mộc Châu mọi người có thể tham khảo
@@ -1094,36 +1074,56 @@
 2. Cá Hồi Thanh Bảy</t>
         </is>
       </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 81, 'photos': 188}</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2 năm trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 81, 'photos': 188}</t>
+          <t>{'name': 'Nguyễn Tấn Thành', 'link': 'https://www.google.com/maps/contrib/117227534316521742646?hl=vi', 'contributor_id': '117227534316521742646', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUCPB87qD_q8UFnvBcCkGu3uE2AN4atMK6XrLGFH3fII6nWymikeg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 35, 'photos': 483}</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
+          <t>Cảnh ở thác rất là đẹp</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>một tháng trước</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Tấn Thành', 'link': 'https://www.google.com/maps/contrib/117227534316521742646?hl=vi', 'contributor_id': '117227534316521742646', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUCPB87qD_q8UFnvBcCkGu3uE2AN4atMK6XrLGFH3fII6nWymikeg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 35, 'photos': 483}</t>
+          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 12, 'photos': 65}</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1131,19 +1131,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cảnh ở thác rất là đẹp</t>
+          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>một tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 12, 'photos': 65}</t>
+          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 72, 'photos': 501}</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1151,39 +1151,40 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
+          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>5 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 72, 'photos': 501}</t>
+          <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 78, 'photos': 260}</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
+          <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
+Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 78, 'photos': 260}</t>
+          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 536, 'photos': 4147}</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1191,8 +1192,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
-Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
+          <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1204,33 +1204,13 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 536, 'photos': 4147}</t>
+          <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 91, 'photos': 574}</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C35" t="inlineStr">
-        <is>
-          <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 91, 'photos': 574}</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>5</v>
-      </c>
-      <c r="C36" t="inlineStr">
         <is>
           <t>Đúng tên gọi của nó. Thác cũng rất đẹp. Nếu vào mùa nước chắc còn đẹp hơn.
 Cảnh quan cũng rất sạch đẹp.
@@ -1239,16 +1219,36 @@
 - vé vào cổng giá phù hợp</t>
         </is>
       </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 652, 'photos': 4196}</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>5</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>Thời gian chỉnh sửa: 2 năm trước</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 652, 'photos': 4196}</t>
+          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 147, 'photos': 517}</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1256,27 +1256,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
+          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Thời gian chỉnh sửa: 2 năm trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 147, 'photos': 517}</t>
+          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 164, 'photos': 234}</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
+          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1288,15 +1288,15 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 164, 'photos': 234}</t>
+          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 134, 'photos': 248}</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
+          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1308,7 +1308,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 134, 'photos': 248}</t>
+          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 190, 'photos': 1652}</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1316,39 +1316,40 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
+          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>10 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 190, 'photos': 1641}</t>
+          <t>{'name': 'ninh Men', 'link': 'https://www.google.com/maps/contrib/103025469094717120638?hl=vi', 'contributor_id': '103025469094717120638', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJr8a3WVJHmayMF2FvRRdJjmyVlo0gmvjXedEtF6z5_xuOtxg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 29, 'photos': 168}</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+          <t>Đi Thác Dải Yếm đúng hôm… uống trà sữa trân châu. 😭
+Vé 150k/người nhưng cá nhân mình thấy hơi hụt hẫng. Thác không quá đặc biệt, đi một vòng là hết, chủ yếu là chụp ảnh. Nếu không thích check-in thì chắc sẽ thấy hơi “không có gì” so với giá vé.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>10 tháng trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>{'name': 'ninh Men', 'link': 'https://www.google.com/maps/contrib/103025469094717120638?hl=vi', 'contributor_id': '103025469094717120638', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJr8a3WVJHmayMF2FvRRdJjmyVlo0gmvjXedEtF6z5_xuOtxg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 29, 'photos': 168}</t>
+          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 50, 'photos': 144}</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1356,61 +1357,60 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Đi Thác Dải Yếm đúng hôm… uống trà sữa trân châu. 😭
-Vé 150k/người nhưng cá nhân mình thấy hơi hụt hẫng. Thác không quá đặc biệt, đi một vòng là hết, chủ yếu là chụp ảnh. Nếu không thích check-in thì chắc sẽ thấy hơi “không có gì” so với giá vé.</t>
+          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 50, 'photos': 144}</t>
+          <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVOAB-25PMt-dfRNT-0Cxi6yv3ndR1rsuSnkmcbVorHpLvMDfzp2g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 149, 'photos': 3873}</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
+          <t>Thác Dải Yếm, còn được gọi là thác Nàng, thác Bản Vặt, là một thác nước hùng vĩ nằm ở xã Mường Sang, huyện Mộc Châu, tỉnh Sơn La. Thác có chiều cao khoảng 100m, chia thành hai dòng thác chính, trông giống như một dải yếm đào mềm mại uốn lượn quanh vách núi.
+Thác Dải Yếm là một địa điểm du lịch hấp dẫn, thu hút khách du lịch trong và ngoài nước. Đây là nơi du khách có thể chiêm ngưỡng vẻ đẹp hùng vĩ của thác nước và tìm hiểu về truyền thuyết về thác.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>3 năm trước</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVOAB-25PMt-dfRNT-0Cxi6yv3ndR1rsuSnkmcbVorHpLvMDfzp2g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 149, 'photos': 3873}</t>
+          <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 97, 'photos': 178}</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm, còn được gọi là thác Nàng, thác Bản Vặt, là một thác nước hùng vĩ nằm ở xã Mường Sang, huyện Mộc Châu, tỉnh Sơn La. Thác có chiều cao khoảng 100m, chia thành hai dòng thác chính, trông giống như một dải yếm đào mềm mại uốn lượn quanh vách núi.
-Thác Dải Yếm là một địa điểm du lịch hấp dẫn, thu hút khách du lịch trong và ngoài nước. Đây là nơi du khách có thể chiêm ngưỡng vẻ đẹp hùng vĩ của thác nước và tìm hiểu về truyền thuyết về thác.</t>
+          <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2 năm trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 97, 'photos': 178}</t>
+          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 28, 'photos': 264}</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
+          <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1430,7 +1430,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 28, 'photos': 264}</t>
+          <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 75, 'photos': 503}</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1438,7 +1438,8 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
+          <t>Thác Dải Yếm nằm trên dòng suối Vặt khởi nguồn từ hai khe nước Bó Co Lắm và Bo Tá Cháu ở đầu bản Vặt, một bản của người Thái có lịch sử lâu đời. Suối Vặt chảy được 5 km đổ vào suối Bó Sập, một dòng suối lớn bắt nguồn từ bản Bó Sập giáp biên giới Việt Lào rồi chảy về đất Yên Châu. Tại nơi hợp lưu của hai suối, dòng nước gặp một vùng đá vôi và đổ xuống phía dưới tạo thành thác Dải Yếm.[5]
+Thác Dải Yếm bao gồm hai phần, thác nước phía trên rộng 70 mét, thác nước phía dưới nằm cách đó 150-200 mét. Vào mùa khô, thác phía dưới chỉ có một dòng chảy từ độ cao 50 m xuống triền đá ở dưới. hai thác đổ xuống với tổng chiều cao 100m, một bên được chia làm 9 tầng, bên còn lại 5 tầng. Cách giữa hai phần thác là một bãi đất phẳng thuận tiện cho việc tham quan của du khách. Thảm thực vật trên đỉnh thác cũng khá phong phú.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1450,74 +1451,53 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 75, 'photos': 503}</t>
+          <t>{'name': 'Chi Ho', 'link': 'https://www.google.com/maps/contrib/102731288821463748765?hl=vi', 'contributor_id': '102731288821463748765', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWV3y9KiqGo7jILq-ZzBkSw28LDZHnwKXBhstpTEeRvr9jffKE=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 85, 'photos': 1557}</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm nằm trên dòng suối Vặt khởi nguồn từ hai khe nước Bó Co Lắm và Bo Tá Cháu ở đầu bản Vặt, một bản của người Thái có lịch sử lâu đời. Suối Vặt chảy được 5 km đổ vào suối Bó Sập, một dòng suối lớn bắt nguồn từ bản Bó Sập giáp biên giới Việt Lào rồi chảy về đất Yên Châu. Tại nơi hợp lưu của hai suối, dòng nước gặp một vùng đá vôi và đổ xuống phía dưới tạo thành thác Dải Yếm.[5]
-Thác Dải Yếm bao gồm hai phần, thác nước phía trên rộng 70 mét, thác nước phía dưới nằm cách đó 150-200 mét. Vào mùa khô, thác phía dưới chỉ có một dòng chảy từ độ cao 50 m xuống triền đá ở dưới. hai thác đổ xuống với tổng chiều cao 100m, một bên được chia làm 9 tầng, bên còn lại 5 tầng. Cách giữa hai phần thác là một bãi đất phẳng thuận tiện cho việc tham quan của du khách. Thảm thực vật trên đỉnh thác cũng khá phong phú.</t>
+          <t>Thác Dải Yếm đẹp và hùng vĩ, xứng đáng cho chuyến picnic cuối tuần. Đường đi hơi gập ghềnh nhưng đến nơi thì quên hết mệt mỏi. Nước mát rượi, âm thanh róc rách rất thư giãn. Tiếc là hơi đông vào cuối tuần, nhưng cảnh đẹp bù đắp tất cả! Nên đi vào ngày thường nếu muốn yên tĩnh hơn.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>{'name': 'Chi Ho', 'link': 'https://www.google.com/maps/contrib/102731288821463748765?hl=vi', 'contributor_id': '102731288821463748765', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWV3y9KiqGo7jILq-ZzBkSw28LDZHnwKXBhstpTEeRvr9jffKE=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 85, 'photos': 1557}</t>
+          <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 8, 'photos': 90}</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm đẹp và hùng vĩ, xứng đáng cho chuyến picnic cuối tuần. Đường đi hơi gập ghềnh nhưng đến nơi thì quên hết mệt mỏi. Nước mát rượi, âm thanh róc rách rất thư giãn. Tiếc là hơi đông vào cuối tuần, nhưng cảnh đẹp bù đắp tất cả! Nên đi vào ngày thường nếu muốn yên tĩnh hơn.</t>
+          <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 8, 'photos': 90}</t>
+          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 151, 'photos': 1293}</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>4</v>
       </c>
       <c r="C49" t="inlineStr">
-        <is>
-          <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 151, 'photos': 1293}</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>4</v>
-      </c>
-      <c r="C50" t="inlineStr">
         <is>
           <t>Thác nhỏ cũng đẹp nhưng được trang trí dành cho du lịch rồi về độ rộng nhiều tầng và thiên nhiên thì không bằng thác Nàng Tiên hoặc thác Chiềng Khoa.
 Thác Dải Yếm được đầu tư khang trang nhưng đi bộ từ bãi gửi xe vào thác hơi bị xa (vé gửi xe 30k), đường đi vào và khu thác bên trong nhiều khu chụp ảnh checkin được trang trí chụp ảnh đẹp mắt. Giá vé tháng 1/2024 là 80k/ người vào cổng nhưng đến 30/4/2024 tăng lên 100k/ng giá vé hơi cao với việc vào ngắm thác.
@@ -1525,16 +1505,36 @@
 - Bản thân mình cảm nhận thì cũng bình thường thác không cao không rộng dài đẹp nhiều tầng bằng thác Nàng Tiên hoặc Chiềng Khoa. Nói chung đi du lịch Mộc Châu ghé qua cho biết thôi. Chứ để quay lại thì ít khả năng.</t>
         </is>
       </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 139, 'photos': 561}</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>View đẹp, chỉ tiếc là ghé hồi tháng 5 lúc đang mùa mưa, nên không được đi trải nghiệm nhiều.</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2 năm trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 139, 'photos': 561}</t>
+          <t>{'name': 'Nguyen Hung Son', 'link': 'https://www.google.com/maps/contrib/103602300698496865451?hl=vi', 'contributor_id': '103602300698496865451', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUZaCtGsEksmQHBlNq8Xrol7h098HYLQGNUZgSqhr55eCVudl46og=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 74, 'photos': 2146}</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>View đẹp, chỉ tiếc là ghé hồi tháng 5 lúc đang mùa mưa, nên không được đi trải nghiệm nhiều.</t>
+          <t>Thác Dải Yếm dường như trở thành một công viên. Lối vào thác khi đi qua cổng và đến Suối Hẹn Hò, khách thăm quan có thể đi theo đường bê tông hoặc đi xuống suối hẹn hò men theo đường lát đá ven suối và núi. Đa phần cá cảnh quan ở đây đã được cải tạo. Các trò chơi như Cầu Kính, Zipline và có lẽ đặc biệt nhất vẫn là check-in tại Thác Dải Yếm khi đầy nước. Vé vào cửa 100k/người lớn, trẻ em 50k (&lt;1,2m). Vé cầu kính 100k, Zipline 50k.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>2 năm trước</t>
         </is>
       </c>
     </row>

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -453,13 +453,33 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>{'name': 'Hanh Vu', 'link': 'https://www.google.com/maps/contrib/101916078015092582424?hl=vi', 'contributor_id': '101916078015092582424', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWKKa85i2VN2RSjhkp53oKKDcXbjK49YmqN3D2BpL8QOof8ZRlo=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 29, 'photos': 34}</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Thác Dải Yếm nằm trong khu du lịch sinh thái Thác Dải Yếm, vé vào 150k/người. Bên trong có thác nước nhưng nước khá đục nên không tắm được, có thêm cầu kính tình yêu để chụp ảnh. Mình thấy khu này không có quá nhiều điểm để tham quan, chủ yếu vào ngắm thác và chụp ảnh, nên nếu kỳ vọng có nhiều hoạt động thì sẽ hơi ít.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>một tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>{'name': 'Hưng Nguyễn Duy (Hưng Photo)', 'link': 'https://www.google.com/maps/contrib/110173941936897044295?hl=vi', 'contributor_id': '110173941936897044295', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXshx7xq3ntsswbv03kbw9Z9KIntVjsKdM747CeNwqebP-xH_RO=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 194, 'photos': 2205}</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>Địa điểm du lịch nổi tiếng nên khám phá khi tới Mộc Châu.
 Chỗ để xe rộng rãi (Phí gửi xe là 30N)
@@ -468,334 +488,258 @@
 Có bán nhiều đồ lưu niệm và đặc sản núi rừng Tây Bắc.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>5 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>{'name': 'Lương Chiến', 'link': 'https://www.google.com/maps/contrib/114003411979925662073?hl=vi', 'contributor_id': '114003411979925662073', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXO1ARmhC-FuyFKY7syAEGS67iDe2z5I4jLEITlCj3qmrZ35FZSCQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 195, 'photos': 2130}</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Review Thác Dải Yếm – Mộc Châu
+Thác Dải Yếm gây ấn tượng với dòng nước trắng xóa đổ xuống giữa núi rừng xanh mát.
+Dòng thác mềm mại như một dải lụa giữa đại ngàn, vừa hùng vĩ vừa thơ mộng.
+Không khí trong lành, cảnh sắc yên bình khiến nơi đây rất thích hợp để thư giãn và check-in.
+Đến Mộc Châu, Thác Dải Yếm chắc chắn là một điểm đến đáng để trải nghiệm.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>một tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>{'name': 'Mun Mèo', 'link': 'https://www.google.com/maps/contrib/107738293793735295575?hl=vi', 'contributor_id': '107738293793735295575', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocImCChsrh0Sth8X67Tx7Y80EKrcpDnaCY8RTbhpvHlYP2hmKg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 43, 'photos': 152}</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Thác trong xanh đẹp lắm nha, giá vé 150k/người bao gồm tham quan thác và vào cầu kính tình yêu. Thác này được phép vào nghịch nước và chụp ảnh. Các tảng đá có rêu và nước, khá trơn trượt, nên đi giày dép có đế chống trượt để đảm bảo an toàn. Có lối đi trên sườn núi để đi từ thác gần có vào qua thác dải yếm, lối này đi trên sườn núi có cây, rất mát mẻ. Nên đi tầm trưa vào ngày trong tuần, khách thăm quan ít nên chụp ảnh sẽ dễ hơn. Mình đi vào ngày trong tuần tầm từ 11-12h là mua vé vào cửa, cả khu chỉ có mình và bạn đồng hành, thư giãn lắm. Một số nơi trong thác có rác thải do khách thăm quan để lại, hi vọng mọi người đi thăm quan thì có ý thức giữ gìn vệ sinh chung để góp phần giữ gìn môi trường thiên nhiên thêm phần sạch đẹp nha ạ.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>một tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>{'name': 'Thanh Lưu', 'link': 'https://www.google.com/maps/contrib/110406765280977992752?hl=vi', 'contributor_id': '110406765280977992752', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJ_yTdPc0gm2s5_UkXQgJMiiGUhoCke1ESwlNAW8_0byLzqjF0=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 34, 'photos': 167}</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>⭐️⭐️⭐️⭐️⭐️ Quá đáng để đi! Cả nhà mê tít 💦
+Cuối tuần rồi nhà mình đưa hai đứa nhỏ lên thác Dải Yếm chơi, không nghĩ là đẹp hơn cả tưởng tượng. Thác chia làm nhiều tầng, nước đổ trắng xóa từ trên cao xuống, đứng dưới gió mát rượi, bụi nước bay vào người mát lạnh giữa trưa nắng luôn. Đúng kiểu "giải nhiệt" tự nhiên không cần điều hòa 😄
+Mình đi đúng mùa nước (tháng 6) nên thác chảy rất mạnh, nhìn cực đã. Có mấy phiến đá tròn bắc ngang suối làm lối đi, mấy đứa nhà mình thích lắm. Nước suối xanh trong, chỗ chân thác có hồ nước đẹp như tranh. Background chụp hình thì khỏi chê, tấm nào lên cũng lung linh, không cần chỉnh nhiều.
+Cầu kính Tình Yêu màu đỏ với mấy trái tim cũng là điểm nhấn nổi bật, đi lên cao ngắm được cả khu thác. Khu này còn có hồ cá Koi, đài phun nước, vườn hoa rực rỡ nên trẻ con tha hồ chạy nhảy, người lớn thì tha hồ "sống ảo".
+📝 Vài lưu ý nhỏ cho ai chuẩn bị đi:
+Đường vào dễ đi, ô tô xe máy đều tới được bãi gửi xe.
+Đi giày/dép quai hậu chống trượt vì đá ướt, có chỗ hơi trơn.
+Mang theo nón, nước uống, và nên đi buổi sáng cho mát, vắng người hơn.
+Có bán đồ ăn vặt, đặc sản Tây Bắc dọc đường, giá cũng hợp lý.
+Vé tham quan và vé cầu kính tính riêng, nên hỏi trước cho chủ động.
+Tóm lại: điểm dừng chân tuyệt vời cho gia đình có con nhỏ, vừa mát, vừa đẹp, vừa nhiều góc chơi. Nhất định sẽ quay lại! 🌿💙</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Thời gian chỉnh sửa: 2 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>{'name': 'Ngoc Vu', 'link': 'https://www.google.com/maps/contrib/108690447901904353450?hl=vi', 'contributor_id': '108690447901904353450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWfxdOn0PeKLec3vPdGma6QAeLm5W13lqA_TdPlL72m402yYLRpcA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 16, 'photos': 19}</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ko có gì nhiều, có thác là điểm nhấn vì thác rất mát, thêm cầu kính ty nhma cảm quan đi cầu kính bạch long chắc chắn và cảm giác an toàn tốt hơn. Giá vé 150k , có quán cf trc mặt thác view đẹp, mát , thiên nhiên diệu kỳ</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>một tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>{'name': 'Nguyễn Anh Quân', 'link': 'https://www.google.com/maps/contrib/111631093743063403454?hl=vi', 'contributor_id': '111631093743063403454', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIy-NjGEZ7ggp1yhLvVSe2iSDFAUAF4AILlK1IHBmSbkPzlKg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 9, 'photos': 24}</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Cảnh đẹp, nhưng xu là đi ngay lúc mưa nên thác có nước như cf</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 302, 'photos': 3623}</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>5 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>{'name': 'Gia Hân Nhâm', 'link': 'https://www.google.com/maps/contrib/105260403784604064817?hl=vi', 'contributor_id': '105260403784604064817', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXW4Eq54WOYUlLcmPr0wFzcfgLQhMAImSwK6dXvpDOyeFlOocZZ7w=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 15, 'photos': 64}</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Thác rất đẹp, bước vào thật sự bị ngộp khung cảnh hùng vĩ của Việt Nam mình. Mỗi nơi đi là mỗi trải nghiệm</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>một tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 12, 'photos': 25}</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>7 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>{'name': 'Cửu Quang Nguyễn', 'link': 'https://www.google.com/maps/contrib/107704339232071144994?hl=vi', 'contributor_id': '107704339232071144994', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV2_oJLqzlVCtXNV77ConxSPDhhMhFP-czjeCf6uCm7cabO88k=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 79, 'photos': 359}</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Thác Dải Yếm nằm trong khu du lịch sinh thái thác Dải Yếm, đường đi khá tiện lợi để ghé vào, tuy nhiên cần chú ý lối vào có khúc cua dốc khá ngoặt. Vé vào là 150k/người, bên trong có khá nhiều vị trí để du ngoạn và ngắm cảnh, đặc biệt là khu vực thác nước rất hùng vĩ và mát mẻ, có cầu dẫn vào nhìn rất thơ mộng và tuyệt vời. Nếu có dịp ghé lên Mộc Châu thì nên ghé vào đây chơi 1 lần để du ngoạn thắng cảnh thiên nhiên tại nơi đây.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>6 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 25, 'photos': 245}</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 377, 'photos': 2666}</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Nơi rất đáng để tham quan, trãi nghiệm chút it về cầu kính và kết hợp đi ngắm thác nước.
 Có nhiều nơi lên hình đẹp, cảnh đẹp. Có bán đặc sản Mộc Châu rất đa dạng.
 😍😍👍</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Thời gian chỉnh sửa: 6 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>{'name': 'Vĩ Lê Bá', 'link': 'https://www.google.com/maps/contrib/115860838984920745696?hl=vi', 'contributor_id': '115860838984920745696', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7wdRrYJWeEmKs7YInZz_FDg-T90l2ImigSwJKL2hWmQu75bzm=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 61, 'photos': 96}</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Đẹp thì đẹp sơ sơ nhưng không gian vẫn khá là thoải mái
-Đi bộ oklea nhưng mà vẫn còn quá nhỏ, đi cỡ 30 phút là xong mất tiêu r
-Tuỳ ngà lượng khách sẽ khác nhau và ảnh hưởng lớn tớ trải nghiệm
-Nói chung là vẫn okela</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>7 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>{'name': 'Hanh Vu', 'link': 'https://www.google.com/maps/contrib/101916078015092582424?hl=vi', 'contributor_id': '101916078015092582424', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWKKa85i2VN2RSjhkp53oKKDcXbjK49YmqN3D2BpL8QOof8ZRlo=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 29, 'photos': 34}</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm nằm trong khu du lịch sinh thái Thác Dải Yếm, vé vào 150k/người. Bên trong có thác nước nhưng nước khá đục nên không tắm được, có thêm cầu kính tình yêu để chụp ảnh. Mình thấy khu này không có quá nhiều điểm để tham quan, chủ yếu vào ngắm thác và chụp ảnh, nên nếu kỳ vọng có nhiều hoạt động thì sẽ hơi ít.</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>một tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>{'name': 'THANH NGUYEN', 'link': 'https://www.google.com/maps/contrib/110418688752170937071?hl=vi', 'contributor_id': '110418688752170937071', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIBtT-SxDlGGJM5jA47OmxpGvFdaG6EOeSswcBwx4VuXgnOdQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 71, 'photos': 238}</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>thác đẹp nhưng nên đi vào mùa nước sẽ thấy sự khác biệt hơn nhiều</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>{'name': 'Cửu Quang Nguyễn', 'link': 'https://www.google.com/maps/contrib/107704339232071144994?hl=vi', 'contributor_id': '107704339232071144994', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV2_oJLqzlVCtXNV77ConxSPDhhMhFP-czjeCf6uCm7cabO88k=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 79, 'photos': 359}</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm nằm trong khu du lịch sinh thái thác Dải Yếm, đường đi khá tiện lợi để ghé vào, tuy nhiên cần chú ý lối vào có khúc cua dốc khá ngoặt. Vé vào là 150k/người, bên trong có khá nhiều vị trí để du ngoạn và ngắm cảnh, đặc biệt là khu vực thác nước rất hùng vĩ và mát mẻ, có cầu dẫn vào nhìn rất thơ mộng và tuyệt vời. Nếu có dịp ghé lên Mộc Châu thì nên ghé vào đây chơi 1 lần để du ngoạn thắng cảnh thiên nhiên tại nơi đây.</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>6 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>{'name': 'Nguyễn Anh Quân', 'link': 'https://www.google.com/maps/contrib/111631093743063403454?hl=vi', 'contributor_id': '111631093743063403454', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIy-NjGEZ7ggp1yhLvVSe2iSDFAUAF4AILlK1IHBmSbkPzlKg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 9, 'photos': 24}</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Cảnh đẹp, nhưng xu là đi ngay lúc mưa nên thác có nước như cf</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 302, 'photos': 3616}</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>5 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>{'name': 'Gia Hân Nhâm', 'link': 'https://www.google.com/maps/contrib/105260403784604064817?hl=vi', 'contributor_id': '105260403784604064817', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXW4Eq54WOYUlLcmPr0wFzcfgLQhMAImSwK6dXvpDOyeFlOocZZ7w=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 15, 'photos': 63}</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Thác rất đẹp, bước vào thật sự bị ngộp khung cảnh hùng vĩ của Việt Nam mình. Mỗi nơi đi là mỗi trải nghiệm</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>một tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 12, 'photos': 25}</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>6 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 16, 'photos': 114}</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Đi tầm trưa nắng đẹp
-Thác nhỏ, đi cũng không mất quá nhiều thời gian
-Có cầu kính</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>8 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>{'name': 'Nghĩa Nguyễn Trung', 'link': 'https://www.google.com/maps/contrib/107253778101970197900?hl=vi', 'contributor_id': '107253778101970197900', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUNLHg5XlpgtWVVTp_oJKOYAejqmQORtgQ_Oe2vusE5W_sQoZc5=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 275, 'photos': 1279}</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Khu vực thác nước đẹp, nhiều cảnh quan, nhiều góc chụp đẹp.</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>3 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>{'name': 'Frugal Flow', 'link': 'https://www.google.com/maps/contrib/107453311426556875441?hl=vi', 'contributor_id': '107453311426556875441', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUspWRVGEEQ_LyS16qRB57xWZ-kgNRIjgdLPY8T7HzvNMFlILCV=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 25, 'photos': 85}</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Đi vào một ngày nắng. Nắng hắt lên mặt nước long lanh nên xinh xắn hẳn:&gt; Chỉ là thác nay có vẻ hơi ít nc nên không như mình tưởng tượng.</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 222, 'photos': 316}</t>
+          <t>{'name': 'Thái Nguyễn', 'link': 'https://www.google.com/maps/contrib/105517365260915933657?hl=vi', 'contributor_id': '105517365260915933657', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXLOkY3FUSH3Mz-aapJXPQUgoCFlQP20PICWZGzVI3cPkRkBIt_ew=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 65, 'photos': 164}</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C15" t="inlineStr">
-        <is>
-          <t>Trải nghiệm vừa phải
-Giá vé theo trải nghiệm đi nhiều thác khác nhau của mình thì là khá cao so với các nơi khác, mình đi vào dịp tết nên thác ít nước.
-Cảnh quan xung quanh thác ở mức bình thường.
-Cá nhân nếu quay lại Mộc Châu sẽ không đến thác này lần nào nữa</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>8 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>{'name': 'La Meu', 'link': 'https://www.google.com/maps/contrib/108858956358165703026?hl=vi', 'contributor_id': '108858956358165703026', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVKW-aZD0iBs1KBFQlmzfMiMTfjpd4PfUn4GO-K2tEt1PLpZ3YY=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 25, 'photos': 117}</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>5</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm là điểm du lịch rất đáng đi. Đường đi dễ, xe máy hay ô tô đều thuận tiện. Không gian mát mẻ, thiên nhiên đẹp và trong lành.
-Nước thác xanh biếc, chảy mạnh nhưng nhìn rất êm và thơ mộng, chụp hình lên đẹp lắm. Khu vực được làm lối đi khá an toàn, dễ tham quan.
-Nhân viên ở đây dễ thương, nhiệt tình, hướng dẫn khách rất chu đáo và thân thiện. Phù hợp đi chơi cùng gia đình hoặc bạn bè để thư giãn, nghỉ ngơi.</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>10 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 25, 'photos': 256}</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>5</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>8 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>{'name': 'Thái Nguyễn', 'link': 'https://www.google.com/maps/contrib/105517365260915933657?hl=vi', 'contributor_id': '105517365260915933657', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXLOkY3FUSH3Mz-aapJXPQUgoCFlQP20PICWZGzVI3cPkRkBIt_ew=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 65, 'photos': 175}</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>5</v>
-      </c>
-      <c r="C18" t="inlineStr">
         <is>
           <t>Nếu đi cùng Lover sẽ đẹp hơn.
 Nếu tự nhìn lại
@@ -863,82 +807,45 @@
 Hơn cả tới thiên đường</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>9 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 57, 'photos': 1256}</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>3</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>9 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 94, 'photos': 1120}</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>5</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 38, 'photos': 73}</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>5</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>3 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>{'name': 'Vĩ Lê Bá', 'link': 'https://www.google.com/maps/contrib/115860838984920745696?hl=vi', 'contributor_id': '115860838984920745696', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7wdRrYJWeEmKs7YInZz_FDg-T90l2ImigSwJKL2hWmQu75bzm=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 61, 'photos': 96}</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Đẹp thì đẹp sơ sơ nhưng không gian vẫn khá là thoải mái
+Đi bộ oklea nhưng mà vẫn còn quá nhỏ, đi cỡ 30 phút là xong mất tiêu r
+Tuỳ ngà lượng khách sẽ khác nhau và ảnh hưởng lớn tớ trải nghiệm
+Nói chung là vẫn okela</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>7 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>{'name': 'ZjmLee YTBer', 'link': 'https://www.google.com/maps/contrib/100979561872983589256?hl=vi', 'contributor_id': '100979561872983589256', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU6i9poRXPBKYv-WgZHmB9chW6jRPCOh3klZ1Z7Yv_DOaukn4g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 79, 'photos': 1213}</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>5</v>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Nghe người địa phương kể lại thì cái tên “Dải Yếm” xuất phát từ truyền thuyết của người Thái. Họ nói rằng dòng thác trắng xóa từ trên cao đổ xuống giống như dải yếm của người con gái, nên từ đó cái tên này được gọi luôn cho tới bây giờ. Nghe vậy nên đứng nhìn dòng thác cũng thấy có chút gì đó rất nên thơ.
 Đi bộ quanh khu thác khá dễ, có lối đi và bậc đá để xuống gần chân thác. Nếu đi vào mùa nước nhiều thì thác nhìn đẹp hơn, nước trắng xóa và tiếng thác nghe rất đã tai. Còn những ngày nắng nhẹ thì không khí ở đây khá chill, kiểu ngồi nghỉ một chút, nghe tiếng nước và nhìn rừng cây xung quanh cũng thấy thư giãn.
@@ -946,36 +853,138 @@
 Nếu đang đi du lịch tự túc ở Mộc Châu, thì Thác Dải Yếm là một nơi khá đáng ghé qua. Không cần quá nhiều thời gian, chỉ cần dành khoảng một tiếng dạo quanh thôi cũng đủ để cảm nhận được một góc thiên nhiên rất đặc trưng của vùng núi này.</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>7 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>{'name': 'La Meu', 'link': 'https://www.google.com/maps/contrib/108858956358165703026?hl=vi', 'contributor_id': '108858956358165703026', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVKW-aZD0iBs1KBFQlmzfMiMTfjpd4PfUn4GO-K2tEt1PLpZ3YY=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 25, 'photos': 117}</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Thác Dải Yếm là điểm du lịch rất đáng đi. Đường đi dễ, xe máy hay ô tô đều thuận tiện. Không gian mát mẻ, thiên nhiên đẹp và trong lành.
+Nước thác xanh biếc, chảy mạnh nhưng nhìn rất êm và thơ mộng, chụp hình lên đẹp lắm. Khu vực được làm lối đi khá an toàn, dễ tham quan.
+Nhân viên ở đây dễ thương, nhiệt tình, hướng dẫn khách rất chu đáo và thân thiện. Phù hợp đi chơi cùng gia đình hoặc bạn bè để thư giãn, nghỉ ngơi.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>10 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>{'name': 'Nghĩa Nguyễn Trung', 'link': 'https://www.google.com/maps/contrib/107253778101970197900?hl=vi', 'contributor_id': '107253778101970197900', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUNLHg5XlpgtWVVTp_oJKOYAejqmQORtgQ_Oe2vusE5W_sQoZc5=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 275, 'photos': 1279}</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Khu vực thác nước đẹp, nhiều cảnh quan, nhiều góc chụp đẹp.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>3 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 114, 'photos': 86}</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>9 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 94, 'photos': 1120}</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 12, 'photos': 41}</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>7 tháng trước</t>
+          <t>10 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 34, 'photos': 79}</t>
+          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 57, 'photos': 1270}</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
+          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4 tháng trước</t>
+          <t>9 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 114, 'photos': 86}</t>
+          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 148, 'photos': 340}</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -983,85 +992,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
+          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>{'name': 'ktshung Pham', 'link': 'https://www.google.com/maps/contrib/101714314764727838199?hl=vi', 'contributor_id': '101714314764727838199', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUy5Fc2uP5d2ErjS9OKQ-LaKmrQ_kkM_SLu0gNjK_5i5QorYFY=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 191, 'photos': 3220}</t>
+          <t>{'name': 'Linh Nguyễn', 'link': 'https://www.google.com/maps/contrib/109820275513447282944?hl=vi', 'contributor_id': '109820275513447282944', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVpZ-SNyOn6byhXW5cnkMUzIYl8pLeo3scME3-VG4n2ps2S2tYx=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 144, 'photos': 992}</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" t="inlineStr">
-        <is>
-          <t>Một địa điểm khá thú vị cho bạn khám phá và thư giãn khi có dịp về Mộc Châu.  Với nước và cỏ cây hoa lá cho bạn lạc bước trong miền thiên nhiên lan tỏa nắng gió và ánh sáng, với khí hậu mát mẻ... Bạn sẽ dễ dàng tìm lại bất kỳ sự hân hoan hứng khởi nào mà bạn muốn có...</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>11 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 12, 'photos': 41}</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>5</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>10 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 148, 'photos': 334}</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>5</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>7 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>{'name': 'Linh Nguyễn', 'link': 'https://www.google.com/maps/contrib/109820275513447282944?hl=vi', 'contributor_id': '109820275513447282944', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVpZ-SNyOn6byhXW5cnkMUzIYl8pLeo3scME3-VG4n2ps2S2tYx=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 144, 'photos': 992}</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>5</v>
-      </c>
-      <c r="C28" t="inlineStr">
         <is>
           <t>Thác đẹp, suối nước tự nhiên, đường đi dọc suối sạch sẽ
 Một số địa điểm du lịch ở Mộc Châu mọi người có thể tham khảo
@@ -1074,36 +1023,96 @@
 2. Cá Hồi Thanh Bảy</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 81, 'photos': 188}</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>8 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>{'name': 'Nguyễn Tấn Thành', 'link': 'https://www.google.com/maps/contrib/117227534316521742646?hl=vi', 'contributor_id': '117227534316521742646', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUCPB87qD_q8UFnvBcCkGu3uE2AN4atMK6XrLGFH3fII6nWymikeg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 35, 'photos': 483}</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Cảnh ở thác rất là đẹp</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>một tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 12, 'photos': 65}</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2 năm trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 81, 'photos': 188}</t>
+          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 38, 'photos': 73}</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
+          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>3 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Tấn Thành', 'link': 'https://www.google.com/maps/contrib/117227534316521742646?hl=vi', 'contributor_id': '117227534316521742646', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUCPB87qD_q8UFnvBcCkGu3uE2AN4atMK6XrLGFH3fII6nWymikeg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 35, 'photos': 483}</t>
+          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 72, 'photos': 501}</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1111,27 +1120,28 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cảnh ở thác rất là đẹp</t>
+          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>một tháng trước</t>
+          <t>5 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 12, 'photos': 65}</t>
+          <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 78, 'photos': 260}</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
+          <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
+Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1143,74 +1153,33 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 72, 'photos': 501}</t>
+          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 536, 'photos': 4147}</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
+          <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 78, 'photos': 260}</t>
+          <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 91, 'photos': 574}</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C33" t="inlineStr">
-        <is>
-          <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
-Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 536, 'photos': 4147}</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>4</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 91, 'photos': 574}</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>5</v>
-      </c>
-      <c r="C35" t="inlineStr">
         <is>
           <t>Đúng tên gọi của nó. Thác cũng rất đẹp. Nếu vào mùa nước chắc còn đẹp hơn.
 Cảnh quan cũng rất sạch đẹp.
@@ -1219,6 +1188,46 @@
 - vé vào cổng giá phù hợp</t>
         </is>
       </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 652, 'photos': 4196}</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Thời gian chỉnh sửa: 2 năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 147, 'photos': 517}</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>5</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
           <t>một năm trước</t>
@@ -1228,35 +1237,38 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 652, 'photos': 4196}</t>
+          <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 222, 'photos': 316}</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
+          <t>Trải nghiệm vừa phải
+Giá vé theo trải nghiệm đi nhiều thác khác nhau của mình thì là khá cao so với các nơi khác, mình đi vào dịp tết nên thác ít nước.
+Cảnh quan xung quanh thác ở mức bình thường.
+Cá nhân nếu quay lại Mộc Châu sẽ không đến thác này lần nào nữa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Thời gian chỉnh sửa: 2 năm trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 147, 'photos': 517}</t>
+          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 164, 'photos': 234}</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
+          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1268,20 +1280,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 164, 'photos': 234}</t>
+          <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 16, 'photos': 114}</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
+          <t>Đi tầm trưa nắng đẹp
+Thác nhỏ, đi cũng không mất quá nhiều thời gian
+Có cầu kính</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
@@ -1328,89 +1342,89 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>{'name': 'THANH NGUYEN', 'link': 'https://www.google.com/maps/contrib/110418688752170937071?hl=vi', 'contributor_id': '110418688752170937071', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIBtT-SxDlGGJM5jA47OmxpGvFdaG6EOeSswcBwx4VuXgnOdQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 71, 'photos': 238}</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>5</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>thác đẹp nhưng nên đi vào mùa nước sẽ thấy sự khác biệt hơn nhiều</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>8 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>{'name': 'ninh Men', 'link': 'https://www.google.com/maps/contrib/103025469094717120638?hl=vi', 'contributor_id': '103025469094717120638', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJr8a3WVJHmayMF2FvRRdJjmyVlo0gmvjXedEtF6z5_xuOtxg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 29, 'photos': 168}</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="B42" t="n">
         <v>4</v>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Đi Thác Dải Yếm đúng hôm… uống trà sữa trân châu. 😭
 Vé 150k/người nhưng cá nhân mình thấy hơi hụt hẫng. Thác không quá đặc biệt, đi một vòng là hết, chủ yếu là chụp ảnh. Nếu không thích check-in thì chắc sẽ thấy hơi “không có gì” so với giá vé.</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>2 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 50, 'photos': 144}</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>4</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 50, 'photos': 144}</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>4</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVOAB-25PMt-dfRNT-0Cxi6yv3ndR1rsuSnkmcbVorHpLvMDfzp2g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 149, 'photos': 3873}</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>5</v>
-      </c>
-      <c r="C43" t="inlineStr">
+      <c r="B44" t="n">
+        <v>5</v>
+      </c>
+      <c r="C44" t="inlineStr">
         <is>
           <t>Thác Dải Yếm, còn được gọi là thác Nàng, thác Bản Vặt, là một thác nước hùng vĩ nằm ở xã Mường Sang, huyện Mộc Châu, tỉnh Sơn La. Thác có chiều cao khoảng 100m, chia thành hai dòng thác chính, trông giống như một dải yếm đào mềm mại uốn lượn quanh vách núi.
 Thác Dải Yếm là một địa điểm du lịch hấp dẫn, thu hút khách du lịch trong và ngoài nước. Đây là nơi du khách có thể chiêm ngưỡng vẻ đẹp hùng vĩ của thác nước và tìm hiểu về truyền thuyết về thác.</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>3 năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 97, 'photos': 178}</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>4</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 28, 'photos': 264}</t>
+          <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 97, 'photos': 178}</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1418,7 +1432,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
+          <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1430,7 +1444,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 75, 'photos': 503}</t>
+          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 28, 'photos': 264}</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1438,66 +1452,86 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 75, 'photos': 503}</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>4</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
           <t>Thác Dải Yếm nằm trên dòng suối Vặt khởi nguồn từ hai khe nước Bó Co Lắm và Bo Tá Cháu ở đầu bản Vặt, một bản của người Thái có lịch sử lâu đời. Suối Vặt chảy được 5 km đổ vào suối Bó Sập, một dòng suối lớn bắt nguồn từ bản Bó Sập giáp biên giới Việt Lào rồi chảy về đất Yên Châu. Tại nơi hợp lưu của hai suối, dòng nước gặp một vùng đá vôi và đổ xuống phía dưới tạo thành thác Dải Yếm.[5]
 Thác Dải Yếm bao gồm hai phần, thác nước phía trên rộng 70 mét, thác nước phía dưới nằm cách đó 150-200 mét. Vào mùa khô, thác phía dưới chỉ có một dòng chảy từ độ cao 50 m xuống triền đá ở dưới. hai thác đổ xuống với tổng chiều cao 100m, một bên được chia làm 9 tầng, bên còn lại 5 tầng. Cách giữa hai phần thác là một bãi đất phẳng thuận tiện cho việc tham quan của du khách. Thảm thực vật trên đỉnh thác cũng khá phong phú.</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>{'name': 'Chi Ho', 'link': 'https://www.google.com/maps/contrib/102731288821463748765?hl=vi', 'contributor_id': '102731288821463748765', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWV3y9KiqGo7jILq-ZzBkSw28LDZHnwKXBhstpTEeRvr9jffKE=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 85, 'photos': 1557}</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>5</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm đẹp và hùng vĩ, xứng đáng cho chuyến picnic cuối tuần. Đường đi hơi gập ghềnh nhưng đến nơi thì quên hết mệt mỏi. Nước mát rượi, âm thanh róc rách rất thư giãn. Tiếc là hơi đông vào cuối tuần, nhưng cảnh đẹp bù đắp tất cả! Nên đi vào ngày thường nếu muốn yên tĩnh hơn.</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 8, 'photos': 90}</t>
+          <t>{'name': 'Chi Ho', 'link': 'https://www.google.com/maps/contrib/102731288821463748765?hl=vi', 'contributor_id': '102731288821463748765', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWV3y9KiqGo7jILq-ZzBkSw28LDZHnwKXBhstpTEeRvr9jffKE=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 84, 'photos': 1557}</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
+          <t>Thác Dải Yếm đẹp và hùng vĩ, xứng đáng cho chuyến picnic cuối tuần. Đường đi hơi gập ghềnh nhưng đến nơi thì quên hết mệt mỏi. Nước mát rượi, âm thanh róc rách rất thư giãn. Tiếc là hơi đông vào cuối tuần, nhưng cảnh đẹp bù đắp tất cả! Nên đi vào ngày thường nếu muốn yên tĩnh hơn.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 151, 'photos': 1293}</t>
+          <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 8, 'photos': 90}</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>4</v>
       </c>
       <c r="C49" t="inlineStr">
+        <is>
+          <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 151, 'photos': 1293}</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C50" t="inlineStr">
         <is>
           <t>Thác nhỏ cũng đẹp nhưng được trang trí dành cho du lịch rồi về độ rộng nhiều tầng và thiên nhiên thì không bằng thác Nàng Tiên hoặc thác Chiềng Khoa.
 Thác Dải Yếm được đầu tư khang trang nhưng đi bộ từ bãi gửi xe vào thác hơi bị xa (vé gửi xe 30k), đường đi vào và khu thác bên trong nhiều khu chụp ảnh checkin được trang trí chụp ảnh đẹp mắt. Giá vé tháng 1/2024 là 80k/ người vào cổng nhưng đến 30/4/2024 tăng lên 100k/ng giá vé hơi cao với việc vào ngắm thác.
@@ -1505,36 +1539,16 @@
 - Bản thân mình cảm nhận thì cũng bình thường thác không cao không rộng dài đẹp nhiều tầng bằng thác Nàng Tiên hoặc Chiềng Khoa. Nói chung đi du lịch Mộc Châu ghé qua cho biết thôi. Chứ để quay lại thì ít khả năng.</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>2 năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>{'name': 'Nam Trịnh', 'link': 'https://www.google.com/maps/contrib/109923724849198466081?hl=vi', 'contributor_id': '109923724849198466081', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVMyxD1p3SKX19GlEjNK4umvctQEJfMbuk2tL83usQxD9neHgsm=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 139, 'photos': 561}</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>4</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>View đẹp, chỉ tiếc là ghé hồi tháng 5 lúc đang mùa mưa, nên không được đi trải nghiệm nhiều.</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyen Hung Son', 'link': 'https://www.google.com/maps/contrib/103602300698496865451?hl=vi', 'contributor_id': '103602300698496865451', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUZaCtGsEksmQHBlNq8Xrol7h098HYLQGNUZgSqhr55eCVudl46og=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 74, 'photos': 2146}</t>
+          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 34, 'photos': 79}</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -1542,12 +1556,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm dường như trở thành một công viên. Lối vào thác khi đi qua cổng và đến Suối Hẹn Hò, khách thăm quan có thể đi theo đường bê tông hoặc đi xuống suối hẹn hò men theo đường lát đá ven suối và núi. Đa phần cá cảnh quan ở đây đã được cải tạo. Các trò chơi như Cầu Kính, Zipline và có lẽ đặc biệt nhất vẫn là check-in tại Thác Dải Yếm khi đầy nước. Vé vào cửa 100k/người lớn, trẻ em 50k (&lt;1,2m). Vé cầu kính 100k, Zipline 50k.</t>
+          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2 năm trước</t>
+          <t>4 tháng trước</t>
         </is>
       </c>
     </row>

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -453,33 +453,13 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{'name': 'Hanh Vu', 'link': 'https://www.google.com/maps/contrib/101916078015092582424?hl=vi', 'contributor_id': '101916078015092582424', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWKKa85i2VN2RSjhkp53oKKDcXbjK49YmqN3D2BpL8QOof8ZRlo=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 29, 'photos': 34}</t>
+          <t>{'name': 'Hưng Nguyễn Duy (Hưng Photo)', 'link': 'https://www.google.com/maps/contrib/110173941936897044295?hl=vi', 'contributor_id': '110173941936897044295', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXshx7xq3ntsswbv03kbw9Z9KIntVjsKdM747CeNwqebP-xH_RO=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 194, 'photos': 2205}</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm nằm trong khu du lịch sinh thái Thác Dải Yếm, vé vào 150k/người. Bên trong có thác nước nhưng nước khá đục nên không tắm được, có thêm cầu kính tình yêu để chụp ảnh. Mình thấy khu này không có quá nhiều điểm để tham quan, chủ yếu vào ngắm thác và chụp ảnh, nên nếu kỳ vọng có nhiều hoạt động thì sẽ hơi ít.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>một tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>{'name': 'Hưng Nguyễn Duy (Hưng Photo)', 'link': 'https://www.google.com/maps/contrib/110173941936897044295?hl=vi', 'contributor_id': '110173941936897044295', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXshx7xq3ntsswbv03kbw9Z9KIntVjsKdM747CeNwqebP-xH_RO=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 194, 'photos': 2205}</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C3" t="inlineStr">
         <is>
           <t>Địa điểm du lịch nổi tiếng nên khám phá khi tới Mộc Châu.
 Chỗ để xe rộng rãi (Phí gửi xe là 30N)
@@ -488,22 +468,22 @@
 Có bán nhiều đồ lưu niệm và đặc sản núi rừng Tây Bắc.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>5 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>{'name': 'Lương Chiến', 'link': 'https://www.google.com/maps/contrib/114003411979925662073?hl=vi', 'contributor_id': '114003411979925662073', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXO1ARmhC-FuyFKY7syAEGS67iDe2z5I4jLEITlCj3qmrZ35FZSCQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 195, 'photos': 2130}</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>Review Thác Dải Yếm – Mộc Châu
 Thác Dải Yếm gây ấn tượng với dòng nước trắng xóa đổ xuống giữa núi rừng xanh mát.
@@ -512,6 +492,26 @@
 Đến Mộc Châu, Thác Dải Yếm chắc chắn là một điểm đến đáng để trải nghiệm.</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>một tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>{'name': 'Mun Mèo', 'link': 'https://www.google.com/maps/contrib/107738293793735295575?hl=vi', 'contributor_id': '107738293793735295575', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocImCChsrh0Sth8X67Tx7Y80EKrcpDnaCY8RTbhpvHlYP2hmKg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 43, 'photos': 152}</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Thác trong xanh đẹp lắm nha, giá vé 150k/người bao gồm tham quan thác và vào cầu kính tình yêu. Thác này được phép vào nghịch nước và chụp ảnh. Các tảng đá có rêu và nước, khá trơn trượt, nên đi giày dép có đế chống trượt để đảm bảo an toàn. Có lối đi trên sườn núi để đi từ thác gần có vào qua thác dải yếm, lối này đi trên sườn núi có cây, rất mát mẻ. Nên đi tầm trưa vào ngày trong tuần, khách thăm quan ít nên chụp ảnh sẽ dễ hơn. Mình đi vào ngày trong tuần tầm từ 11-12h là mua vé vào cửa, cả khu chỉ có mình và bạn đồng hành, thư giãn lắm. Một số nơi trong thác có rác thải do khách thăm quan để lại, hi vọng mọi người đi thăm quan thì có ý thức giữ gìn vệ sinh chung để góp phần giữ gìn môi trường thiên nhiên thêm phần sạch đẹp nha ạ.</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>một tháng trước</t>
@@ -521,33 +521,13 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>{'name': 'Mun Mèo', 'link': 'https://www.google.com/maps/contrib/107738293793735295575?hl=vi', 'contributor_id': '107738293793735295575', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocImCChsrh0Sth8X67Tx7Y80EKrcpDnaCY8RTbhpvHlYP2hmKg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 43, 'photos': 152}</t>
+          <t>{'name': 'Thanh Lưu', 'link': 'https://www.google.com/maps/contrib/110406765280977992752?hl=vi', 'contributor_id': '110406765280977992752', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJ_yTdPc0gm2s5_UkXQgJMiiGUhoCke1ESwlNAW8_0byLzqjF0=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 34, 'photos': 167}</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>5</v>
       </c>
       <c r="C5" t="inlineStr">
-        <is>
-          <t>Thác trong xanh đẹp lắm nha, giá vé 150k/người bao gồm tham quan thác và vào cầu kính tình yêu. Thác này được phép vào nghịch nước và chụp ảnh. Các tảng đá có rêu và nước, khá trơn trượt, nên đi giày dép có đế chống trượt để đảm bảo an toàn. Có lối đi trên sườn núi để đi từ thác gần có vào qua thác dải yếm, lối này đi trên sườn núi có cây, rất mát mẻ. Nên đi tầm trưa vào ngày trong tuần, khách thăm quan ít nên chụp ảnh sẽ dễ hơn. Mình đi vào ngày trong tuần tầm từ 11-12h là mua vé vào cửa, cả khu chỉ có mình và bạn đồng hành, thư giãn lắm. Một số nơi trong thác có rác thải do khách thăm quan để lại, hi vọng mọi người đi thăm quan thì có ý thức giữ gìn vệ sinh chung để góp phần giữ gìn môi trường thiên nhiên thêm phần sạch đẹp nha ạ.</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>một tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>{'name': 'Thanh Lưu', 'link': 'https://www.google.com/maps/contrib/110406765280977992752?hl=vi', 'contributor_id': '110406765280977992752', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJ_yTdPc0gm2s5_UkXQgJMiiGUhoCke1ESwlNAW8_0byLzqjF0=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 34, 'photos': 167}</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" t="inlineStr">
         <is>
           <t>⭐️⭐️⭐️⭐️⭐️ Quá đáng để đi! Cả nhà mê tít 💦
 Cuối tuần rồi nhà mình đưa hai đứa nhỏ lên thác Dải Yếm chơi, không nghĩ là đẹp hơn cả tưởng tượng. Thác chia làm nhiều tầng, nước đổ trắng xóa từ trên cao xuống, đứng dưới gió mát rượi, bụi nước bay vào người mát lạnh giữa trưa nắng luôn. Đúng kiểu "giải nhiệt" tự nhiên không cần điều hòa 😄
@@ -562,24 +542,47 @@
 Tóm lại: điểm dừng chân tuyệt vời cho gia đình có con nhỏ, vừa mát, vừa đẹp, vừa nhiều góc chơi. Nhất định sẽ quay lại! 🌿💙</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Thời gian chỉnh sửa: 2 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>{'name': 'ZjmLee YTBer', 'link': 'https://www.google.com/maps/contrib/100979561872983589256?hl=vi', 'contributor_id': '100979561872983589256', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU6i9poRXPBKYv-WgZHmB9chW6jRPCOh3klZ1Z7Yv_DOaukn4g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 79, 'photos': 1213}</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Nghe người địa phương kể lại thì cái tên “Dải Yếm” xuất phát từ truyền thuyết của người Thái. Họ nói rằng dòng thác trắng xóa từ trên cao đổ xuống giống như dải yếm của người con gái, nên từ đó cái tên này được gọi luôn cho tới bây giờ. Nghe vậy nên đứng nhìn dòng thác cũng thấy có chút gì đó rất nên thơ.
+Đi bộ quanh khu thác khá dễ, có lối đi và bậc đá để xuống gần chân thác. Nếu đi vào mùa nước nhiều thì thác nhìn đẹp hơn, nước trắng xóa và tiếng thác nghe rất đã tai. Còn những ngày nắng nhẹ thì không khí ở đây khá chill, kiểu ngồi nghỉ một chút, nghe tiếng nước và nhìn rừng cây xung quanh cũng thấy thư giãn.
+Mình thấy Thác Dải Yếm hợp với kiểu du lịch nhẹ nhàng: dừng chân, đi bộ một vòng, chụp vài bức ảnh rồi tiếp tục hành trình khám phá Mộc Châu. Nó không phải kiểu điểm du lịch quá hoành tráng, nhưng lại có cái nét mộc mạc và dễ chịu đúng chất cao nguyên.
+Nếu đang đi du lịch tự túc ở Mộc Châu, thì Thác Dải Yếm là một nơi khá đáng ghé qua. Không cần quá nhiều thời gian, chỉ cần dành khoảng một tiếng dạo quanh thôi cũng đủ để cảm nhận được một góc thiên nhiên rất đặc trưng của vùng núi này.</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Thời gian chỉnh sửa: 2 tháng trước</t>
+          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>{'name': 'Ngoc Vu', 'link': 'https://www.google.com/maps/contrib/108690447901904353450?hl=vi', 'contributor_id': '108690447901904353450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWfxdOn0PeKLec3vPdGma6QAeLm5W13lqA_TdPlL72m402yYLRpcA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 16, 'photos': 19}</t>
+          <t>{'name': 'Hanh Vu', 'link': 'https://www.google.com/maps/contrib/101916078015092582424?hl=vi', 'contributor_id': '101916078015092582424', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWKKa85i2VN2RSjhkp53oKKDcXbjK49YmqN3D2BpL8QOof8ZRlo=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 29, 'photos': 34}</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ko có gì nhiều, có thác là điểm nhấn vì thác rất mát, thêm cầu kính ty nhma cảm quan đi cầu kính bạch long chắc chắn và cảm giác an toàn tốt hơn. Giá vé 150k , có quán cf trc mặt thác view đẹp, mát , thiên nhiên diệu kỳ</t>
+          <t>Thác Dải Yếm nằm trong khu du lịch sinh thái Thác Dải Yếm, vé vào 150k/người. Bên trong có thác nước nhưng nước khá đục nên không tắm được, có thêm cầu kính tình yêu để chụp ảnh. Mình thấy khu này không có quá nhiều điểm để tham quan, chủ yếu vào ngắm thác và chụp ảnh, nên nếu kỳ vọng có nhiều hoạt động thì sẽ hơi ít.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -591,7 +594,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Anh Quân', 'link': 'https://www.google.com/maps/contrib/111631093743063403454?hl=vi', 'contributor_id': '111631093743063403454', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIy-NjGEZ7ggp1yhLvVSe2iSDFAUAF4AILlK1IHBmSbkPzlKg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 9, 'photos': 24}</t>
+          <t>{'name': 'Ngoc Vu', 'link': 'https://www.google.com/maps/contrib/108690447901904353450?hl=vi', 'contributor_id': '108690447901904353450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWfxdOn0PeKLec3vPdGma6QAeLm5W13lqA_TdPlL72m402yYLRpcA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 16, 'photos': 19}</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -599,19 +602,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cảnh đẹp, nhưng xu là đi ngay lúc mưa nên thác có nước như cf</t>
+          <t>Ko có gì nhiều, có thác là điểm nhấn vì thác rất mát, thêm cầu kính ty nhma cảm quan đi cầu kính bạch long chắc chắn và cảm giác an toàn tốt hơn. Giá vé 150k , có quán cf trc mặt thác view đẹp, mát , thiên nhiên diệu kỳ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2 tháng trước</t>
+          <t>một tháng trước</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 302, 'photos': 3623}</t>
+          <t>{'name': 'Nguyễn Anh Quân', 'link': 'https://www.google.com/maps/contrib/111631093743063403454?hl=vi', 'contributor_id': '111631093743063403454', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIy-NjGEZ7ggp1yhLvVSe2iSDFAUAF4AILlK1IHBmSbkPzlKg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 9, 'photos': 24}</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -619,19 +622,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
+          <t>Cảnh đẹp, nhưng xu là đi ngay lúc mưa nên thác có nước như cf</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5 tháng trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>{'name': 'Gia Hân Nhâm', 'link': 'https://www.google.com/maps/contrib/105260403784604064817?hl=vi', 'contributor_id': '105260403784604064817', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXW4Eq54WOYUlLcmPr0wFzcfgLQhMAImSwK6dXvpDOyeFlOocZZ7w=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 15, 'photos': 64}</t>
+          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 302, 'photos': 3623}</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -639,19 +642,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thác rất đẹp, bước vào thật sự bị ngộp khung cảnh hùng vĩ của Việt Nam mình. Mỗi nơi đi là mỗi trải nghiệm</t>
+          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>một tháng trước</t>
+          <t>5 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 12, 'photos': 25}</t>
+          <t>{'name': 'Gia Hân Nhâm', 'link': 'https://www.google.com/maps/contrib/105260403784604064817?hl=vi', 'contributor_id': '105260403784604064817', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXW4Eq54WOYUlLcmPr0wFzcfgLQhMAImSwK6dXvpDOyeFlOocZZ7w=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 15, 'photos': 64}</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -659,19 +662,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
+          <t>Thác rất đẹp, bước vào thật sự bị ngộp khung cảnh hùng vĩ của Việt Nam mình. Mỗi nơi đi là mỗi trải nghiệm</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7 tháng trước</t>
+          <t>một tháng trước</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>{'name': 'Cửu Quang Nguyễn', 'link': 'https://www.google.com/maps/contrib/107704339232071144994?hl=vi', 'contributor_id': '107704339232071144994', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV2_oJLqzlVCtXNV77ConxSPDhhMhFP-czjeCf6uCm7cabO88k=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 79, 'photos': 359}</t>
+          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 12, 'photos': 25}</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -679,19 +682,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm nằm trong khu du lịch sinh thái thác Dải Yếm, đường đi khá tiện lợi để ghé vào, tuy nhiên cần chú ý lối vào có khúc cua dốc khá ngoặt. Vé vào là 150k/người, bên trong có khá nhiều vị trí để du ngoạn và ngắm cảnh, đặc biệt là khu vực thác nước rất hùng vĩ và mát mẻ, có cầu dẫn vào nhìn rất thơ mộng và tuyệt vời. Nếu có dịp ghé lên Mộc Châu thì nên ghé vào đây chơi 1 lần để du ngoạn thắng cảnh thiên nhiên tại nơi đây.</t>
+          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6 tháng trước</t>
+          <t>7 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 25, 'photos': 245}</t>
+          <t>{'name': 'Cửu Quang Nguyễn', 'link': 'https://www.google.com/maps/contrib/107704339232071144994?hl=vi', 'contributor_id': '107704339232071144994', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV2_oJLqzlVCtXNV77ConxSPDhhMhFP-czjeCf6uCm7cabO88k=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 79, 'photos': 359}</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -699,47 +702,90 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
+          <t>Thác Dải Yếm nằm trong khu du lịch sinh thái thác Dải Yếm, đường đi khá tiện lợi để ghé vào, tuy nhiên cần chú ý lối vào có khúc cua dốc khá ngoặt. Vé vào là 150k/người, bên trong có khá nhiều vị trí để du ngoạn và ngắm cảnh, đặc biệt là khu vực thác nước rất hùng vĩ và mát mẻ, có cầu dẫn vào nhìn rất thơ mộng và tuyệt vời. Nếu có dịp ghé lên Mộc Châu thì nên ghé vào đây chơi 1 lần để du ngoạn thắng cảnh thiên nhiên tại nơi đây.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>6 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 377, 'photos': 2666}</t>
+          <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 222, 'photos': 316}</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C14" t="inlineStr">
+        <is>
+          <t>Trải nghiệm vừa phải
+Giá vé theo trải nghiệm đi nhiều thác khác nhau của mình thì là khá cao so với các nơi khác, mình đi vào dịp tết nên thác ít nước.
+Cảnh quan xung quanh thác ở mức bình thường.
+Cá nhân nếu quay lại Mộc Châu sẽ không đến thác này lần nào nữa</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 24, 'photos': 245}</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 378, 'photos': 2666}</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>Nơi rất đáng để tham quan, trãi nghiệm chút it về cầu kính và kết hợp đi ngắm thác nước.
 Có nhiều nơi lên hình đẹp, cảnh đẹp. Có bán đặc sản Mộc Châu rất đa dạng.
 😍😍👍</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Thời gian chỉnh sửa: 6 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Thời gian chỉnh sửa: 7 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>{'name': 'Thái Nguyễn', 'link': 'https://www.google.com/maps/contrib/105517365260915933657?hl=vi', 'contributor_id': '105517365260915933657', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXLOkY3FUSH3Mz-aapJXPQUgoCFlQP20PICWZGzVI3cPkRkBIt_ew=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 65, 'photos': 164}</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>5</v>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Nếu đi cùng Lover sẽ đẹp hơn.
 Nếu tự nhìn lại
@@ -807,22 +853,22 @@
 Hơn cả tới thiên đường</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>9 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>{'name': 'Vĩ Lê Bá', 'link': 'https://www.google.com/maps/contrib/115860838984920745696?hl=vi', 'contributor_id': '115860838984920745696', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7wdRrYJWeEmKs7YInZz_FDg-T90l2ImigSwJKL2hWmQu75bzm=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 61, 'photos': 96}</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B18" t="n">
         <v>4</v>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Đẹp thì đẹp sơ sơ nhưng không gian vẫn khá là thoải mái
 Đi bộ oklea nhưng mà vẫn còn quá nhỏ, đi cỡ 30 phút là xong mất tiêu r
@@ -830,81 +876,38 @@
 Nói chung là vẫn okela</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>7 tháng trước</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>{'name': 'ZjmLee YTBer', 'link': 'https://www.google.com/maps/contrib/100979561872983589256?hl=vi', 'contributor_id': '100979561872983589256', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU6i9poRXPBKYv-WgZHmB9chW6jRPCOh3klZ1Z7Yv_DOaukn4g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 79, 'photos': 1213}</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>5</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Nghe người địa phương kể lại thì cái tên “Dải Yếm” xuất phát từ truyền thuyết của người Thái. Họ nói rằng dòng thác trắng xóa từ trên cao đổ xuống giống như dải yếm của người con gái, nên từ đó cái tên này được gọi luôn cho tới bây giờ. Nghe vậy nên đứng nhìn dòng thác cũng thấy có chút gì đó rất nên thơ.
-Đi bộ quanh khu thác khá dễ, có lối đi và bậc đá để xuống gần chân thác. Nếu đi vào mùa nước nhiều thì thác nhìn đẹp hơn, nước trắng xóa và tiếng thác nghe rất đã tai. Còn những ngày nắng nhẹ thì không khí ở đây khá chill, kiểu ngồi nghỉ một chút, nghe tiếng nước và nhìn rừng cây xung quanh cũng thấy thư giãn.
-Mình thấy Thác Dải Yếm hợp với kiểu du lịch nhẹ nhàng: dừng chân, đi bộ một vòng, chụp vài bức ảnh rồi tiếp tục hành trình khám phá Mộc Châu. Nó không phải kiểu điểm du lịch quá hoành tráng, nhưng lại có cái nét mộc mạc và dễ chịu đúng chất cao nguyên.
-Nếu đang đi du lịch tự túc ở Mộc Châu, thì Thác Dải Yếm là một nơi khá đáng ghé qua. Không cần quá nhiều thời gian, chỉ cần dành khoảng một tiếng dạo quanh thôi cũng đủ để cảm nhận được một góc thiên nhiên rất đặc trưng của vùng núi này.</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>7 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>{'name': 'La Meu', 'link': 'https://www.google.com/maps/contrib/108858956358165703026?hl=vi', 'contributor_id': '108858956358165703026', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVKW-aZD0iBs1KBFQlmzfMiMTfjpd4PfUn4GO-K2tEt1PLpZ3YY=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 25, 'photos': 117}</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>5</v>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Thác Dải Yếm là điểm du lịch rất đáng đi. Đường đi dễ, xe máy hay ô tô đều thuận tiện. Không gian mát mẻ, thiên nhiên đẹp và trong lành.
 Nước thác xanh biếc, chảy mạnh nhưng nhìn rất êm và thơ mộng, chụp hình lên đẹp lắm. Khu vực được làm lối đi khá an toàn, dễ tham quan.
 Nhân viên ở đây dễ thương, nhiệt tình, hướng dẫn khách rất chu đáo và thân thiện. Phù hợp đi chơi cùng gia đình hoặc bạn bè để thư giãn, nghỉ ngơi.</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>10 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>{'name': 'Nghĩa Nguyễn Trung', 'link': 'https://www.google.com/maps/contrib/107253778101970197900?hl=vi', 'contributor_id': '107253778101970197900', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUNLHg5XlpgtWVVTp_oJKOYAejqmQORtgQ_Oe2vusE5W_sQoZc5=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 275, 'photos': 1279}</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>5</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Khu vực thác nước đẹp, nhiều cảnh quan, nhiều góc chụp đẹp.</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>3 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 114, 'photos': 86}</t>
+          <t>{'name': 'Nghĩa Nguyễn Trung', 'link': 'https://www.google.com/maps/contrib/107253778101970197900?hl=vi', 'contributor_id': '107253778101970197900', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUNLHg5XlpgtWVVTp_oJKOYAejqmQORtgQ_Oe2vusE5W_sQoZc5=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 275, 'photos': 1279}</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -912,19 +915,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
+          <t>Khu vực thác nước đẹp, nhiều cảnh quan, nhiều góc chụp đẹp.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>3 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 94, 'photos': 1120}</t>
+          <t>{'name': 'Kevin Nguyen', 'link': 'https://www.google.com/maps/contrib/109877646150463185293?hl=vi', 'contributor_id': '109877646150463185293', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8DBDTE93d9fOU8oWxOJsmtZJfMmPykLC5PI7_MTW1SjxWlVG1=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 115, 'photos': 86}</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -932,19 +935,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
+          <t>Thác  đẹp. Giá vé vào cổng hơi mắc 150k.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>9 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 12, 'photos': 41}</t>
+          <t>{'name': 'Triệu Ngọc Tuyền', 'link': 'https://www.google.com/maps/contrib/115340519559472111474?hl=vi', 'contributor_id': '115340519559472111474', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVmDJuhgwxVbQsk8Q3nJDJsuXIMsgGFYkY-Ri40CMV5eFoibU8=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 94, 'photos': 1120}</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -952,65 +955,85 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
+          <t>1 điểm không nên bỏ qua khi đến vùng đất cao nguyên Mộc Châu. Giá vé vào cửa hợp lý, nhiều điểm check in và giao lưu văn hoá văn nghệ với các hoạt động của dân bản. Khi du lịch được quy hoạch đẹp, khoa học với các quầy hàng, quán mang đậm nét vùng Tây Bắc.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 57, 'photos': 1270}</t>
+          <t>{'name': 'Duong Phuong', 'link': 'https://www.google.com/maps/contrib/110918140221216861103?hl=vi', 'contributor_id': '110918140221216861103', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU1E27GBPzvY6u895WCFjSGwkGxK_hKlzGxtsDoDEiL_7mMOtv8=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 12, 'photos': 41}</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
+          <t>Thác đẹp, mùa này vẫn có nước nhưng ít, mình đi có cầu vồng trên thác luôn, đẹp mê</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>9 tháng trước</t>
+          <t>10 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 148, 'photos': 340}</t>
+          <t>{'name': 'hoi Mike', 'link': 'https://www.google.com/maps/contrib/107625295750892007907?hl=vi', 'contributor_id': '107625295750892007907', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocINbklthRhU6YoHkw0cHbHmqdWrKvVvwsaYssLzBj1rvYFSmw=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 59, 'photos': 1270}</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
+          <t>Trở lại sau 5 năm thấy thác Dải Yếm, Cầu kính Tình yêu vẫn đẹp, nhưng thiếu hoa, như là thiếu khởi sắc như xưa. Đẹp và độc đáo đấy, mạnh mẽ lên như Đà Lạt, Mộc Châu nhé.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7 tháng trước</t>
+          <t>9 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>{'name': 'Quynh Nhu Truong', 'link': 'https://www.google.com/maps/contrib/101900043964393079715?hl=vi', 'contributor_id': '101900043964393079715', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVIzO7WDniNUOXI8Nblms_0o03GlgmxjWjMX7NWkKqi66E-WzOx=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 150, 'photos': 340}</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Đi dịp Tết nên hơi đông. Cảnh quan đẹp nhưng hơi ít hoa. Nhớ thuê đồ chụp cho đẹp. Bộ của mình hơi cồng kềnh nên 250k. Mấy bộ khác rẻ hơn.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>8 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>{'name': 'Linh Nguyễn', 'link': 'https://www.google.com/maps/contrib/109820275513447282944?hl=vi', 'contributor_id': '109820275513447282944', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVpZ-SNyOn6byhXW5cnkMUzIYl8pLeo3scME3-VG4n2ps2S2tYx=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 144, 'photos': 992}</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>5</v>
-      </c>
-      <c r="C25" t="inlineStr">
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>Thác đẹp, suối nước tự nhiên, đường đi dọc suối sạch sẽ
 Một số địa điểm du lịch ở Mộc Châu mọi người có thể tham khảo
@@ -1023,56 +1046,36 @@
 2. Cá Hồi Thanh Bảy</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>2 năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 81, 'photos': 188}</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>4</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Tấn Thành', 'link': 'https://www.google.com/maps/contrib/117227534316521742646?hl=vi', 'contributor_id': '117227534316521742646', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUCPB87qD_q8UFnvBcCkGu3uE2AN4atMK6XrLGFH3fII6nWymikeg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 35, 'photos': 483}</t>
+          <t>{'name': 'Phạm Hồng Sơn', 'link': 'https://www.google.com/maps/contrib/108328635569869277244?hl=vi', 'contributor_id': '108328635569869277244', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXuufgcm0-P0X8fZ6W5jCBlB3y04BUqsrEU09rNtYI4Y_OfGijC=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 81, 'photos': 188}</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cảnh ở thác rất là đẹp</t>
+          <t>Đi vào đợt có nước chắc sẽ đẹp hơn.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>một tháng trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 12, 'photos': 65}</t>
+          <t>{'name': 'Nguyễn Tấn Thành', 'link': 'https://www.google.com/maps/contrib/117227534316521742646?hl=vi', 'contributor_id': '117227534316521742646', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUCPB87qD_q8UFnvBcCkGu3uE2AN4atMK6XrLGFH3fII6nWymikeg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 35, 'photos': 483}</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1080,19 +1083,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
+          <t>Cảnh ở thác rất là đẹp</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>một tháng trước</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 38, 'photos': 73}</t>
+          <t>{'name': 'Thư Phạm', 'link': 'https://www.google.com/maps/contrib/102926703811086728792?hl=vi', 'contributor_id': '102926703811086728792', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVb8MtZXwih2fSSNR9rLlq_A6Luy84R4Vyd-NM8rAkY_tqlJGZl=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 12, 'photos': 65}</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1100,19 +1103,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
+          <t>Thác thương mại hóa rồi nên đi rất dễ, phù hợp với các gia đình có con nhỏ. Cầu kính không quá cao nhưng hơi lắc lư cũng thú vị. Cảnh đẹp. Mình đi sau bão nên nước siêu mạnh và đục không ra thác chơi được.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 72, 'photos': 501}</t>
+          <t>{'name': 'Nguyễn Hằng', 'link': 'https://www.google.com/maps/contrib/101926288744472028041?hl=vi', 'contributor_id': '101926288744472028041', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8qNNIC2IBAt05drbV8NJd2Oh9SEBfmsbl31HOVsCx1uJSCJgVfg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 38, 'photos': 73}</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1120,50 +1123,50 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
+          <t>Thác rất đẹp, mát và sạch. Nếu đến Mộc Châu thì ko nên bỏ qua điểm check-in này</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5 tháng trước</t>
+          <t>3 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>{'name': 'Nông Thu Trang', 'link': 'https://www.google.com/maps/contrib/101419221009364011913?hl=vi', 'contributor_id': '101419221009364011913', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWUbk3dnLb_4jtQx0y2CInSDUCmCSRwDkEfgS-5PunCjpndXA1uPw=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 72, 'photos': 501}</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Thác đẹp nha. Mình đã chơi zipline ở đây và khá thú vị.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>5 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>{'name': 'Vịnh Đỗ', 'link': 'https://www.google.com/maps/contrib/113253627891220040007?hl=vi', 'contributor_id': '113253627891220040007', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUQ86HB-XwphFy1EiLKx95cfcbfdEimExlwlLXvcY0QzCQTZ_6g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 78, 'photos': 260}</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="B32" t="n">
         <v>4</v>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Tuỳ vào mùa các bạn đi, nếu đi mùa mưa thì nước sông sẽ hơi đục. Cũng nên thăm quan trải nghiệm.
 Vé vào cửa và vé lên cầu kính là 2 vé khác nhau. Mua vé vào cửa trải nghiệm các địa điểm xong nếu muốn lên cầu kính thì mua thêm</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 536, 'photos': 4147}</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>4</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
-        </is>
-      </c>
       <c r="D32" t="inlineStr">
         <is>
           <t>một năm trước</t>
@@ -1173,13 +1176,33 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>{'name': 'Ngọc Thái', 'link': 'https://www.google.com/maps/contrib/117081670390080818115?hl=vi', 'contributor_id': '117081670390080818115', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUH1v94jq-ECOPMaFku84PMkmUB-Id6JDSW1oBOPg7lHFU3dZ82=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 536, 'photos': 4147}</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Điểm du lịch có thác và có cầu kính tình yêu. Mặc dù không hot lắm nhưng mà cũng nên trải nghiệm. Đường đi xuống dễ cho cả ô tô và xe máy. Trước cửa khu là đồi chè, đi bộ vào trong cuối sẽ thấy thác dải yếm và cầu tình yêu.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>{'name': 'copa chino', 'link': 'https://www.google.com/maps/contrib/114746861312686284450?hl=vi', 'contributor_id': '114746861312686284450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXqDofHduvDqoyuk8-F8cAvVWkTjDCg_k4s6CaWINK53zksjE8-=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 91, 'photos': 574}</t>
         </is>
       </c>
-      <c r="B33" t="n">
-        <v>5</v>
-      </c>
-      <c r="C33" t="inlineStr">
+      <c r="B34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>Đúng tên gọi của nó. Thác cũng rất đẹp. Nếu vào mùa nước chắc còn đẹp hơn.
 Cảnh quan cũng rất sạch đẹp.
@@ -1188,36 +1211,16 @@
 - vé vào cổng giá phù hợp</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 652, 'photos': 4196}</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>5</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Thời gian chỉnh sửa: 2 năm trước</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 147, 'photos': 517}</t>
+          <t>{'name': 'Quý Trần Bá', 'link': 'https://www.google.com/maps/contrib/107648513496371165690?hl=vi', 'contributor_id': '107648513496371165690', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV3t1deDwhhFPVxuzoLFNf6IGu5ihJWKFtlZbFqvWLtAj5hL9c=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 652, 'photos': 4206}</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1225,104 +1228,101 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
+          <t>Tháng 1/2024 nước ở thác khá ít, nhưng vẫn rất đẹp. Giá vé 80.000đ là khá cao để tham quan 1 thác nước. Vé đi cầu kính riêng là 100.000đ, nhưng mình nghĩ nó không đáng. Đường đi dễ dàng, hiện tại bên trong khu vực thác đang xây dựng thêm nhiều hạng mục. Nên đi tham quan buổi chiều, vì khi đó Mặt Trời chiếu thẳng vào thác nước sẽ đẹp hơn buổi sáng.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>Thời gian chỉnh sửa: 2 năm trước</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 222, 'photos': 316}</t>
+          <t>{'name': 'Uno Uno', 'link': 'https://www.google.com/maps/contrib/100478726171248623880?hl=vi', 'contributor_id': '100478726171248623880', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocK29XlqDcjJogEei22sBiF9swsoQaiiJxlT4buPGC80LS4TXA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 147, 'photos': 517}</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Trải nghiệm vừa phải
-Giá vé theo trải nghiệm đi nhiều thác khác nhau của mình thì là khá cao so với các nơi khác, mình đi vào dịp tết nên thác ít nước.
-Cảnh quan xung quanh thác ở mức bình thường.
-Cá nhân nếu quay lại Mộc Châu sẽ không đến thác này lần nào nữa</t>
+          <t>Thác Dải Yếm khá hùng vĩ, đi đến cuối chụp ảnh đẹp. Từ cổng đi bộ vào hết khoảng 1 tiếng. Giá vé trung bình</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 164, 'photos': 234}</t>
+          <t>{'name': 'Frugal Flow', 'link': 'https://www.google.com/maps/contrib/107453311426556875441?hl=vi', 'contributor_id': '107453311426556875441', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUspWRVGEEQ_LyS16qRB57xWZ-kgNRIjgdLPY8T7HzvNMFlILCV=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 25, 'photos': 85}</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
+          <t>Đi vào một ngày nắng. Nắng hắt lên mặt nước long lanh nên xinh xắn hẳn:&gt; Chỉ là thác nay có vẻ hơi ít nc nên không như mình tưởng tượng.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>8 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>{'name': 'Sơn Nam Nguyễn Lê', 'link': 'https://www.google.com/maps/contrib/117776124129500576238?hl=vi', 'contributor_id': '117776124129500576238', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV8Y1H3e7DNBWkre9LHOZCvlbt_HRr2418mWZUGeZ2v7pqjrGYcrQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 164, 'photos': 234}</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>4</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Thác đẹp tuy nhiên hơi ít chỗ để chơi. Cảm giác vé 100k/ng là khá đắt. Đi bộ tầm 5 phút là hết đường rồi. Muốn lên cầu kính phải mua riêng nhưng cầu cũng ko đẹp lắm</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>{'name': 'Phượng Khúc', 'link': 'https://www.google.com/maps/contrib/113203842862691931923?hl=vi', 'contributor_id': '113203842862691931923', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVW0wyQy2FeBDydoEoMtJlgMO0CLovSixx1ioFuyxKYGSy77OLS=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 16, 'photos': 114}</t>
         </is>
       </c>
-      <c r="B38" t="n">
-        <v>5</v>
-      </c>
-      <c r="C38" t="inlineStr">
+      <c r="B39" t="n">
+        <v>5</v>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>Đi tầm trưa nắng đẹp
 Thác nhỏ, đi cũng không mất quá nhiều thời gian
 Có cầu kính</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>8 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 134, 'photos': 248}</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>5</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 190, 'photos': 1652}</t>
+          <t>{'name': 'Minh Nguyễn Bá', 'link': 'https://www.google.com/maps/contrib/115842117636224794565?hl=vi', 'contributor_id': '115842117636224794565', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjUDCwDVi9SF0o3_3TgOX0UwkUI-libBYW7QeE8khpsDRgBIeJ9-=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 134, 'photos': 248}</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1330,19 +1330,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
+          <t>Đi đúng dịp mưa xong lên nước ko đc trong lắm nhưng cũng là 1 trải nghiệm 😅 giá vé vào cổng 150k /1ng bao gồm cả đi cầu kính tình yêu</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>10 tháng trước</t>
+          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>{'name': 'THANH NGUYEN', 'link': 'https://www.google.com/maps/contrib/110418688752170937071?hl=vi', 'contributor_id': '110418688752170937071', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIBtT-SxDlGGJM5jA47OmxpGvFdaG6EOeSswcBwx4VuXgnOdQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 71, 'photos': 238}</t>
+          <t>{'name': 'Nhà Sách EmBoy', 'link': 'https://www.google.com/maps/contrib/118380242786497531992?hl=vi', 'contributor_id': '118380242786497531992', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVbdVO9wDaVfyhzeq4rVufLzTYc1-0rDhiU8CgRkhMe8-KvFCr4=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 190, 'photos': 1652}</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1350,101 +1350,101 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>thác đẹp nhưng nên đi vào mùa nước sẽ thấy sự khác biệt hơn nhiều</t>
+          <t>Thác tự nhiên nước mát lạnh thời tiết se se lạnh rất tuyệt vời. Một địa điểm đáng mong đợi.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8 tháng trước</t>
+          <t>10 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>{'name': 'THANH NGUYEN', 'link': 'https://www.google.com/maps/contrib/110418688752170937071?hl=vi', 'contributor_id': '110418688752170937071', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIBtT-SxDlGGJM5jA47OmxpGvFdaG6EOeSswcBwx4VuXgnOdQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 71, 'photos': 238}</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>5</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>thác đẹp nhưng nên đi vào mùa nước sẽ thấy sự khác biệt hơn nhiều</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>8 tháng trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>{'name': 'ninh Men', 'link': 'https://www.google.com/maps/contrib/103025469094717120638?hl=vi', 'contributor_id': '103025469094717120638', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJr8a3WVJHmayMF2FvRRdJjmyVlo0gmvjXedEtF6z5_xuOtxg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 29, 'photos': 168}</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B43" t="n">
         <v>4</v>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Đi Thác Dải Yếm đúng hôm… uống trà sữa trân châu. 😭
 Vé 150k/người nhưng cá nhân mình thấy hơi hụt hẫng. Thác không quá đặc biệt, đi một vòng là hết, chủ yếu là chụp ảnh. Nếu không thích check-in thì chắc sẽ thấy hơi “không có gì” so với giá vé.</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>2 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 50, 'photos': 144}</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>4</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>{'name': 'Lợi Phạm Văn', 'link': 'https://www.google.com/maps/contrib/104497610998910623417?hl=vi', 'contributor_id': '104497610998910623417', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU42oIpt5zEaQUYQaGFaLMV0xGgry3q_TJPWssV8BK_uAVPJpLt=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 50, 'photos': 144}</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>4</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Thác Dải yếm vào mùa đông mực nước trên và dưới thác đều thấp nên dễ dàng đến tháp sau khi vượt qua một đập tràn ngang qua suối Tình yêu để men theo con đường nhỏ bên hữu ngạn còn suối.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>{'name': 'Rong Con (Mr. Dragon)', 'link': 'https://www.google.com/maps/contrib/108876935347880146957?hl=vi', 'contributor_id': '108876935347880146957', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVOAB-25PMt-dfRNT-0Cxi6yv3ndR1rsuSnkmcbVorHpLvMDfzp2g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 149, 'photos': 3873}</t>
         </is>
       </c>
-      <c r="B44" t="n">
-        <v>5</v>
-      </c>
-      <c r="C44" t="inlineStr">
+      <c r="B45" t="n">
+        <v>5</v>
+      </c>
+      <c r="C45" t="inlineStr">
         <is>
           <t>Thác Dải Yếm, còn được gọi là thác Nàng, thác Bản Vặt, là một thác nước hùng vĩ nằm ở xã Mường Sang, huyện Mộc Châu, tỉnh Sơn La. Thác có chiều cao khoảng 100m, chia thành hai dòng thác chính, trông giống như một dải yếm đào mềm mại uốn lượn quanh vách núi.
 Thác Dải Yếm là một địa điểm du lịch hấp dẫn, thu hút khách du lịch trong và ngoài nước. Đây là nơi du khách có thể chiêm ngưỡng vẻ đẹp hùng vĩ của thác nước và tìm hiểu về truyền thuyết về thác.</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>3 năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 97, 'photos': 178}</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>4</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>một năm trước</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 28, 'photos': 264}</t>
+          <t>{'name': 'son hai', 'link': 'https://www.google.com/maps/contrib/115068056146363063986?hl=vi', 'contributor_id': '115068056146363063986', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjX1wbYvRXREDWiLVF31hW_hn9hpRVpOpMHWsl6tsYZyVkesyU-q=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 97, 'photos': 178}</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
+          <t>Mình đi vào tháng 8, thác nước đẹp, cầu kính cũng hay. Tuy nhiên phí dịch vụ cao.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1464,7 +1464,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 75, 'photos': 503}</t>
+          <t>{'name': 'Lê Văn Tuyến', 'link': 'https://www.google.com/maps/contrib/110898979794966301347?hl=vi', 'contributor_id': '110898979794966301347', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXDiKgigV1VNJ7iMg5GLsHA7Www_jFS-1lJFHQUMYCtE9s9oS3N=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 28, 'photos': 264}</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1472,66 +1472,86 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
+          <t>Thác Dải Yếm, hay còn gọi là thác Nàng, là một địa điểm du lịch nổi tiếng ở Mộc Châu, Sơn La, được yêu thích bởi vẻ đẹp hoang sơ, hùng vĩ và những trải nghiệm thú vị. Đến đây, bạn có thể chiêm ngưỡng dòng thác trắng xóa, tham gia các hoạt động như chèo thuyền kayak, đi cầu kính, trượt zipline và khám phá những điều thú vị khác.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>{'name': 'Duong Nguyen Quang', 'link': 'https://www.google.com/maps/contrib/113370945279567838535?hl=vi', 'contributor_id': '113370945279567838535', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocJPMN8rQwpxASMOYr-ooG3qo8-AWaVQ6HPFkWOd-XePnnmE_A=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 75, 'photos': 503}</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>4</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
           <t>Thác Dải Yếm nằm trên dòng suối Vặt khởi nguồn từ hai khe nước Bó Co Lắm và Bo Tá Cháu ở đầu bản Vặt, một bản của người Thái có lịch sử lâu đời. Suối Vặt chảy được 5 km đổ vào suối Bó Sập, một dòng suối lớn bắt nguồn từ bản Bó Sập giáp biên giới Việt Lào rồi chảy về đất Yên Châu. Tại nơi hợp lưu của hai suối, dòng nước gặp một vùng đá vôi và đổ xuống phía dưới tạo thành thác Dải Yếm.[5]
 Thác Dải Yếm bao gồm hai phần, thác nước phía trên rộng 70 mét, thác nước phía dưới nằm cách đó 150-200 mét. Vào mùa khô, thác phía dưới chỉ có một dòng chảy từ độ cao 50 m xuống triền đá ở dưới. hai thác đổ xuống với tổng chiều cao 100m, một bên được chia làm 9 tầng, bên còn lại 5 tầng. Cách giữa hai phần thác là một bãi đất phẳng thuận tiện cho việc tham quan của du khách. Thảm thực vật trên đỉnh thác cũng khá phong phú.</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>một năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>{'name': 'Chi Ho', 'link': 'https://www.google.com/maps/contrib/102731288821463748765?hl=vi', 'contributor_id': '102731288821463748765', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWV3y9KiqGo7jILq-ZzBkSw28LDZHnwKXBhstpTEeRvr9jffKE=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 84, 'photos': 1557}</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>5</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm đẹp và hùng vĩ, xứng đáng cho chuyến picnic cuối tuần. Đường đi hơi gập ghềnh nhưng đến nơi thì quên hết mệt mỏi. Nước mát rượi, âm thanh róc rách rất thư giãn. Tiếc là hơi đông vào cuối tuần, nhưng cảnh đẹp bù đắp tất cả! Nên đi vào ngày thường nếu muốn yên tĩnh hơn.</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 8, 'photos': 90}</t>
+          <t>{'name': 'Chi Ho', 'link': 'https://www.google.com/maps/contrib/102731288821463748765?hl=vi', 'contributor_id': '102731288821463748765', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWV3y9KiqGo7jILq-ZzBkSw28LDZHnwKXBhstpTEeRvr9jffKE=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 84, 'photos': 1557}</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
+          <t>Thác Dải Yếm đẹp và hùng vĩ, xứng đáng cho chuyến picnic cuối tuần. Đường đi hơi gập ghềnh nhưng đến nơi thì quên hết mệt mỏi. Nước mát rượi, âm thanh róc rách rất thư giãn. Tiếc là hơi đông vào cuối tuần, nhưng cảnh đẹp bù đắp tất cả! Nên đi vào ngày thường nếu muốn yên tĩnh hơn.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>một năm trước</t>
+          <t>2 tháng trước</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 151, 'photos': 1293}</t>
+          <t>{'name': 'Tiến Việt', 'link': 'https://www.google.com/maps/contrib/113105952542492887997?hl=vi', 'contributor_id': '113105952542492887997', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjVvvuGPV4L6cUUeOQC1YCrvONU46qaXb1VoATPgxmJocoMgpTuZ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 8, 'photos': 90}</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>4</v>
       </c>
       <c r="C50" t="inlineStr">
+        <is>
+          <t>Thời tiết khá mát mẻ, nhiều cây cối. Phù hợp để đi chơi thư giãn.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>một năm trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>{'name': 'Phạm Dũng', 'link': 'https://www.google.com/maps/contrib/117969227539333824124?hl=vi', 'contributor_id': '117969227539333824124', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXrhD3qCUFY5KEJUKBcoFps9q4JNxuWHLCo6c_oUSuhea9Pdxw8=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 151, 'photos': 1293}</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>4</v>
+      </c>
+      <c r="C51" t="inlineStr">
         <is>
           <t>Thác nhỏ cũng đẹp nhưng được trang trí dành cho du lịch rồi về độ rộng nhiều tầng và thiên nhiên thì không bằng thác Nàng Tiên hoặc thác Chiềng Khoa.
 Thác Dải Yếm được đầu tư khang trang nhưng đi bộ từ bãi gửi xe vào thác hơi bị xa (vé gửi xe 30k), đường đi vào và khu thác bên trong nhiều khu chụp ảnh checkin được trang trí chụp ảnh đẹp mắt. Giá vé tháng 1/2024 là 80k/ người vào cổng nhưng đến 30/4/2024 tăng lên 100k/ng giá vé hơi cao với việc vào ngắm thác.
@@ -1539,29 +1559,9 @@
 - Bản thân mình cảm nhận thì cũng bình thường thác không cao không rộng dài đẹp nhiều tầng bằng thác Nàng Tiên hoặc Chiềng Khoa. Nói chung đi du lịch Mộc Châu ghé qua cho biết thôi. Chứ để quay lại thì ít khả năng.</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>2 năm trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>{'name': 'Dong Dong', 'link': 'https://www.google.com/maps/contrib/102921151921093537699?hl=vi', 'contributor_id': '102921151921093537699', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXXHwC3OQ531U5w1o2bIWMTi260CsRqaGZi-yfq9sMUaAuJ5amnJQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 34, 'photos': 79}</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>4</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Cũng gọi là ok, vừa đẹp phù hợp với mức giá vé 150k</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>4 tháng trước</t>
         </is>
       </c>
     </row>

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,211 +571,6 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>{'name': 'Hanh Vu', 'link': 'https://www.google.com/maps/contrib/101916078015092582424?hl=vi', 'contributor_id': '101916078015092582424', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWKKa85i2VN2RSjhkp53oKKDcXbjK49YmqN3D2BpL8QOof8ZRlo=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 29, 'photos': 34}</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm nằm trong khu du lịch sinh thái Thác Dải Yếm, vé vào 150k/người. Bên trong có thác nước nhưng nước khá đục nên không tắm được, có thêm cầu kính tình yêu để chụp ảnh. Mình thấy khu này không có quá nhiều điểm để tham quan, chủ yếu vào ngắm thác và chụp ảnh, nên nếu kỳ vọng có nhiều hoạt động thì sẽ hơi ít.</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>một tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>{'name': 'Ngoc Vu', 'link': 'https://www.google.com/maps/contrib/108690447901904353450?hl=vi', 'contributor_id': '108690447901904353450', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjWfxdOn0PeKLec3vPdGma6QAeLm5W13lqA_TdPlL72m402yYLRpcA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 16, 'photos': 19}</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ko có gì nhiều, có thác là điểm nhấn vì thác rất mát, thêm cầu kính ty nhma cảm quan đi cầu kính bạch long chắc chắn và cảm giác an toàn tốt hơn. Giá vé 150k , có quán cf trc mặt thác view đẹp, mát , thiên nhiên diệu kỳ</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>một tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>{'name': 'Nguyễn Anh Quân', 'link': 'https://www.google.com/maps/contrib/111631093743063403454?hl=vi', 'contributor_id': '111631093743063403454', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocIy-NjGEZ7ggp1yhLvVSe2iSDFAUAF4AILlK1IHBmSbkPzlKg=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 9, 'photos': 24}</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Cảnh đẹp, nhưng xu là đi ngay lúc mưa nên thác có nước như cf</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>{'name': 'Son Nguyen', 'link': 'https://www.google.com/maps/contrib/115586226693929364137?hl=vi', 'contributor_id': '115586226693929364137', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5xUVH9DelLo5ZMn6wEeKwkRq-OoMAGo9OPuGsoErGJ2Ng11MJ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 302, 'photos': 3603}</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Khu du lịch Thác Dải Yếm sẽ rất đẹp như tên gọi vào mùa có nhiều nước và không mưa.</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>5 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>{'name': 'Gia Hân Nhâm', 'link': 'https://www.google.com/maps/contrib/105260403784604064817?hl=vi', 'contributor_id': '105260403784604064817', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXW4Eq54WOYUlLcmPr0wFzcfgLQhMAImSwK6dXvpDOyeFlOocZZ7w=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 16, 'photos': 64}</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Thác rất đẹp, bước vào thật sự bị ngộp khung cảnh hùng vĩ của Việt Nam mình. Mỗi nơi đi là mỗi trải nghiệm</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>một tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>{'name': 'Trang Hoang', 'link': 'https://www.google.com/maps/contrib/110742896718606605149?hl=vi', 'contributor_id': '110742896718606605149', 'thumbnail': 'https://lh3.googleusercontent.com/a/ACg8ocL4Aw763gF8bHLD_WDuBrKsYVvIHemJH2yZFOXjRoUuQPHzmA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 12, 'photos': 25}</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>M thấy bên này chủ yếu là mấy cô chú lớn tuổi hay đi, vé vào cổng là 150K/ng. Trong có quán cafe cầu kính, hồ , thác nước, không gian rất chill</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>7 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>{'name': 'Cửu Quang Nguyễn', 'link': 'https://www.google.com/maps/contrib/107704339232071144994?hl=vi', 'contributor_id': '107704339232071144994', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV2_oJLqzlVCtXNV77ConxSPDhhMhFP-czjeCf6uCm7cabO88k=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 79, 'photos': 359}</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Thác Dải Yếm nằm trong khu du lịch sinh thái thác Dải Yếm, đường đi khá tiện lợi để ghé vào, tuy nhiên cần chú ý lối vào có khúc cua dốc khá ngoặt. Vé vào là 150k/người, bên trong có khá nhiều vị trí để du ngoạn và ngắm cảnh, đặc biệt là khu vực thác nước rất hùng vĩ và mát mẻ, có cầu dẫn vào nhìn rất thơ mộng và tuyệt vời. Nếu có dịp ghé lên Mộc Châu thì nên ghé vào đây chơi 1 lần để du ngoạn thắng cảnh thiên nhiên tại nơi đây.</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>6 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>{'name': 'Quân Nguyễn', 'link': 'https://www.google.com/maps/contrib/115288812982384432724?hl=vi', 'contributor_id': '115288812982384432724', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV5chBiUnKVOKUuW1RludfuuZv7HlBhAzO3uxI6WnwRk6Q3cG6YmQ=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 222, 'photos': 316}</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>3</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Trải nghiệm vừa phải
-Giá vé theo trải nghiệm đi nhiều thác khác nhau của mình thì là khá cao so với các nơi khác, mình đi vào dịp tết nên thác ít nước.
-Cảnh quan xung quanh thác ở mức bình thường.
-Cá nhân nếu quay lại Mộc Châu sẽ không đến thác này lần nào nữa</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>8 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>{'name': 'Huyen Tran Thi Thanh', 'link': 'https://www.google.com/maps/contrib/109350093277321172741?hl=vi', 'contributor_id': '109350093277321172741', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjV7Kso1JGd6PkIfoXJN3ZZqeaoLlIbkZTe9pykq-DShR-dba6C2=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 24, 'photos': 245}</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>5</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Khu rộng rãi có các thác nước đẹp , hùng vĩ có các trò chơi mạo hiểm</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>8 tháng trước</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>{'name': 'Phiyen Chau', 'link': 'https://www.google.com/maps/contrib/111709720092455461785?hl=vi', 'contributor_id': '111709720092455461785', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjXFnhoLX3K4pbDewwJYW0tlZ8ztN7LmA9vMEDLI9_Jv47vMOAV_yA=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 378, 'photos': 2655}</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>5</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Nơi rất đáng để tham quan, trãi nghiệm chút it về cầu kính và kết hợp đi ngắm thác nước.
-Có nhiều nơi lên hình đẹp, cảnh đẹp. Có bán đặc sản Mộc Châu rất đa dạng.
-😍😍👍</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Thời gian chỉnh sửa: 7 tháng trước</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/du_lieu_binh_luan.xlsx
+++ b/du_lieu_binh_luan.xlsx
@@ -551,7 +551,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>{'name': 'ZjmLee YTBer', 'link': 'https://www.google.com/maps/contrib/100979561872983589256?hl=vi', 'contributor_id': '100979561872983589256', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU6i9poRXPBKYv-WgZHmB9chW6jRPCOh3klZ1Z7Yv_DOaukn4g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 79, 'photos': 1204}</t>
+          <t>{'name': 'ZjmLee YTBer', 'link': 'https://www.google.com/maps/contrib/100979561872983589256?hl=vi', 'contributor_id': '100979561872983589256', 'thumbnail': 'https://lh3.googleusercontent.com/a-/ALV-UjU6i9poRXPBKYv-WgZHmB9chW6jRPCOh3klZ1Z7Yv_DOaukn4g=s120-c-rp-mo-ba12-br100', 'local_guide': True, 'reviews': 78, 'photos': 1204}</t>
         </is>
       </c>
       <c r="B6" t="n">
